--- a/files/Adhiparasakthi Students Data 1.xlsx
+++ b/files/Adhiparasakthi Students Data 1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://edunetfoundationorg-my.sharepoint.com/personal/vignesh_edunetfoundation_org/Documents/IBM SB4Academia/Skillsbuild - 2026/GLE - 2026/September 2026/Adhiparasakthi Engineering College/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vigne\Google_Backup\Github\sb4c\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="8_{C351972E-9C50-E341-B986-DAE08E350E9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{94BF3B6C-80C6-4DB5-B0F8-2CD6B4B0B6D0}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74262C99-C121-4B1F-83CC-E6383FB9A842}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E3F0EEA9-6BAE-46A1-95E3-E9CE509FC50B}"/>
   </bookViews>
@@ -2481,12 +2481,6 @@
     <t>Edu#641736</t>
   </si>
   <si>
-    <t>EFIBM26535693726@edunetmail.com</t>
-  </si>
-  <si>
-    <t>Edu#121762</t>
-  </si>
-  <si>
     <t>EFIBM26547021097@edunetmail.com</t>
   </si>
   <si>
@@ -4087,6 +4081,12 @@
   </si>
   <si>
     <t>EduB5#303230</t>
+  </si>
+  <si>
+    <t>EFIBM26B5812372475@edunetmail.com</t>
+  </si>
+  <si>
+    <t>EduB5#879054</t>
   </si>
 </sst>
 </file>
@@ -4130,7 +4130,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -4252,6 +4252,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -4270,28 +4285,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4637,10 +4652,10 @@
       <c r="E1" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="3" t="s">
         <v>681</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="3" t="s">
         <v>682</v>
       </c>
     </row>
@@ -4660,10 +4675,10 @@
       <c r="E2" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="5" t="s">
         <v>683</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="7" t="s">
         <v>684</v>
       </c>
     </row>
@@ -4683,10 +4698,10 @@
       <c r="E3" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="6" t="s">
         <v>685</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="8" t="s">
         <v>686</v>
       </c>
     </row>
@@ -4706,10 +4721,10 @@
       <c r="E4" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="6" t="s">
         <v>687</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="8" t="s">
         <v>688</v>
       </c>
     </row>
@@ -4729,10 +4744,10 @@
       <c r="E5" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="6" t="s">
         <v>689</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="G5" s="8" t="s">
         <v>690</v>
       </c>
     </row>
@@ -4752,10 +4767,10 @@
       <c r="E6" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="6" t="s">
         <v>691</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="G6" s="8" t="s">
         <v>692</v>
       </c>
     </row>
@@ -4775,10 +4790,10 @@
       <c r="E7" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="6" t="s">
         <v>693</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="G7" s="8" t="s">
         <v>694</v>
       </c>
     </row>
@@ -4798,10 +4813,10 @@
       <c r="E8" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="6" t="s">
         <v>695</v>
       </c>
-      <c r="G8" s="9" t="s">
+      <c r="G8" s="8" t="s">
         <v>696</v>
       </c>
     </row>
@@ -4821,10 +4836,10 @@
       <c r="E9" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="6" t="s">
         <v>697</v>
       </c>
-      <c r="G9" s="9" t="s">
+      <c r="G9" s="8" t="s">
         <v>698</v>
       </c>
     </row>
@@ -4844,10 +4859,10 @@
       <c r="E10" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="6" t="s">
         <v>699</v>
       </c>
-      <c r="G10" s="9" t="s">
+      <c r="G10" s="8" t="s">
         <v>700</v>
       </c>
     </row>
@@ -4867,10 +4882,10 @@
       <c r="E11" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="6" t="s">
         <v>701</v>
       </c>
-      <c r="G11" s="9" t="s">
+      <c r="G11" s="8" t="s">
         <v>702</v>
       </c>
     </row>
@@ -4890,10 +4905,10 @@
       <c r="E12" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="6" t="s">
         <v>703</v>
       </c>
-      <c r="G12" s="9" t="s">
+      <c r="G12" s="8" t="s">
         <v>704</v>
       </c>
     </row>
@@ -4913,10 +4928,10 @@
       <c r="E13" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="6" t="s">
         <v>705</v>
       </c>
-      <c r="G13" s="9" t="s">
+      <c r="G13" s="8" t="s">
         <v>706</v>
       </c>
     </row>
@@ -4936,10 +4951,10 @@
       <c r="E14" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" s="6" t="s">
         <v>707</v>
       </c>
-      <c r="G14" s="9" t="s">
+      <c r="G14" s="8" t="s">
         <v>708</v>
       </c>
     </row>
@@ -4959,10 +4974,10 @@
       <c r="E15" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="F15" s="6" t="s">
         <v>709</v>
       </c>
-      <c r="G15" s="9" t="s">
+      <c r="G15" s="8" t="s">
         <v>710</v>
       </c>
     </row>
@@ -4982,10 +4997,10 @@
       <c r="E16" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="F16" s="6" t="s">
         <v>711</v>
       </c>
-      <c r="G16" s="9" t="s">
+      <c r="G16" s="8" t="s">
         <v>712</v>
       </c>
     </row>
@@ -5005,10 +5020,10 @@
       <c r="E17" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F17" s="7" t="s">
+      <c r="F17" s="6" t="s">
         <v>713</v>
       </c>
-      <c r="G17" s="9" t="s">
+      <c r="G17" s="8" t="s">
         <v>714</v>
       </c>
     </row>
@@ -5028,10 +5043,10 @@
       <c r="E18" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="F18" s="6" t="s">
         <v>715</v>
       </c>
-      <c r="G18" s="9" t="s">
+      <c r="G18" s="8" t="s">
         <v>716</v>
       </c>
     </row>
@@ -5051,10 +5066,10 @@
       <c r="E19" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F19" s="7" t="s">
+      <c r="F19" s="6" t="s">
         <v>717</v>
       </c>
-      <c r="G19" s="9" t="s">
+      <c r="G19" s="8" t="s">
         <v>718</v>
       </c>
     </row>
@@ -5074,10 +5089,10 @@
       <c r="E20" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F20" s="7" t="s">
+      <c r="F20" s="6" t="s">
         <v>719</v>
       </c>
-      <c r="G20" s="9" t="s">
+      <c r="G20" s="8" t="s">
         <v>720</v>
       </c>
     </row>
@@ -5097,10 +5112,10 @@
       <c r="E21" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F21" s="7" t="s">
+      <c r="F21" s="6" t="s">
         <v>721</v>
       </c>
-      <c r="G21" s="9" t="s">
+      <c r="G21" s="8" t="s">
         <v>722</v>
       </c>
     </row>
@@ -5120,10 +5135,10 @@
       <c r="E22" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F22" s="7" t="s">
+      <c r="F22" s="6" t="s">
         <v>723</v>
       </c>
-      <c r="G22" s="9" t="s">
+      <c r="G22" s="8" t="s">
         <v>724</v>
       </c>
     </row>
@@ -5143,10 +5158,10 @@
       <c r="E23" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F23" s="7" t="s">
+      <c r="F23" s="6" t="s">
         <v>725</v>
       </c>
-      <c r="G23" s="9" t="s">
+      <c r="G23" s="8" t="s">
         <v>726</v>
       </c>
     </row>
@@ -5166,10 +5181,10 @@
       <c r="E24" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F24" s="7" t="s">
+      <c r="F24" s="6" t="s">
         <v>727</v>
       </c>
-      <c r="G24" s="9" t="s">
+      <c r="G24" s="8" t="s">
         <v>728</v>
       </c>
     </row>
@@ -5189,10 +5204,10 @@
       <c r="E25" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F25" s="7" t="s">
+      <c r="F25" s="6" t="s">
         <v>729</v>
       </c>
-      <c r="G25" s="9" t="s">
+      <c r="G25" s="8" t="s">
         <v>730</v>
       </c>
     </row>
@@ -5212,10 +5227,10 @@
       <c r="E26" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F26" s="7" t="s">
+      <c r="F26" s="6" t="s">
         <v>731</v>
       </c>
-      <c r="G26" s="9" t="s">
+      <c r="G26" s="8" t="s">
         <v>732</v>
       </c>
     </row>
@@ -5235,10 +5250,10 @@
       <c r="E27" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F27" s="7" t="s">
+      <c r="F27" s="6" t="s">
         <v>733</v>
       </c>
-      <c r="G27" s="9" t="s">
+      <c r="G27" s="8" t="s">
         <v>734</v>
       </c>
     </row>
@@ -5258,10 +5273,10 @@
       <c r="E28" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F28" s="7" t="s">
+      <c r="F28" s="6" t="s">
         <v>735</v>
       </c>
-      <c r="G28" s="9" t="s">
+      <c r="G28" s="8" t="s">
         <v>736</v>
       </c>
     </row>
@@ -5281,10 +5296,10 @@
       <c r="E29" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F29" s="7" t="s">
+      <c r="F29" s="6" t="s">
         <v>737</v>
       </c>
-      <c r="G29" s="9" t="s">
+      <c r="G29" s="8" t="s">
         <v>738</v>
       </c>
     </row>
@@ -5304,10 +5319,10 @@
       <c r="E30" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F30" s="7" t="s">
+      <c r="F30" s="6" t="s">
         <v>739</v>
       </c>
-      <c r="G30" s="9" t="s">
+      <c r="G30" s="8" t="s">
         <v>740</v>
       </c>
     </row>
@@ -5327,10 +5342,10 @@
       <c r="E31" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F31" s="7" t="s">
+      <c r="F31" s="6" t="s">
         <v>741</v>
       </c>
-      <c r="G31" s="9" t="s">
+      <c r="G31" s="8" t="s">
         <v>742</v>
       </c>
     </row>
@@ -5350,10 +5365,10 @@
       <c r="E32" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F32" s="7" t="s">
+      <c r="F32" s="6" t="s">
         <v>743</v>
       </c>
-      <c r="G32" s="9" t="s">
+      <c r="G32" s="8" t="s">
         <v>744</v>
       </c>
     </row>
@@ -5373,10 +5388,10 @@
       <c r="E33" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F33" s="7" t="s">
+      <c r="F33" s="6" t="s">
         <v>745</v>
       </c>
-      <c r="G33" s="9" t="s">
+      <c r="G33" s="8" t="s">
         <v>746</v>
       </c>
     </row>
@@ -5396,10 +5411,10 @@
       <c r="E34" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F34" s="7" t="s">
+      <c r="F34" s="6" t="s">
         <v>747</v>
       </c>
-      <c r="G34" s="9" t="s">
+      <c r="G34" s="8" t="s">
         <v>748</v>
       </c>
     </row>
@@ -5419,10 +5434,10 @@
       <c r="E35" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F35" s="7" t="s">
+      <c r="F35" s="6" t="s">
         <v>749</v>
       </c>
-      <c r="G35" s="9" t="s">
+      <c r="G35" s="8" t="s">
         <v>750</v>
       </c>
     </row>
@@ -5442,10 +5457,10 @@
       <c r="E36" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F36" s="7" t="s">
+      <c r="F36" s="6" t="s">
         <v>751</v>
       </c>
-      <c r="G36" s="9" t="s">
+      <c r="G36" s="8" t="s">
         <v>752</v>
       </c>
     </row>
@@ -5465,10 +5480,10 @@
       <c r="E37" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F37" s="7" t="s">
+      <c r="F37" s="6" t="s">
         <v>753</v>
       </c>
-      <c r="G37" s="9" t="s">
+      <c r="G37" s="8" t="s">
         <v>754</v>
       </c>
     </row>
@@ -5488,10 +5503,10 @@
       <c r="E38" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F38" s="7" t="s">
+      <c r="F38" s="6" t="s">
         <v>755</v>
       </c>
-      <c r="G38" s="9" t="s">
+      <c r="G38" s="8" t="s">
         <v>756</v>
       </c>
     </row>
@@ -5511,10 +5526,10 @@
       <c r="E39" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F39" s="7" t="s">
+      <c r="F39" s="6" t="s">
         <v>757</v>
       </c>
-      <c r="G39" s="9" t="s">
+      <c r="G39" s="8" t="s">
         <v>758</v>
       </c>
     </row>
@@ -5534,10 +5549,10 @@
       <c r="E40" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F40" s="7" t="s">
+      <c r="F40" s="6" t="s">
         <v>759</v>
       </c>
-      <c r="G40" s="9" t="s">
+      <c r="G40" s="8" t="s">
         <v>760</v>
       </c>
     </row>
@@ -5557,10 +5572,10 @@
       <c r="E41" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F41" s="7" t="s">
+      <c r="F41" s="6" t="s">
         <v>761</v>
       </c>
-      <c r="G41" s="9" t="s">
+      <c r="G41" s="8" t="s">
         <v>762</v>
       </c>
     </row>
@@ -5580,10 +5595,10 @@
       <c r="E42" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F42" s="7" t="s">
+      <c r="F42" s="6" t="s">
         <v>763</v>
       </c>
-      <c r="G42" s="9" t="s">
+      <c r="G42" s="8" t="s">
         <v>764</v>
       </c>
     </row>
@@ -5603,10 +5618,10 @@
       <c r="E43" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F43" s="7" t="s">
+      <c r="F43" s="6" t="s">
         <v>765</v>
       </c>
-      <c r="G43" s="9" t="s">
+      <c r="G43" s="8" t="s">
         <v>766</v>
       </c>
     </row>
@@ -5626,10 +5641,10 @@
       <c r="E44" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F44" s="7" t="s">
+      <c r="F44" s="6" t="s">
         <v>767</v>
       </c>
-      <c r="G44" s="9" t="s">
+      <c r="G44" s="8" t="s">
         <v>768</v>
       </c>
     </row>
@@ -5649,10 +5664,10 @@
       <c r="E45" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F45" s="7" t="s">
+      <c r="F45" s="6" t="s">
         <v>769</v>
       </c>
-      <c r="G45" s="9" t="s">
+      <c r="G45" s="8" t="s">
         <v>770</v>
       </c>
     </row>
@@ -5672,10 +5687,10 @@
       <c r="E46" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F46" s="7" t="s">
+      <c r="F46" s="6" t="s">
         <v>771</v>
       </c>
-      <c r="G46" s="9" t="s">
+      <c r="G46" s="8" t="s">
         <v>772</v>
       </c>
     </row>
@@ -5695,10 +5710,10 @@
       <c r="E47" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F47" s="7" t="s">
+      <c r="F47" s="6" t="s">
         <v>773</v>
       </c>
-      <c r="G47" s="9" t="s">
+      <c r="G47" s="8" t="s">
         <v>774</v>
       </c>
     </row>
@@ -5718,10 +5733,10 @@
       <c r="E48" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F48" s="7" t="s">
+      <c r="F48" s="6" t="s">
         <v>775</v>
       </c>
-      <c r="G48" s="9" t="s">
+      <c r="G48" s="8" t="s">
         <v>776</v>
       </c>
     </row>
@@ -5741,10 +5756,10 @@
       <c r="E49" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F49" s="7" t="s">
+      <c r="F49" s="6" t="s">
         <v>777</v>
       </c>
-      <c r="G49" s="9" t="s">
+      <c r="G49" s="8" t="s">
         <v>778</v>
       </c>
     </row>
@@ -5764,10 +5779,10 @@
       <c r="E50" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F50" s="7" t="s">
+      <c r="F50" s="6" t="s">
         <v>779</v>
       </c>
-      <c r="G50" s="9" t="s">
+      <c r="G50" s="8" t="s">
         <v>780</v>
       </c>
     </row>
@@ -5787,10 +5802,10 @@
       <c r="E51" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F51" s="7" t="s">
+      <c r="F51" s="6" t="s">
         <v>781</v>
       </c>
-      <c r="G51" s="9" t="s">
+      <c r="G51" s="8" t="s">
         <v>782</v>
       </c>
     </row>
@@ -5810,10 +5825,10 @@
       <c r="E52" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F52" s="7" t="s">
+      <c r="F52" s="6" t="s">
         <v>783</v>
       </c>
-      <c r="G52" s="9" t="s">
+      <c r="G52" s="8" t="s">
         <v>784</v>
       </c>
     </row>
@@ -5833,10 +5848,10 @@
       <c r="E53" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F53" s="7" t="s">
+      <c r="F53" s="6" t="s">
         <v>785</v>
       </c>
-      <c r="G53" s="9" t="s">
+      <c r="G53" s="8" t="s">
         <v>786</v>
       </c>
     </row>
@@ -5856,10 +5871,10 @@
       <c r="E54" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F54" s="7" t="s">
+      <c r="F54" s="6" t="s">
         <v>787</v>
       </c>
-      <c r="G54" s="9" t="s">
+      <c r="G54" s="8" t="s">
         <v>788</v>
       </c>
     </row>
@@ -5879,10 +5894,10 @@
       <c r="E55" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F55" s="7" t="s">
+      <c r="F55" s="6" t="s">
         <v>789</v>
       </c>
-      <c r="G55" s="9" t="s">
+      <c r="G55" s="8" t="s">
         <v>790</v>
       </c>
     </row>
@@ -5902,10 +5917,10 @@
       <c r="E56" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F56" s="7" t="s">
+      <c r="F56" s="6" t="s">
         <v>791</v>
       </c>
-      <c r="G56" s="9" t="s">
+      <c r="G56" s="8" t="s">
         <v>792</v>
       </c>
     </row>
@@ -5925,10 +5940,10 @@
       <c r="E57" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F57" s="7" t="s">
+      <c r="F57" s="6" t="s">
         <v>793</v>
       </c>
-      <c r="G57" s="9" t="s">
+      <c r="G57" s="8" t="s">
         <v>794</v>
       </c>
     </row>
@@ -5948,10 +5963,10 @@
       <c r="E58" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F58" s="7" t="s">
+      <c r="F58" s="6" t="s">
         <v>795</v>
       </c>
-      <c r="G58" s="9" t="s">
+      <c r="G58" s="8" t="s">
         <v>796</v>
       </c>
     </row>
@@ -5971,10 +5986,10 @@
       <c r="E59" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F59" s="7" t="s">
+      <c r="F59" s="6" t="s">
         <v>797</v>
       </c>
-      <c r="G59" s="9" t="s">
+      <c r="G59" s="8" t="s">
         <v>798</v>
       </c>
     </row>
@@ -5994,10 +6009,10 @@
       <c r="E60" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F60" s="7" t="s">
+      <c r="F60" s="6" t="s">
         <v>799</v>
       </c>
-      <c r="G60" s="9" t="s">
+      <c r="G60" s="8" t="s">
         <v>800</v>
       </c>
     </row>
@@ -6017,10 +6032,10 @@
       <c r="E61" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F61" s="7" t="s">
+      <c r="F61" s="6" t="s">
         <v>801</v>
       </c>
-      <c r="G61" s="9" t="s">
+      <c r="G61" s="8" t="s">
         <v>802</v>
       </c>
     </row>
@@ -6040,10 +6055,10 @@
       <c r="E62" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F62" s="7" t="s">
+      <c r="F62" s="6" t="s">
         <v>803</v>
       </c>
-      <c r="G62" s="9" t="s">
+      <c r="G62" s="8" t="s">
         <v>804</v>
       </c>
     </row>
@@ -6063,10 +6078,10 @@
       <c r="E63" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F63" s="7" t="s">
+      <c r="F63" s="6" t="s">
         <v>805</v>
       </c>
-      <c r="G63" s="9" t="s">
+      <c r="G63" s="8" t="s">
         <v>806</v>
       </c>
     </row>
@@ -6086,10 +6101,10 @@
       <c r="E64" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F64" s="7" t="s">
+      <c r="F64" s="6" t="s">
         <v>807</v>
       </c>
-      <c r="G64" s="9" t="s">
+      <c r="G64" s="8" t="s">
         <v>808</v>
       </c>
     </row>
@@ -6109,10 +6124,10 @@
       <c r="E65" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F65" s="7" t="s">
+      <c r="F65" s="6" t="s">
         <v>809</v>
       </c>
-      <c r="G65" s="9" t="s">
+      <c r="G65" s="8" t="s">
         <v>810</v>
       </c>
     </row>
@@ -6132,10 +6147,10 @@
       <c r="E66" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F66" s="7" t="s">
+      <c r="F66" s="6" t="s">
         <v>811</v>
       </c>
-      <c r="G66" s="9" t="s">
+      <c r="G66" s="8" t="s">
         <v>812</v>
       </c>
     </row>
@@ -6155,10 +6170,10 @@
       <c r="E67" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F67" s="7" t="s">
+      <c r="F67" s="6" t="s">
         <v>813</v>
       </c>
-      <c r="G67" s="9" t="s">
+      <c r="G67" s="8" t="s">
         <v>814</v>
       </c>
     </row>
@@ -6178,11 +6193,11 @@
       <c r="E68" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F68" s="7" t="s">
-        <v>815</v>
-      </c>
-      <c r="G68" s="9" t="s">
-        <v>816</v>
+      <c r="F68" s="12" t="s">
+        <v>1349</v>
+      </c>
+      <c r="G68" s="12" t="s">
+        <v>1350</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6201,11 +6216,11 @@
       <c r="E69" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F69" s="7" t="s">
-        <v>817</v>
-      </c>
-      <c r="G69" s="9" t="s">
-        <v>818</v>
+      <c r="F69" s="6" t="s">
+        <v>815</v>
+      </c>
+      <c r="G69" s="8" t="s">
+        <v>816</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6224,11 +6239,11 @@
       <c r="E70" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F70" s="7" t="s">
-        <v>819</v>
-      </c>
-      <c r="G70" s="9" t="s">
-        <v>820</v>
+      <c r="F70" s="6" t="s">
+        <v>817</v>
+      </c>
+      <c r="G70" s="8" t="s">
+        <v>818</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6247,11 +6262,11 @@
       <c r="E71" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F71" s="7" t="s">
-        <v>821</v>
-      </c>
-      <c r="G71" s="9" t="s">
-        <v>822</v>
+      <c r="F71" s="6" t="s">
+        <v>819</v>
+      </c>
+      <c r="G71" s="8" t="s">
+        <v>820</v>
       </c>
     </row>
     <row r="72" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6270,11 +6285,11 @@
       <c r="E72" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F72" s="7" t="s">
-        <v>823</v>
-      </c>
-      <c r="G72" s="9" t="s">
-        <v>824</v>
+      <c r="F72" s="6" t="s">
+        <v>821</v>
+      </c>
+      <c r="G72" s="8" t="s">
+        <v>822</v>
       </c>
     </row>
     <row r="73" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6293,11 +6308,11 @@
       <c r="E73" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F73" s="7" t="s">
-        <v>825</v>
-      </c>
-      <c r="G73" s="9" t="s">
-        <v>826</v>
+      <c r="F73" s="6" t="s">
+        <v>823</v>
+      </c>
+      <c r="G73" s="8" t="s">
+        <v>824</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6316,11 +6331,11 @@
       <c r="E74" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F74" s="7" t="s">
-        <v>827</v>
-      </c>
-      <c r="G74" s="9" t="s">
-        <v>828</v>
+      <c r="F74" s="6" t="s">
+        <v>825</v>
+      </c>
+      <c r="G74" s="8" t="s">
+        <v>826</v>
       </c>
     </row>
     <row r="75" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6339,11 +6354,11 @@
       <c r="E75" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F75" s="7" t="s">
-        <v>829</v>
-      </c>
-      <c r="G75" s="9" t="s">
-        <v>830</v>
+      <c r="F75" s="6" t="s">
+        <v>827</v>
+      </c>
+      <c r="G75" s="8" t="s">
+        <v>828</v>
       </c>
     </row>
     <row r="76" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6362,11 +6377,11 @@
       <c r="E76" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F76" s="7" t="s">
-        <v>831</v>
-      </c>
-      <c r="G76" s="9" t="s">
-        <v>832</v>
+      <c r="F76" s="6" t="s">
+        <v>829</v>
+      </c>
+      <c r="G76" s="8" t="s">
+        <v>830</v>
       </c>
     </row>
     <row r="77" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6385,11 +6400,11 @@
       <c r="E77" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F77" s="7" t="s">
-        <v>833</v>
-      </c>
-      <c r="G77" s="9" t="s">
-        <v>834</v>
+      <c r="F77" s="6" t="s">
+        <v>831</v>
+      </c>
+      <c r="G77" s="8" t="s">
+        <v>832</v>
       </c>
     </row>
     <row r="78" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6408,11 +6423,11 @@
       <c r="E78" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F78" s="7" t="s">
-        <v>835</v>
-      </c>
-      <c r="G78" s="9" t="s">
-        <v>836</v>
+      <c r="F78" s="6" t="s">
+        <v>833</v>
+      </c>
+      <c r="G78" s="8" t="s">
+        <v>834</v>
       </c>
     </row>
     <row r="79" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6431,11 +6446,11 @@
       <c r="E79" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F79" s="7" t="s">
-        <v>837</v>
-      </c>
-      <c r="G79" s="9" t="s">
-        <v>838</v>
+      <c r="F79" s="6" t="s">
+        <v>835</v>
+      </c>
+      <c r="G79" s="8" t="s">
+        <v>836</v>
       </c>
     </row>
     <row r="80" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6454,11 +6469,11 @@
       <c r="E80" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F80" s="7" t="s">
-        <v>839</v>
-      </c>
-      <c r="G80" s="9" t="s">
-        <v>840</v>
+      <c r="F80" s="6" t="s">
+        <v>837</v>
+      </c>
+      <c r="G80" s="8" t="s">
+        <v>838</v>
       </c>
     </row>
     <row r="81" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6477,11 +6492,11 @@
       <c r="E81" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F81" s="7" t="s">
-        <v>841</v>
-      </c>
-      <c r="G81" s="9" t="s">
-        <v>842</v>
+      <c r="F81" s="6" t="s">
+        <v>839</v>
+      </c>
+      <c r="G81" s="8" t="s">
+        <v>840</v>
       </c>
     </row>
     <row r="82" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6500,11 +6515,11 @@
       <c r="E82" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F82" s="7" t="s">
-        <v>843</v>
-      </c>
-      <c r="G82" s="9" t="s">
-        <v>844</v>
+      <c r="F82" s="6" t="s">
+        <v>841</v>
+      </c>
+      <c r="G82" s="8" t="s">
+        <v>842</v>
       </c>
     </row>
     <row r="83" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6523,11 +6538,11 @@
       <c r="E83" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F83" s="7" t="s">
-        <v>845</v>
-      </c>
-      <c r="G83" s="9" t="s">
-        <v>846</v>
+      <c r="F83" s="6" t="s">
+        <v>843</v>
+      </c>
+      <c r="G83" s="8" t="s">
+        <v>844</v>
       </c>
     </row>
     <row r="84" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6546,11 +6561,11 @@
       <c r="E84" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F84" s="7" t="s">
-        <v>847</v>
-      </c>
-      <c r="G84" s="9" t="s">
-        <v>848</v>
+      <c r="F84" s="6" t="s">
+        <v>845</v>
+      </c>
+      <c r="G84" s="8" t="s">
+        <v>846</v>
       </c>
     </row>
     <row r="85" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6569,11 +6584,11 @@
       <c r="E85" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F85" s="7" t="s">
-        <v>849</v>
-      </c>
-      <c r="G85" s="9" t="s">
-        <v>850</v>
+      <c r="F85" s="6" t="s">
+        <v>847</v>
+      </c>
+      <c r="G85" s="8" t="s">
+        <v>848</v>
       </c>
     </row>
     <row r="86" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6592,11 +6607,11 @@
       <c r="E86" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F86" s="7" t="s">
-        <v>851</v>
-      </c>
-      <c r="G86" s="9" t="s">
-        <v>852</v>
+      <c r="F86" s="6" t="s">
+        <v>849</v>
+      </c>
+      <c r="G86" s="8" t="s">
+        <v>850</v>
       </c>
     </row>
     <row r="87" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6615,11 +6630,11 @@
       <c r="E87" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F87" s="7" t="s">
-        <v>853</v>
-      </c>
-      <c r="G87" s="9" t="s">
-        <v>854</v>
+      <c r="F87" s="6" t="s">
+        <v>851</v>
+      </c>
+      <c r="G87" s="8" t="s">
+        <v>852</v>
       </c>
     </row>
     <row r="88" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6638,11 +6653,11 @@
       <c r="E88" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F88" s="7" t="s">
-        <v>855</v>
-      </c>
-      <c r="G88" s="9" t="s">
-        <v>856</v>
+      <c r="F88" s="6" t="s">
+        <v>853</v>
+      </c>
+      <c r="G88" s="8" t="s">
+        <v>854</v>
       </c>
     </row>
     <row r="89" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6661,11 +6676,11 @@
       <c r="E89" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F89" s="7" t="s">
-        <v>857</v>
-      </c>
-      <c r="G89" s="9" t="s">
-        <v>858</v>
+      <c r="F89" s="6" t="s">
+        <v>855</v>
+      </c>
+      <c r="G89" s="8" t="s">
+        <v>856</v>
       </c>
     </row>
     <row r="90" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6684,11 +6699,11 @@
       <c r="E90" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F90" s="7" t="s">
-        <v>859</v>
-      </c>
-      <c r="G90" s="9" t="s">
-        <v>860</v>
+      <c r="F90" s="6" t="s">
+        <v>857</v>
+      </c>
+      <c r="G90" s="8" t="s">
+        <v>858</v>
       </c>
     </row>
     <row r="91" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6707,11 +6722,11 @@
       <c r="E91" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F91" s="7" t="s">
-        <v>861</v>
-      </c>
-      <c r="G91" s="9" t="s">
-        <v>862</v>
+      <c r="F91" s="6" t="s">
+        <v>859</v>
+      </c>
+      <c r="G91" s="8" t="s">
+        <v>860</v>
       </c>
     </row>
     <row r="92" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6730,11 +6745,11 @@
       <c r="E92" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F92" s="7" t="s">
-        <v>863</v>
-      </c>
-      <c r="G92" s="9" t="s">
-        <v>864</v>
+      <c r="F92" s="6" t="s">
+        <v>861</v>
+      </c>
+      <c r="G92" s="8" t="s">
+        <v>862</v>
       </c>
     </row>
     <row r="93" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6753,11 +6768,11 @@
       <c r="E93" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F93" s="7" t="s">
-        <v>865</v>
-      </c>
-      <c r="G93" s="9" t="s">
-        <v>866</v>
+      <c r="F93" s="6" t="s">
+        <v>863</v>
+      </c>
+      <c r="G93" s="8" t="s">
+        <v>864</v>
       </c>
     </row>
     <row r="94" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6776,11 +6791,11 @@
       <c r="E94" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F94" s="7" t="s">
-        <v>867</v>
-      </c>
-      <c r="G94" s="9" t="s">
-        <v>868</v>
+      <c r="F94" s="6" t="s">
+        <v>865</v>
+      </c>
+      <c r="G94" s="8" t="s">
+        <v>866</v>
       </c>
     </row>
     <row r="95" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6799,11 +6814,11 @@
       <c r="E95" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F95" s="7" t="s">
-        <v>869</v>
-      </c>
-      <c r="G95" s="9" t="s">
-        <v>870</v>
+      <c r="F95" s="6" t="s">
+        <v>867</v>
+      </c>
+      <c r="G95" s="8" t="s">
+        <v>868</v>
       </c>
     </row>
     <row r="96" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6822,11 +6837,11 @@
       <c r="E96" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F96" s="7" t="s">
-        <v>871</v>
-      </c>
-      <c r="G96" s="9" t="s">
-        <v>872</v>
+      <c r="F96" s="6" t="s">
+        <v>869</v>
+      </c>
+      <c r="G96" s="8" t="s">
+        <v>870</v>
       </c>
     </row>
     <row r="97" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6845,11 +6860,11 @@
       <c r="E97" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F97" s="7" t="s">
-        <v>873</v>
-      </c>
-      <c r="G97" s="9" t="s">
-        <v>874</v>
+      <c r="F97" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="G97" s="8" t="s">
+        <v>872</v>
       </c>
     </row>
     <row r="98" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6868,11 +6883,11 @@
       <c r="E98" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F98" s="7" t="s">
-        <v>875</v>
-      </c>
-      <c r="G98" s="9" t="s">
-        <v>876</v>
+      <c r="F98" s="6" t="s">
+        <v>873</v>
+      </c>
+      <c r="G98" s="8" t="s">
+        <v>874</v>
       </c>
     </row>
     <row r="99" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6891,11 +6906,11 @@
       <c r="E99" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F99" s="7" t="s">
-        <v>877</v>
-      </c>
-      <c r="G99" s="9" t="s">
-        <v>878</v>
+      <c r="F99" s="6" t="s">
+        <v>875</v>
+      </c>
+      <c r="G99" s="8" t="s">
+        <v>876</v>
       </c>
     </row>
     <row r="100" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6914,11 +6929,11 @@
       <c r="E100" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F100" s="7" t="s">
-        <v>879</v>
-      </c>
-      <c r="G100" s="9" t="s">
-        <v>880</v>
+      <c r="F100" s="6" t="s">
+        <v>877</v>
+      </c>
+      <c r="G100" s="8" t="s">
+        <v>878</v>
       </c>
     </row>
     <row r="101" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6937,11 +6952,11 @@
       <c r="E101" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F101" s="7" t="s">
-        <v>881</v>
-      </c>
-      <c r="G101" s="9" t="s">
-        <v>882</v>
+      <c r="F101" s="6" t="s">
+        <v>879</v>
+      </c>
+      <c r="G101" s="8" t="s">
+        <v>880</v>
       </c>
     </row>
     <row r="102" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6960,11 +6975,11 @@
       <c r="E102" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F102" s="7" t="s">
-        <v>883</v>
-      </c>
-      <c r="G102" s="9" t="s">
-        <v>884</v>
+      <c r="F102" s="6" t="s">
+        <v>881</v>
+      </c>
+      <c r="G102" s="8" t="s">
+        <v>882</v>
       </c>
     </row>
     <row r="103" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6983,11 +6998,11 @@
       <c r="E103" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F103" s="7" t="s">
-        <v>885</v>
-      </c>
-      <c r="G103" s="9" t="s">
-        <v>886</v>
+      <c r="F103" s="6" t="s">
+        <v>883</v>
+      </c>
+      <c r="G103" s="8" t="s">
+        <v>884</v>
       </c>
     </row>
     <row r="104" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7006,11 +7021,11 @@
       <c r="E104" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F104" s="7" t="s">
-        <v>887</v>
-      </c>
-      <c r="G104" s="9" t="s">
-        <v>888</v>
+      <c r="F104" s="6" t="s">
+        <v>885</v>
+      </c>
+      <c r="G104" s="8" t="s">
+        <v>886</v>
       </c>
     </row>
     <row r="105" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7029,11 +7044,11 @@
       <c r="E105" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F105" s="7" t="s">
-        <v>889</v>
-      </c>
-      <c r="G105" s="9" t="s">
-        <v>890</v>
+      <c r="F105" s="6" t="s">
+        <v>887</v>
+      </c>
+      <c r="G105" s="8" t="s">
+        <v>888</v>
       </c>
     </row>
     <row r="106" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7052,11 +7067,11 @@
       <c r="E106" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F106" s="7" t="s">
-        <v>891</v>
-      </c>
-      <c r="G106" s="9" t="s">
-        <v>892</v>
+      <c r="F106" s="6" t="s">
+        <v>889</v>
+      </c>
+      <c r="G106" s="8" t="s">
+        <v>890</v>
       </c>
     </row>
     <row r="107" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7075,11 +7090,11 @@
       <c r="E107" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F107" s="7" t="s">
-        <v>893</v>
-      </c>
-      <c r="G107" s="9" t="s">
-        <v>894</v>
+      <c r="F107" s="6" t="s">
+        <v>891</v>
+      </c>
+      <c r="G107" s="8" t="s">
+        <v>892</v>
       </c>
     </row>
     <row r="108" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7098,11 +7113,11 @@
       <c r="E108" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F108" s="7" t="s">
-        <v>895</v>
-      </c>
-      <c r="G108" s="9" t="s">
-        <v>896</v>
+      <c r="F108" s="6" t="s">
+        <v>893</v>
+      </c>
+      <c r="G108" s="8" t="s">
+        <v>894</v>
       </c>
     </row>
     <row r="109" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7121,11 +7136,11 @@
       <c r="E109" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F109" s="7" t="s">
-        <v>897</v>
-      </c>
-      <c r="G109" s="9" t="s">
-        <v>898</v>
+      <c r="F109" s="6" t="s">
+        <v>895</v>
+      </c>
+      <c r="G109" s="8" t="s">
+        <v>896</v>
       </c>
     </row>
     <row r="110" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7144,11 +7159,11 @@
       <c r="E110" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F110" s="7" t="s">
-        <v>899</v>
-      </c>
-      <c r="G110" s="9" t="s">
-        <v>900</v>
+      <c r="F110" s="6" t="s">
+        <v>897</v>
+      </c>
+      <c r="G110" s="8" t="s">
+        <v>898</v>
       </c>
     </row>
     <row r="111" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7167,11 +7182,11 @@
       <c r="E111" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F111" s="7" t="s">
-        <v>901</v>
-      </c>
-      <c r="G111" s="9" t="s">
-        <v>902</v>
+      <c r="F111" s="6" t="s">
+        <v>899</v>
+      </c>
+      <c r="G111" s="8" t="s">
+        <v>900</v>
       </c>
     </row>
     <row r="112" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7190,11 +7205,11 @@
       <c r="E112" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F112" s="7" t="s">
-        <v>903</v>
-      </c>
-      <c r="G112" s="9" t="s">
-        <v>904</v>
+      <c r="F112" s="6" t="s">
+        <v>901</v>
+      </c>
+      <c r="G112" s="8" t="s">
+        <v>902</v>
       </c>
     </row>
     <row r="113" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7213,11 +7228,11 @@
       <c r="E113" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F113" s="7" t="s">
-        <v>905</v>
-      </c>
-      <c r="G113" s="9" t="s">
-        <v>906</v>
+      <c r="F113" s="6" t="s">
+        <v>903</v>
+      </c>
+      <c r="G113" s="8" t="s">
+        <v>904</v>
       </c>
     </row>
     <row r="114" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7236,11 +7251,11 @@
       <c r="E114" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F114" s="7" t="s">
-        <v>907</v>
-      </c>
-      <c r="G114" s="9" t="s">
-        <v>908</v>
+      <c r="F114" s="6" t="s">
+        <v>905</v>
+      </c>
+      <c r="G114" s="8" t="s">
+        <v>906</v>
       </c>
     </row>
     <row r="115" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7259,11 +7274,11 @@
       <c r="E115" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F115" s="7" t="s">
-        <v>909</v>
-      </c>
-      <c r="G115" s="9" t="s">
-        <v>910</v>
+      <c r="F115" s="6" t="s">
+        <v>907</v>
+      </c>
+      <c r="G115" s="8" t="s">
+        <v>908</v>
       </c>
     </row>
     <row r="116" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7282,11 +7297,11 @@
       <c r="E116" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F116" s="7" t="s">
-        <v>911</v>
-      </c>
-      <c r="G116" s="9" t="s">
-        <v>912</v>
+      <c r="F116" s="6" t="s">
+        <v>909</v>
+      </c>
+      <c r="G116" s="8" t="s">
+        <v>910</v>
       </c>
     </row>
     <row r="117" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7305,11 +7320,11 @@
       <c r="E117" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F117" s="7" t="s">
-        <v>913</v>
-      </c>
-      <c r="G117" s="9" t="s">
-        <v>914</v>
+      <c r="F117" s="6" t="s">
+        <v>911</v>
+      </c>
+      <c r="G117" s="8" t="s">
+        <v>912</v>
       </c>
     </row>
     <row r="118" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7328,11 +7343,11 @@
       <c r="E118" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F118" s="7" t="s">
-        <v>915</v>
-      </c>
-      <c r="G118" s="9" t="s">
-        <v>916</v>
+      <c r="F118" s="6" t="s">
+        <v>913</v>
+      </c>
+      <c r="G118" s="8" t="s">
+        <v>914</v>
       </c>
     </row>
     <row r="119" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7351,11 +7366,11 @@
       <c r="E119" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F119" s="7" t="s">
-        <v>917</v>
-      </c>
-      <c r="G119" s="9" t="s">
-        <v>918</v>
+      <c r="F119" s="6" t="s">
+        <v>915</v>
+      </c>
+      <c r="G119" s="8" t="s">
+        <v>916</v>
       </c>
     </row>
     <row r="120" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7374,11 +7389,11 @@
       <c r="E120" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F120" s="7" t="s">
-        <v>919</v>
-      </c>
-      <c r="G120" s="9" t="s">
-        <v>920</v>
+      <c r="F120" s="6" t="s">
+        <v>917</v>
+      </c>
+      <c r="G120" s="8" t="s">
+        <v>918</v>
       </c>
     </row>
     <row r="121" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7397,11 +7412,11 @@
       <c r="E121" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F121" s="7" t="s">
-        <v>921</v>
-      </c>
-      <c r="G121" s="9" t="s">
-        <v>922</v>
+      <c r="F121" s="6" t="s">
+        <v>919</v>
+      </c>
+      <c r="G121" s="8" t="s">
+        <v>920</v>
       </c>
     </row>
     <row r="122" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7420,11 +7435,11 @@
       <c r="E122" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F122" s="7" t="s">
-        <v>923</v>
-      </c>
-      <c r="G122" s="9" t="s">
-        <v>924</v>
+      <c r="F122" s="6" t="s">
+        <v>921</v>
+      </c>
+      <c r="G122" s="8" t="s">
+        <v>922</v>
       </c>
     </row>
     <row r="123" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7443,11 +7458,11 @@
       <c r="E123" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F123" s="7" t="s">
-        <v>925</v>
-      </c>
-      <c r="G123" s="9" t="s">
-        <v>926</v>
+      <c r="F123" s="6" t="s">
+        <v>923</v>
+      </c>
+      <c r="G123" s="8" t="s">
+        <v>924</v>
       </c>
     </row>
     <row r="124" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7466,11 +7481,11 @@
       <c r="E124" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F124" s="7" t="s">
-        <v>927</v>
-      </c>
-      <c r="G124" s="9" t="s">
-        <v>928</v>
+      <c r="F124" s="6" t="s">
+        <v>925</v>
+      </c>
+      <c r="G124" s="8" t="s">
+        <v>926</v>
       </c>
     </row>
     <row r="125" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7489,11 +7504,11 @@
       <c r="E125" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F125" s="7" t="s">
-        <v>929</v>
-      </c>
-      <c r="G125" s="9" t="s">
-        <v>930</v>
+      <c r="F125" s="6" t="s">
+        <v>927</v>
+      </c>
+      <c r="G125" s="8" t="s">
+        <v>928</v>
       </c>
     </row>
     <row r="126" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7512,11 +7527,11 @@
       <c r="E126" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F126" s="7" t="s">
-        <v>931</v>
-      </c>
-      <c r="G126" s="9" t="s">
-        <v>932</v>
+      <c r="F126" s="6" t="s">
+        <v>929</v>
+      </c>
+      <c r="G126" s="8" t="s">
+        <v>930</v>
       </c>
     </row>
     <row r="127" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7535,11 +7550,11 @@
       <c r="E127" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F127" s="7" t="s">
-        <v>933</v>
-      </c>
-      <c r="G127" s="9" t="s">
-        <v>934</v>
+      <c r="F127" s="6" t="s">
+        <v>931</v>
+      </c>
+      <c r="G127" s="8" t="s">
+        <v>932</v>
       </c>
     </row>
     <row r="128" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7558,11 +7573,11 @@
       <c r="E128" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F128" s="7" t="s">
-        <v>935</v>
-      </c>
-      <c r="G128" s="9" t="s">
-        <v>936</v>
+      <c r="F128" s="6" t="s">
+        <v>933</v>
+      </c>
+      <c r="G128" s="8" t="s">
+        <v>934</v>
       </c>
     </row>
     <row r="129" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7581,11 +7596,11 @@
       <c r="E129" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F129" s="7" t="s">
-        <v>937</v>
-      </c>
-      <c r="G129" s="9" t="s">
-        <v>938</v>
+      <c r="F129" s="6" t="s">
+        <v>935</v>
+      </c>
+      <c r="G129" s="8" t="s">
+        <v>936</v>
       </c>
     </row>
     <row r="130" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7604,11 +7619,11 @@
       <c r="E130" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F130" s="7" t="s">
-        <v>939</v>
-      </c>
-      <c r="G130" s="9" t="s">
-        <v>940</v>
+      <c r="F130" s="6" t="s">
+        <v>937</v>
+      </c>
+      <c r="G130" s="8" t="s">
+        <v>938</v>
       </c>
     </row>
     <row r="131" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7627,11 +7642,11 @@
       <c r="E131" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F131" s="7" t="s">
-        <v>941</v>
-      </c>
-      <c r="G131" s="9" t="s">
-        <v>942</v>
+      <c r="F131" s="6" t="s">
+        <v>939</v>
+      </c>
+      <c r="G131" s="8" t="s">
+        <v>940</v>
       </c>
     </row>
     <row r="132" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7650,11 +7665,11 @@
       <c r="E132" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F132" s="7" t="s">
-        <v>943</v>
-      </c>
-      <c r="G132" s="9" t="s">
-        <v>944</v>
+      <c r="F132" s="6" t="s">
+        <v>941</v>
+      </c>
+      <c r="G132" s="8" t="s">
+        <v>942</v>
       </c>
     </row>
     <row r="133" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7673,11 +7688,11 @@
       <c r="E133" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F133" s="7" t="s">
-        <v>945</v>
-      </c>
-      <c r="G133" s="9" t="s">
-        <v>946</v>
+      <c r="F133" s="6" t="s">
+        <v>943</v>
+      </c>
+      <c r="G133" s="8" t="s">
+        <v>944</v>
       </c>
     </row>
     <row r="134" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7696,11 +7711,11 @@
       <c r="E134" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F134" s="7" t="s">
-        <v>947</v>
-      </c>
-      <c r="G134" s="9" t="s">
-        <v>948</v>
+      <c r="F134" s="6" t="s">
+        <v>945</v>
+      </c>
+      <c r="G134" s="8" t="s">
+        <v>946</v>
       </c>
     </row>
     <row r="135" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7719,11 +7734,11 @@
       <c r="E135" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F135" s="7" t="s">
-        <v>949</v>
-      </c>
-      <c r="G135" s="9" t="s">
-        <v>950</v>
+      <c r="F135" s="6" t="s">
+        <v>947</v>
+      </c>
+      <c r="G135" s="8" t="s">
+        <v>948</v>
       </c>
     </row>
     <row r="136" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7742,11 +7757,11 @@
       <c r="E136" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F136" s="7" t="s">
-        <v>951</v>
-      </c>
-      <c r="G136" s="9" t="s">
-        <v>952</v>
+      <c r="F136" s="6" t="s">
+        <v>949</v>
+      </c>
+      <c r="G136" s="8" t="s">
+        <v>950</v>
       </c>
     </row>
     <row r="137" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7765,11 +7780,11 @@
       <c r="E137" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F137" s="7" t="s">
-        <v>953</v>
-      </c>
-      <c r="G137" s="9" t="s">
-        <v>954</v>
+      <c r="F137" s="6" t="s">
+        <v>951</v>
+      </c>
+      <c r="G137" s="8" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="138" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7788,11 +7803,11 @@
       <c r="E138" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F138" s="7" t="s">
-        <v>955</v>
-      </c>
-      <c r="G138" s="9" t="s">
-        <v>956</v>
+      <c r="F138" s="6" t="s">
+        <v>953</v>
+      </c>
+      <c r="G138" s="8" t="s">
+        <v>954</v>
       </c>
     </row>
     <row r="139" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7811,11 +7826,11 @@
       <c r="E139" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F139" s="7" t="s">
-        <v>957</v>
-      </c>
-      <c r="G139" s="9" t="s">
-        <v>958</v>
+      <c r="F139" s="6" t="s">
+        <v>955</v>
+      </c>
+      <c r="G139" s="8" t="s">
+        <v>956</v>
       </c>
     </row>
     <row r="140" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7834,11 +7849,11 @@
       <c r="E140" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F140" s="7" t="s">
-        <v>959</v>
-      </c>
-      <c r="G140" s="9" t="s">
-        <v>960</v>
+      <c r="F140" s="6" t="s">
+        <v>957</v>
+      </c>
+      <c r="G140" s="8" t="s">
+        <v>958</v>
       </c>
     </row>
     <row r="141" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7857,11 +7872,11 @@
       <c r="E141" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F141" s="7" t="s">
-        <v>961</v>
-      </c>
-      <c r="G141" s="9" t="s">
-        <v>962</v>
+      <c r="F141" s="6" t="s">
+        <v>959</v>
+      </c>
+      <c r="G141" s="8" t="s">
+        <v>960</v>
       </c>
     </row>
     <row r="142" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7880,11 +7895,11 @@
       <c r="E142" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F142" s="7" t="s">
-        <v>963</v>
-      </c>
-      <c r="G142" s="9" t="s">
-        <v>964</v>
+      <c r="F142" s="6" t="s">
+        <v>961</v>
+      </c>
+      <c r="G142" s="8" t="s">
+        <v>962</v>
       </c>
     </row>
     <row r="143" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7903,11 +7918,11 @@
       <c r="E143" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F143" s="7" t="s">
-        <v>965</v>
-      </c>
-      <c r="G143" s="9" t="s">
-        <v>966</v>
+      <c r="F143" s="6" t="s">
+        <v>963</v>
+      </c>
+      <c r="G143" s="8" t="s">
+        <v>964</v>
       </c>
     </row>
     <row r="144" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7926,11 +7941,11 @@
       <c r="E144" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F144" s="7" t="s">
-        <v>967</v>
-      </c>
-      <c r="G144" s="9" t="s">
-        <v>968</v>
+      <c r="F144" s="6" t="s">
+        <v>965</v>
+      </c>
+      <c r="G144" s="8" t="s">
+        <v>966</v>
       </c>
     </row>
     <row r="145" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7949,11 +7964,11 @@
       <c r="E145" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F145" s="7" t="s">
-        <v>969</v>
-      </c>
-      <c r="G145" s="9" t="s">
-        <v>970</v>
+      <c r="F145" s="6" t="s">
+        <v>967</v>
+      </c>
+      <c r="G145" s="8" t="s">
+        <v>968</v>
       </c>
     </row>
     <row r="146" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7972,11 +7987,11 @@
       <c r="E146" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F146" s="7" t="s">
-        <v>971</v>
-      </c>
-      <c r="G146" s="9" t="s">
-        <v>972</v>
+      <c r="F146" s="6" t="s">
+        <v>969</v>
+      </c>
+      <c r="G146" s="8" t="s">
+        <v>970</v>
       </c>
     </row>
     <row r="147" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7995,11 +8010,11 @@
       <c r="E147" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F147" s="7" t="s">
-        <v>973</v>
-      </c>
-      <c r="G147" s="9" t="s">
-        <v>974</v>
+      <c r="F147" s="6" t="s">
+        <v>971</v>
+      </c>
+      <c r="G147" s="8" t="s">
+        <v>972</v>
       </c>
     </row>
     <row r="148" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8018,11 +8033,11 @@
       <c r="E148" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F148" s="7" t="s">
-        <v>975</v>
-      </c>
-      <c r="G148" s="9" t="s">
-        <v>976</v>
+      <c r="F148" s="6" t="s">
+        <v>973</v>
+      </c>
+      <c r="G148" s="8" t="s">
+        <v>974</v>
       </c>
     </row>
     <row r="149" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8041,11 +8056,11 @@
       <c r="E149" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F149" s="7" t="s">
-        <v>977</v>
-      </c>
-      <c r="G149" s="9" t="s">
-        <v>978</v>
+      <c r="F149" s="6" t="s">
+        <v>975</v>
+      </c>
+      <c r="G149" s="8" t="s">
+        <v>976</v>
       </c>
     </row>
     <row r="150" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8064,11 +8079,11 @@
       <c r="E150" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F150" s="7" t="s">
-        <v>979</v>
-      </c>
-      <c r="G150" s="9" t="s">
-        <v>980</v>
+      <c r="F150" s="6" t="s">
+        <v>977</v>
+      </c>
+      <c r="G150" s="8" t="s">
+        <v>978</v>
       </c>
     </row>
     <row r="151" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8087,11 +8102,11 @@
       <c r="E151" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F151" s="7" t="s">
-        <v>981</v>
-      </c>
-      <c r="G151" s="9" t="s">
-        <v>982</v>
+      <c r="F151" s="6" t="s">
+        <v>979</v>
+      </c>
+      <c r="G151" s="8" t="s">
+        <v>980</v>
       </c>
     </row>
     <row r="152" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8110,11 +8125,11 @@
       <c r="E152" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F152" s="7" t="s">
-        <v>983</v>
-      </c>
-      <c r="G152" s="9" t="s">
-        <v>984</v>
+      <c r="F152" s="6" t="s">
+        <v>981</v>
+      </c>
+      <c r="G152" s="8" t="s">
+        <v>982</v>
       </c>
     </row>
     <row r="153" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8133,11 +8148,11 @@
       <c r="E153" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F153" s="7" t="s">
-        <v>985</v>
-      </c>
-      <c r="G153" s="9" t="s">
-        <v>986</v>
+      <c r="F153" s="6" t="s">
+        <v>983</v>
+      </c>
+      <c r="G153" s="8" t="s">
+        <v>984</v>
       </c>
     </row>
     <row r="154" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8156,11 +8171,11 @@
       <c r="E154" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F154" s="7" t="s">
-        <v>987</v>
-      </c>
-      <c r="G154" s="9" t="s">
-        <v>988</v>
+      <c r="F154" s="6" t="s">
+        <v>985</v>
+      </c>
+      <c r="G154" s="8" t="s">
+        <v>986</v>
       </c>
     </row>
     <row r="155" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8179,11 +8194,11 @@
       <c r="E155" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F155" s="7" t="s">
-        <v>989</v>
-      </c>
-      <c r="G155" s="9" t="s">
-        <v>990</v>
+      <c r="F155" s="6" t="s">
+        <v>987</v>
+      </c>
+      <c r="G155" s="8" t="s">
+        <v>988</v>
       </c>
     </row>
     <row r="156" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8202,11 +8217,11 @@
       <c r="E156" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F156" s="7" t="s">
-        <v>991</v>
-      </c>
-      <c r="G156" s="9" t="s">
-        <v>992</v>
+      <c r="F156" s="6" t="s">
+        <v>989</v>
+      </c>
+      <c r="G156" s="8" t="s">
+        <v>990</v>
       </c>
     </row>
     <row r="157" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8225,11 +8240,11 @@
       <c r="E157" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F157" s="7" t="s">
-        <v>993</v>
-      </c>
-      <c r="G157" s="9" t="s">
-        <v>994</v>
+      <c r="F157" s="6" t="s">
+        <v>991</v>
+      </c>
+      <c r="G157" s="8" t="s">
+        <v>992</v>
       </c>
     </row>
     <row r="158" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8248,11 +8263,11 @@
       <c r="E158" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F158" s="7" t="s">
-        <v>995</v>
-      </c>
-      <c r="G158" s="9" t="s">
-        <v>996</v>
+      <c r="F158" s="6" t="s">
+        <v>993</v>
+      </c>
+      <c r="G158" s="8" t="s">
+        <v>994</v>
       </c>
     </row>
     <row r="159" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8271,11 +8286,11 @@
       <c r="E159" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F159" s="7" t="s">
-        <v>997</v>
-      </c>
-      <c r="G159" s="9" t="s">
-        <v>998</v>
+      <c r="F159" s="6" t="s">
+        <v>995</v>
+      </c>
+      <c r="G159" s="8" t="s">
+        <v>996</v>
       </c>
     </row>
     <row r="160" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8294,11 +8309,11 @@
       <c r="E160" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F160" s="7" t="s">
-        <v>999</v>
-      </c>
-      <c r="G160" s="9" t="s">
-        <v>1000</v>
+      <c r="F160" s="6" t="s">
+        <v>997</v>
+      </c>
+      <c r="G160" s="8" t="s">
+        <v>998</v>
       </c>
     </row>
     <row r="161" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8317,11 +8332,11 @@
       <c r="E161" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F161" s="7" t="s">
-        <v>1001</v>
-      </c>
-      <c r="G161" s="9" t="s">
-        <v>1002</v>
+      <c r="F161" s="6" t="s">
+        <v>999</v>
+      </c>
+      <c r="G161" s="8" t="s">
+        <v>1000</v>
       </c>
     </row>
     <row r="162" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8340,11 +8355,11 @@
       <c r="E162" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F162" s="7" t="s">
-        <v>1003</v>
-      </c>
-      <c r="G162" s="9" t="s">
-        <v>1004</v>
+      <c r="F162" s="6" t="s">
+        <v>1001</v>
+      </c>
+      <c r="G162" s="8" t="s">
+        <v>1002</v>
       </c>
     </row>
     <row r="163" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8363,11 +8378,11 @@
       <c r="E163" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F163" s="7" t="s">
-        <v>1005</v>
-      </c>
-      <c r="G163" s="9" t="s">
-        <v>1006</v>
+      <c r="F163" s="6" t="s">
+        <v>1003</v>
+      </c>
+      <c r="G163" s="8" t="s">
+        <v>1004</v>
       </c>
     </row>
     <row r="164" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8386,11 +8401,11 @@
       <c r="E164" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F164" s="7" t="s">
-        <v>1007</v>
-      </c>
-      <c r="G164" s="9" t="s">
-        <v>1008</v>
+      <c r="F164" s="6" t="s">
+        <v>1005</v>
+      </c>
+      <c r="G164" s="8" t="s">
+        <v>1006</v>
       </c>
     </row>
     <row r="165" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8409,11 +8424,11 @@
       <c r="E165" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F165" s="7" t="s">
-        <v>1009</v>
-      </c>
-      <c r="G165" s="9" t="s">
-        <v>1010</v>
+      <c r="F165" s="6" t="s">
+        <v>1007</v>
+      </c>
+      <c r="G165" s="8" t="s">
+        <v>1008</v>
       </c>
     </row>
     <row r="166" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8432,11 +8447,11 @@
       <c r="E166" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F166" s="7" t="s">
-        <v>1011</v>
-      </c>
-      <c r="G166" s="9" t="s">
-        <v>1012</v>
+      <c r="F166" s="6" t="s">
+        <v>1009</v>
+      </c>
+      <c r="G166" s="8" t="s">
+        <v>1010</v>
       </c>
     </row>
     <row r="167" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8455,11 +8470,11 @@
       <c r="E167" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F167" s="7" t="s">
-        <v>1013</v>
-      </c>
-      <c r="G167" s="9" t="s">
-        <v>1014</v>
+      <c r="F167" s="6" t="s">
+        <v>1011</v>
+      </c>
+      <c r="G167" s="8" t="s">
+        <v>1012</v>
       </c>
     </row>
     <row r="168" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8478,11 +8493,11 @@
       <c r="E168" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F168" s="7" t="s">
-        <v>1015</v>
-      </c>
-      <c r="G168" s="9" t="s">
-        <v>1016</v>
+      <c r="F168" s="6" t="s">
+        <v>1013</v>
+      </c>
+      <c r="G168" s="8" t="s">
+        <v>1014</v>
       </c>
     </row>
     <row r="169" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8501,11 +8516,11 @@
       <c r="E169" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F169" s="7" t="s">
-        <v>1017</v>
-      </c>
-      <c r="G169" s="9" t="s">
-        <v>1018</v>
+      <c r="F169" s="6" t="s">
+        <v>1015</v>
+      </c>
+      <c r="G169" s="8" t="s">
+        <v>1016</v>
       </c>
     </row>
     <row r="170" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8524,11 +8539,11 @@
       <c r="E170" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F170" s="7" t="s">
-        <v>1019</v>
-      </c>
-      <c r="G170" s="9" t="s">
-        <v>1020</v>
+      <c r="F170" s="6" t="s">
+        <v>1017</v>
+      </c>
+      <c r="G170" s="8" t="s">
+        <v>1018</v>
       </c>
     </row>
     <row r="171" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8547,11 +8562,11 @@
       <c r="E171" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F171" s="7" t="s">
-        <v>1021</v>
-      </c>
-      <c r="G171" s="9" t="s">
-        <v>1022</v>
+      <c r="F171" s="6" t="s">
+        <v>1019</v>
+      </c>
+      <c r="G171" s="8" t="s">
+        <v>1020</v>
       </c>
     </row>
     <row r="172" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8570,11 +8585,11 @@
       <c r="E172" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F172" s="7" t="s">
-        <v>1023</v>
-      </c>
-      <c r="G172" s="9" t="s">
-        <v>1024</v>
+      <c r="F172" s="6" t="s">
+        <v>1021</v>
+      </c>
+      <c r="G172" s="8" t="s">
+        <v>1022</v>
       </c>
     </row>
     <row r="173" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8593,11 +8608,11 @@
       <c r="E173" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F173" s="7" t="s">
-        <v>1025</v>
-      </c>
-      <c r="G173" s="9" t="s">
-        <v>1026</v>
+      <c r="F173" s="6" t="s">
+        <v>1023</v>
+      </c>
+      <c r="G173" s="8" t="s">
+        <v>1024</v>
       </c>
     </row>
     <row r="174" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8616,11 +8631,11 @@
       <c r="E174" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F174" s="7" t="s">
-        <v>1027</v>
-      </c>
-      <c r="G174" s="9" t="s">
-        <v>1028</v>
+      <c r="F174" s="6" t="s">
+        <v>1025</v>
+      </c>
+      <c r="G174" s="8" t="s">
+        <v>1026</v>
       </c>
     </row>
     <row r="175" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8639,11 +8654,11 @@
       <c r="E175" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F175" s="7" t="s">
-        <v>1029</v>
-      </c>
-      <c r="G175" s="9" t="s">
-        <v>1030</v>
+      <c r="F175" s="6" t="s">
+        <v>1027</v>
+      </c>
+      <c r="G175" s="8" t="s">
+        <v>1028</v>
       </c>
     </row>
     <row r="176" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8662,11 +8677,11 @@
       <c r="E176" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F176" s="7" t="s">
-        <v>1031</v>
-      </c>
-      <c r="G176" s="9" t="s">
-        <v>1032</v>
+      <c r="F176" s="6" t="s">
+        <v>1029</v>
+      </c>
+      <c r="G176" s="8" t="s">
+        <v>1030</v>
       </c>
     </row>
     <row r="177" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8685,11 +8700,11 @@
       <c r="E177" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F177" s="7" t="s">
-        <v>1033</v>
-      </c>
-      <c r="G177" s="9" t="s">
-        <v>1034</v>
+      <c r="F177" s="6" t="s">
+        <v>1031</v>
+      </c>
+      <c r="G177" s="8" t="s">
+        <v>1032</v>
       </c>
     </row>
     <row r="178" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8708,11 +8723,11 @@
       <c r="E178" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F178" s="7" t="s">
-        <v>1035</v>
-      </c>
-      <c r="G178" s="9" t="s">
-        <v>1036</v>
+      <c r="F178" s="6" t="s">
+        <v>1033</v>
+      </c>
+      <c r="G178" s="8" t="s">
+        <v>1034</v>
       </c>
     </row>
     <row r="179" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8731,11 +8746,11 @@
       <c r="E179" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F179" s="7" t="s">
-        <v>1037</v>
-      </c>
-      <c r="G179" s="9" t="s">
-        <v>1038</v>
+      <c r="F179" s="6" t="s">
+        <v>1035</v>
+      </c>
+      <c r="G179" s="8" t="s">
+        <v>1036</v>
       </c>
     </row>
     <row r="180" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8754,11 +8769,11 @@
       <c r="E180" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F180" s="7" t="s">
-        <v>1039</v>
-      </c>
-      <c r="G180" s="9" t="s">
-        <v>1040</v>
+      <c r="F180" s="6" t="s">
+        <v>1037</v>
+      </c>
+      <c r="G180" s="8" t="s">
+        <v>1038</v>
       </c>
     </row>
     <row r="181" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8777,11 +8792,11 @@
       <c r="E181" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F181" s="7" t="s">
-        <v>1041</v>
-      </c>
-      <c r="G181" s="9" t="s">
-        <v>1042</v>
+      <c r="F181" s="6" t="s">
+        <v>1039</v>
+      </c>
+      <c r="G181" s="8" t="s">
+        <v>1040</v>
       </c>
     </row>
     <row r="182" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8800,11 +8815,11 @@
       <c r="E182" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F182" s="7" t="s">
-        <v>1043</v>
-      </c>
-      <c r="G182" s="9" t="s">
-        <v>1044</v>
+      <c r="F182" s="6" t="s">
+        <v>1041</v>
+      </c>
+      <c r="G182" s="8" t="s">
+        <v>1042</v>
       </c>
     </row>
     <row r="183" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8823,11 +8838,11 @@
       <c r="E183" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F183" s="7" t="s">
-        <v>1045</v>
-      </c>
-      <c r="G183" s="9" t="s">
-        <v>1046</v>
+      <c r="F183" s="6" t="s">
+        <v>1043</v>
+      </c>
+      <c r="G183" s="8" t="s">
+        <v>1044</v>
       </c>
     </row>
     <row r="184" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8846,11 +8861,11 @@
       <c r="E184" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F184" s="7" t="s">
-        <v>1047</v>
-      </c>
-      <c r="G184" s="9" t="s">
-        <v>1048</v>
+      <c r="F184" s="6" t="s">
+        <v>1045</v>
+      </c>
+      <c r="G184" s="8" t="s">
+        <v>1046</v>
       </c>
     </row>
     <row r="185" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8869,11 +8884,11 @@
       <c r="E185" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F185" s="7" t="s">
-        <v>1049</v>
-      </c>
-      <c r="G185" s="9" t="s">
-        <v>1050</v>
+      <c r="F185" s="6" t="s">
+        <v>1047</v>
+      </c>
+      <c r="G185" s="8" t="s">
+        <v>1048</v>
       </c>
     </row>
     <row r="186" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8892,11 +8907,11 @@
       <c r="E186" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F186" s="7" t="s">
-        <v>1051</v>
-      </c>
-      <c r="G186" s="9" t="s">
-        <v>1052</v>
+      <c r="F186" s="6" t="s">
+        <v>1049</v>
+      </c>
+      <c r="G186" s="8" t="s">
+        <v>1050</v>
       </c>
     </row>
     <row r="187" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8915,11 +8930,11 @@
       <c r="E187" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F187" s="7" t="s">
-        <v>1053</v>
-      </c>
-      <c r="G187" s="9" t="s">
-        <v>1054</v>
+      <c r="F187" s="6" t="s">
+        <v>1051</v>
+      </c>
+      <c r="G187" s="8" t="s">
+        <v>1052</v>
       </c>
     </row>
     <row r="188" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8938,11 +8953,11 @@
       <c r="E188" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F188" s="7" t="s">
-        <v>1055</v>
-      </c>
-      <c r="G188" s="9" t="s">
-        <v>1056</v>
+      <c r="F188" s="6" t="s">
+        <v>1053</v>
+      </c>
+      <c r="G188" s="8" t="s">
+        <v>1054</v>
       </c>
     </row>
     <row r="189" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8961,11 +8976,11 @@
       <c r="E189" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F189" s="7" t="s">
-        <v>1057</v>
-      </c>
-      <c r="G189" s="9" t="s">
-        <v>1058</v>
+      <c r="F189" s="6" t="s">
+        <v>1055</v>
+      </c>
+      <c r="G189" s="8" t="s">
+        <v>1056</v>
       </c>
     </row>
     <row r="190" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8984,11 +8999,11 @@
       <c r="E190" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F190" s="7" t="s">
-        <v>1059</v>
-      </c>
-      <c r="G190" s="9" t="s">
-        <v>1060</v>
+      <c r="F190" s="6" t="s">
+        <v>1057</v>
+      </c>
+      <c r="G190" s="8" t="s">
+        <v>1058</v>
       </c>
     </row>
     <row r="191" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9007,11 +9022,11 @@
       <c r="E191" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F191" s="7" t="s">
-        <v>1061</v>
-      </c>
-      <c r="G191" s="9" t="s">
-        <v>1062</v>
+      <c r="F191" s="6" t="s">
+        <v>1059</v>
+      </c>
+      <c r="G191" s="8" t="s">
+        <v>1060</v>
       </c>
     </row>
     <row r="192" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9030,11 +9045,11 @@
       <c r="E192" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F192" s="7" t="s">
-        <v>1063</v>
-      </c>
-      <c r="G192" s="9" t="s">
-        <v>1064</v>
+      <c r="F192" s="6" t="s">
+        <v>1061</v>
+      </c>
+      <c r="G192" s="8" t="s">
+        <v>1062</v>
       </c>
     </row>
     <row r="193" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9053,11 +9068,11 @@
       <c r="E193" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F193" s="7" t="s">
-        <v>1065</v>
-      </c>
-      <c r="G193" s="9" t="s">
-        <v>1066</v>
+      <c r="F193" s="6" t="s">
+        <v>1063</v>
+      </c>
+      <c r="G193" s="8" t="s">
+        <v>1064</v>
       </c>
     </row>
     <row r="194" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9076,11 +9091,11 @@
       <c r="E194" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F194" s="7" t="s">
-        <v>1067</v>
-      </c>
-      <c r="G194" s="9" t="s">
-        <v>1068</v>
+      <c r="F194" s="6" t="s">
+        <v>1065</v>
+      </c>
+      <c r="G194" s="8" t="s">
+        <v>1066</v>
       </c>
     </row>
     <row r="195" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9099,11 +9114,11 @@
       <c r="E195" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F195" s="7" t="s">
-        <v>1069</v>
-      </c>
-      <c r="G195" s="9" t="s">
-        <v>1070</v>
+      <c r="F195" s="6" t="s">
+        <v>1067</v>
+      </c>
+      <c r="G195" s="8" t="s">
+        <v>1068</v>
       </c>
     </row>
     <row r="196" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9122,11 +9137,11 @@
       <c r="E196" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F196" s="7" t="s">
-        <v>1071</v>
-      </c>
-      <c r="G196" s="9" t="s">
-        <v>1072</v>
+      <c r="F196" s="6" t="s">
+        <v>1069</v>
+      </c>
+      <c r="G196" s="8" t="s">
+        <v>1070</v>
       </c>
     </row>
     <row r="197" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9145,11 +9160,11 @@
       <c r="E197" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F197" s="7" t="s">
-        <v>1073</v>
-      </c>
-      <c r="G197" s="9" t="s">
-        <v>1074</v>
+      <c r="F197" s="6" t="s">
+        <v>1071</v>
+      </c>
+      <c r="G197" s="8" t="s">
+        <v>1072</v>
       </c>
     </row>
     <row r="198" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9168,11 +9183,11 @@
       <c r="E198" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F198" s="7" t="s">
-        <v>1075</v>
-      </c>
-      <c r="G198" s="9" t="s">
-        <v>1076</v>
+      <c r="F198" s="6" t="s">
+        <v>1073</v>
+      </c>
+      <c r="G198" s="8" t="s">
+        <v>1074</v>
       </c>
     </row>
     <row r="199" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9191,11 +9206,11 @@
       <c r="E199" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F199" s="7" t="s">
-        <v>1077</v>
-      </c>
-      <c r="G199" s="9" t="s">
-        <v>1078</v>
+      <c r="F199" s="6" t="s">
+        <v>1075</v>
+      </c>
+      <c r="G199" s="8" t="s">
+        <v>1076</v>
       </c>
     </row>
     <row r="200" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9214,11 +9229,11 @@
       <c r="E200" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F200" s="7" t="s">
-        <v>1079</v>
-      </c>
-      <c r="G200" s="9" t="s">
-        <v>1080</v>
+      <c r="F200" s="6" t="s">
+        <v>1077</v>
+      </c>
+      <c r="G200" s="8" t="s">
+        <v>1078</v>
       </c>
     </row>
     <row r="201" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9237,11 +9252,11 @@
       <c r="E201" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F201" s="7" t="s">
-        <v>1081</v>
-      </c>
-      <c r="G201" s="9" t="s">
-        <v>1082</v>
+      <c r="F201" s="6" t="s">
+        <v>1079</v>
+      </c>
+      <c r="G201" s="8" t="s">
+        <v>1080</v>
       </c>
     </row>
     <row r="202" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9260,11 +9275,11 @@
       <c r="E202" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F202" s="7" t="s">
-        <v>1083</v>
-      </c>
-      <c r="G202" s="9" t="s">
-        <v>1084</v>
+      <c r="F202" s="6" t="s">
+        <v>1081</v>
+      </c>
+      <c r="G202" s="8" t="s">
+        <v>1082</v>
       </c>
     </row>
     <row r="203" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9283,11 +9298,11 @@
       <c r="E203" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F203" s="7" t="s">
-        <v>1085</v>
-      </c>
-      <c r="G203" s="9" t="s">
-        <v>1086</v>
+      <c r="F203" s="6" t="s">
+        <v>1083</v>
+      </c>
+      <c r="G203" s="8" t="s">
+        <v>1084</v>
       </c>
     </row>
     <row r="204" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9306,11 +9321,11 @@
       <c r="E204" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F204" s="7" t="s">
-        <v>1087</v>
-      </c>
-      <c r="G204" s="9" t="s">
-        <v>1088</v>
+      <c r="F204" s="6" t="s">
+        <v>1085</v>
+      </c>
+      <c r="G204" s="8" t="s">
+        <v>1086</v>
       </c>
     </row>
     <row r="205" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9329,11 +9344,11 @@
       <c r="E205" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F205" s="7" t="s">
-        <v>1089</v>
-      </c>
-      <c r="G205" s="9" t="s">
-        <v>1090</v>
+      <c r="F205" s="6" t="s">
+        <v>1087</v>
+      </c>
+      <c r="G205" s="8" t="s">
+        <v>1088</v>
       </c>
     </row>
     <row r="206" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9352,11 +9367,11 @@
       <c r="E206" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F206" s="7" t="s">
-        <v>1091</v>
-      </c>
-      <c r="G206" s="9" t="s">
-        <v>1092</v>
+      <c r="F206" s="6" t="s">
+        <v>1089</v>
+      </c>
+      <c r="G206" s="8" t="s">
+        <v>1090</v>
       </c>
     </row>
     <row r="207" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9375,11 +9390,11 @@
       <c r="E207" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F207" s="7" t="s">
-        <v>1093</v>
-      </c>
-      <c r="G207" s="9" t="s">
-        <v>1094</v>
+      <c r="F207" s="6" t="s">
+        <v>1091</v>
+      </c>
+      <c r="G207" s="8" t="s">
+        <v>1092</v>
       </c>
     </row>
     <row r="208" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9398,11 +9413,11 @@
       <c r="E208" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F208" s="7" t="s">
-        <v>1095</v>
-      </c>
-      <c r="G208" s="9" t="s">
-        <v>1096</v>
+      <c r="F208" s="6" t="s">
+        <v>1093</v>
+      </c>
+      <c r="G208" s="8" t="s">
+        <v>1094</v>
       </c>
     </row>
     <row r="209" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9421,11 +9436,11 @@
       <c r="E209" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F209" s="7" t="s">
-        <v>1097</v>
-      </c>
-      <c r="G209" s="9" t="s">
-        <v>1098</v>
+      <c r="F209" s="6" t="s">
+        <v>1095</v>
+      </c>
+      <c r="G209" s="8" t="s">
+        <v>1096</v>
       </c>
     </row>
     <row r="210" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9444,11 +9459,11 @@
       <c r="E210" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F210" s="7" t="s">
-        <v>1099</v>
-      </c>
-      <c r="G210" s="9" t="s">
-        <v>1100</v>
+      <c r="F210" s="6" t="s">
+        <v>1097</v>
+      </c>
+      <c r="G210" s="8" t="s">
+        <v>1098</v>
       </c>
     </row>
     <row r="211" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9467,11 +9482,11 @@
       <c r="E211" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F211" s="7" t="s">
-        <v>1101</v>
-      </c>
-      <c r="G211" s="9" t="s">
-        <v>1102</v>
+      <c r="F211" s="6" t="s">
+        <v>1099</v>
+      </c>
+      <c r="G211" s="8" t="s">
+        <v>1100</v>
       </c>
     </row>
     <row r="212" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9490,11 +9505,11 @@
       <c r="E212" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F212" s="7" t="s">
-        <v>1103</v>
-      </c>
-      <c r="G212" s="9" t="s">
-        <v>1104</v>
+      <c r="F212" s="6" t="s">
+        <v>1101</v>
+      </c>
+      <c r="G212" s="8" t="s">
+        <v>1102</v>
       </c>
     </row>
     <row r="213" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9513,11 +9528,11 @@
       <c r="E213" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F213" s="7" t="s">
-        <v>1105</v>
-      </c>
-      <c r="G213" s="9" t="s">
-        <v>1106</v>
+      <c r="F213" s="6" t="s">
+        <v>1103</v>
+      </c>
+      <c r="G213" s="8" t="s">
+        <v>1104</v>
       </c>
     </row>
     <row r="214" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9536,11 +9551,11 @@
       <c r="E214" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F214" s="7" t="s">
-        <v>1107</v>
-      </c>
-      <c r="G214" s="9" t="s">
-        <v>1108</v>
+      <c r="F214" s="6" t="s">
+        <v>1105</v>
+      </c>
+      <c r="G214" s="8" t="s">
+        <v>1106</v>
       </c>
     </row>
     <row r="215" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9559,11 +9574,11 @@
       <c r="E215" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F215" s="7" t="s">
-        <v>1109</v>
-      </c>
-      <c r="G215" s="9" t="s">
-        <v>1110</v>
+      <c r="F215" s="6" t="s">
+        <v>1107</v>
+      </c>
+      <c r="G215" s="8" t="s">
+        <v>1108</v>
       </c>
     </row>
     <row r="216" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9582,11 +9597,11 @@
       <c r="E216" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F216" s="7" t="s">
-        <v>1111</v>
-      </c>
-      <c r="G216" s="9" t="s">
-        <v>1112</v>
+      <c r="F216" s="6" t="s">
+        <v>1109</v>
+      </c>
+      <c r="G216" s="8" t="s">
+        <v>1110</v>
       </c>
     </row>
     <row r="217" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9605,11 +9620,11 @@
       <c r="E217" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F217" s="7" t="s">
-        <v>1113</v>
-      </c>
-      <c r="G217" s="9" t="s">
-        <v>1114</v>
+      <c r="F217" s="6" t="s">
+        <v>1111</v>
+      </c>
+      <c r="G217" s="8" t="s">
+        <v>1112</v>
       </c>
     </row>
     <row r="218" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9628,11 +9643,11 @@
       <c r="E218" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F218" s="7" t="s">
-        <v>1115</v>
-      </c>
-      <c r="G218" s="9" t="s">
-        <v>1116</v>
+      <c r="F218" s="6" t="s">
+        <v>1113</v>
+      </c>
+      <c r="G218" s="8" t="s">
+        <v>1114</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.3">
@@ -9651,11 +9666,11 @@
       <c r="E219" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F219" s="10" t="s">
-        <v>1117</v>
-      </c>
-      <c r="G219" s="11" t="s">
-        <v>1118</v>
+      <c r="F219" s="9" t="s">
+        <v>1115</v>
+      </c>
+      <c r="G219" s="10" t="s">
+        <v>1116</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.3">
@@ -9674,11 +9689,11 @@
       <c r="E220" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F220" s="12" t="s">
-        <v>1119</v>
-      </c>
-      <c r="G220" s="12" t="s">
-        <v>1120</v>
+      <c r="F220" s="11" t="s">
+        <v>1117</v>
+      </c>
+      <c r="G220" s="11" t="s">
+        <v>1118</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.3">
@@ -9697,11 +9712,11 @@
       <c r="E221" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F221" s="12" t="s">
-        <v>1121</v>
-      </c>
-      <c r="G221" s="12" t="s">
-        <v>1122</v>
+      <c r="F221" s="11" t="s">
+        <v>1119</v>
+      </c>
+      <c r="G221" s="11" t="s">
+        <v>1120</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.3">
@@ -9720,11 +9735,11 @@
       <c r="E222" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F222" s="12" t="s">
-        <v>1123</v>
-      </c>
-      <c r="G222" s="12" t="s">
-        <v>1124</v>
+      <c r="F222" s="11" t="s">
+        <v>1121</v>
+      </c>
+      <c r="G222" s="11" t="s">
+        <v>1122</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.3">
@@ -9743,11 +9758,11 @@
       <c r="E223" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F223" s="12" t="s">
-        <v>1125</v>
-      </c>
-      <c r="G223" s="12" t="s">
-        <v>1126</v>
+      <c r="F223" s="11" t="s">
+        <v>1123</v>
+      </c>
+      <c r="G223" s="11" t="s">
+        <v>1124</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.3">
@@ -9766,11 +9781,11 @@
       <c r="E224" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F224" s="12" t="s">
-        <v>1127</v>
-      </c>
-      <c r="G224" s="12" t="s">
-        <v>1128</v>
+      <c r="F224" s="11" t="s">
+        <v>1125</v>
+      </c>
+      <c r="G224" s="11" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.3">
@@ -9789,11 +9804,11 @@
       <c r="E225" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F225" s="12" t="s">
-        <v>1129</v>
-      </c>
-      <c r="G225" s="12" t="s">
-        <v>1130</v>
+      <c r="F225" s="11" t="s">
+        <v>1127</v>
+      </c>
+      <c r="G225" s="11" t="s">
+        <v>1128</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.3">
@@ -9812,11 +9827,11 @@
       <c r="E226" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F226" s="12" t="s">
-        <v>1131</v>
-      </c>
-      <c r="G226" s="12" t="s">
-        <v>1132</v>
+      <c r="F226" s="11" t="s">
+        <v>1129</v>
+      </c>
+      <c r="G226" s="11" t="s">
+        <v>1130</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.3">
@@ -9835,11 +9850,11 @@
       <c r="E227" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F227" s="12" t="s">
-        <v>1133</v>
-      </c>
-      <c r="G227" s="12" t="s">
-        <v>1134</v>
+      <c r="F227" s="11" t="s">
+        <v>1131</v>
+      </c>
+      <c r="G227" s="11" t="s">
+        <v>1132</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.3">
@@ -9858,11 +9873,11 @@
       <c r="E228" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F228" s="12" t="s">
-        <v>1135</v>
-      </c>
-      <c r="G228" s="12" t="s">
-        <v>1136</v>
+      <c r="F228" s="11" t="s">
+        <v>1133</v>
+      </c>
+      <c r="G228" s="11" t="s">
+        <v>1134</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.3">
@@ -9881,11 +9896,11 @@
       <c r="E229" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F229" s="12" t="s">
-        <v>1137</v>
-      </c>
-      <c r="G229" s="12" t="s">
-        <v>1138</v>
+      <c r="F229" s="11" t="s">
+        <v>1135</v>
+      </c>
+      <c r="G229" s="11" t="s">
+        <v>1136</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.3">
@@ -9904,11 +9919,11 @@
       <c r="E230" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F230" s="12" t="s">
-        <v>1139</v>
-      </c>
-      <c r="G230" s="12" t="s">
-        <v>1140</v>
+      <c r="F230" s="11" t="s">
+        <v>1137</v>
+      </c>
+      <c r="G230" s="11" t="s">
+        <v>1138</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.3">
@@ -9927,11 +9942,11 @@
       <c r="E231" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F231" s="12" t="s">
-        <v>1141</v>
-      </c>
-      <c r="G231" s="12" t="s">
-        <v>1142</v>
+      <c r="F231" s="11" t="s">
+        <v>1139</v>
+      </c>
+      <c r="G231" s="11" t="s">
+        <v>1140</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.3">
@@ -9950,11 +9965,11 @@
       <c r="E232" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F232" s="12" t="s">
-        <v>1143</v>
-      </c>
-      <c r="G232" s="12" t="s">
-        <v>1144</v>
+      <c r="F232" s="11" t="s">
+        <v>1141</v>
+      </c>
+      <c r="G232" s="11" t="s">
+        <v>1142</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.3">
@@ -9973,11 +9988,11 @@
       <c r="E233" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F233" s="12" t="s">
-        <v>1145</v>
-      </c>
-      <c r="G233" s="12" t="s">
-        <v>1146</v>
+      <c r="F233" s="11" t="s">
+        <v>1143</v>
+      </c>
+      <c r="G233" s="11" t="s">
+        <v>1144</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.3">
@@ -9996,11 +10011,11 @@
       <c r="E234" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F234" s="12" t="s">
-        <v>1147</v>
-      </c>
-      <c r="G234" s="12" t="s">
-        <v>1148</v>
+      <c r="F234" s="11" t="s">
+        <v>1145</v>
+      </c>
+      <c r="G234" s="11" t="s">
+        <v>1146</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.3">
@@ -10019,11 +10034,11 @@
       <c r="E235" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F235" s="12" t="s">
-        <v>1149</v>
-      </c>
-      <c r="G235" s="12" t="s">
-        <v>1150</v>
+      <c r="F235" s="11" t="s">
+        <v>1147</v>
+      </c>
+      <c r="G235" s="11" t="s">
+        <v>1148</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.3">
@@ -10042,11 +10057,11 @@
       <c r="E236" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F236" s="12" t="s">
-        <v>1151</v>
-      </c>
-      <c r="G236" s="12" t="s">
-        <v>1152</v>
+      <c r="F236" s="11" t="s">
+        <v>1149</v>
+      </c>
+      <c r="G236" s="11" t="s">
+        <v>1150</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.3">
@@ -10065,11 +10080,11 @@
       <c r="E237" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F237" s="12" t="s">
-        <v>1153</v>
-      </c>
-      <c r="G237" s="12" t="s">
-        <v>1154</v>
+      <c r="F237" s="11" t="s">
+        <v>1151</v>
+      </c>
+      <c r="G237" s="11" t="s">
+        <v>1152</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.3">
@@ -10088,11 +10103,11 @@
       <c r="E238" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F238" s="12" t="s">
-        <v>1155</v>
-      </c>
-      <c r="G238" s="12" t="s">
-        <v>1156</v>
+      <c r="F238" s="11" t="s">
+        <v>1153</v>
+      </c>
+      <c r="G238" s="11" t="s">
+        <v>1154</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.3">
@@ -10111,11 +10126,11 @@
       <c r="E239" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F239" s="12" t="s">
-        <v>1157</v>
-      </c>
-      <c r="G239" s="12" t="s">
-        <v>1158</v>
+      <c r="F239" s="11" t="s">
+        <v>1155</v>
+      </c>
+      <c r="G239" s="11" t="s">
+        <v>1156</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.3">
@@ -10134,11 +10149,11 @@
       <c r="E240" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F240" s="12" t="s">
-        <v>1159</v>
-      </c>
-      <c r="G240" s="12" t="s">
-        <v>1160</v>
+      <c r="F240" s="11" t="s">
+        <v>1157</v>
+      </c>
+      <c r="G240" s="11" t="s">
+        <v>1158</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.3">
@@ -10157,11 +10172,11 @@
       <c r="E241" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F241" s="12" t="s">
-        <v>1161</v>
-      </c>
-      <c r="G241" s="12" t="s">
-        <v>1162</v>
+      <c r="F241" s="11" t="s">
+        <v>1159</v>
+      </c>
+      <c r="G241" s="11" t="s">
+        <v>1160</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.3">
@@ -10180,11 +10195,11 @@
       <c r="E242" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F242" s="12" t="s">
-        <v>1163</v>
-      </c>
-      <c r="G242" s="12" t="s">
-        <v>1164</v>
+      <c r="F242" s="11" t="s">
+        <v>1161</v>
+      </c>
+      <c r="G242" s="11" t="s">
+        <v>1162</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.3">
@@ -10203,11 +10218,11 @@
       <c r="E243" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F243" s="12" t="s">
-        <v>1165</v>
-      </c>
-      <c r="G243" s="12" t="s">
-        <v>1166</v>
+      <c r="F243" s="11" t="s">
+        <v>1163</v>
+      </c>
+      <c r="G243" s="11" t="s">
+        <v>1164</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.3">
@@ -10226,11 +10241,11 @@
       <c r="E244" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F244" s="12" t="s">
-        <v>1167</v>
-      </c>
-      <c r="G244" s="12" t="s">
-        <v>1168</v>
+      <c r="F244" s="11" t="s">
+        <v>1165</v>
+      </c>
+      <c r="G244" s="11" t="s">
+        <v>1166</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.3">
@@ -10249,11 +10264,11 @@
       <c r="E245" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F245" s="12" t="s">
-        <v>1169</v>
-      </c>
-      <c r="G245" s="12" t="s">
-        <v>1170</v>
+      <c r="F245" s="11" t="s">
+        <v>1167</v>
+      </c>
+      <c r="G245" s="11" t="s">
+        <v>1168</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.3">
@@ -10272,11 +10287,11 @@
       <c r="E246" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F246" s="12" t="s">
-        <v>1171</v>
-      </c>
-      <c r="G246" s="12" t="s">
-        <v>1172</v>
+      <c r="F246" s="11" t="s">
+        <v>1169</v>
+      </c>
+      <c r="G246" s="11" t="s">
+        <v>1170</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.3">
@@ -10295,11 +10310,11 @@
       <c r="E247" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F247" s="12" t="s">
-        <v>1173</v>
-      </c>
-      <c r="G247" s="12" t="s">
-        <v>1174</v>
+      <c r="F247" s="11" t="s">
+        <v>1171</v>
+      </c>
+      <c r="G247" s="11" t="s">
+        <v>1172</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.3">
@@ -10318,11 +10333,11 @@
       <c r="E248" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F248" s="12" t="s">
-        <v>1175</v>
-      </c>
-      <c r="G248" s="12" t="s">
-        <v>1176</v>
+      <c r="F248" s="11" t="s">
+        <v>1173</v>
+      </c>
+      <c r="G248" s="11" t="s">
+        <v>1174</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.3">
@@ -10341,11 +10356,11 @@
       <c r="E249" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F249" s="12" t="s">
-        <v>1177</v>
-      </c>
-      <c r="G249" s="12" t="s">
-        <v>1178</v>
+      <c r="F249" s="11" t="s">
+        <v>1175</v>
+      </c>
+      <c r="G249" s="11" t="s">
+        <v>1176</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.3">
@@ -10364,11 +10379,11 @@
       <c r="E250" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F250" s="12" t="s">
-        <v>1179</v>
-      </c>
-      <c r="G250" s="12" t="s">
-        <v>1180</v>
+      <c r="F250" s="11" t="s">
+        <v>1177</v>
+      </c>
+      <c r="G250" s="11" t="s">
+        <v>1178</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.3">
@@ -10387,11 +10402,11 @@
       <c r="E251" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F251" s="12" t="s">
-        <v>1181</v>
-      </c>
-      <c r="G251" s="12" t="s">
-        <v>1182</v>
+      <c r="F251" s="11" t="s">
+        <v>1179</v>
+      </c>
+      <c r="G251" s="11" t="s">
+        <v>1180</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.3">
@@ -10410,11 +10425,11 @@
       <c r="E252" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F252" s="12" t="s">
-        <v>1183</v>
-      </c>
-      <c r="G252" s="12" t="s">
-        <v>1184</v>
+      <c r="F252" s="11" t="s">
+        <v>1181</v>
+      </c>
+      <c r="G252" s="11" t="s">
+        <v>1182</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.3">
@@ -10433,11 +10448,11 @@
       <c r="E253" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F253" s="12" t="s">
-        <v>1185</v>
-      </c>
-      <c r="G253" s="12" t="s">
-        <v>1186</v>
+      <c r="F253" s="11" t="s">
+        <v>1183</v>
+      </c>
+      <c r="G253" s="11" t="s">
+        <v>1184</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.3">
@@ -10456,11 +10471,11 @@
       <c r="E254" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F254" s="12" t="s">
-        <v>1187</v>
-      </c>
-      <c r="G254" s="12" t="s">
-        <v>1188</v>
+      <c r="F254" s="11" t="s">
+        <v>1185</v>
+      </c>
+      <c r="G254" s="11" t="s">
+        <v>1186</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.3">
@@ -10479,11 +10494,11 @@
       <c r="E255" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F255" s="12" t="s">
-        <v>1189</v>
-      </c>
-      <c r="G255" s="12" t="s">
-        <v>1190</v>
+      <c r="F255" s="11" t="s">
+        <v>1187</v>
+      </c>
+      <c r="G255" s="11" t="s">
+        <v>1188</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.3">
@@ -10502,11 +10517,11 @@
       <c r="E256" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F256" s="12" t="s">
-        <v>1191</v>
-      </c>
-      <c r="G256" s="12" t="s">
-        <v>1192</v>
+      <c r="F256" s="11" t="s">
+        <v>1189</v>
+      </c>
+      <c r="G256" s="11" t="s">
+        <v>1190</v>
       </c>
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.3">
@@ -10525,11 +10540,11 @@
       <c r="E257" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F257" s="12" t="s">
-        <v>1193</v>
-      </c>
-      <c r="G257" s="12" t="s">
-        <v>1194</v>
+      <c r="F257" s="11" t="s">
+        <v>1191</v>
+      </c>
+      <c r="G257" s="11" t="s">
+        <v>1192</v>
       </c>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.3">
@@ -10548,11 +10563,11 @@
       <c r="E258" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F258" s="12" t="s">
-        <v>1195</v>
-      </c>
-      <c r="G258" s="12" t="s">
-        <v>1196</v>
+      <c r="F258" s="11" t="s">
+        <v>1193</v>
+      </c>
+      <c r="G258" s="11" t="s">
+        <v>1194</v>
       </c>
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.3">
@@ -10571,11 +10586,11 @@
       <c r="E259" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F259" s="12" t="s">
-        <v>1197</v>
-      </c>
-      <c r="G259" s="12" t="s">
-        <v>1198</v>
+      <c r="F259" s="11" t="s">
+        <v>1195</v>
+      </c>
+      <c r="G259" s="11" t="s">
+        <v>1196</v>
       </c>
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.3">
@@ -10594,11 +10609,11 @@
       <c r="E260" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F260" s="12" t="s">
-        <v>1199</v>
-      </c>
-      <c r="G260" s="12" t="s">
-        <v>1200</v>
+      <c r="F260" s="11" t="s">
+        <v>1197</v>
+      </c>
+      <c r="G260" s="11" t="s">
+        <v>1198</v>
       </c>
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.3">
@@ -10617,11 +10632,11 @@
       <c r="E261" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F261" s="12" t="s">
-        <v>1201</v>
-      </c>
-      <c r="G261" s="12" t="s">
-        <v>1202</v>
+      <c r="F261" s="11" t="s">
+        <v>1199</v>
+      </c>
+      <c r="G261" s="11" t="s">
+        <v>1200</v>
       </c>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.3">
@@ -10640,11 +10655,11 @@
       <c r="E262" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F262" s="12" t="s">
-        <v>1203</v>
-      </c>
-      <c r="G262" s="12" t="s">
-        <v>1204</v>
+      <c r="F262" s="11" t="s">
+        <v>1201</v>
+      </c>
+      <c r="G262" s="11" t="s">
+        <v>1202</v>
       </c>
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.3">
@@ -10663,11 +10678,11 @@
       <c r="E263" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F263" s="12" t="s">
-        <v>1205</v>
-      </c>
-      <c r="G263" s="12" t="s">
-        <v>1206</v>
+      <c r="F263" s="11" t="s">
+        <v>1203</v>
+      </c>
+      <c r="G263" s="11" t="s">
+        <v>1204</v>
       </c>
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.3">
@@ -10686,11 +10701,11 @@
       <c r="E264" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F264" s="12" t="s">
-        <v>1207</v>
-      </c>
-      <c r="G264" s="12" t="s">
-        <v>1208</v>
+      <c r="F264" s="11" t="s">
+        <v>1205</v>
+      </c>
+      <c r="G264" s="11" t="s">
+        <v>1206</v>
       </c>
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.3">
@@ -10709,11 +10724,11 @@
       <c r="E265" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F265" s="12" t="s">
-        <v>1209</v>
-      </c>
-      <c r="G265" s="12" t="s">
-        <v>1210</v>
+      <c r="F265" s="11" t="s">
+        <v>1207</v>
+      </c>
+      <c r="G265" s="11" t="s">
+        <v>1208</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.3">
@@ -10732,11 +10747,11 @@
       <c r="E266" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F266" s="12" t="s">
-        <v>1211</v>
-      </c>
-      <c r="G266" s="12" t="s">
-        <v>1212</v>
+      <c r="F266" s="11" t="s">
+        <v>1209</v>
+      </c>
+      <c r="G266" s="11" t="s">
+        <v>1210</v>
       </c>
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.3">
@@ -10755,11 +10770,11 @@
       <c r="E267" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F267" s="12" t="s">
-        <v>1213</v>
-      </c>
-      <c r="G267" s="12" t="s">
-        <v>1214</v>
+      <c r="F267" s="11" t="s">
+        <v>1211</v>
+      </c>
+      <c r="G267" s="11" t="s">
+        <v>1212</v>
       </c>
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.3">
@@ -10778,11 +10793,11 @@
       <c r="E268" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F268" s="12" t="s">
-        <v>1215</v>
-      </c>
-      <c r="G268" s="12" t="s">
-        <v>1216</v>
+      <c r="F268" s="11" t="s">
+        <v>1213</v>
+      </c>
+      <c r="G268" s="11" t="s">
+        <v>1214</v>
       </c>
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.3">
@@ -10801,11 +10816,11 @@
       <c r="E269" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F269" s="12" t="s">
-        <v>1217</v>
-      </c>
-      <c r="G269" s="12" t="s">
-        <v>1218</v>
+      <c r="F269" s="11" t="s">
+        <v>1215</v>
+      </c>
+      <c r="G269" s="11" t="s">
+        <v>1216</v>
       </c>
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.3">
@@ -10824,11 +10839,11 @@
       <c r="E270" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F270" s="12" t="s">
-        <v>1219</v>
-      </c>
-      <c r="G270" s="12" t="s">
-        <v>1220</v>
+      <c r="F270" s="11" t="s">
+        <v>1217</v>
+      </c>
+      <c r="G270" s="11" t="s">
+        <v>1218</v>
       </c>
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.3">
@@ -10847,11 +10862,11 @@
       <c r="E271" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F271" s="12" t="s">
-        <v>1221</v>
-      </c>
-      <c r="G271" s="12" t="s">
-        <v>1222</v>
+      <c r="F271" s="11" t="s">
+        <v>1219</v>
+      </c>
+      <c r="G271" s="11" t="s">
+        <v>1220</v>
       </c>
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.3">
@@ -10870,11 +10885,11 @@
       <c r="E272" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F272" s="12" t="s">
-        <v>1223</v>
-      </c>
-      <c r="G272" s="12" t="s">
-        <v>1224</v>
+      <c r="F272" s="11" t="s">
+        <v>1221</v>
+      </c>
+      <c r="G272" s="11" t="s">
+        <v>1222</v>
       </c>
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.3">
@@ -10893,11 +10908,11 @@
       <c r="E273" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F273" s="12" t="s">
-        <v>1225</v>
-      </c>
-      <c r="G273" s="12" t="s">
-        <v>1226</v>
+      <c r="F273" s="11" t="s">
+        <v>1223</v>
+      </c>
+      <c r="G273" s="11" t="s">
+        <v>1224</v>
       </c>
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.3">
@@ -10916,11 +10931,11 @@
       <c r="E274" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F274" s="12" t="s">
-        <v>1227</v>
-      </c>
-      <c r="G274" s="12" t="s">
-        <v>1228</v>
+      <c r="F274" s="11" t="s">
+        <v>1225</v>
+      </c>
+      <c r="G274" s="11" t="s">
+        <v>1226</v>
       </c>
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.3">
@@ -10939,11 +10954,11 @@
       <c r="E275" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F275" s="12" t="s">
-        <v>1229</v>
-      </c>
-      <c r="G275" s="12" t="s">
-        <v>1230</v>
+      <c r="F275" s="11" t="s">
+        <v>1227</v>
+      </c>
+      <c r="G275" s="11" t="s">
+        <v>1228</v>
       </c>
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.3">
@@ -10962,11 +10977,11 @@
       <c r="E276" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F276" s="12" t="s">
-        <v>1231</v>
-      </c>
-      <c r="G276" s="12" t="s">
-        <v>1232</v>
+      <c r="F276" s="11" t="s">
+        <v>1229</v>
+      </c>
+      <c r="G276" s="11" t="s">
+        <v>1230</v>
       </c>
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.3">
@@ -10985,11 +11000,11 @@
       <c r="E277" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F277" s="12" t="s">
-        <v>1233</v>
-      </c>
-      <c r="G277" s="12" t="s">
-        <v>1234</v>
+      <c r="F277" s="11" t="s">
+        <v>1231</v>
+      </c>
+      <c r="G277" s="11" t="s">
+        <v>1232</v>
       </c>
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.3">
@@ -11008,11 +11023,11 @@
       <c r="E278" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F278" s="12" t="s">
-        <v>1235</v>
-      </c>
-      <c r="G278" s="12" t="s">
-        <v>1236</v>
+      <c r="F278" s="11" t="s">
+        <v>1233</v>
+      </c>
+      <c r="G278" s="11" t="s">
+        <v>1234</v>
       </c>
     </row>
     <row r="279" spans="1:7" x14ac:dyDescent="0.3">
@@ -11031,11 +11046,11 @@
       <c r="E279" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F279" s="12" t="s">
-        <v>1237</v>
-      </c>
-      <c r="G279" s="12" t="s">
-        <v>1238</v>
+      <c r="F279" s="11" t="s">
+        <v>1235</v>
+      </c>
+      <c r="G279" s="11" t="s">
+        <v>1236</v>
       </c>
     </row>
     <row r="280" spans="1:7" x14ac:dyDescent="0.3">
@@ -11054,11 +11069,11 @@
       <c r="E280" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F280" s="12" t="s">
-        <v>1239</v>
-      </c>
-      <c r="G280" s="12" t="s">
-        <v>1240</v>
+      <c r="F280" s="11" t="s">
+        <v>1237</v>
+      </c>
+      <c r="G280" s="11" t="s">
+        <v>1238</v>
       </c>
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.3">
@@ -11077,11 +11092,11 @@
       <c r="E281" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F281" s="12" t="s">
-        <v>1241</v>
-      </c>
-      <c r="G281" s="12" t="s">
-        <v>1242</v>
+      <c r="F281" s="11" t="s">
+        <v>1239</v>
+      </c>
+      <c r="G281" s="11" t="s">
+        <v>1240</v>
       </c>
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.3">
@@ -11100,11 +11115,11 @@
       <c r="E282" s="4" t="s">
         <v>603</v>
       </c>
-      <c r="F282" s="12" t="s">
-        <v>1243</v>
-      </c>
-      <c r="G282" s="12" t="s">
-        <v>1244</v>
+      <c r="F282" s="11" t="s">
+        <v>1241</v>
+      </c>
+      <c r="G282" s="11" t="s">
+        <v>1242</v>
       </c>
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.3">
@@ -11123,11 +11138,11 @@
       <c r="E283" s="4" t="s">
         <v>603</v>
       </c>
-      <c r="F283" s="12" t="s">
-        <v>1245</v>
-      </c>
-      <c r="G283" s="12" t="s">
-        <v>1246</v>
+      <c r="F283" s="11" t="s">
+        <v>1243</v>
+      </c>
+      <c r="G283" s="11" t="s">
+        <v>1244</v>
       </c>
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.3">
@@ -11146,11 +11161,11 @@
       <c r="E284" s="4" t="s">
         <v>603</v>
       </c>
-      <c r="F284" s="12" t="s">
-        <v>1247</v>
-      </c>
-      <c r="G284" s="12" t="s">
-        <v>1248</v>
+      <c r="F284" s="11" t="s">
+        <v>1245</v>
+      </c>
+      <c r="G284" s="11" t="s">
+        <v>1246</v>
       </c>
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.3">
@@ -11169,11 +11184,11 @@
       <c r="E285" s="4" t="s">
         <v>603</v>
       </c>
-      <c r="F285" s="12" t="s">
-        <v>1249</v>
-      </c>
-      <c r="G285" s="12" t="s">
-        <v>1250</v>
+      <c r="F285" s="11" t="s">
+        <v>1247</v>
+      </c>
+      <c r="G285" s="11" t="s">
+        <v>1248</v>
       </c>
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.3">
@@ -11192,11 +11207,11 @@
       <c r="E286" s="4" t="s">
         <v>603</v>
       </c>
-      <c r="F286" s="12" t="s">
-        <v>1251</v>
-      </c>
-      <c r="G286" s="12" t="s">
-        <v>1252</v>
+      <c r="F286" s="11" t="s">
+        <v>1249</v>
+      </c>
+      <c r="G286" s="11" t="s">
+        <v>1250</v>
       </c>
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.3">
@@ -11215,11 +11230,11 @@
       <c r="E287" s="4" t="s">
         <v>603</v>
       </c>
-      <c r="F287" s="12" t="s">
-        <v>1253</v>
-      </c>
-      <c r="G287" s="12" t="s">
-        <v>1254</v>
+      <c r="F287" s="11" t="s">
+        <v>1251</v>
+      </c>
+      <c r="G287" s="11" t="s">
+        <v>1252</v>
       </c>
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.3">
@@ -11238,11 +11253,11 @@
       <c r="E288" s="4" t="s">
         <v>603</v>
       </c>
-      <c r="F288" s="12" t="s">
-        <v>1255</v>
-      </c>
-      <c r="G288" s="12" t="s">
-        <v>1256</v>
+      <c r="F288" s="11" t="s">
+        <v>1253</v>
+      </c>
+      <c r="G288" s="11" t="s">
+        <v>1254</v>
       </c>
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.3">
@@ -11261,11 +11276,11 @@
       <c r="E289" s="4" t="s">
         <v>603</v>
       </c>
-      <c r="F289" s="12" t="s">
-        <v>1257</v>
-      </c>
-      <c r="G289" s="12" t="s">
-        <v>1258</v>
+      <c r="F289" s="11" t="s">
+        <v>1255</v>
+      </c>
+      <c r="G289" s="11" t="s">
+        <v>1256</v>
       </c>
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.3">
@@ -11284,11 +11299,11 @@
       <c r="E290" s="4" t="s">
         <v>603</v>
       </c>
-      <c r="F290" s="12" t="s">
-        <v>1259</v>
-      </c>
-      <c r="G290" s="12" t="s">
-        <v>1260</v>
+      <c r="F290" s="11" t="s">
+        <v>1257</v>
+      </c>
+      <c r="G290" s="11" t="s">
+        <v>1258</v>
       </c>
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.3">
@@ -11307,11 +11322,11 @@
       <c r="E291" s="4" t="s">
         <v>603</v>
       </c>
-      <c r="F291" s="12" t="s">
-        <v>1261</v>
-      </c>
-      <c r="G291" s="12" t="s">
-        <v>1262</v>
+      <c r="F291" s="11" t="s">
+        <v>1259</v>
+      </c>
+      <c r="G291" s="11" t="s">
+        <v>1260</v>
       </c>
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.3">
@@ -11330,11 +11345,11 @@
       <c r="E292" s="4" t="s">
         <v>603</v>
       </c>
-      <c r="F292" s="12" t="s">
-        <v>1263</v>
-      </c>
-      <c r="G292" s="12" t="s">
-        <v>1264</v>
+      <c r="F292" s="11" t="s">
+        <v>1261</v>
+      </c>
+      <c r="G292" s="11" t="s">
+        <v>1262</v>
       </c>
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.3">
@@ -11353,11 +11368,11 @@
       <c r="E293" s="4" t="s">
         <v>603</v>
       </c>
-      <c r="F293" s="12" t="s">
-        <v>1265</v>
-      </c>
-      <c r="G293" s="12" t="s">
-        <v>1266</v>
+      <c r="F293" s="11" t="s">
+        <v>1263</v>
+      </c>
+      <c r="G293" s="11" t="s">
+        <v>1264</v>
       </c>
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.3">
@@ -11376,11 +11391,11 @@
       <c r="E294" s="4" t="s">
         <v>603</v>
       </c>
-      <c r="F294" s="12" t="s">
-        <v>1267</v>
-      </c>
-      <c r="G294" s="12" t="s">
-        <v>1268</v>
+      <c r="F294" s="11" t="s">
+        <v>1265</v>
+      </c>
+      <c r="G294" s="11" t="s">
+        <v>1266</v>
       </c>
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.3">
@@ -11399,11 +11414,11 @@
       <c r="E295" s="4" t="s">
         <v>603</v>
       </c>
-      <c r="F295" s="12" t="s">
-        <v>1269</v>
-      </c>
-      <c r="G295" s="12" t="s">
-        <v>1270</v>
+      <c r="F295" s="11" t="s">
+        <v>1267</v>
+      </c>
+      <c r="G295" s="11" t="s">
+        <v>1268</v>
       </c>
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.3">
@@ -11422,11 +11437,11 @@
       <c r="E296" s="4" t="s">
         <v>603</v>
       </c>
-      <c r="F296" s="12" t="s">
-        <v>1271</v>
-      </c>
-      <c r="G296" s="12" t="s">
-        <v>1272</v>
+      <c r="F296" s="11" t="s">
+        <v>1269</v>
+      </c>
+      <c r="G296" s="11" t="s">
+        <v>1270</v>
       </c>
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.3">
@@ -11445,11 +11460,11 @@
       <c r="E297" s="4" t="s">
         <v>603</v>
       </c>
-      <c r="F297" s="12" t="s">
-        <v>1273</v>
-      </c>
-      <c r="G297" s="12" t="s">
-        <v>1274</v>
+      <c r="F297" s="11" t="s">
+        <v>1271</v>
+      </c>
+      <c r="G297" s="11" t="s">
+        <v>1272</v>
       </c>
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.3">
@@ -11468,11 +11483,11 @@
       <c r="E298" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F298" s="12" t="s">
-        <v>1275</v>
-      </c>
-      <c r="G298" s="12" t="s">
-        <v>1276</v>
+      <c r="F298" s="11" t="s">
+        <v>1273</v>
+      </c>
+      <c r="G298" s="11" t="s">
+        <v>1274</v>
       </c>
     </row>
     <row r="299" spans="1:7" x14ac:dyDescent="0.3">
@@ -11491,11 +11506,11 @@
       <c r="E299" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F299" s="12" t="s">
-        <v>1277</v>
-      </c>
-      <c r="G299" s="12" t="s">
-        <v>1278</v>
+      <c r="F299" s="11" t="s">
+        <v>1275</v>
+      </c>
+      <c r="G299" s="11" t="s">
+        <v>1276</v>
       </c>
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.3">
@@ -11514,11 +11529,11 @@
       <c r="E300" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F300" s="12" t="s">
-        <v>1279</v>
-      </c>
-      <c r="G300" s="12" t="s">
-        <v>1280</v>
+      <c r="F300" s="11" t="s">
+        <v>1277</v>
+      </c>
+      <c r="G300" s="11" t="s">
+        <v>1278</v>
       </c>
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.3">
@@ -11537,11 +11552,11 @@
       <c r="E301" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F301" s="12" t="s">
-        <v>1281</v>
-      </c>
-      <c r="G301" s="12" t="s">
-        <v>1282</v>
+      <c r="F301" s="11" t="s">
+        <v>1279</v>
+      </c>
+      <c r="G301" s="11" t="s">
+        <v>1280</v>
       </c>
     </row>
     <row r="302" spans="1:7" x14ac:dyDescent="0.3">
@@ -11560,11 +11575,11 @@
       <c r="E302" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F302" s="12" t="s">
-        <v>1283</v>
-      </c>
-      <c r="G302" s="12" t="s">
-        <v>1284</v>
+      <c r="F302" s="11" t="s">
+        <v>1281</v>
+      </c>
+      <c r="G302" s="11" t="s">
+        <v>1282</v>
       </c>
     </row>
     <row r="303" spans="1:7" x14ac:dyDescent="0.3">
@@ -11583,11 +11598,11 @@
       <c r="E303" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F303" s="12" t="s">
-        <v>1285</v>
-      </c>
-      <c r="G303" s="12" t="s">
-        <v>1286</v>
+      <c r="F303" s="11" t="s">
+        <v>1283</v>
+      </c>
+      <c r="G303" s="11" t="s">
+        <v>1284</v>
       </c>
     </row>
     <row r="304" spans="1:7" x14ac:dyDescent="0.3">
@@ -11606,11 +11621,11 @@
       <c r="E304" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F304" s="12" t="s">
-        <v>1287</v>
-      </c>
-      <c r="G304" s="12" t="s">
-        <v>1288</v>
+      <c r="F304" s="11" t="s">
+        <v>1285</v>
+      </c>
+      <c r="G304" s="11" t="s">
+        <v>1286</v>
       </c>
     </row>
     <row r="305" spans="1:7" x14ac:dyDescent="0.3">
@@ -11629,11 +11644,11 @@
       <c r="E305" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F305" s="12" t="s">
-        <v>1289</v>
-      </c>
-      <c r="G305" s="12" t="s">
-        <v>1290</v>
+      <c r="F305" s="11" t="s">
+        <v>1287</v>
+      </c>
+      <c r="G305" s="11" t="s">
+        <v>1288</v>
       </c>
     </row>
     <row r="306" spans="1:7" x14ac:dyDescent="0.3">
@@ -11652,11 +11667,11 @@
       <c r="E306" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F306" s="12" t="s">
-        <v>1291</v>
-      </c>
-      <c r="G306" s="12" t="s">
-        <v>1292</v>
+      <c r="F306" s="11" t="s">
+        <v>1289</v>
+      </c>
+      <c r="G306" s="11" t="s">
+        <v>1290</v>
       </c>
     </row>
     <row r="307" spans="1:7" x14ac:dyDescent="0.3">
@@ -11675,11 +11690,11 @@
       <c r="E307" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F307" s="12" t="s">
-        <v>1293</v>
-      </c>
-      <c r="G307" s="12" t="s">
-        <v>1294</v>
+      <c r="F307" s="11" t="s">
+        <v>1291</v>
+      </c>
+      <c r="G307" s="11" t="s">
+        <v>1292</v>
       </c>
     </row>
     <row r="308" spans="1:7" x14ac:dyDescent="0.3">
@@ -11698,11 +11713,11 @@
       <c r="E308" s="4" t="s">
         <v>603</v>
       </c>
-      <c r="F308" s="12" t="s">
-        <v>1295</v>
-      </c>
-      <c r="G308" s="12" t="s">
-        <v>1296</v>
+      <c r="F308" s="11" t="s">
+        <v>1293</v>
+      </c>
+      <c r="G308" s="11" t="s">
+        <v>1294</v>
       </c>
     </row>
     <row r="309" spans="1:7" x14ac:dyDescent="0.3">
@@ -11721,11 +11736,11 @@
       <c r="E309" s="4" t="s">
         <v>603</v>
       </c>
-      <c r="F309" s="12" t="s">
-        <v>1297</v>
-      </c>
-      <c r="G309" s="12" t="s">
-        <v>1298</v>
+      <c r="F309" s="11" t="s">
+        <v>1295</v>
+      </c>
+      <c r="G309" s="11" t="s">
+        <v>1296</v>
       </c>
     </row>
     <row r="310" spans="1:7" x14ac:dyDescent="0.3">
@@ -11744,11 +11759,11 @@
       <c r="E310" s="4" t="s">
         <v>603</v>
       </c>
-      <c r="F310" s="12" t="s">
-        <v>1299</v>
-      </c>
-      <c r="G310" s="12" t="s">
-        <v>1300</v>
+      <c r="F310" s="11" t="s">
+        <v>1297</v>
+      </c>
+      <c r="G310" s="11" t="s">
+        <v>1298</v>
       </c>
     </row>
     <row r="311" spans="1:7" x14ac:dyDescent="0.3">
@@ -11767,11 +11782,11 @@
       <c r="E311" s="4" t="s">
         <v>603</v>
       </c>
-      <c r="F311" s="12" t="s">
-        <v>1301</v>
-      </c>
-      <c r="G311" s="12" t="s">
-        <v>1302</v>
+      <c r="F311" s="11" t="s">
+        <v>1299</v>
+      </c>
+      <c r="G311" s="11" t="s">
+        <v>1300</v>
       </c>
     </row>
     <row r="312" spans="1:7" x14ac:dyDescent="0.3">
@@ -11790,11 +11805,11 @@
       <c r="E312" s="4" t="s">
         <v>603</v>
       </c>
-      <c r="F312" s="12" t="s">
-        <v>1303</v>
-      </c>
-      <c r="G312" s="12" t="s">
-        <v>1304</v>
+      <c r="F312" s="11" t="s">
+        <v>1301</v>
+      </c>
+      <c r="G312" s="11" t="s">
+        <v>1302</v>
       </c>
     </row>
     <row r="313" spans="1:7" x14ac:dyDescent="0.3">
@@ -11813,11 +11828,11 @@
       <c r="E313" s="4" t="s">
         <v>603</v>
       </c>
-      <c r="F313" s="12" t="s">
-        <v>1305</v>
-      </c>
-      <c r="G313" s="12" t="s">
-        <v>1306</v>
+      <c r="F313" s="11" t="s">
+        <v>1303</v>
+      </c>
+      <c r="G313" s="11" t="s">
+        <v>1304</v>
       </c>
     </row>
     <row r="314" spans="1:7" x14ac:dyDescent="0.3">
@@ -11836,11 +11851,11 @@
       <c r="E314" s="4" t="s">
         <v>603</v>
       </c>
-      <c r="F314" s="12" t="s">
-        <v>1307</v>
-      </c>
-      <c r="G314" s="12" t="s">
-        <v>1308</v>
+      <c r="F314" s="11" t="s">
+        <v>1305</v>
+      </c>
+      <c r="G314" s="11" t="s">
+        <v>1306</v>
       </c>
     </row>
     <row r="315" spans="1:7" x14ac:dyDescent="0.3">
@@ -11859,11 +11874,11 @@
       <c r="E315" s="4" t="s">
         <v>603</v>
       </c>
-      <c r="F315" s="12" t="s">
-        <v>1309</v>
-      </c>
-      <c r="G315" s="12" t="s">
-        <v>1310</v>
+      <c r="F315" s="11" t="s">
+        <v>1307</v>
+      </c>
+      <c r="G315" s="11" t="s">
+        <v>1308</v>
       </c>
     </row>
     <row r="316" spans="1:7" x14ac:dyDescent="0.3">
@@ -11882,11 +11897,11 @@
       <c r="E316" s="4" t="s">
         <v>603</v>
       </c>
-      <c r="F316" s="12" t="s">
-        <v>1311</v>
-      </c>
-      <c r="G316" s="12" t="s">
-        <v>1312</v>
+      <c r="F316" s="11" t="s">
+        <v>1309</v>
+      </c>
+      <c r="G316" s="11" t="s">
+        <v>1310</v>
       </c>
     </row>
     <row r="317" spans="1:7" x14ac:dyDescent="0.3">
@@ -11905,11 +11920,11 @@
       <c r="E317" s="4" t="s">
         <v>603</v>
       </c>
-      <c r="F317" s="12" t="s">
-        <v>1313</v>
-      </c>
-      <c r="G317" s="12" t="s">
-        <v>1314</v>
+      <c r="F317" s="11" t="s">
+        <v>1311</v>
+      </c>
+      <c r="G317" s="11" t="s">
+        <v>1312</v>
       </c>
     </row>
     <row r="318" spans="1:7" x14ac:dyDescent="0.3">
@@ -11928,11 +11943,11 @@
       <c r="E318" s="4" t="s">
         <v>603</v>
       </c>
-      <c r="F318" s="12" t="s">
-        <v>1315</v>
-      </c>
-      <c r="G318" s="12" t="s">
-        <v>1316</v>
+      <c r="F318" s="11" t="s">
+        <v>1313</v>
+      </c>
+      <c r="G318" s="11" t="s">
+        <v>1314</v>
       </c>
     </row>
     <row r="319" spans="1:7" x14ac:dyDescent="0.3">
@@ -11951,11 +11966,11 @@
       <c r="E319" s="4" t="s">
         <v>603</v>
       </c>
-      <c r="F319" s="12" t="s">
-        <v>1317</v>
-      </c>
-      <c r="G319" s="12" t="s">
-        <v>1318</v>
+      <c r="F319" s="11" t="s">
+        <v>1315</v>
+      </c>
+      <c r="G319" s="11" t="s">
+        <v>1316</v>
       </c>
     </row>
     <row r="320" spans="1:7" x14ac:dyDescent="0.3">
@@ -11974,11 +11989,11 @@
       <c r="E320" s="4" t="s">
         <v>603</v>
       </c>
-      <c r="F320" s="12" t="s">
-        <v>1319</v>
-      </c>
-      <c r="G320" s="12" t="s">
-        <v>1320</v>
+      <c r="F320" s="11" t="s">
+        <v>1317</v>
+      </c>
+      <c r="G320" s="11" t="s">
+        <v>1318</v>
       </c>
     </row>
     <row r="321" spans="1:7" x14ac:dyDescent="0.3">
@@ -11997,11 +12012,11 @@
       <c r="E321" s="4" t="s">
         <v>603</v>
       </c>
-      <c r="F321" s="12" t="s">
-        <v>1321</v>
-      </c>
-      <c r="G321" s="12" t="s">
-        <v>1322</v>
+      <c r="F321" s="11" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G321" s="11" t="s">
+        <v>1320</v>
       </c>
     </row>
     <row r="322" spans="1:7" x14ac:dyDescent="0.3">
@@ -12020,11 +12035,11 @@
       <c r="E322" s="4" t="s">
         <v>603</v>
       </c>
-      <c r="F322" s="12" t="s">
-        <v>1323</v>
-      </c>
-      <c r="G322" s="12" t="s">
-        <v>1324</v>
+      <c r="F322" s="11" t="s">
+        <v>1321</v>
+      </c>
+      <c r="G322" s="11" t="s">
+        <v>1322</v>
       </c>
     </row>
     <row r="323" spans="1:7" x14ac:dyDescent="0.3">
@@ -12043,11 +12058,11 @@
       <c r="E323" s="4" t="s">
         <v>603</v>
       </c>
-      <c r="F323" s="12" t="s">
-        <v>1325</v>
-      </c>
-      <c r="G323" s="12" t="s">
-        <v>1326</v>
+      <c r="F323" s="11" t="s">
+        <v>1323</v>
+      </c>
+      <c r="G323" s="11" t="s">
+        <v>1324</v>
       </c>
     </row>
     <row r="324" spans="1:7" x14ac:dyDescent="0.3">
@@ -12066,11 +12081,11 @@
       <c r="E324" s="4" t="s">
         <v>603</v>
       </c>
-      <c r="F324" s="12" t="s">
-        <v>1327</v>
-      </c>
-      <c r="G324" s="12" t="s">
-        <v>1328</v>
+      <c r="F324" s="11" t="s">
+        <v>1325</v>
+      </c>
+      <c r="G324" s="11" t="s">
+        <v>1326</v>
       </c>
     </row>
     <row r="325" spans="1:7" x14ac:dyDescent="0.3">
@@ -12089,11 +12104,11 @@
       <c r="E325" s="4" t="s">
         <v>603</v>
       </c>
-      <c r="F325" s="12" t="s">
-        <v>1329</v>
-      </c>
-      <c r="G325" s="12" t="s">
-        <v>1330</v>
+      <c r="F325" s="11" t="s">
+        <v>1327</v>
+      </c>
+      <c r="G325" s="11" t="s">
+        <v>1328</v>
       </c>
     </row>
     <row r="326" spans="1:7" x14ac:dyDescent="0.3">
@@ -12112,11 +12127,11 @@
       <c r="E326" s="4" t="s">
         <v>603</v>
       </c>
-      <c r="F326" s="12" t="s">
-        <v>1331</v>
-      </c>
-      <c r="G326" s="12" t="s">
-        <v>1332</v>
+      <c r="F326" s="11" t="s">
+        <v>1329</v>
+      </c>
+      <c r="G326" s="11" t="s">
+        <v>1330</v>
       </c>
     </row>
     <row r="327" spans="1:7" x14ac:dyDescent="0.3">
@@ -12135,11 +12150,11 @@
       <c r="E327" s="4" t="s">
         <v>603</v>
       </c>
-      <c r="F327" s="12" t="s">
-        <v>1333</v>
-      </c>
-      <c r="G327" s="12" t="s">
-        <v>1334</v>
+      <c r="F327" s="11" t="s">
+        <v>1331</v>
+      </c>
+      <c r="G327" s="11" t="s">
+        <v>1332</v>
       </c>
     </row>
     <row r="328" spans="1:7" x14ac:dyDescent="0.3">
@@ -12158,11 +12173,11 @@
       <c r="E328" s="4" t="s">
         <v>603</v>
       </c>
-      <c r="F328" s="12" t="s">
-        <v>1335</v>
-      </c>
-      <c r="G328" s="12" t="s">
-        <v>1336</v>
+      <c r="F328" s="11" t="s">
+        <v>1333</v>
+      </c>
+      <c r="G328" s="11" t="s">
+        <v>1334</v>
       </c>
     </row>
     <row r="329" spans="1:7" x14ac:dyDescent="0.3">
@@ -12181,11 +12196,11 @@
       <c r="E329" s="4" t="s">
         <v>603</v>
       </c>
-      <c r="F329" s="12" t="s">
-        <v>1337</v>
-      </c>
-      <c r="G329" s="12" t="s">
-        <v>1338</v>
+      <c r="F329" s="11" t="s">
+        <v>1335</v>
+      </c>
+      <c r="G329" s="11" t="s">
+        <v>1336</v>
       </c>
     </row>
     <row r="330" spans="1:7" x14ac:dyDescent="0.3">
@@ -12204,11 +12219,11 @@
       <c r="E330" s="4" t="s">
         <v>603</v>
       </c>
-      <c r="F330" s="12" t="s">
-        <v>1339</v>
-      </c>
-      <c r="G330" s="12" t="s">
-        <v>1340</v>
+      <c r="F330" s="11" t="s">
+        <v>1337</v>
+      </c>
+      <c r="G330" s="11" t="s">
+        <v>1338</v>
       </c>
     </row>
     <row r="331" spans="1:7" x14ac:dyDescent="0.3">
@@ -12227,11 +12242,11 @@
       <c r="E331" s="4" t="s">
         <v>603</v>
       </c>
-      <c r="F331" s="12" t="s">
-        <v>1341</v>
-      </c>
-      <c r="G331" s="12" t="s">
-        <v>1342</v>
+      <c r="F331" s="11" t="s">
+        <v>1339</v>
+      </c>
+      <c r="G331" s="11" t="s">
+        <v>1340</v>
       </c>
     </row>
     <row r="332" spans="1:7" x14ac:dyDescent="0.3">
@@ -12250,11 +12265,11 @@
       <c r="E332" s="4" t="s">
         <v>603</v>
       </c>
-      <c r="F332" s="12" t="s">
-        <v>1343</v>
-      </c>
-      <c r="G332" s="12" t="s">
-        <v>1344</v>
+      <c r="F332" s="11" t="s">
+        <v>1341</v>
+      </c>
+      <c r="G332" s="11" t="s">
+        <v>1342</v>
       </c>
     </row>
     <row r="333" spans="1:7" x14ac:dyDescent="0.3">
@@ -12273,11 +12288,11 @@
       <c r="E333" s="4" t="s">
         <v>603</v>
       </c>
-      <c r="F333" s="12" t="s">
-        <v>1345</v>
-      </c>
-      <c r="G333" s="12" t="s">
-        <v>1346</v>
+      <c r="F333" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="G333" s="11" t="s">
+        <v>1344</v>
       </c>
     </row>
     <row r="334" spans="1:7" x14ac:dyDescent="0.3">
@@ -12296,11 +12311,11 @@
       <c r="E334" s="4" t="s">
         <v>603</v>
       </c>
-      <c r="F334" s="12" t="s">
-        <v>1347</v>
-      </c>
-      <c r="G334" s="12" t="s">
-        <v>1348</v>
+      <c r="F334" s="11" t="s">
+        <v>1345</v>
+      </c>
+      <c r="G334" s="11" t="s">
+        <v>1346</v>
       </c>
     </row>
     <row r="335" spans="1:7" x14ac:dyDescent="0.3">
@@ -12319,11 +12334,11 @@
       <c r="E335" s="4" t="s">
         <v>603</v>
       </c>
-      <c r="F335" s="12" t="s">
-        <v>1349</v>
-      </c>
-      <c r="G335" s="12" t="s">
-        <v>1350</v>
+      <c r="F335" s="11" t="s">
+        <v>1347</v>
+      </c>
+      <c r="G335" s="11" t="s">
+        <v>1348</v>
       </c>
     </row>
   </sheetData>

--- a/files/Adhiparasakthi Students Data 1.xlsx
+++ b/files/Adhiparasakthi Students Data 1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vigne\Google_Backup\Github\sb4c\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74262C99-C121-4B1F-83CC-E6383FB9A842}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10B87436-3423-4997-A84A-4196033CA334}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E3F0EEA9-6BAE-46A1-95E3-E9CE509FC50B}"/>
   </bookViews>
@@ -2571,12 +2571,6 @@
     <t>Edu#244335</t>
   </si>
   <si>
-    <t>EFIBM26268566789@edunetmail.com</t>
-  </si>
-  <si>
-    <t>Edu#721902</t>
-  </si>
-  <si>
     <t>EFIBM26963340792@edunetmail.com</t>
   </si>
   <si>
@@ -2607,12 +2601,6 @@
     <t>Edu#461981</t>
   </si>
   <si>
-    <t>EFIBM26630872231@edunetmail.com</t>
-  </si>
-  <si>
-    <t>Edu#781997</t>
-  </si>
-  <si>
     <t>EFIBM26782374290@edunetmail.com</t>
   </si>
   <si>
@@ -2817,12 +2805,6 @@
     <t>Edu#842997</t>
   </si>
   <si>
-    <t>EFIBM26363139860@edunetmail.com</t>
-  </si>
-  <si>
-    <t>Edu#576105</t>
-  </si>
-  <si>
     <t>EFIBM26671192948@edunetmail.com</t>
   </si>
   <si>
@@ -2877,12 +2859,6 @@
     <t>Edu#466001</t>
   </si>
   <si>
-    <t>EFIBM26399751281@edunetmail.com</t>
-  </si>
-  <si>
-    <t>Edu#789853</t>
-  </si>
-  <si>
     <t>EFIBM26420476671@edunetmail.com</t>
   </si>
   <si>
@@ -2913,12 +2889,6 @@
     <t>Edu#929690</t>
   </si>
   <si>
-    <t>EFIBM26365745181@edunetmail.com</t>
-  </si>
-  <si>
-    <t>Edu#552173</t>
-  </si>
-  <si>
     <t>EFIBM26186546889@edunetmail.com</t>
   </si>
   <si>
@@ -2931,24 +2901,12 @@
     <t>Edu#675000</t>
   </si>
   <si>
-    <t>EFIBM26602786685@edunetmail.com</t>
-  </si>
-  <si>
-    <t>Edu#192643</t>
-  </si>
-  <si>
     <t>EFIBM26547127422@edunetmail.com</t>
   </si>
   <si>
     <t>Edu#161354</t>
   </si>
   <si>
-    <t>EFIBM26656179421@edunetmail.com</t>
-  </si>
-  <si>
-    <t>Edu#351991</t>
-  </si>
-  <si>
     <t>EFIBM26729250746@edunetmail.com</t>
   </si>
   <si>
@@ -3027,12 +2985,6 @@
     <t>Edu#813279</t>
   </si>
   <si>
-    <t>EFIBM26778629465@edunetmail.com</t>
-  </si>
-  <si>
-    <t>Edu#409736</t>
-  </si>
-  <si>
     <t>EFIBM26797604544@edunetmail.com</t>
   </si>
   <si>
@@ -4087,6 +4039,54 @@
   </si>
   <si>
     <t>EduB5#879054</t>
+  </si>
+  <si>
+    <t>EFIBM26B5831478319@edunetmail.com</t>
+  </si>
+  <si>
+    <t>EduB5#724582</t>
+  </si>
+  <si>
+    <t>EFIBM26B5975455986@edunetmail.com</t>
+  </si>
+  <si>
+    <t>EduB5#555057</t>
+  </si>
+  <si>
+    <t>EFIBM26B5641608072@edunetmail.com</t>
+  </si>
+  <si>
+    <t>EduB5#675561</t>
+  </si>
+  <si>
+    <t>EFIBM26B5794832136@edunetmail.com</t>
+  </si>
+  <si>
+    <t>EduB5#953603</t>
+  </si>
+  <si>
+    <t>EFIBM26B5651048524@edunetmail.com</t>
+  </si>
+  <si>
+    <t>EduB5#898232</t>
+  </si>
+  <si>
+    <t>EFIBM26B5328311810@edunetmail.com</t>
+  </si>
+  <si>
+    <t>EduB5#370453</t>
+  </si>
+  <si>
+    <t>EFIBM26B5697829380@edunetmail.com</t>
+  </si>
+  <si>
+    <t>EduB5#865150</t>
+  </si>
+  <si>
+    <t>EFIBM26B5243461614@edunetmail.com</t>
+  </si>
+  <si>
+    <t>EduB5#998024</t>
   </si>
 </sst>
 </file>
@@ -6194,10 +6194,10 @@
         <v>138</v>
       </c>
       <c r="F68" s="12" t="s">
-        <v>1349</v>
+        <v>1333</v>
       </c>
       <c r="G68" s="12" t="s">
-        <v>1350</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6561,11 +6561,11 @@
       <c r="E84" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F84" s="6" t="s">
-        <v>845</v>
-      </c>
-      <c r="G84" s="8" t="s">
-        <v>846</v>
+      <c r="F84" s="12" t="s">
+        <v>1347</v>
+      </c>
+      <c r="G84" s="12" t="s">
+        <v>1348</v>
       </c>
     </row>
     <row r="85" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6585,10 +6585,10 @@
         <v>138</v>
       </c>
       <c r="F85" s="6" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="G85" s="8" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
     </row>
     <row r="86" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6608,10 +6608,10 @@
         <v>138</v>
       </c>
       <c r="F86" s="6" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="G86" s="8" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
     </row>
     <row r="87" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6631,10 +6631,10 @@
         <v>138</v>
       </c>
       <c r="F87" s="6" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="G87" s="8" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
     </row>
     <row r="88" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6654,10 +6654,10 @@
         <v>138</v>
       </c>
       <c r="F88" s="6" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="G88" s="8" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
     </row>
     <row r="89" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6677,10 +6677,10 @@
         <v>138</v>
       </c>
       <c r="F89" s="6" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="G89" s="8" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
     </row>
     <row r="90" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6699,11 +6699,11 @@
       <c r="E90" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F90" s="6" t="s">
-        <v>857</v>
-      </c>
-      <c r="G90" s="8" t="s">
-        <v>858</v>
+      <c r="F90" s="12" t="s">
+        <v>1349</v>
+      </c>
+      <c r="G90" s="12" t="s">
+        <v>1350</v>
       </c>
     </row>
     <row r="91" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6723,10 +6723,10 @@
         <v>138</v>
       </c>
       <c r="F91" s="6" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="G91" s="8" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
     </row>
     <row r="92" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6746,10 +6746,10 @@
         <v>138</v>
       </c>
       <c r="F92" s="6" t="s">
-        <v>861</v>
+        <v>857</v>
       </c>
       <c r="G92" s="8" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
     </row>
     <row r="93" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6769,10 +6769,10 @@
         <v>138</v>
       </c>
       <c r="F93" s="6" t="s">
-        <v>863</v>
+        <v>859</v>
       </c>
       <c r="G93" s="8" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
     </row>
     <row r="94" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6792,10 +6792,10 @@
         <v>138</v>
       </c>
       <c r="F94" s="6" t="s">
-        <v>865</v>
+        <v>861</v>
       </c>
       <c r="G94" s="8" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
     </row>
     <row r="95" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6815,10 +6815,10 @@
         <v>138</v>
       </c>
       <c r="F95" s="6" t="s">
-        <v>867</v>
+        <v>863</v>
       </c>
       <c r="G95" s="8" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
     </row>
     <row r="96" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6838,10 +6838,10 @@
         <v>138</v>
       </c>
       <c r="F96" s="6" t="s">
-        <v>869</v>
+        <v>865</v>
       </c>
       <c r="G96" s="8" t="s">
-        <v>870</v>
+        <v>866</v>
       </c>
     </row>
     <row r="97" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6861,10 +6861,10 @@
         <v>138</v>
       </c>
       <c r="F97" s="6" t="s">
-        <v>871</v>
+        <v>867</v>
       </c>
       <c r="G97" s="8" t="s">
-        <v>872</v>
+        <v>868</v>
       </c>
     </row>
     <row r="98" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6884,10 +6884,10 @@
         <v>138</v>
       </c>
       <c r="F98" s="6" t="s">
-        <v>873</v>
+        <v>869</v>
       </c>
       <c r="G98" s="8" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
     </row>
     <row r="99" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6907,10 +6907,10 @@
         <v>138</v>
       </c>
       <c r="F99" s="6" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="G99" s="8" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
     </row>
     <row r="100" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6930,10 +6930,10 @@
         <v>138</v>
       </c>
       <c r="F100" s="6" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="G100" s="8" t="s">
-        <v>878</v>
+        <v>874</v>
       </c>
     </row>
     <row r="101" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6953,10 +6953,10 @@
         <v>138</v>
       </c>
       <c r="F101" s="6" t="s">
-        <v>879</v>
+        <v>875</v>
       </c>
       <c r="G101" s="8" t="s">
-        <v>880</v>
+        <v>876</v>
       </c>
     </row>
     <row r="102" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6976,10 +6976,10 @@
         <v>138</v>
       </c>
       <c r="F102" s="6" t="s">
-        <v>881</v>
+        <v>877</v>
       </c>
       <c r="G102" s="8" t="s">
-        <v>882</v>
+        <v>878</v>
       </c>
     </row>
     <row r="103" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6999,10 +6999,10 @@
         <v>138</v>
       </c>
       <c r="F103" s="6" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
       <c r="G103" s="8" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
     </row>
     <row r="104" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7022,10 +7022,10 @@
         <v>138</v>
       </c>
       <c r="F104" s="6" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="G104" s="8" t="s">
-        <v>886</v>
+        <v>882</v>
       </c>
     </row>
     <row r="105" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7045,10 +7045,10 @@
         <v>138</v>
       </c>
       <c r="F105" s="6" t="s">
-        <v>887</v>
+        <v>883</v>
       </c>
       <c r="G105" s="8" t="s">
-        <v>888</v>
+        <v>884</v>
       </c>
     </row>
     <row r="106" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7068,10 +7068,10 @@
         <v>138</v>
       </c>
       <c r="F106" s="6" t="s">
-        <v>889</v>
+        <v>885</v>
       </c>
       <c r="G106" s="8" t="s">
-        <v>890</v>
+        <v>886</v>
       </c>
     </row>
     <row r="107" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7091,10 +7091,10 @@
         <v>138</v>
       </c>
       <c r="F107" s="6" t="s">
-        <v>891</v>
+        <v>887</v>
       </c>
       <c r="G107" s="8" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
     </row>
     <row r="108" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7114,10 +7114,10 @@
         <v>138</v>
       </c>
       <c r="F108" s="6" t="s">
-        <v>893</v>
+        <v>889</v>
       </c>
       <c r="G108" s="8" t="s">
-        <v>894</v>
+        <v>890</v>
       </c>
     </row>
     <row r="109" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7137,10 +7137,10 @@
         <v>138</v>
       </c>
       <c r="F109" s="6" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
       <c r="G109" s="8" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
     </row>
     <row r="110" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7160,10 +7160,10 @@
         <v>138</v>
       </c>
       <c r="F110" s="6" t="s">
-        <v>897</v>
+        <v>893</v>
       </c>
       <c r="G110" s="8" t="s">
-        <v>898</v>
+        <v>894</v>
       </c>
     </row>
     <row r="111" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7183,10 +7183,10 @@
         <v>138</v>
       </c>
       <c r="F111" s="6" t="s">
-        <v>899</v>
+        <v>895</v>
       </c>
       <c r="G111" s="8" t="s">
-        <v>900</v>
+        <v>896</v>
       </c>
     </row>
     <row r="112" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7206,10 +7206,10 @@
         <v>138</v>
       </c>
       <c r="F112" s="6" t="s">
-        <v>901</v>
+        <v>897</v>
       </c>
       <c r="G112" s="8" t="s">
-        <v>902</v>
+        <v>898</v>
       </c>
     </row>
     <row r="113" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7229,10 +7229,10 @@
         <v>138</v>
       </c>
       <c r="F113" s="6" t="s">
-        <v>903</v>
+        <v>899</v>
       </c>
       <c r="G113" s="8" t="s">
-        <v>904</v>
+        <v>900</v>
       </c>
     </row>
     <row r="114" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7252,10 +7252,10 @@
         <v>138</v>
       </c>
       <c r="F114" s="6" t="s">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="G114" s="8" t="s">
-        <v>906</v>
+        <v>902</v>
       </c>
     </row>
     <row r="115" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7275,10 +7275,10 @@
         <v>138</v>
       </c>
       <c r="F115" s="6" t="s">
-        <v>907</v>
+        <v>903</v>
       </c>
       <c r="G115" s="8" t="s">
-        <v>908</v>
+        <v>904</v>
       </c>
     </row>
     <row r="116" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7298,10 +7298,10 @@
         <v>138</v>
       </c>
       <c r="F116" s="6" t="s">
-        <v>909</v>
+        <v>905</v>
       </c>
       <c r="G116" s="8" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
     </row>
     <row r="117" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7321,10 +7321,10 @@
         <v>138</v>
       </c>
       <c r="F117" s="6" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
       <c r="G117" s="8" t="s">
-        <v>912</v>
+        <v>908</v>
       </c>
     </row>
     <row r="118" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7344,10 +7344,10 @@
         <v>138</v>
       </c>
       <c r="F118" s="6" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="G118" s="8" t="s">
-        <v>914</v>
+        <v>910</v>
       </c>
     </row>
     <row r="119" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7367,10 +7367,10 @@
         <v>138</v>
       </c>
       <c r="F119" s="6" t="s">
-        <v>915</v>
+        <v>911</v>
       </c>
       <c r="G119" s="8" t="s">
-        <v>916</v>
+        <v>912</v>
       </c>
     </row>
     <row r="120" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7390,10 +7390,10 @@
         <v>138</v>
       </c>
       <c r="F120" s="6" t="s">
-        <v>917</v>
+        <v>913</v>
       </c>
       <c r="G120" s="8" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
     </row>
     <row r="121" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7413,10 +7413,10 @@
         <v>138</v>
       </c>
       <c r="F121" s="6" t="s">
-        <v>919</v>
+        <v>915</v>
       </c>
       <c r="G121" s="8" t="s">
-        <v>920</v>
+        <v>916</v>
       </c>
     </row>
     <row r="122" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7436,10 +7436,10 @@
         <v>138</v>
       </c>
       <c r="F122" s="6" t="s">
-        <v>921</v>
+        <v>917</v>
       </c>
       <c r="G122" s="8" t="s">
-        <v>922</v>
+        <v>918</v>
       </c>
     </row>
     <row r="123" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7459,10 +7459,10 @@
         <v>138</v>
       </c>
       <c r="F123" s="6" t="s">
-        <v>923</v>
+        <v>919</v>
       </c>
       <c r="G123" s="8" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
     </row>
     <row r="124" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7482,10 +7482,10 @@
         <v>138</v>
       </c>
       <c r="F124" s="6" t="s">
-        <v>925</v>
+        <v>921</v>
       </c>
       <c r="G124" s="8" t="s">
-        <v>926</v>
+        <v>922</v>
       </c>
     </row>
     <row r="125" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7504,11 +7504,11 @@
       <c r="E125" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F125" s="6" t="s">
-        <v>927</v>
-      </c>
-      <c r="G125" s="8" t="s">
-        <v>928</v>
+      <c r="F125" s="12" t="s">
+        <v>1339</v>
+      </c>
+      <c r="G125" s="12" t="s">
+        <v>1340</v>
       </c>
     </row>
     <row r="126" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7528,10 +7528,10 @@
         <v>138</v>
       </c>
       <c r="F126" s="6" t="s">
-        <v>929</v>
+        <v>923</v>
       </c>
       <c r="G126" s="8" t="s">
-        <v>930</v>
+        <v>924</v>
       </c>
     </row>
     <row r="127" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7551,10 +7551,10 @@
         <v>138</v>
       </c>
       <c r="F127" s="6" t="s">
-        <v>931</v>
+        <v>925</v>
       </c>
       <c r="G127" s="8" t="s">
-        <v>932</v>
+        <v>926</v>
       </c>
     </row>
     <row r="128" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7574,10 +7574,10 @@
         <v>138</v>
       </c>
       <c r="F128" s="6" t="s">
-        <v>933</v>
+        <v>927</v>
       </c>
       <c r="G128" s="8" t="s">
-        <v>934</v>
+        <v>928</v>
       </c>
     </row>
     <row r="129" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7597,10 +7597,10 @@
         <v>138</v>
       </c>
       <c r="F129" s="6" t="s">
-        <v>935</v>
+        <v>929</v>
       </c>
       <c r="G129" s="8" t="s">
-        <v>936</v>
+        <v>930</v>
       </c>
     </row>
     <row r="130" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7620,10 +7620,10 @@
         <v>138</v>
       </c>
       <c r="F130" s="6" t="s">
-        <v>937</v>
+        <v>931</v>
       </c>
       <c r="G130" s="8" t="s">
-        <v>938</v>
+        <v>932</v>
       </c>
     </row>
     <row r="131" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7643,10 +7643,10 @@
         <v>138</v>
       </c>
       <c r="F131" s="6" t="s">
-        <v>939</v>
+        <v>933</v>
       </c>
       <c r="G131" s="8" t="s">
-        <v>940</v>
+        <v>934</v>
       </c>
     </row>
     <row r="132" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7666,10 +7666,10 @@
         <v>138</v>
       </c>
       <c r="F132" s="6" t="s">
-        <v>941</v>
+        <v>935</v>
       </c>
       <c r="G132" s="8" t="s">
-        <v>942</v>
+        <v>936</v>
       </c>
     </row>
     <row r="133" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7689,10 +7689,10 @@
         <v>138</v>
       </c>
       <c r="F133" s="6" t="s">
-        <v>943</v>
+        <v>937</v>
       </c>
       <c r="G133" s="8" t="s">
-        <v>944</v>
+        <v>938</v>
       </c>
     </row>
     <row r="134" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7712,10 +7712,10 @@
         <v>138</v>
       </c>
       <c r="F134" s="6" t="s">
-        <v>945</v>
+        <v>939</v>
       </c>
       <c r="G134" s="8" t="s">
-        <v>946</v>
+        <v>940</v>
       </c>
     </row>
     <row r="135" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7734,11 +7734,11 @@
       <c r="E135" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F135" s="6" t="s">
-        <v>947</v>
-      </c>
-      <c r="G135" s="8" t="s">
-        <v>948</v>
+      <c r="F135" s="12" t="s">
+        <v>1345</v>
+      </c>
+      <c r="G135" s="12" t="s">
+        <v>1346</v>
       </c>
     </row>
     <row r="136" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7758,10 +7758,10 @@
         <v>138</v>
       </c>
       <c r="F136" s="6" t="s">
-        <v>949</v>
+        <v>941</v>
       </c>
       <c r="G136" s="8" t="s">
-        <v>950</v>
+        <v>942</v>
       </c>
     </row>
     <row r="137" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7781,10 +7781,10 @@
         <v>138</v>
       </c>
       <c r="F137" s="6" t="s">
-        <v>951</v>
+        <v>943</v>
       </c>
       <c r="G137" s="8" t="s">
-        <v>952</v>
+        <v>944</v>
       </c>
     </row>
     <row r="138" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7804,10 +7804,10 @@
         <v>138</v>
       </c>
       <c r="F138" s="6" t="s">
-        <v>953</v>
+        <v>945</v>
       </c>
       <c r="G138" s="8" t="s">
-        <v>954</v>
+        <v>946</v>
       </c>
     </row>
     <row r="139" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7827,10 +7827,10 @@
         <v>138</v>
       </c>
       <c r="F139" s="6" t="s">
-        <v>955</v>
+        <v>947</v>
       </c>
       <c r="G139" s="8" t="s">
-        <v>956</v>
+        <v>948</v>
       </c>
     </row>
     <row r="140" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7850,10 +7850,10 @@
         <v>138</v>
       </c>
       <c r="F140" s="6" t="s">
-        <v>957</v>
+        <v>949</v>
       </c>
       <c r="G140" s="8" t="s">
-        <v>958</v>
+        <v>950</v>
       </c>
     </row>
     <row r="141" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7872,11 +7872,11 @@
       <c r="E141" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F141" s="6" t="s">
-        <v>959</v>
-      </c>
-      <c r="G141" s="8" t="s">
-        <v>960</v>
+      <c r="F141" s="12" t="s">
+        <v>1335</v>
+      </c>
+      <c r="G141" s="12" t="s">
+        <v>1336</v>
       </c>
     </row>
     <row r="142" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7896,10 +7896,10 @@
         <v>138</v>
       </c>
       <c r="F142" s="6" t="s">
-        <v>961</v>
+        <v>951</v>
       </c>
       <c r="G142" s="8" t="s">
-        <v>962</v>
+        <v>952</v>
       </c>
     </row>
     <row r="143" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7919,10 +7919,10 @@
         <v>138</v>
       </c>
       <c r="F143" s="6" t="s">
-        <v>963</v>
+        <v>953</v>
       </c>
       <c r="G143" s="8" t="s">
-        <v>964</v>
+        <v>954</v>
       </c>
     </row>
     <row r="144" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7941,11 +7941,11 @@
       <c r="E144" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F144" s="6" t="s">
-        <v>965</v>
-      </c>
-      <c r="G144" s="8" t="s">
-        <v>966</v>
+      <c r="F144" s="12" t="s">
+        <v>1337</v>
+      </c>
+      <c r="G144" s="12" t="s">
+        <v>1338</v>
       </c>
     </row>
     <row r="145" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7965,10 +7965,10 @@
         <v>138</v>
       </c>
       <c r="F145" s="6" t="s">
-        <v>967</v>
+        <v>955</v>
       </c>
       <c r="G145" s="8" t="s">
-        <v>968</v>
+        <v>956</v>
       </c>
     </row>
     <row r="146" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7987,11 +7987,11 @@
       <c r="E146" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F146" s="6" t="s">
-        <v>969</v>
-      </c>
-      <c r="G146" s="8" t="s">
-        <v>970</v>
+      <c r="F146" s="12" t="s">
+        <v>1343</v>
+      </c>
+      <c r="G146" s="12" t="s">
+        <v>1344</v>
       </c>
     </row>
     <row r="147" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8011,10 +8011,10 @@
         <v>138</v>
       </c>
       <c r="F147" s="6" t="s">
-        <v>971</v>
+        <v>957</v>
       </c>
       <c r="G147" s="8" t="s">
-        <v>972</v>
+        <v>958</v>
       </c>
     </row>
     <row r="148" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8034,10 +8034,10 @@
         <v>138</v>
       </c>
       <c r="F148" s="6" t="s">
-        <v>973</v>
+        <v>959</v>
       </c>
       <c r="G148" s="8" t="s">
-        <v>974</v>
+        <v>960</v>
       </c>
     </row>
     <row r="149" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8057,10 +8057,10 @@
         <v>138</v>
       </c>
       <c r="F149" s="6" t="s">
-        <v>975</v>
+        <v>961</v>
       </c>
       <c r="G149" s="8" t="s">
-        <v>976</v>
+        <v>962</v>
       </c>
     </row>
     <row r="150" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8080,10 +8080,10 @@
         <v>138</v>
       </c>
       <c r="F150" s="6" t="s">
-        <v>977</v>
+        <v>963</v>
       </c>
       <c r="G150" s="8" t="s">
-        <v>978</v>
+        <v>964</v>
       </c>
     </row>
     <row r="151" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8103,10 +8103,10 @@
         <v>138</v>
       </c>
       <c r="F151" s="6" t="s">
-        <v>979</v>
+        <v>965</v>
       </c>
       <c r="G151" s="8" t="s">
-        <v>980</v>
+        <v>966</v>
       </c>
     </row>
     <row r="152" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8126,10 +8126,10 @@
         <v>138</v>
       </c>
       <c r="F152" s="6" t="s">
-        <v>981</v>
+        <v>967</v>
       </c>
       <c r="G152" s="8" t="s">
-        <v>982</v>
+        <v>968</v>
       </c>
     </row>
     <row r="153" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8149,10 +8149,10 @@
         <v>138</v>
       </c>
       <c r="F153" s="6" t="s">
-        <v>983</v>
+        <v>969</v>
       </c>
       <c r="G153" s="8" t="s">
-        <v>984</v>
+        <v>970</v>
       </c>
     </row>
     <row r="154" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8172,10 +8172,10 @@
         <v>138</v>
       </c>
       <c r="F154" s="6" t="s">
-        <v>985</v>
+        <v>971</v>
       </c>
       <c r="G154" s="8" t="s">
-        <v>986</v>
+        <v>972</v>
       </c>
     </row>
     <row r="155" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8195,10 +8195,10 @@
         <v>138</v>
       </c>
       <c r="F155" s="6" t="s">
-        <v>987</v>
+        <v>973</v>
       </c>
       <c r="G155" s="8" t="s">
-        <v>988</v>
+        <v>974</v>
       </c>
     </row>
     <row r="156" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8218,10 +8218,10 @@
         <v>138</v>
       </c>
       <c r="F156" s="6" t="s">
-        <v>989</v>
+        <v>975</v>
       </c>
       <c r="G156" s="8" t="s">
-        <v>990</v>
+        <v>976</v>
       </c>
     </row>
     <row r="157" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8241,10 +8241,10 @@
         <v>138</v>
       </c>
       <c r="F157" s="6" t="s">
-        <v>991</v>
+        <v>977</v>
       </c>
       <c r="G157" s="8" t="s">
-        <v>992</v>
+        <v>978</v>
       </c>
     </row>
     <row r="158" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8264,10 +8264,10 @@
         <v>138</v>
       </c>
       <c r="F158" s="6" t="s">
-        <v>993</v>
+        <v>979</v>
       </c>
       <c r="G158" s="8" t="s">
-        <v>994</v>
+        <v>980</v>
       </c>
     </row>
     <row r="159" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8287,10 +8287,10 @@
         <v>138</v>
       </c>
       <c r="F159" s="6" t="s">
-        <v>995</v>
+        <v>981</v>
       </c>
       <c r="G159" s="8" t="s">
-        <v>996</v>
+        <v>982</v>
       </c>
     </row>
     <row r="160" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8309,11 +8309,11 @@
       <c r="E160" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F160" s="6" t="s">
-        <v>997</v>
-      </c>
-      <c r="G160" s="8" t="s">
-        <v>998</v>
+      <c r="F160" s="12" t="s">
+        <v>1341</v>
+      </c>
+      <c r="G160" s="12" t="s">
+        <v>1342</v>
       </c>
     </row>
     <row r="161" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8333,10 +8333,10 @@
         <v>138</v>
       </c>
       <c r="F161" s="6" t="s">
-        <v>999</v>
+        <v>983</v>
       </c>
       <c r="G161" s="8" t="s">
-        <v>1000</v>
+        <v>984</v>
       </c>
     </row>
     <row r="162" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8356,10 +8356,10 @@
         <v>138</v>
       </c>
       <c r="F162" s="6" t="s">
-        <v>1001</v>
+        <v>985</v>
       </c>
       <c r="G162" s="8" t="s">
-        <v>1002</v>
+        <v>986</v>
       </c>
     </row>
     <row r="163" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8379,10 +8379,10 @@
         <v>138</v>
       </c>
       <c r="F163" s="6" t="s">
-        <v>1003</v>
+        <v>987</v>
       </c>
       <c r="G163" s="8" t="s">
-        <v>1004</v>
+        <v>988</v>
       </c>
     </row>
     <row r="164" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8402,10 +8402,10 @@
         <v>138</v>
       </c>
       <c r="F164" s="6" t="s">
-        <v>1005</v>
+        <v>989</v>
       </c>
       <c r="G164" s="8" t="s">
-        <v>1006</v>
+        <v>990</v>
       </c>
     </row>
     <row r="165" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8425,10 +8425,10 @@
         <v>138</v>
       </c>
       <c r="F165" s="6" t="s">
-        <v>1007</v>
+        <v>991</v>
       </c>
       <c r="G165" s="8" t="s">
-        <v>1008</v>
+        <v>992</v>
       </c>
     </row>
     <row r="166" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8448,10 +8448,10 @@
         <v>138</v>
       </c>
       <c r="F166" s="6" t="s">
-        <v>1009</v>
+        <v>993</v>
       </c>
       <c r="G166" s="8" t="s">
-        <v>1010</v>
+        <v>994</v>
       </c>
     </row>
     <row r="167" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8471,10 +8471,10 @@
         <v>138</v>
       </c>
       <c r="F167" s="6" t="s">
-        <v>1011</v>
+        <v>995</v>
       </c>
       <c r="G167" s="8" t="s">
-        <v>1012</v>
+        <v>996</v>
       </c>
     </row>
     <row r="168" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8494,10 +8494,10 @@
         <v>138</v>
       </c>
       <c r="F168" s="6" t="s">
-        <v>1013</v>
+        <v>997</v>
       </c>
       <c r="G168" s="8" t="s">
-        <v>1014</v>
+        <v>998</v>
       </c>
     </row>
     <row r="169" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8517,10 +8517,10 @@
         <v>138</v>
       </c>
       <c r="F169" s="6" t="s">
-        <v>1015</v>
+        <v>999</v>
       </c>
       <c r="G169" s="8" t="s">
-        <v>1016</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="170" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8540,10 +8540,10 @@
         <v>138</v>
       </c>
       <c r="F170" s="6" t="s">
-        <v>1017</v>
+        <v>1001</v>
       </c>
       <c r="G170" s="8" t="s">
-        <v>1018</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="171" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8563,10 +8563,10 @@
         <v>138</v>
       </c>
       <c r="F171" s="6" t="s">
-        <v>1019</v>
+        <v>1003</v>
       </c>
       <c r="G171" s="8" t="s">
-        <v>1020</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="172" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8586,10 +8586,10 @@
         <v>138</v>
       </c>
       <c r="F172" s="6" t="s">
-        <v>1021</v>
+        <v>1005</v>
       </c>
       <c r="G172" s="8" t="s">
-        <v>1022</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="173" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8609,10 +8609,10 @@
         <v>138</v>
       </c>
       <c r="F173" s="6" t="s">
-        <v>1023</v>
+        <v>1007</v>
       </c>
       <c r="G173" s="8" t="s">
-        <v>1024</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="174" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8632,10 +8632,10 @@
         <v>138</v>
       </c>
       <c r="F174" s="6" t="s">
-        <v>1025</v>
+        <v>1009</v>
       </c>
       <c r="G174" s="8" t="s">
-        <v>1026</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="175" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8655,10 +8655,10 @@
         <v>138</v>
       </c>
       <c r="F175" s="6" t="s">
-        <v>1027</v>
+        <v>1011</v>
       </c>
       <c r="G175" s="8" t="s">
-        <v>1028</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="176" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8678,10 +8678,10 @@
         <v>138</v>
       </c>
       <c r="F176" s="6" t="s">
-        <v>1029</v>
+        <v>1013</v>
       </c>
       <c r="G176" s="8" t="s">
-        <v>1030</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="177" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8701,10 +8701,10 @@
         <v>138</v>
       </c>
       <c r="F177" s="6" t="s">
-        <v>1031</v>
+        <v>1015</v>
       </c>
       <c r="G177" s="8" t="s">
-        <v>1032</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="178" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8724,10 +8724,10 @@
         <v>138</v>
       </c>
       <c r="F178" s="6" t="s">
-        <v>1033</v>
+        <v>1017</v>
       </c>
       <c r="G178" s="8" t="s">
-        <v>1034</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="179" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8747,10 +8747,10 @@
         <v>138</v>
       </c>
       <c r="F179" s="6" t="s">
-        <v>1035</v>
+        <v>1019</v>
       </c>
       <c r="G179" s="8" t="s">
-        <v>1036</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="180" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8770,10 +8770,10 @@
         <v>138</v>
       </c>
       <c r="F180" s="6" t="s">
-        <v>1037</v>
+        <v>1021</v>
       </c>
       <c r="G180" s="8" t="s">
-        <v>1038</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="181" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8793,10 +8793,10 @@
         <v>138</v>
       </c>
       <c r="F181" s="6" t="s">
-        <v>1039</v>
+        <v>1023</v>
       </c>
       <c r="G181" s="8" t="s">
-        <v>1040</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="182" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8816,10 +8816,10 @@
         <v>138</v>
       </c>
       <c r="F182" s="6" t="s">
-        <v>1041</v>
+        <v>1025</v>
       </c>
       <c r="G182" s="8" t="s">
-        <v>1042</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="183" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8839,10 +8839,10 @@
         <v>138</v>
       </c>
       <c r="F183" s="6" t="s">
-        <v>1043</v>
+        <v>1027</v>
       </c>
       <c r="G183" s="8" t="s">
-        <v>1044</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="184" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8862,10 +8862,10 @@
         <v>138</v>
       </c>
       <c r="F184" s="6" t="s">
-        <v>1045</v>
+        <v>1029</v>
       </c>
       <c r="G184" s="8" t="s">
-        <v>1046</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="185" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8885,10 +8885,10 @@
         <v>138</v>
       </c>
       <c r="F185" s="6" t="s">
-        <v>1047</v>
+        <v>1031</v>
       </c>
       <c r="G185" s="8" t="s">
-        <v>1048</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="186" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8908,10 +8908,10 @@
         <v>138</v>
       </c>
       <c r="F186" s="6" t="s">
-        <v>1049</v>
+        <v>1033</v>
       </c>
       <c r="G186" s="8" t="s">
-        <v>1050</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="187" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8931,10 +8931,10 @@
         <v>138</v>
       </c>
       <c r="F187" s="6" t="s">
-        <v>1051</v>
+        <v>1035</v>
       </c>
       <c r="G187" s="8" t="s">
-        <v>1052</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="188" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8954,10 +8954,10 @@
         <v>138</v>
       </c>
       <c r="F188" s="6" t="s">
-        <v>1053</v>
+        <v>1037</v>
       </c>
       <c r="G188" s="8" t="s">
-        <v>1054</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="189" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8977,10 +8977,10 @@
         <v>138</v>
       </c>
       <c r="F189" s="6" t="s">
-        <v>1055</v>
+        <v>1039</v>
       </c>
       <c r="G189" s="8" t="s">
-        <v>1056</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="190" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9000,10 +9000,10 @@
         <v>138</v>
       </c>
       <c r="F190" s="6" t="s">
-        <v>1057</v>
+        <v>1041</v>
       </c>
       <c r="G190" s="8" t="s">
-        <v>1058</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="191" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9023,10 +9023,10 @@
         <v>138</v>
       </c>
       <c r="F191" s="6" t="s">
-        <v>1059</v>
+        <v>1043</v>
       </c>
       <c r="G191" s="8" t="s">
-        <v>1060</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="192" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9046,10 +9046,10 @@
         <v>138</v>
       </c>
       <c r="F192" s="6" t="s">
-        <v>1061</v>
+        <v>1045</v>
       </c>
       <c r="G192" s="8" t="s">
-        <v>1062</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="193" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9069,10 +9069,10 @@
         <v>138</v>
       </c>
       <c r="F193" s="6" t="s">
-        <v>1063</v>
+        <v>1047</v>
       </c>
       <c r="G193" s="8" t="s">
-        <v>1064</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="194" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9092,10 +9092,10 @@
         <v>138</v>
       </c>
       <c r="F194" s="6" t="s">
-        <v>1065</v>
+        <v>1049</v>
       </c>
       <c r="G194" s="8" t="s">
-        <v>1066</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="195" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9115,10 +9115,10 @@
         <v>138</v>
       </c>
       <c r="F195" s="6" t="s">
-        <v>1067</v>
+        <v>1051</v>
       </c>
       <c r="G195" s="8" t="s">
-        <v>1068</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="196" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9138,10 +9138,10 @@
         <v>138</v>
       </c>
       <c r="F196" s="6" t="s">
-        <v>1069</v>
+        <v>1053</v>
       </c>
       <c r="G196" s="8" t="s">
-        <v>1070</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="197" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9161,10 +9161,10 @@
         <v>138</v>
       </c>
       <c r="F197" s="6" t="s">
-        <v>1071</v>
+        <v>1055</v>
       </c>
       <c r="G197" s="8" t="s">
-        <v>1072</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="198" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9184,10 +9184,10 @@
         <v>138</v>
       </c>
       <c r="F198" s="6" t="s">
-        <v>1073</v>
+        <v>1057</v>
       </c>
       <c r="G198" s="8" t="s">
-        <v>1074</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="199" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9207,10 +9207,10 @@
         <v>138</v>
       </c>
       <c r="F199" s="6" t="s">
-        <v>1075</v>
+        <v>1059</v>
       </c>
       <c r="G199" s="8" t="s">
-        <v>1076</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="200" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9230,10 +9230,10 @@
         <v>138</v>
       </c>
       <c r="F200" s="6" t="s">
-        <v>1077</v>
+        <v>1061</v>
       </c>
       <c r="G200" s="8" t="s">
-        <v>1078</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="201" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9253,10 +9253,10 @@
         <v>138</v>
       </c>
       <c r="F201" s="6" t="s">
-        <v>1079</v>
+        <v>1063</v>
       </c>
       <c r="G201" s="8" t="s">
-        <v>1080</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="202" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9276,10 +9276,10 @@
         <v>138</v>
       </c>
       <c r="F202" s="6" t="s">
-        <v>1081</v>
+        <v>1065</v>
       </c>
       <c r="G202" s="8" t="s">
-        <v>1082</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="203" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9299,10 +9299,10 @@
         <v>138</v>
       </c>
       <c r="F203" s="6" t="s">
-        <v>1083</v>
+        <v>1067</v>
       </c>
       <c r="G203" s="8" t="s">
-        <v>1084</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="204" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9322,10 +9322,10 @@
         <v>138</v>
       </c>
       <c r="F204" s="6" t="s">
-        <v>1085</v>
+        <v>1069</v>
       </c>
       <c r="G204" s="8" t="s">
-        <v>1086</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="205" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9345,10 +9345,10 @@
         <v>138</v>
       </c>
       <c r="F205" s="6" t="s">
-        <v>1087</v>
+        <v>1071</v>
       </c>
       <c r="G205" s="8" t="s">
-        <v>1088</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="206" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9368,10 +9368,10 @@
         <v>138</v>
       </c>
       <c r="F206" s="6" t="s">
-        <v>1089</v>
+        <v>1073</v>
       </c>
       <c r="G206" s="8" t="s">
-        <v>1090</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="207" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9391,10 +9391,10 @@
         <v>138</v>
       </c>
       <c r="F207" s="6" t="s">
-        <v>1091</v>
+        <v>1075</v>
       </c>
       <c r="G207" s="8" t="s">
-        <v>1092</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="208" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9414,10 +9414,10 @@
         <v>138</v>
       </c>
       <c r="F208" s="6" t="s">
-        <v>1093</v>
+        <v>1077</v>
       </c>
       <c r="G208" s="8" t="s">
-        <v>1094</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="209" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9437,10 +9437,10 @@
         <v>138</v>
       </c>
       <c r="F209" s="6" t="s">
-        <v>1095</v>
+        <v>1079</v>
       </c>
       <c r="G209" s="8" t="s">
-        <v>1096</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="210" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9460,10 +9460,10 @@
         <v>138</v>
       </c>
       <c r="F210" s="6" t="s">
-        <v>1097</v>
+        <v>1081</v>
       </c>
       <c r="G210" s="8" t="s">
-        <v>1098</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="211" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9483,10 +9483,10 @@
         <v>138</v>
       </c>
       <c r="F211" s="6" t="s">
-        <v>1099</v>
+        <v>1083</v>
       </c>
       <c r="G211" s="8" t="s">
-        <v>1100</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="212" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9506,10 +9506,10 @@
         <v>138</v>
       </c>
       <c r="F212" s="6" t="s">
-        <v>1101</v>
+        <v>1085</v>
       </c>
       <c r="G212" s="8" t="s">
-        <v>1102</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="213" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9529,10 +9529,10 @@
         <v>138</v>
       </c>
       <c r="F213" s="6" t="s">
-        <v>1103</v>
+        <v>1087</v>
       </c>
       <c r="G213" s="8" t="s">
-        <v>1104</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="214" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9552,10 +9552,10 @@
         <v>138</v>
       </c>
       <c r="F214" s="6" t="s">
-        <v>1105</v>
+        <v>1089</v>
       </c>
       <c r="G214" s="8" t="s">
-        <v>1106</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="215" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9575,10 +9575,10 @@
         <v>138</v>
       </c>
       <c r="F215" s="6" t="s">
-        <v>1107</v>
+        <v>1091</v>
       </c>
       <c r="G215" s="8" t="s">
-        <v>1108</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="216" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9598,10 +9598,10 @@
         <v>138</v>
       </c>
       <c r="F216" s="6" t="s">
-        <v>1109</v>
+        <v>1093</v>
       </c>
       <c r="G216" s="8" t="s">
-        <v>1110</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="217" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9621,10 +9621,10 @@
         <v>138</v>
       </c>
       <c r="F217" s="6" t="s">
-        <v>1111</v>
+        <v>1095</v>
       </c>
       <c r="G217" s="8" t="s">
-        <v>1112</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="218" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9644,10 +9644,10 @@
         <v>138</v>
       </c>
       <c r="F218" s="6" t="s">
-        <v>1113</v>
+        <v>1097</v>
       </c>
       <c r="G218" s="8" t="s">
-        <v>1114</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.3">
@@ -9667,10 +9667,10 @@
         <v>138</v>
       </c>
       <c r="F219" s="9" t="s">
-        <v>1115</v>
+        <v>1099</v>
       </c>
       <c r="G219" s="10" t="s">
-        <v>1116</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.3">
@@ -9690,10 +9690,10 @@
         <v>138</v>
       </c>
       <c r="F220" s="11" t="s">
-        <v>1117</v>
+        <v>1101</v>
       </c>
       <c r="G220" s="11" t="s">
-        <v>1118</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.3">
@@ -9713,10 +9713,10 @@
         <v>138</v>
       </c>
       <c r="F221" s="11" t="s">
-        <v>1119</v>
+        <v>1103</v>
       </c>
       <c r="G221" s="11" t="s">
-        <v>1120</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.3">
@@ -9736,10 +9736,10 @@
         <v>138</v>
       </c>
       <c r="F222" s="11" t="s">
-        <v>1121</v>
+        <v>1105</v>
       </c>
       <c r="G222" s="11" t="s">
-        <v>1122</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.3">
@@ -9759,10 +9759,10 @@
         <v>138</v>
       </c>
       <c r="F223" s="11" t="s">
-        <v>1123</v>
+        <v>1107</v>
       </c>
       <c r="G223" s="11" t="s">
-        <v>1124</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.3">
@@ -9782,10 +9782,10 @@
         <v>138</v>
       </c>
       <c r="F224" s="11" t="s">
-        <v>1125</v>
+        <v>1109</v>
       </c>
       <c r="G224" s="11" t="s">
-        <v>1126</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.3">
@@ -9805,10 +9805,10 @@
         <v>138</v>
       </c>
       <c r="F225" s="11" t="s">
-        <v>1127</v>
+        <v>1111</v>
       </c>
       <c r="G225" s="11" t="s">
-        <v>1128</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.3">
@@ -9828,10 +9828,10 @@
         <v>138</v>
       </c>
       <c r="F226" s="11" t="s">
-        <v>1129</v>
+        <v>1113</v>
       </c>
       <c r="G226" s="11" t="s">
-        <v>1130</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.3">
@@ -9851,10 +9851,10 @@
         <v>138</v>
       </c>
       <c r="F227" s="11" t="s">
-        <v>1131</v>
+        <v>1115</v>
       </c>
       <c r="G227" s="11" t="s">
-        <v>1132</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.3">
@@ -9874,10 +9874,10 @@
         <v>138</v>
       </c>
       <c r="F228" s="11" t="s">
-        <v>1133</v>
+        <v>1117</v>
       </c>
       <c r="G228" s="11" t="s">
-        <v>1134</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.3">
@@ -9897,10 +9897,10 @@
         <v>138</v>
       </c>
       <c r="F229" s="11" t="s">
-        <v>1135</v>
+        <v>1119</v>
       </c>
       <c r="G229" s="11" t="s">
-        <v>1136</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.3">
@@ -9920,10 +9920,10 @@
         <v>138</v>
       </c>
       <c r="F230" s="11" t="s">
-        <v>1137</v>
+        <v>1121</v>
       </c>
       <c r="G230" s="11" t="s">
-        <v>1138</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.3">
@@ -9943,10 +9943,10 @@
         <v>138</v>
       </c>
       <c r="F231" s="11" t="s">
-        <v>1139</v>
+        <v>1123</v>
       </c>
       <c r="G231" s="11" t="s">
-        <v>1140</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.3">
@@ -9966,10 +9966,10 @@
         <v>138</v>
       </c>
       <c r="F232" s="11" t="s">
-        <v>1141</v>
+        <v>1125</v>
       </c>
       <c r="G232" s="11" t="s">
-        <v>1142</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.3">
@@ -9989,10 +9989,10 @@
         <v>138</v>
       </c>
       <c r="F233" s="11" t="s">
-        <v>1143</v>
+        <v>1127</v>
       </c>
       <c r="G233" s="11" t="s">
-        <v>1144</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.3">
@@ -10012,10 +10012,10 @@
         <v>138</v>
       </c>
       <c r="F234" s="11" t="s">
-        <v>1145</v>
+        <v>1129</v>
       </c>
       <c r="G234" s="11" t="s">
-        <v>1146</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.3">
@@ -10035,10 +10035,10 @@
         <v>138</v>
       </c>
       <c r="F235" s="11" t="s">
-        <v>1147</v>
+        <v>1131</v>
       </c>
       <c r="G235" s="11" t="s">
-        <v>1148</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.3">
@@ -10058,10 +10058,10 @@
         <v>138</v>
       </c>
       <c r="F236" s="11" t="s">
-        <v>1149</v>
+        <v>1133</v>
       </c>
       <c r="G236" s="11" t="s">
-        <v>1150</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.3">
@@ -10081,10 +10081,10 @@
         <v>138</v>
       </c>
       <c r="F237" s="11" t="s">
-        <v>1151</v>
+        <v>1135</v>
       </c>
       <c r="G237" s="11" t="s">
-        <v>1152</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.3">
@@ -10104,10 +10104,10 @@
         <v>138</v>
       </c>
       <c r="F238" s="11" t="s">
-        <v>1153</v>
+        <v>1137</v>
       </c>
       <c r="G238" s="11" t="s">
-        <v>1154</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.3">
@@ -10127,10 +10127,10 @@
         <v>138</v>
       </c>
       <c r="F239" s="11" t="s">
-        <v>1155</v>
+        <v>1139</v>
       </c>
       <c r="G239" s="11" t="s">
-        <v>1156</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.3">
@@ -10150,10 +10150,10 @@
         <v>138</v>
       </c>
       <c r="F240" s="11" t="s">
-        <v>1157</v>
+        <v>1141</v>
       </c>
       <c r="G240" s="11" t="s">
-        <v>1158</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.3">
@@ -10173,10 +10173,10 @@
         <v>138</v>
       </c>
       <c r="F241" s="11" t="s">
-        <v>1159</v>
+        <v>1143</v>
       </c>
       <c r="G241" s="11" t="s">
-        <v>1160</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.3">
@@ -10196,10 +10196,10 @@
         <v>138</v>
       </c>
       <c r="F242" s="11" t="s">
-        <v>1161</v>
+        <v>1145</v>
       </c>
       <c r="G242" s="11" t="s">
-        <v>1162</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.3">
@@ -10219,10 +10219,10 @@
         <v>138</v>
       </c>
       <c r="F243" s="11" t="s">
-        <v>1163</v>
+        <v>1147</v>
       </c>
       <c r="G243" s="11" t="s">
-        <v>1164</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.3">
@@ -10242,10 +10242,10 @@
         <v>138</v>
       </c>
       <c r="F244" s="11" t="s">
-        <v>1165</v>
+        <v>1149</v>
       </c>
       <c r="G244" s="11" t="s">
-        <v>1166</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.3">
@@ -10265,10 +10265,10 @@
         <v>138</v>
       </c>
       <c r="F245" s="11" t="s">
-        <v>1167</v>
+        <v>1151</v>
       </c>
       <c r="G245" s="11" t="s">
-        <v>1168</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.3">
@@ -10288,10 +10288,10 @@
         <v>138</v>
       </c>
       <c r="F246" s="11" t="s">
-        <v>1169</v>
+        <v>1153</v>
       </c>
       <c r="G246" s="11" t="s">
-        <v>1170</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.3">
@@ -10311,10 +10311,10 @@
         <v>138</v>
       </c>
       <c r="F247" s="11" t="s">
-        <v>1171</v>
+        <v>1155</v>
       </c>
       <c r="G247" s="11" t="s">
-        <v>1172</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.3">
@@ -10334,10 +10334,10 @@
         <v>138</v>
       </c>
       <c r="F248" s="11" t="s">
-        <v>1173</v>
+        <v>1157</v>
       </c>
       <c r="G248" s="11" t="s">
-        <v>1174</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.3">
@@ -10357,10 +10357,10 @@
         <v>138</v>
       </c>
       <c r="F249" s="11" t="s">
-        <v>1175</v>
+        <v>1159</v>
       </c>
       <c r="G249" s="11" t="s">
-        <v>1176</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.3">
@@ -10380,10 +10380,10 @@
         <v>138</v>
       </c>
       <c r="F250" s="11" t="s">
-        <v>1177</v>
+        <v>1161</v>
       </c>
       <c r="G250" s="11" t="s">
-        <v>1178</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.3">
@@ -10403,10 +10403,10 @@
         <v>138</v>
       </c>
       <c r="F251" s="11" t="s">
-        <v>1179</v>
+        <v>1163</v>
       </c>
       <c r="G251" s="11" t="s">
-        <v>1180</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.3">
@@ -10426,10 +10426,10 @@
         <v>138</v>
       </c>
       <c r="F252" s="11" t="s">
-        <v>1181</v>
+        <v>1165</v>
       </c>
       <c r="G252" s="11" t="s">
-        <v>1182</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.3">
@@ -10449,10 +10449,10 @@
         <v>138</v>
       </c>
       <c r="F253" s="11" t="s">
-        <v>1183</v>
+        <v>1167</v>
       </c>
       <c r="G253" s="11" t="s">
-        <v>1184</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.3">
@@ -10472,10 +10472,10 @@
         <v>138</v>
       </c>
       <c r="F254" s="11" t="s">
-        <v>1185</v>
+        <v>1169</v>
       </c>
       <c r="G254" s="11" t="s">
-        <v>1186</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.3">
@@ -10495,10 +10495,10 @@
         <v>138</v>
       </c>
       <c r="F255" s="11" t="s">
-        <v>1187</v>
+        <v>1171</v>
       </c>
       <c r="G255" s="11" t="s">
-        <v>1188</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.3">
@@ -10518,10 +10518,10 @@
         <v>138</v>
       </c>
       <c r="F256" s="11" t="s">
-        <v>1189</v>
+        <v>1173</v>
       </c>
       <c r="G256" s="11" t="s">
-        <v>1190</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.3">
@@ -10541,10 +10541,10 @@
         <v>138</v>
       </c>
       <c r="F257" s="11" t="s">
-        <v>1191</v>
+        <v>1175</v>
       </c>
       <c r="G257" s="11" t="s">
-        <v>1192</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.3">
@@ -10564,10 +10564,10 @@
         <v>138</v>
       </c>
       <c r="F258" s="11" t="s">
-        <v>1193</v>
+        <v>1177</v>
       </c>
       <c r="G258" s="11" t="s">
-        <v>1194</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.3">
@@ -10587,10 +10587,10 @@
         <v>138</v>
       </c>
       <c r="F259" s="11" t="s">
-        <v>1195</v>
+        <v>1179</v>
       </c>
       <c r="G259" s="11" t="s">
-        <v>1196</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.3">
@@ -10610,10 +10610,10 @@
         <v>138</v>
       </c>
       <c r="F260" s="11" t="s">
-        <v>1197</v>
+        <v>1181</v>
       </c>
       <c r="G260" s="11" t="s">
-        <v>1198</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.3">
@@ -10633,10 +10633,10 @@
         <v>138</v>
       </c>
       <c r="F261" s="11" t="s">
-        <v>1199</v>
+        <v>1183</v>
       </c>
       <c r="G261" s="11" t="s">
-        <v>1200</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.3">
@@ -10656,10 +10656,10 @@
         <v>138</v>
       </c>
       <c r="F262" s="11" t="s">
-        <v>1201</v>
+        <v>1185</v>
       </c>
       <c r="G262" s="11" t="s">
-        <v>1202</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.3">
@@ -10679,10 +10679,10 @@
         <v>138</v>
       </c>
       <c r="F263" s="11" t="s">
-        <v>1203</v>
+        <v>1187</v>
       </c>
       <c r="G263" s="11" t="s">
-        <v>1204</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.3">
@@ -10702,10 +10702,10 @@
         <v>138</v>
       </c>
       <c r="F264" s="11" t="s">
-        <v>1205</v>
+        <v>1189</v>
       </c>
       <c r="G264" s="11" t="s">
-        <v>1206</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.3">
@@ -10725,10 +10725,10 @@
         <v>138</v>
       </c>
       <c r="F265" s="11" t="s">
-        <v>1207</v>
+        <v>1191</v>
       </c>
       <c r="G265" s="11" t="s">
-        <v>1208</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.3">
@@ -10748,10 +10748,10 @@
         <v>138</v>
       </c>
       <c r="F266" s="11" t="s">
-        <v>1209</v>
+        <v>1193</v>
       </c>
       <c r="G266" s="11" t="s">
-        <v>1210</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.3">
@@ -10771,10 +10771,10 @@
         <v>138</v>
       </c>
       <c r="F267" s="11" t="s">
-        <v>1211</v>
+        <v>1195</v>
       </c>
       <c r="G267" s="11" t="s">
-        <v>1212</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.3">
@@ -10794,10 +10794,10 @@
         <v>138</v>
       </c>
       <c r="F268" s="11" t="s">
-        <v>1213</v>
+        <v>1197</v>
       </c>
       <c r="G268" s="11" t="s">
-        <v>1214</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.3">
@@ -10817,10 +10817,10 @@
         <v>138</v>
       </c>
       <c r="F269" s="11" t="s">
-        <v>1215</v>
+        <v>1199</v>
       </c>
       <c r="G269" s="11" t="s">
-        <v>1216</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.3">
@@ -10840,10 +10840,10 @@
         <v>138</v>
       </c>
       <c r="F270" s="11" t="s">
-        <v>1217</v>
+        <v>1201</v>
       </c>
       <c r="G270" s="11" t="s">
-        <v>1218</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.3">
@@ -10863,10 +10863,10 @@
         <v>138</v>
       </c>
       <c r="F271" s="11" t="s">
-        <v>1219</v>
+        <v>1203</v>
       </c>
       <c r="G271" s="11" t="s">
-        <v>1220</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.3">
@@ -10886,10 +10886,10 @@
         <v>138</v>
       </c>
       <c r="F272" s="11" t="s">
-        <v>1221</v>
+        <v>1205</v>
       </c>
       <c r="G272" s="11" t="s">
-        <v>1222</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.3">
@@ -10909,10 +10909,10 @@
         <v>138</v>
       </c>
       <c r="F273" s="11" t="s">
-        <v>1223</v>
+        <v>1207</v>
       </c>
       <c r="G273" s="11" t="s">
-        <v>1224</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.3">
@@ -10932,10 +10932,10 @@
         <v>138</v>
       </c>
       <c r="F274" s="11" t="s">
-        <v>1225</v>
+        <v>1209</v>
       </c>
       <c r="G274" s="11" t="s">
-        <v>1226</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.3">
@@ -10955,10 +10955,10 @@
         <v>138</v>
       </c>
       <c r="F275" s="11" t="s">
-        <v>1227</v>
+        <v>1211</v>
       </c>
       <c r="G275" s="11" t="s">
-        <v>1228</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.3">
@@ -10978,10 +10978,10 @@
         <v>138</v>
       </c>
       <c r="F276" s="11" t="s">
-        <v>1229</v>
+        <v>1213</v>
       </c>
       <c r="G276" s="11" t="s">
-        <v>1230</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.3">
@@ -11001,10 +11001,10 @@
         <v>138</v>
       </c>
       <c r="F277" s="11" t="s">
-        <v>1231</v>
+        <v>1215</v>
       </c>
       <c r="G277" s="11" t="s">
-        <v>1232</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.3">
@@ -11024,10 +11024,10 @@
         <v>138</v>
       </c>
       <c r="F278" s="11" t="s">
-        <v>1233</v>
+        <v>1217</v>
       </c>
       <c r="G278" s="11" t="s">
-        <v>1234</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="279" spans="1:7" x14ac:dyDescent="0.3">
@@ -11047,10 +11047,10 @@
         <v>138</v>
       </c>
       <c r="F279" s="11" t="s">
-        <v>1235</v>
+        <v>1219</v>
       </c>
       <c r="G279" s="11" t="s">
-        <v>1236</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="280" spans="1:7" x14ac:dyDescent="0.3">
@@ -11070,10 +11070,10 @@
         <v>138</v>
       </c>
       <c r="F280" s="11" t="s">
-        <v>1237</v>
+        <v>1221</v>
       </c>
       <c r="G280" s="11" t="s">
-        <v>1238</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.3">
@@ -11093,10 +11093,10 @@
         <v>138</v>
       </c>
       <c r="F281" s="11" t="s">
-        <v>1239</v>
+        <v>1223</v>
       </c>
       <c r="G281" s="11" t="s">
-        <v>1240</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.3">
@@ -11116,10 +11116,10 @@
         <v>603</v>
       </c>
       <c r="F282" s="11" t="s">
-        <v>1241</v>
+        <v>1225</v>
       </c>
       <c r="G282" s="11" t="s">
-        <v>1242</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.3">
@@ -11139,10 +11139,10 @@
         <v>603</v>
       </c>
       <c r="F283" s="11" t="s">
-        <v>1243</v>
+        <v>1227</v>
       </c>
       <c r="G283" s="11" t="s">
-        <v>1244</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.3">
@@ -11162,10 +11162,10 @@
         <v>603</v>
       </c>
       <c r="F284" s="11" t="s">
-        <v>1245</v>
+        <v>1229</v>
       </c>
       <c r="G284" s="11" t="s">
-        <v>1246</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.3">
@@ -11185,10 +11185,10 @@
         <v>603</v>
       </c>
       <c r="F285" s="11" t="s">
-        <v>1247</v>
+        <v>1231</v>
       </c>
       <c r="G285" s="11" t="s">
-        <v>1248</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.3">
@@ -11208,10 +11208,10 @@
         <v>603</v>
       </c>
       <c r="F286" s="11" t="s">
-        <v>1249</v>
+        <v>1233</v>
       </c>
       <c r="G286" s="11" t="s">
-        <v>1250</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.3">
@@ -11231,10 +11231,10 @@
         <v>603</v>
       </c>
       <c r="F287" s="11" t="s">
-        <v>1251</v>
+        <v>1235</v>
       </c>
       <c r="G287" s="11" t="s">
-        <v>1252</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.3">
@@ -11254,10 +11254,10 @@
         <v>603</v>
       </c>
       <c r="F288" s="11" t="s">
-        <v>1253</v>
+        <v>1237</v>
       </c>
       <c r="G288" s="11" t="s">
-        <v>1254</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.3">
@@ -11277,10 +11277,10 @@
         <v>603</v>
       </c>
       <c r="F289" s="11" t="s">
-        <v>1255</v>
+        <v>1239</v>
       </c>
       <c r="G289" s="11" t="s">
-        <v>1256</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.3">
@@ -11300,10 +11300,10 @@
         <v>603</v>
       </c>
       <c r="F290" s="11" t="s">
-        <v>1257</v>
+        <v>1241</v>
       </c>
       <c r="G290" s="11" t="s">
-        <v>1258</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.3">
@@ -11323,10 +11323,10 @@
         <v>603</v>
       </c>
       <c r="F291" s="11" t="s">
-        <v>1259</v>
+        <v>1243</v>
       </c>
       <c r="G291" s="11" t="s">
-        <v>1260</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.3">
@@ -11346,10 +11346,10 @@
         <v>603</v>
       </c>
       <c r="F292" s="11" t="s">
-        <v>1261</v>
+        <v>1245</v>
       </c>
       <c r="G292" s="11" t="s">
-        <v>1262</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.3">
@@ -11369,10 +11369,10 @@
         <v>603</v>
       </c>
       <c r="F293" s="11" t="s">
-        <v>1263</v>
+        <v>1247</v>
       </c>
       <c r="G293" s="11" t="s">
-        <v>1264</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.3">
@@ -11392,10 +11392,10 @@
         <v>603</v>
       </c>
       <c r="F294" s="11" t="s">
-        <v>1265</v>
+        <v>1249</v>
       </c>
       <c r="G294" s="11" t="s">
-        <v>1266</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.3">
@@ -11415,10 +11415,10 @@
         <v>603</v>
       </c>
       <c r="F295" s="11" t="s">
-        <v>1267</v>
+        <v>1251</v>
       </c>
       <c r="G295" s="11" t="s">
-        <v>1268</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.3">
@@ -11438,10 +11438,10 @@
         <v>603</v>
       </c>
       <c r="F296" s="11" t="s">
-        <v>1269</v>
+        <v>1253</v>
       </c>
       <c r="G296" s="11" t="s">
-        <v>1270</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.3">
@@ -11461,10 +11461,10 @@
         <v>603</v>
       </c>
       <c r="F297" s="11" t="s">
-        <v>1271</v>
+        <v>1255</v>
       </c>
       <c r="G297" s="11" t="s">
-        <v>1272</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.3">
@@ -11484,10 +11484,10 @@
         <v>138</v>
       </c>
       <c r="F298" s="11" t="s">
-        <v>1273</v>
+        <v>1257</v>
       </c>
       <c r="G298" s="11" t="s">
-        <v>1274</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="299" spans="1:7" x14ac:dyDescent="0.3">
@@ -11507,10 +11507,10 @@
         <v>138</v>
       </c>
       <c r="F299" s="11" t="s">
-        <v>1275</v>
+        <v>1259</v>
       </c>
       <c r="G299" s="11" t="s">
-        <v>1276</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.3">
@@ -11530,10 +11530,10 @@
         <v>138</v>
       </c>
       <c r="F300" s="11" t="s">
-        <v>1277</v>
+        <v>1261</v>
       </c>
       <c r="G300" s="11" t="s">
-        <v>1278</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.3">
@@ -11553,10 +11553,10 @@
         <v>138</v>
       </c>
       <c r="F301" s="11" t="s">
-        <v>1279</v>
+        <v>1263</v>
       </c>
       <c r="G301" s="11" t="s">
-        <v>1280</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="302" spans="1:7" x14ac:dyDescent="0.3">
@@ -11576,10 +11576,10 @@
         <v>138</v>
       </c>
       <c r="F302" s="11" t="s">
-        <v>1281</v>
+        <v>1265</v>
       </c>
       <c r="G302" s="11" t="s">
-        <v>1282</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="303" spans="1:7" x14ac:dyDescent="0.3">
@@ -11599,10 +11599,10 @@
         <v>138</v>
       </c>
       <c r="F303" s="11" t="s">
-        <v>1283</v>
+        <v>1267</v>
       </c>
       <c r="G303" s="11" t="s">
-        <v>1284</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="304" spans="1:7" x14ac:dyDescent="0.3">
@@ -11622,10 +11622,10 @@
         <v>138</v>
       </c>
       <c r="F304" s="11" t="s">
-        <v>1285</v>
+        <v>1269</v>
       </c>
       <c r="G304" s="11" t="s">
-        <v>1286</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="305" spans="1:7" x14ac:dyDescent="0.3">
@@ -11645,10 +11645,10 @@
         <v>138</v>
       </c>
       <c r="F305" s="11" t="s">
-        <v>1287</v>
+        <v>1271</v>
       </c>
       <c r="G305" s="11" t="s">
-        <v>1288</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="306" spans="1:7" x14ac:dyDescent="0.3">
@@ -11668,10 +11668,10 @@
         <v>138</v>
       </c>
       <c r="F306" s="11" t="s">
-        <v>1289</v>
+        <v>1273</v>
       </c>
       <c r="G306" s="11" t="s">
-        <v>1290</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="307" spans="1:7" x14ac:dyDescent="0.3">
@@ -11691,10 +11691,10 @@
         <v>138</v>
       </c>
       <c r="F307" s="11" t="s">
-        <v>1291</v>
+        <v>1275</v>
       </c>
       <c r="G307" s="11" t="s">
-        <v>1292</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="308" spans="1:7" x14ac:dyDescent="0.3">
@@ -11714,10 +11714,10 @@
         <v>603</v>
       </c>
       <c r="F308" s="11" t="s">
-        <v>1293</v>
+        <v>1277</v>
       </c>
       <c r="G308" s="11" t="s">
-        <v>1294</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="309" spans="1:7" x14ac:dyDescent="0.3">
@@ -11737,10 +11737,10 @@
         <v>603</v>
       </c>
       <c r="F309" s="11" t="s">
-        <v>1295</v>
+        <v>1279</v>
       </c>
       <c r="G309" s="11" t="s">
-        <v>1296</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="310" spans="1:7" x14ac:dyDescent="0.3">
@@ -11760,10 +11760,10 @@
         <v>603</v>
       </c>
       <c r="F310" s="11" t="s">
-        <v>1297</v>
+        <v>1281</v>
       </c>
       <c r="G310" s="11" t="s">
-        <v>1298</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="311" spans="1:7" x14ac:dyDescent="0.3">
@@ -11783,10 +11783,10 @@
         <v>603</v>
       </c>
       <c r="F311" s="11" t="s">
-        <v>1299</v>
+        <v>1283</v>
       </c>
       <c r="G311" s="11" t="s">
-        <v>1300</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="312" spans="1:7" x14ac:dyDescent="0.3">
@@ -11806,10 +11806,10 @@
         <v>603</v>
       </c>
       <c r="F312" s="11" t="s">
-        <v>1301</v>
+        <v>1285</v>
       </c>
       <c r="G312" s="11" t="s">
-        <v>1302</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="313" spans="1:7" x14ac:dyDescent="0.3">
@@ -11829,10 +11829,10 @@
         <v>603</v>
       </c>
       <c r="F313" s="11" t="s">
-        <v>1303</v>
+        <v>1287</v>
       </c>
       <c r="G313" s="11" t="s">
-        <v>1304</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="314" spans="1:7" x14ac:dyDescent="0.3">
@@ -11852,10 +11852,10 @@
         <v>603</v>
       </c>
       <c r="F314" s="11" t="s">
-        <v>1305</v>
+        <v>1289</v>
       </c>
       <c r="G314" s="11" t="s">
-        <v>1306</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="315" spans="1:7" x14ac:dyDescent="0.3">
@@ -11875,10 +11875,10 @@
         <v>603</v>
       </c>
       <c r="F315" s="11" t="s">
-        <v>1307</v>
+        <v>1291</v>
       </c>
       <c r="G315" s="11" t="s">
-        <v>1308</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="316" spans="1:7" x14ac:dyDescent="0.3">
@@ -11898,10 +11898,10 @@
         <v>603</v>
       </c>
       <c r="F316" s="11" t="s">
-        <v>1309</v>
+        <v>1293</v>
       </c>
       <c r="G316" s="11" t="s">
-        <v>1310</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="317" spans="1:7" x14ac:dyDescent="0.3">
@@ -11921,10 +11921,10 @@
         <v>603</v>
       </c>
       <c r="F317" s="11" t="s">
-        <v>1311</v>
+        <v>1295</v>
       </c>
       <c r="G317" s="11" t="s">
-        <v>1312</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="318" spans="1:7" x14ac:dyDescent="0.3">
@@ -11944,10 +11944,10 @@
         <v>603</v>
       </c>
       <c r="F318" s="11" t="s">
-        <v>1313</v>
+        <v>1297</v>
       </c>
       <c r="G318" s="11" t="s">
-        <v>1314</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="319" spans="1:7" x14ac:dyDescent="0.3">
@@ -11967,10 +11967,10 @@
         <v>603</v>
       </c>
       <c r="F319" s="11" t="s">
-        <v>1315</v>
+        <v>1299</v>
       </c>
       <c r="G319" s="11" t="s">
-        <v>1316</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="320" spans="1:7" x14ac:dyDescent="0.3">
@@ -11990,10 +11990,10 @@
         <v>603</v>
       </c>
       <c r="F320" s="11" t="s">
-        <v>1317</v>
+        <v>1301</v>
       </c>
       <c r="G320" s="11" t="s">
-        <v>1318</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="321" spans="1:7" x14ac:dyDescent="0.3">
@@ -12013,10 +12013,10 @@
         <v>603</v>
       </c>
       <c r="F321" s="11" t="s">
-        <v>1319</v>
+        <v>1303</v>
       </c>
       <c r="G321" s="11" t="s">
-        <v>1320</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="322" spans="1:7" x14ac:dyDescent="0.3">
@@ -12036,10 +12036,10 @@
         <v>603</v>
       </c>
       <c r="F322" s="11" t="s">
-        <v>1321</v>
+        <v>1305</v>
       </c>
       <c r="G322" s="11" t="s">
-        <v>1322</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="323" spans="1:7" x14ac:dyDescent="0.3">
@@ -12059,10 +12059,10 @@
         <v>603</v>
       </c>
       <c r="F323" s="11" t="s">
-        <v>1323</v>
+        <v>1307</v>
       </c>
       <c r="G323" s="11" t="s">
-        <v>1324</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="324" spans="1:7" x14ac:dyDescent="0.3">
@@ -12082,10 +12082,10 @@
         <v>603</v>
       </c>
       <c r="F324" s="11" t="s">
-        <v>1325</v>
+        <v>1309</v>
       </c>
       <c r="G324" s="11" t="s">
-        <v>1326</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="325" spans="1:7" x14ac:dyDescent="0.3">
@@ -12105,10 +12105,10 @@
         <v>603</v>
       </c>
       <c r="F325" s="11" t="s">
-        <v>1327</v>
+        <v>1311</v>
       </c>
       <c r="G325" s="11" t="s">
-        <v>1328</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="326" spans="1:7" x14ac:dyDescent="0.3">
@@ -12128,10 +12128,10 @@
         <v>603</v>
       </c>
       <c r="F326" s="11" t="s">
-        <v>1329</v>
+        <v>1313</v>
       </c>
       <c r="G326" s="11" t="s">
-        <v>1330</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="327" spans="1:7" x14ac:dyDescent="0.3">
@@ -12151,10 +12151,10 @@
         <v>603</v>
       </c>
       <c r="F327" s="11" t="s">
-        <v>1331</v>
+        <v>1315</v>
       </c>
       <c r="G327" s="11" t="s">
-        <v>1332</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="328" spans="1:7" x14ac:dyDescent="0.3">
@@ -12174,10 +12174,10 @@
         <v>603</v>
       </c>
       <c r="F328" s="11" t="s">
-        <v>1333</v>
+        <v>1317</v>
       </c>
       <c r="G328" s="11" t="s">
-        <v>1334</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="329" spans="1:7" x14ac:dyDescent="0.3">
@@ -12197,10 +12197,10 @@
         <v>603</v>
       </c>
       <c r="F329" s="11" t="s">
-        <v>1335</v>
+        <v>1319</v>
       </c>
       <c r="G329" s="11" t="s">
-        <v>1336</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="330" spans="1:7" x14ac:dyDescent="0.3">
@@ -12220,10 +12220,10 @@
         <v>603</v>
       </c>
       <c r="F330" s="11" t="s">
-        <v>1337</v>
+        <v>1321</v>
       </c>
       <c r="G330" s="11" t="s">
-        <v>1338</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="331" spans="1:7" x14ac:dyDescent="0.3">
@@ -12243,10 +12243,10 @@
         <v>603</v>
       </c>
       <c r="F331" s="11" t="s">
-        <v>1339</v>
+        <v>1323</v>
       </c>
       <c r="G331" s="11" t="s">
-        <v>1340</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="332" spans="1:7" x14ac:dyDescent="0.3">
@@ -12266,10 +12266,10 @@
         <v>603</v>
       </c>
       <c r="F332" s="11" t="s">
-        <v>1341</v>
+        <v>1325</v>
       </c>
       <c r="G332" s="11" t="s">
-        <v>1342</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="333" spans="1:7" x14ac:dyDescent="0.3">
@@ -12289,10 +12289,10 @@
         <v>603</v>
       </c>
       <c r="F333" s="11" t="s">
-        <v>1343</v>
+        <v>1327</v>
       </c>
       <c r="G333" s="11" t="s">
-        <v>1344</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="334" spans="1:7" x14ac:dyDescent="0.3">
@@ -12312,10 +12312,10 @@
         <v>603</v>
       </c>
       <c r="F334" s="11" t="s">
-        <v>1345</v>
+        <v>1329</v>
       </c>
       <c r="G334" s="11" t="s">
-        <v>1346</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="335" spans="1:7" x14ac:dyDescent="0.3">
@@ -12335,10 +12335,10 @@
         <v>603</v>
       </c>
       <c r="F335" s="11" t="s">
-        <v>1347</v>
+        <v>1331</v>
       </c>
       <c r="G335" s="11" t="s">
-        <v>1348</v>
+        <v>1332</v>
       </c>
     </row>
   </sheetData>

--- a/files/Adhiparasakthi Students Data 1.xlsx
+++ b/files/Adhiparasakthi Students Data 1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vigne\Google_Backup\Github\sb4c\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10B87436-3423-4997-A84A-4196033CA334}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E42DE63E-E73B-423E-9195-E867206429ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E3F0EEA9-6BAE-46A1-95E3-E9CE509FC50B}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2011" uniqueCount="1351">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2010" uniqueCount="1350">
   <si>
     <t>ABINAYA SRI  M V</t>
   </si>
@@ -534,9 +534,6 @@
     <t>arivumathiselvam76@gmail.com</t>
   </si>
   <si>
-    <t>ashwinvolleyball790@gmail.com</t>
-  </si>
-  <si>
     <t>ayshaalavudheen04@gmail.com</t>
   </si>
   <si>
@@ -771,9 +768,6 @@
     <t>Nithesh S</t>
   </si>
   <si>
-    <t>resh090505@gmail.com</t>
-  </si>
-  <si>
     <t>Siva L</t>
   </si>
   <si>
@@ -2487,12 +2481,6 @@
     <t>Edu#377816</t>
   </si>
   <si>
-    <t>EFIBM26587253441@edunetmail.com</t>
-  </si>
-  <si>
-    <t>Edu#361158</t>
-  </si>
-  <si>
     <t>EFIBM26784908968@edunetmail.com</t>
   </si>
   <si>
@@ -2541,24 +2529,12 @@
     <t>Edu#831895</t>
   </si>
   <si>
-    <t>EFIBM26445430154@edunetmail.com</t>
-  </si>
-  <si>
-    <t>Edu#135589</t>
-  </si>
-  <si>
     <t>EFIBM26867543535@edunetmail.com</t>
   </si>
   <si>
     <t>Edu#306392</t>
   </si>
   <si>
-    <t>EFIBM26843225674@edunetmail.com</t>
-  </si>
-  <si>
-    <t>Edu#718563</t>
-  </si>
-  <si>
     <t>EFIBM26866604102@edunetmail.com</t>
   </si>
   <si>
@@ -2571,12 +2547,6 @@
     <t>Edu#244335</t>
   </si>
   <si>
-    <t>EFIBM26963340792@edunetmail.com</t>
-  </si>
-  <si>
-    <t>Edu#915408</t>
-  </si>
-  <si>
     <t>EFIBM26323508832@edunetmail.com</t>
   </si>
   <si>
@@ -2685,24 +2655,12 @@
     <t>Edu#825408</t>
   </si>
   <si>
-    <t>EFIBM26546921645@edunetmail.com</t>
-  </si>
-  <si>
-    <t>Edu#707055</t>
-  </si>
-  <si>
     <t>EFIBM26796769284@edunetmail.com</t>
   </si>
   <si>
     <t>Edu#164884</t>
   </si>
   <si>
-    <t>EFIBM26278266287@edunetmail.com</t>
-  </si>
-  <si>
-    <t>Edu#634363</t>
-  </si>
-  <si>
     <t>EFIBM26743507634@edunetmail.com</t>
   </si>
   <si>
@@ -2727,24 +2685,12 @@
     <t>Edu#900037</t>
   </si>
   <si>
-    <t>EFIBM26448536237@edunetmail.com</t>
-  </si>
-  <si>
-    <t>Edu#832047</t>
-  </si>
-  <si>
     <t>EFIBM26387503884@edunetmail.com</t>
   </si>
   <si>
     <t>Edu#509281</t>
   </si>
   <si>
-    <t>EFIBM26644418070@edunetmail.com</t>
-  </si>
-  <si>
-    <t>Edu#820600</t>
-  </si>
-  <si>
     <t>EFIBM26830874596@edunetmail.com</t>
   </si>
   <si>
@@ -2769,24 +2715,12 @@
     <t>Edu#135952</t>
   </si>
   <si>
-    <t>EFIBM26920859812@edunetmail.com</t>
-  </si>
-  <si>
-    <t>Edu#220115</t>
-  </si>
-  <si>
     <t>EFIBM26955105177@edunetmail.com</t>
   </si>
   <si>
     <t>Edu#912118</t>
   </si>
   <si>
-    <t>EFIBM26681251719@edunetmail.com</t>
-  </si>
-  <si>
-    <t>Edu#231519</t>
-  </si>
-  <si>
     <t>EFIBM26963771892@edunetmail.com</t>
   </si>
   <si>
@@ -2805,12 +2739,6 @@
     <t>Edu#842997</t>
   </si>
   <si>
-    <t>EFIBM26671192948@edunetmail.com</t>
-  </si>
-  <si>
-    <t>Edu#992217</t>
-  </si>
-  <si>
     <t>EFIBM26409807669@edunetmail.com</t>
   </si>
   <si>
@@ -2829,12 +2757,6 @@
     <t>Edu#463947</t>
   </si>
   <si>
-    <t>EFIBM26176435841@edunetmail.com</t>
-  </si>
-  <si>
-    <t>Edu#996649</t>
-  </si>
-  <si>
     <t>EFIBM26415063909@edunetmail.com</t>
   </si>
   <si>
@@ -2895,12 +2817,6 @@
     <t>Edu#486657</t>
   </si>
   <si>
-    <t>EFIBM26287403542@edunetmail.com</t>
-  </si>
-  <si>
-    <t>Edu#675000</t>
-  </si>
-  <si>
     <t>EFIBM26547127422@edunetmail.com</t>
   </si>
   <si>
@@ -2937,12 +2853,6 @@
     <t>Edu#974762</t>
   </si>
   <si>
-    <t>EFIBM26198947257@edunetmail.com</t>
-  </si>
-  <si>
-    <t>Edu#194707</t>
-  </si>
-  <si>
     <t>EFIBM26467400553@edunetmail.com</t>
   </si>
   <si>
@@ -2967,12 +2877,6 @@
     <t>Edu#744574</t>
   </si>
   <si>
-    <t>EFIBM26685085104@edunetmail.com</t>
-  </si>
-  <si>
-    <t>Edu#763365</t>
-  </si>
-  <si>
     <t>EFIBM26327461852@edunetmail.com</t>
   </si>
   <si>
@@ -4087,13 +3991,106 @@
   </si>
   <si>
     <t>EduB5#998024</t>
+  </si>
+  <si>
+    <t>EFIBM26B5708246419@edunetmail.com</t>
+  </si>
+  <si>
+    <t>EduB5#382130</t>
+  </si>
+  <si>
+    <t>EFIBM26B5632682500@edunetmail.com</t>
+  </si>
+  <si>
+    <t>EduB5#298583</t>
+  </si>
+  <si>
+    <t>EFIBM26B5686595459@edunetmail.com</t>
+  </si>
+  <si>
+    <t>EduB5#984784</t>
+  </si>
+  <si>
+    <t>EFIBM26B5445320459@edunetmail.com</t>
+  </si>
+  <si>
+    <t>EduB5#548082</t>
+  </si>
+  <si>
+    <t>EFIBM26B5701262764@edunetmail.com</t>
+  </si>
+  <si>
+    <t>EduB5#928784</t>
+  </si>
+  <si>
+    <t>EFIBM26B5805611238@edunetmail.com</t>
+  </si>
+  <si>
+    <t>EduB5#827141</t>
+  </si>
+  <si>
+    <t>EFIBM26B5578964306@edunetmail.com</t>
+  </si>
+  <si>
+    <t>EduB5#846525</t>
+  </si>
+  <si>
+    <t>EFIBM26B5478483793@edunetmail.com</t>
+  </si>
+  <si>
+    <t>EduB5#660794</t>
+  </si>
+  <si>
+    <t>EFIBM26B5879823233@edunetmail.com</t>
+  </si>
+  <si>
+    <t>EduB5#626496</t>
+  </si>
+  <si>
+    <t>aashwxn@gmail.com</t>
+  </si>
+  <si>
+    <t>EFIBM26B5429612337@edunetmail.com</t>
+  </si>
+  <si>
+    <t>EduB5#997561</t>
+  </si>
+  <si>
+    <t>EFIBM26B5474953159@edunetmail.com</t>
+  </si>
+  <si>
+    <t>EduB5#891694</t>
+  </si>
+  <si>
+    <t>EFIBM26B5239389085@edunetmail.com</t>
+  </si>
+  <si>
+    <t>EduB5#936740</t>
+  </si>
+  <si>
+    <t>EFIBM26B5300462222@edunetmail.com</t>
+  </si>
+  <si>
+    <t>EduB5#952201</t>
+  </si>
+  <si>
+    <t>EFIBM26B5383855945@edunetmail.com</t>
+  </si>
+  <si>
+    <t>EduB5#195040</t>
+  </si>
+  <si>
+    <t>EFIBM26643396730@edunetmail.com</t>
+  </si>
+  <si>
+    <t>Edu#495569</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4121,6 +4118,14 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -4130,7 +4135,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -4267,11 +4272,53 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4309,8 +4356,24 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -4653,10 +4716,10 @@
         <v>136</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -4676,10 +4739,10 @@
         <v>138</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -4699,10 +4762,10 @@
         <v>138</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -4722,10 +4785,10 @@
         <v>138</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -4745,10 +4808,10 @@
         <v>138</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -4768,10 +4831,10 @@
         <v>138</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -4791,10 +4854,10 @@
         <v>138</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -4814,10 +4877,10 @@
         <v>138</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -4837,10 +4900,10 @@
         <v>138</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -4860,10 +4923,10 @@
         <v>138</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -4883,10 +4946,10 @@
         <v>138</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -4906,10 +4969,10 @@
         <v>138</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -4929,10 +4992,10 @@
         <v>138</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -4952,10 +5015,10 @@
         <v>138</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -4975,10 +5038,10 @@
         <v>138</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -4998,10 +5061,10 @@
         <v>138</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5021,10 +5084,10 @@
         <v>138</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5044,10 +5107,10 @@
         <v>138</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5067,10 +5130,10 @@
         <v>138</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5090,10 +5153,10 @@
         <v>138</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5113,10 +5176,10 @@
         <v>138</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5136,10 +5199,10 @@
         <v>138</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5159,10 +5222,10 @@
         <v>138</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5182,10 +5245,10 @@
         <v>138</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5205,10 +5268,10 @@
         <v>138</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5228,10 +5291,10 @@
         <v>138</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5251,10 +5314,10 @@
         <v>138</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5274,10 +5337,10 @@
         <v>138</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5297,10 +5360,10 @@
         <v>138</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5320,10 +5383,10 @@
         <v>138</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5343,10 +5406,10 @@
         <v>138</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5366,10 +5429,10 @@
         <v>138</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5389,10 +5452,10 @@
         <v>138</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5412,10 +5475,10 @@
         <v>138</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5435,10 +5498,10 @@
         <v>138</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5458,10 +5521,10 @@
         <v>138</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5481,10 +5544,10 @@
         <v>138</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5504,10 +5567,10 @@
         <v>138</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5527,10 +5590,10 @@
         <v>138</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5550,10 +5613,10 @@
         <v>138</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5573,10 +5636,10 @@
         <v>138</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5596,10 +5659,10 @@
         <v>138</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5619,10 +5682,10 @@
         <v>138</v>
       </c>
       <c r="F43" s="6" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5642,10 +5705,10 @@
         <v>138</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5665,10 +5728,10 @@
         <v>138</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5688,10 +5751,10 @@
         <v>138</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5711,10 +5774,10 @@
         <v>138</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5734,10 +5797,10 @@
         <v>138</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5757,10 +5820,10 @@
         <v>138</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5780,10 +5843,10 @@
         <v>138</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5803,10 +5866,10 @@
         <v>138</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5826,10 +5889,10 @@
         <v>138</v>
       </c>
       <c r="F52" s="6" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5849,10 +5912,10 @@
         <v>138</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5872,10 +5935,10 @@
         <v>138</v>
       </c>
       <c r="F54" s="6" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="G54" s="8" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5895,10 +5958,10 @@
         <v>138</v>
       </c>
       <c r="F55" s="6" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5918,10 +5981,10 @@
         <v>138</v>
       </c>
       <c r="F56" s="6" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5941,10 +6004,10 @@
         <v>138</v>
       </c>
       <c r="F57" s="6" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5964,10 +6027,10 @@
         <v>138</v>
       </c>
       <c r="F58" s="6" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="G58" s="8" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5987,10 +6050,10 @@
         <v>138</v>
       </c>
       <c r="F59" s="6" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6010,10 +6073,10 @@
         <v>138</v>
       </c>
       <c r="F60" s="6" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="G60" s="8" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6033,10 +6096,10 @@
         <v>138</v>
       </c>
       <c r="F61" s="6" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6056,10 +6119,10 @@
         <v>138</v>
       </c>
       <c r="F62" s="6" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="G62" s="8" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6079,10 +6142,10 @@
         <v>138</v>
       </c>
       <c r="F63" s="6" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6102,10 +6165,10 @@
         <v>138</v>
       </c>
       <c r="F64" s="6" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="G64" s="8" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6125,10 +6188,10 @@
         <v>138</v>
       </c>
       <c r="F65" s="6" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6148,10 +6211,10 @@
         <v>138</v>
       </c>
       <c r="F66" s="6" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="G66" s="8" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6171,10 +6234,10 @@
         <v>138</v>
       </c>
       <c r="F67" s="6" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="G67" s="8" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6188,16 +6251,16 @@
         <v>164</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F68" s="12" t="s">
-        <v>1333</v>
+        <v>1301</v>
       </c>
       <c r="G68" s="12" t="s">
-        <v>1334</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6211,16 +6274,16 @@
         <v>165</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F69" s="6" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="G69" s="8" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6230,20 +6293,20 @@
       <c r="B70" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="C70" s="1" t="s">
-        <v>166</v>
+      <c r="C70" s="16" t="s">
+        <v>1337</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F70" s="6" t="s">
-        <v>817</v>
-      </c>
-      <c r="G70" s="8" t="s">
-        <v>818</v>
+      <c r="F70" s="12" t="s">
+        <v>1335</v>
+      </c>
+      <c r="G70" s="12" t="s">
+        <v>1336</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6254,19 +6317,19 @@
         <v>142</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F71" s="6" t="s">
-        <v>819</v>
+        <v>815</v>
       </c>
       <c r="G71" s="8" t="s">
-        <v>820</v>
+        <v>816</v>
       </c>
     </row>
     <row r="72" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6277,19 +6340,19 @@
         <v>143</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F72" s="6" t="s">
-        <v>821</v>
+        <v>817</v>
       </c>
       <c r="G72" s="8" t="s">
-        <v>822</v>
+        <v>818</v>
       </c>
     </row>
     <row r="73" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6300,19 +6363,19 @@
         <v>144</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F73" s="6" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="G73" s="8" t="s">
-        <v>824</v>
+        <v>820</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6323,19 +6386,19 @@
         <v>145</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F74" s="6" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
       <c r="G74" s="8" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
     </row>
     <row r="75" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6346,19 +6409,19 @@
         <v>146</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F75" s="6" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="G75" s="8" t="s">
-        <v>828</v>
+        <v>824</v>
       </c>
     </row>
     <row r="76" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6369,19 +6432,19 @@
         <v>147</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F76" s="6" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
       <c r="G76" s="8" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
     </row>
     <row r="77" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6392,19 +6455,19 @@
         <v>148</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F77" s="6" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="G77" s="8" t="s">
-        <v>832</v>
+        <v>828</v>
       </c>
     </row>
     <row r="78" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6415,19 +6478,19 @@
         <v>149</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F78" s="6" t="s">
-        <v>833</v>
-      </c>
-      <c r="G78" s="8" t="s">
-        <v>834</v>
+      <c r="F78" s="9" t="s">
+        <v>829</v>
+      </c>
+      <c r="G78" s="10" t="s">
+        <v>830</v>
       </c>
     </row>
     <row r="79" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6438,22 +6501,22 @@
         <v>150</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="E79" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="F79" s="6" t="s">
-        <v>835</v>
-      </c>
-      <c r="G79" s="8" t="s">
-        <v>836</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>188</v>
+      </c>
+      <c r="E79" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="F79" s="12" t="s">
+        <v>1333</v>
+      </c>
+      <c r="G79" s="12" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>79</v>
       </c>
@@ -6461,22 +6524,22 @@
         <v>151</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="E80" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="F80" s="6" t="s">
-        <v>837</v>
-      </c>
-      <c r="G80" s="8" t="s">
-        <v>838</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>188</v>
+      </c>
+      <c r="E80" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="F80" s="15" t="s">
+        <v>831</v>
+      </c>
+      <c r="G80" s="15" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <v>80</v>
       </c>
@@ -6484,22 +6547,22 @@
         <v>152</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="E81" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="F81" s="6" t="s">
-        <v>839</v>
-      </c>
-      <c r="G81" s="8" t="s">
-        <v>840</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>188</v>
+      </c>
+      <c r="E81" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="F81" s="11" t="s">
+        <v>1325</v>
+      </c>
+      <c r="G81" s="11" t="s">
+        <v>1326</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <v>81</v>
       </c>
@@ -6507,22 +6570,22 @@
         <v>153</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="F82" s="6" t="s">
-        <v>841</v>
-      </c>
-      <c r="G82" s="8" t="s">
-        <v>842</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>188</v>
+      </c>
+      <c r="E82" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="F82" s="15" t="s">
+        <v>833</v>
+      </c>
+      <c r="G82" s="15" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
         <v>82</v>
       </c>
@@ -6530,22 +6593,22 @@
         <v>154</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="E83" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="F83" s="6" t="s">
-        <v>843</v>
-      </c>
-      <c r="G83" s="8" t="s">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>188</v>
+      </c>
+      <c r="E83" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="F83" s="15" t="s">
+        <v>835</v>
+      </c>
+      <c r="G83" s="15" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
         <v>83</v>
       </c>
@@ -6553,22 +6616,22 @@
         <v>155</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="E84" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="F84" s="12" t="s">
-        <v>1347</v>
-      </c>
-      <c r="G84" s="12" t="s">
-        <v>1348</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>188</v>
+      </c>
+      <c r="E84" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="F84" s="11" t="s">
+        <v>1315</v>
+      </c>
+      <c r="G84" s="11" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
         <v>84</v>
       </c>
@@ -6576,22 +6639,22 @@
         <v>156</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="E85" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="F85" s="6" t="s">
-        <v>845</v>
-      </c>
-      <c r="G85" s="8" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>188</v>
+      </c>
+      <c r="E85" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="F85" s="11" t="s">
+        <v>1327</v>
+      </c>
+      <c r="G85" s="11" t="s">
+        <v>1328</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
         <v>85</v>
       </c>
@@ -6599,22 +6662,22 @@
         <v>157</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="E86" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="F86" s="6" t="s">
-        <v>847</v>
-      </c>
-      <c r="G86" s="8" t="s">
-        <v>848</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>188</v>
+      </c>
+      <c r="E86" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="F86" s="15" t="s">
+        <v>837</v>
+      </c>
+      <c r="G86" s="15" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
         <v>86</v>
       </c>
@@ -6622,22 +6685,22 @@
         <v>158</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="E87" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="F87" s="6" t="s">
-        <v>849</v>
-      </c>
-      <c r="G87" s="8" t="s">
-        <v>850</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>188</v>
+      </c>
+      <c r="E87" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="F87" s="15" t="s">
+        <v>839</v>
+      </c>
+      <c r="G87" s="15" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
         <v>87</v>
       </c>
@@ -6645,22 +6708,22 @@
         <v>159</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="E88" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="F88" s="6" t="s">
-        <v>851</v>
-      </c>
-      <c r="G88" s="8" t="s">
-        <v>852</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>188</v>
+      </c>
+      <c r="E88" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="F88" s="15" t="s">
+        <v>841</v>
+      </c>
+      <c r="G88" s="15" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
         <v>88</v>
       </c>
@@ -6668,22 +6731,22 @@
         <v>160</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="E89" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="F89" s="6" t="s">
-        <v>853</v>
-      </c>
-      <c r="G89" s="8" t="s">
-        <v>854</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>188</v>
+      </c>
+      <c r="E89" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="F89" s="15" t="s">
+        <v>843</v>
+      </c>
+      <c r="G89" s="15" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
         <v>89</v>
       </c>
@@ -6691,22 +6754,22 @@
         <v>161</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="E90" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="F90" s="12" t="s">
-        <v>1349</v>
-      </c>
-      <c r="G90" s="12" t="s">
-        <v>1350</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>188</v>
+      </c>
+      <c r="E90" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="F90" s="11" t="s">
+        <v>1317</v>
+      </c>
+      <c r="G90" s="11" t="s">
+        <v>1318</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <v>90</v>
       </c>
@@ -6714,22 +6777,22 @@
         <v>162</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="E91" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="F91" s="6" t="s">
-        <v>855</v>
-      </c>
-      <c r="G91" s="8" t="s">
-        <v>856</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>188</v>
+      </c>
+      <c r="E91" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="F91" s="15" t="s">
+        <v>845</v>
+      </c>
+      <c r="G91" s="15" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
         <v>91</v>
       </c>
@@ -6737,19 +6800,19 @@
         <v>163</v>
       </c>
       <c r="C92" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D92" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="D92" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="E92" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="F92" s="6" t="s">
-        <v>857</v>
-      </c>
-      <c r="G92" s="8" t="s">
-        <v>858</v>
+      <c r="E92" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="F92" s="15" t="s">
+        <v>847</v>
+      </c>
+      <c r="G92" s="15" t="s">
+        <v>848</v>
       </c>
     </row>
     <row r="93" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6757,22 +6820,22 @@
         <v>92</v>
       </c>
       <c r="B93" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="C93" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="C93" s="1" t="s">
-        <v>191</v>
-      </c>
       <c r="D93" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E93" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F93" s="6" t="s">
-        <v>859</v>
-      </c>
-      <c r="G93" s="8" t="s">
-        <v>860</v>
+      <c r="F93" s="13" t="s">
+        <v>849</v>
+      </c>
+      <c r="G93" s="14" t="s">
+        <v>850</v>
       </c>
     </row>
     <row r="94" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6780,22 +6843,22 @@
         <v>93</v>
       </c>
       <c r="B94" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C94" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="C94" s="1" t="s">
-        <v>193</v>
-      </c>
       <c r="D94" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E94" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F94" s="6" t="s">
-        <v>861</v>
+        <v>851</v>
       </c>
       <c r="G94" s="8" t="s">
-        <v>862</v>
+        <v>852</v>
       </c>
     </row>
     <row r="95" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6803,22 +6866,22 @@
         <v>94</v>
       </c>
       <c r="B95" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C95" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="C95" s="1" t="s">
-        <v>195</v>
-      </c>
       <c r="D95" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E95" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F95" s="6" t="s">
-        <v>863</v>
+        <v>853</v>
       </c>
       <c r="G95" s="8" t="s">
-        <v>864</v>
+        <v>854</v>
       </c>
     </row>
     <row r="96" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6826,22 +6889,22 @@
         <v>95</v>
       </c>
       <c r="B96" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C96" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="C96" s="1" t="s">
-        <v>197</v>
-      </c>
       <c r="D96" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F96" s="6" t="s">
-        <v>865</v>
+        <v>855</v>
       </c>
       <c r="G96" s="8" t="s">
-        <v>866</v>
+        <v>856</v>
       </c>
     </row>
     <row r="97" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6849,22 +6912,22 @@
         <v>96</v>
       </c>
       <c r="B97" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C97" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="C97" s="1" t="s">
-        <v>199</v>
-      </c>
       <c r="D97" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F97" s="6" t="s">
-        <v>867</v>
+        <v>857</v>
       </c>
       <c r="G97" s="8" t="s">
-        <v>868</v>
+        <v>858</v>
       </c>
     </row>
     <row r="98" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6872,22 +6935,22 @@
         <v>97</v>
       </c>
       <c r="B98" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C98" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="C98" s="1" t="s">
-        <v>201</v>
-      </c>
       <c r="D98" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F98" s="6" t="s">
-        <v>869</v>
+        <v>859</v>
       </c>
       <c r="G98" s="8" t="s">
-        <v>870</v>
+        <v>860</v>
       </c>
     </row>
     <row r="99" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6895,22 +6958,22 @@
         <v>98</v>
       </c>
       <c r="B99" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="C99" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="C99" s="1" t="s">
-        <v>203</v>
-      </c>
       <c r="D99" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E99" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F99" s="6" t="s">
-        <v>871</v>
+        <v>861</v>
       </c>
       <c r="G99" s="8" t="s">
-        <v>872</v>
+        <v>862</v>
       </c>
     </row>
     <row r="100" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6918,22 +6981,22 @@
         <v>99</v>
       </c>
       <c r="B100" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C100" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="C100" s="1" t="s">
-        <v>205</v>
-      </c>
       <c r="D100" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F100" s="6" t="s">
-        <v>873</v>
+        <v>863</v>
       </c>
       <c r="G100" s="8" t="s">
-        <v>874</v>
+        <v>864</v>
       </c>
     </row>
     <row r="101" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6941,22 +7004,22 @@
         <v>100</v>
       </c>
       <c r="B101" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="C101" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="C101" s="1" t="s">
-        <v>207</v>
-      </c>
       <c r="D101" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F101" s="6" t="s">
-        <v>875</v>
+        <v>865</v>
       </c>
       <c r="G101" s="8" t="s">
-        <v>876</v>
+        <v>866</v>
       </c>
     </row>
     <row r="102" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6964,22 +7027,22 @@
         <v>101</v>
       </c>
       <c r="B102" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="C102" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="C102" s="1" t="s">
-        <v>209</v>
-      </c>
       <c r="D102" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E102" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F102" s="6" t="s">
-        <v>877</v>
+        <v>867</v>
       </c>
       <c r="G102" s="8" t="s">
-        <v>878</v>
+        <v>868</v>
       </c>
     </row>
     <row r="103" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6987,22 +7050,22 @@
         <v>102</v>
       </c>
       <c r="B103" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C103" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C103" s="1" t="s">
-        <v>211</v>
-      </c>
       <c r="D103" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E103" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F103" s="6" t="s">
-        <v>879</v>
+        <v>869</v>
       </c>
       <c r="G103" s="8" t="s">
-        <v>880</v>
+        <v>870</v>
       </c>
     </row>
     <row r="104" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7010,22 +7073,22 @@
         <v>103</v>
       </c>
       <c r="B104" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C104" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="C104" s="1" t="s">
-        <v>213</v>
-      </c>
       <c r="D104" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E104" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F104" s="6" t="s">
-        <v>881</v>
+        <v>871</v>
       </c>
       <c r="G104" s="8" t="s">
-        <v>882</v>
+        <v>872</v>
       </c>
     </row>
     <row r="105" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7033,22 +7096,22 @@
         <v>104</v>
       </c>
       <c r="B105" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C105" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="C105" s="1" t="s">
-        <v>215</v>
-      </c>
       <c r="D105" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E105" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F105" s="6" t="s">
-        <v>883</v>
-      </c>
-      <c r="G105" s="8" t="s">
-        <v>884</v>
+      <c r="F105" s="12" t="s">
+        <v>1340</v>
+      </c>
+      <c r="G105" s="12" t="s">
+        <v>1341</v>
       </c>
     </row>
     <row r="106" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7056,22 +7119,22 @@
         <v>105</v>
       </c>
       <c r="B106" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C106" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="C106" s="1" t="s">
-        <v>217</v>
-      </c>
       <c r="D106" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E106" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F106" s="6" t="s">
-        <v>885</v>
+        <v>873</v>
       </c>
       <c r="G106" s="8" t="s">
-        <v>886</v>
+        <v>874</v>
       </c>
     </row>
     <row r="107" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7079,22 +7142,22 @@
         <v>106</v>
       </c>
       <c r="B107" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C107" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="C107" s="1" t="s">
-        <v>219</v>
-      </c>
       <c r="D107" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E107" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F107" s="6" t="s">
-        <v>887</v>
-      </c>
-      <c r="G107" s="8" t="s">
-        <v>888</v>
+      <c r="F107" s="5" t="s">
+        <v>1348</v>
+      </c>
+      <c r="G107" s="7" t="s">
+        <v>1349</v>
       </c>
     </row>
     <row r="108" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7102,22 +7165,22 @@
         <v>107</v>
       </c>
       <c r="B108" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C108" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="C108" s="1" t="s">
-        <v>221</v>
-      </c>
       <c r="D108" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F108" s="6" t="s">
-        <v>889</v>
+        <v>875</v>
       </c>
       <c r="G108" s="8" t="s">
-        <v>890</v>
+        <v>876</v>
       </c>
     </row>
     <row r="109" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7125,22 +7188,22 @@
         <v>108</v>
       </c>
       <c r="B109" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="C109" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="C109" s="1" t="s">
-        <v>223</v>
-      </c>
       <c r="D109" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E109" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F109" s="6" t="s">
-        <v>891</v>
+        <v>877</v>
       </c>
       <c r="G109" s="8" t="s">
-        <v>892</v>
+        <v>878</v>
       </c>
     </row>
     <row r="110" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7148,22 +7211,22 @@
         <v>109</v>
       </c>
       <c r="B110" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="C110" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="C110" s="1" t="s">
-        <v>225</v>
-      </c>
       <c r="D110" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E110" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F110" s="6" t="s">
-        <v>893</v>
+        <v>879</v>
       </c>
       <c r="G110" s="8" t="s">
-        <v>894</v>
+        <v>880</v>
       </c>
     </row>
     <row r="111" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7171,22 +7234,22 @@
         <v>110</v>
       </c>
       <c r="B111" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="C111" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="C111" s="1" t="s">
-        <v>227</v>
-      </c>
       <c r="D111" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E111" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F111" s="6" t="s">
-        <v>895</v>
+        <v>881</v>
       </c>
       <c r="G111" s="8" t="s">
-        <v>896</v>
+        <v>882</v>
       </c>
     </row>
     <row r="112" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7194,22 +7257,22 @@
         <v>111</v>
       </c>
       <c r="B112" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C112" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="C112" s="1" t="s">
-        <v>229</v>
-      </c>
       <c r="D112" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E112" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F112" s="6" t="s">
-        <v>897</v>
-      </c>
-      <c r="G112" s="8" t="s">
-        <v>898</v>
+      <c r="F112" s="17" t="s">
+        <v>1346</v>
+      </c>
+      <c r="G112" s="17" t="s">
+        <v>1347</v>
       </c>
     </row>
     <row r="113" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7217,22 +7280,22 @@
         <v>112</v>
       </c>
       <c r="B113" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="C113" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="C113" s="1" t="s">
-        <v>231</v>
-      </c>
       <c r="D113" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E113" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F113" s="6" t="s">
-        <v>899</v>
+        <v>883</v>
       </c>
       <c r="G113" s="8" t="s">
-        <v>900</v>
+        <v>884</v>
       </c>
     </row>
     <row r="114" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7240,22 +7303,22 @@
         <v>113</v>
       </c>
       <c r="B114" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="C114" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="C114" s="1" t="s">
-        <v>233</v>
-      </c>
       <c r="D114" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E114" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F114" s="6" t="s">
-        <v>901</v>
-      </c>
-      <c r="G114" s="8" t="s">
-        <v>902</v>
+      <c r="F114" s="12" t="s">
+        <v>1342</v>
+      </c>
+      <c r="G114" s="12" t="s">
+        <v>1343</v>
       </c>
     </row>
     <row r="115" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7263,22 +7326,22 @@
         <v>114</v>
       </c>
       <c r="B115" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="C115" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="C115" s="1" t="s">
-        <v>235</v>
-      </c>
       <c r="D115" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F115" s="6" t="s">
-        <v>903</v>
+        <v>885</v>
       </c>
       <c r="G115" s="8" t="s">
-        <v>904</v>
+        <v>886</v>
       </c>
     </row>
     <row r="116" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7286,22 +7349,22 @@
         <v>115</v>
       </c>
       <c r="B116" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="C116" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="C116" s="1" t="s">
-        <v>237</v>
-      </c>
       <c r="D116" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E116" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F116" s="6" t="s">
-        <v>905</v>
+        <v>887</v>
       </c>
       <c r="G116" s="8" t="s">
-        <v>906</v>
+        <v>888</v>
       </c>
     </row>
     <row r="117" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7309,22 +7372,22 @@
         <v>116</v>
       </c>
       <c r="B117" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="C117" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="C117" s="1" t="s">
-        <v>239</v>
-      </c>
       <c r="D117" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E117" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F117" s="6" t="s">
-        <v>907</v>
+        <v>889</v>
       </c>
       <c r="G117" s="8" t="s">
-        <v>908</v>
+        <v>890</v>
       </c>
     </row>
     <row r="118" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7332,22 +7395,19 @@
         <v>117</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="C118" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E118" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F118" s="6" t="s">
-        <v>909</v>
+        <v>891</v>
       </c>
       <c r="G118" s="8" t="s">
-        <v>910</v>
+        <v>892</v>
       </c>
     </row>
     <row r="119" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7355,22 +7415,22 @@
         <v>118</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E119" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F119" s="6" t="s">
-        <v>911</v>
-      </c>
-      <c r="G119" s="8" t="s">
-        <v>912</v>
+      <c r="F119" s="12" t="s">
+        <v>1338</v>
+      </c>
+      <c r="G119" s="12" t="s">
+        <v>1339</v>
       </c>
     </row>
     <row r="120" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7378,22 +7438,22 @@
         <v>119</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E120" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F120" s="6" t="s">
-        <v>913</v>
+        <v>893</v>
       </c>
       <c r="G120" s="8" t="s">
-        <v>914</v>
+        <v>894</v>
       </c>
     </row>
     <row r="121" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7401,22 +7461,22 @@
         <v>120</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F121" s="6" t="s">
-        <v>915</v>
-      </c>
-      <c r="G121" s="8" t="s">
-        <v>916</v>
+      <c r="F121" s="12" t="s">
+        <v>1344</v>
+      </c>
+      <c r="G121" s="12" t="s">
+        <v>1345</v>
       </c>
     </row>
     <row r="122" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7424,22 +7484,22 @@
         <v>121</v>
       </c>
       <c r="B122" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="D122" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="C122" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="D122" s="1" t="s">
-        <v>250</v>
-      </c>
       <c r="E122" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F122" s="6" t="s">
-        <v>917</v>
+        <v>895</v>
       </c>
       <c r="G122" s="8" t="s">
-        <v>918</v>
+        <v>896</v>
       </c>
     </row>
     <row r="123" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7447,22 +7507,22 @@
         <v>122</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E123" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F123" s="6" t="s">
-        <v>919</v>
+        <v>897</v>
       </c>
       <c r="G123" s="8" t="s">
-        <v>920</v>
+        <v>898</v>
       </c>
     </row>
     <row r="124" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7470,22 +7530,22 @@
         <v>123</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E124" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F124" s="6" t="s">
-        <v>921</v>
+        <v>899</v>
       </c>
       <c r="G124" s="8" t="s">
-        <v>922</v>
+        <v>900</v>
       </c>
     </row>
     <row r="125" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7493,22 +7553,22 @@
         <v>124</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E125" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F125" s="12" t="s">
-        <v>1339</v>
+        <v>1307</v>
       </c>
       <c r="G125" s="12" t="s">
-        <v>1340</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="126" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7516,22 +7576,22 @@
         <v>125</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E126" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F126" s="6" t="s">
-        <v>923</v>
-      </c>
-      <c r="G126" s="8" t="s">
-        <v>924</v>
+      <c r="F126" s="12" t="s">
+        <v>1321</v>
+      </c>
+      <c r="G126" s="12" t="s">
+        <v>1322</v>
       </c>
     </row>
     <row r="127" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7539,22 +7599,22 @@
         <v>126</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E127" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F127" s="6" t="s">
-        <v>925</v>
+        <v>901</v>
       </c>
       <c r="G127" s="8" t="s">
-        <v>926</v>
+        <v>902</v>
       </c>
     </row>
     <row r="128" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7562,22 +7622,22 @@
         <v>127</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E128" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F128" s="6" t="s">
-        <v>927</v>
+        <v>903</v>
       </c>
       <c r="G128" s="8" t="s">
-        <v>928</v>
+        <v>904</v>
       </c>
     </row>
     <row r="129" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7585,22 +7645,22 @@
         <v>128</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E129" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F129" s="6" t="s">
-        <v>929</v>
+        <v>905</v>
       </c>
       <c r="G129" s="8" t="s">
-        <v>930</v>
+        <v>906</v>
       </c>
     </row>
     <row r="130" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7608,22 +7668,22 @@
         <v>129</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E130" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F130" s="6" t="s">
-        <v>931</v>
-      </c>
-      <c r="G130" s="8" t="s">
-        <v>932</v>
+      <c r="F130" s="12" t="s">
+        <v>1329</v>
+      </c>
+      <c r="G130" s="12" t="s">
+        <v>1330</v>
       </c>
     </row>
     <row r="131" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7631,22 +7691,22 @@
         <v>130</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E131" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F131" s="6" t="s">
-        <v>933</v>
+        <v>907</v>
       </c>
       <c r="G131" s="8" t="s">
-        <v>934</v>
+        <v>908</v>
       </c>
     </row>
     <row r="132" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7654,22 +7714,22 @@
         <v>131</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E132" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F132" s="6" t="s">
-        <v>935</v>
+        <v>909</v>
       </c>
       <c r="G132" s="8" t="s">
-        <v>936</v>
+        <v>910</v>
       </c>
     </row>
     <row r="133" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7677,22 +7737,22 @@
         <v>132</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E133" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F133" s="6" t="s">
-        <v>937</v>
+        <v>911</v>
       </c>
       <c r="G133" s="8" t="s">
-        <v>938</v>
+        <v>912</v>
       </c>
     </row>
     <row r="134" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7700,22 +7760,22 @@
         <v>133</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E134" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F134" s="6" t="s">
-        <v>939</v>
+        <v>913</v>
       </c>
       <c r="G134" s="8" t="s">
-        <v>940</v>
+        <v>914</v>
       </c>
     </row>
     <row r="135" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7723,22 +7783,22 @@
         <v>134</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E135" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F135" s="12" t="s">
-        <v>1345</v>
+        <v>1313</v>
       </c>
       <c r="G135" s="12" t="s">
-        <v>1346</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="136" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7746,22 +7806,22 @@
         <v>135</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E136" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F136" s="6" t="s">
-        <v>941</v>
+        <v>915</v>
       </c>
       <c r="G136" s="8" t="s">
-        <v>942</v>
+        <v>916</v>
       </c>
     </row>
     <row r="137" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7769,22 +7829,22 @@
         <v>136</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E137" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F137" s="6" t="s">
-        <v>943</v>
+        <v>917</v>
       </c>
       <c r="G137" s="8" t="s">
-        <v>944</v>
+        <v>918</v>
       </c>
     </row>
     <row r="138" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7792,344 +7852,344 @@
         <v>137</v>
       </c>
       <c r="B138" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="F138" s="6" t="s">
+        <v>919</v>
+      </c>
+      <c r="G138" s="8" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A139" s="1">
+        <v>138</v>
+      </c>
+      <c r="B139" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="C138" s="1" t="s">
+      <c r="C139" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="D138" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="E138" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="F138" s="6" t="s">
-        <v>945</v>
-      </c>
-      <c r="G138" s="8" t="s">
-        <v>946</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A139" s="1">
-        <v>138</v>
-      </c>
-      <c r="B139" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="C139" s="1" t="s">
-        <v>283</v>
-      </c>
       <c r="D139" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E139" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F139" s="6" t="s">
-        <v>947</v>
-      </c>
-      <c r="G139" s="8" t="s">
-        <v>948</v>
-      </c>
-    </row>
-    <row r="140" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F139" s="9" t="s">
+        <v>921</v>
+      </c>
+      <c r="G139" s="10" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140" s="1">
         <v>139</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="E140" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="F140" s="6" t="s">
-        <v>949</v>
-      </c>
-      <c r="G140" s="8" t="s">
-        <v>950</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>404</v>
+      </c>
+      <c r="E140" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="F140" s="15" t="s">
+        <v>923</v>
+      </c>
+      <c r="G140" s="15" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A141" s="1">
         <v>140</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="E141" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="F141" s="12" t="s">
-        <v>1335</v>
-      </c>
-      <c r="G141" s="12" t="s">
-        <v>1336</v>
-      </c>
-    </row>
-    <row r="142" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>404</v>
+      </c>
+      <c r="E141" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="F141" s="11" t="s">
+        <v>1303</v>
+      </c>
+      <c r="G141" s="11" t="s">
+        <v>1304</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A142" s="1">
         <v>141</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="E142" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="F142" s="6" t="s">
-        <v>951</v>
-      </c>
-      <c r="G142" s="8" t="s">
-        <v>952</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>404</v>
+      </c>
+      <c r="E142" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="F142" s="15" t="s">
+        <v>925</v>
+      </c>
+      <c r="G142" s="15" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A143" s="1">
         <v>142</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="E143" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="F143" s="6" t="s">
-        <v>953</v>
-      </c>
-      <c r="G143" s="8" t="s">
-        <v>954</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>404</v>
+      </c>
+      <c r="E143" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="F143" s="11" t="s">
+        <v>1331</v>
+      </c>
+      <c r="G143" s="11" t="s">
+        <v>1332</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144" s="1">
         <v>143</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="E144" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="F144" s="12" t="s">
-        <v>1337</v>
-      </c>
-      <c r="G144" s="12" t="s">
-        <v>1338</v>
-      </c>
-    </row>
-    <row r="145" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>404</v>
+      </c>
+      <c r="E144" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="F144" s="11" t="s">
+        <v>1305</v>
+      </c>
+      <c r="G144" s="11" t="s">
+        <v>1306</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A145" s="1">
         <v>144</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="E145" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="F145" s="6" t="s">
-        <v>955</v>
-      </c>
-      <c r="G145" s="8" t="s">
-        <v>956</v>
-      </c>
-    </row>
-    <row r="146" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>404</v>
+      </c>
+      <c r="E145" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="F145" s="15" t="s">
+        <v>927</v>
+      </c>
+      <c r="G145" s="15" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A146" s="1">
         <v>145</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="E146" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="F146" s="12" t="s">
-        <v>1343</v>
-      </c>
-      <c r="G146" s="12" t="s">
-        <v>1344</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>404</v>
+      </c>
+      <c r="E146" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="F146" s="11" t="s">
+        <v>1311</v>
+      </c>
+      <c r="G146" s="11" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A147" s="1">
         <v>146</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="E147" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="F147" s="6" t="s">
-        <v>957</v>
-      </c>
-      <c r="G147" s="8" t="s">
-        <v>958</v>
-      </c>
-    </row>
-    <row r="148" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>404</v>
+      </c>
+      <c r="E147" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="F147" s="15" t="s">
+        <v>929</v>
+      </c>
+      <c r="G147" s="15" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A148" s="1">
         <v>147</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="E148" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="F148" s="6" t="s">
-        <v>959</v>
-      </c>
-      <c r="G148" s="8" t="s">
-        <v>960</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>404</v>
+      </c>
+      <c r="E148" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="F148" s="15" t="s">
+        <v>931</v>
+      </c>
+      <c r="G148" s="15" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A149" s="1">
         <v>148</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="E149" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="F149" s="6" t="s">
-        <v>961</v>
-      </c>
-      <c r="G149" s="8" t="s">
-        <v>962</v>
-      </c>
-    </row>
-    <row r="150" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>404</v>
+      </c>
+      <c r="E149" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="F149" s="15" t="s">
+        <v>933</v>
+      </c>
+      <c r="G149" s="15" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A150" s="1">
         <v>149</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="E150" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="F150" s="6" t="s">
-        <v>963</v>
-      </c>
-      <c r="G150" s="8" t="s">
-        <v>964</v>
-      </c>
-    </row>
-    <row r="151" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>404</v>
+      </c>
+      <c r="E150" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="F150" s="15" t="s">
+        <v>935</v>
+      </c>
+      <c r="G150" s="15" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A151" s="1">
         <v>150</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="E151" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="F151" s="6" t="s">
-        <v>965</v>
-      </c>
-      <c r="G151" s="8" t="s">
-        <v>966</v>
-      </c>
-    </row>
-    <row r="152" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>404</v>
+      </c>
+      <c r="E151" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="F151" s="15" t="s">
+        <v>937</v>
+      </c>
+      <c r="G151" s="15" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A152" s="1">
         <v>151</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="E152" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="F152" s="6" t="s">
-        <v>967</v>
-      </c>
-      <c r="G152" s="8" t="s">
-        <v>968</v>
+        <v>404</v>
+      </c>
+      <c r="E152" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="F152" s="11" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G152" s="11" t="s">
+        <v>1320</v>
       </c>
     </row>
     <row r="153" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8137,22 +8197,22 @@
         <v>152</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E153" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F153" s="6" t="s">
-        <v>969</v>
-      </c>
-      <c r="G153" s="8" t="s">
-        <v>970</v>
+      <c r="F153" s="13" t="s">
+        <v>939</v>
+      </c>
+      <c r="G153" s="14" t="s">
+        <v>940</v>
       </c>
     </row>
     <row r="154" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8160,22 +8220,22 @@
         <v>153</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E154" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F154" s="6" t="s">
-        <v>971</v>
+        <v>941</v>
       </c>
       <c r="G154" s="8" t="s">
-        <v>972</v>
+        <v>942</v>
       </c>
     </row>
     <row r="155" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8183,22 +8243,22 @@
         <v>154</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E155" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F155" s="6" t="s">
-        <v>973</v>
+        <v>943</v>
       </c>
       <c r="G155" s="8" t="s">
-        <v>974</v>
+        <v>944</v>
       </c>
     </row>
     <row r="156" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8206,22 +8266,22 @@
         <v>155</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E156" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F156" s="6" t="s">
-        <v>975</v>
+        <v>945</v>
       </c>
       <c r="G156" s="8" t="s">
-        <v>976</v>
+        <v>946</v>
       </c>
     </row>
     <row r="157" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8229,22 +8289,22 @@
         <v>156</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E157" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F157" s="6" t="s">
-        <v>977</v>
-      </c>
-      <c r="G157" s="8" t="s">
-        <v>978</v>
+      <c r="F157" s="12" t="s">
+        <v>1323</v>
+      </c>
+      <c r="G157" s="12" t="s">
+        <v>1324</v>
       </c>
     </row>
     <row r="158" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8252,22 +8312,22 @@
         <v>157</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E158" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F158" s="6" t="s">
-        <v>979</v>
+        <v>947</v>
       </c>
       <c r="G158" s="8" t="s">
-        <v>980</v>
+        <v>948</v>
       </c>
     </row>
     <row r="159" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8275,22 +8335,22 @@
         <v>158</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E159" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F159" s="6" t="s">
-        <v>981</v>
+        <v>949</v>
       </c>
       <c r="G159" s="8" t="s">
-        <v>982</v>
+        <v>950</v>
       </c>
     </row>
     <row r="160" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8298,22 +8358,22 @@
         <v>159</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E160" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F160" s="12" t="s">
-        <v>1341</v>
+        <v>1309</v>
       </c>
       <c r="G160" s="12" t="s">
-        <v>1342</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="161" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8321,22 +8381,22 @@
         <v>160</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E161" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F161" s="6" t="s">
-        <v>983</v>
+        <v>951</v>
       </c>
       <c r="G161" s="8" t="s">
-        <v>984</v>
+        <v>952</v>
       </c>
     </row>
     <row r="162" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8344,22 +8404,22 @@
         <v>161</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E162" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F162" s="6" t="s">
-        <v>985</v>
+        <v>953</v>
       </c>
       <c r="G162" s="8" t="s">
-        <v>986</v>
+        <v>954</v>
       </c>
     </row>
     <row r="163" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8367,22 +8427,22 @@
         <v>162</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E163" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F163" s="6" t="s">
-        <v>987</v>
+        <v>955</v>
       </c>
       <c r="G163" s="8" t="s">
-        <v>988</v>
+        <v>956</v>
       </c>
     </row>
     <row r="164" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8390,22 +8450,22 @@
         <v>163</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E164" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F164" s="6" t="s">
-        <v>989</v>
+        <v>957</v>
       </c>
       <c r="G164" s="8" t="s">
-        <v>990</v>
+        <v>958</v>
       </c>
     </row>
     <row r="165" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8413,22 +8473,22 @@
         <v>164</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E165" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F165" s="6" t="s">
-        <v>991</v>
+        <v>959</v>
       </c>
       <c r="G165" s="8" t="s">
-        <v>992</v>
+        <v>960</v>
       </c>
     </row>
     <row r="166" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8436,22 +8496,22 @@
         <v>165</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E166" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F166" s="6" t="s">
-        <v>993</v>
+        <v>961</v>
       </c>
       <c r="G166" s="8" t="s">
-        <v>994</v>
+        <v>962</v>
       </c>
     </row>
     <row r="167" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8459,22 +8519,22 @@
         <v>166</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E167" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F167" s="6" t="s">
-        <v>995</v>
+        <v>963</v>
       </c>
       <c r="G167" s="8" t="s">
-        <v>996</v>
+        <v>964</v>
       </c>
     </row>
     <row r="168" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8482,22 +8542,22 @@
         <v>167</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E168" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F168" s="6" t="s">
-        <v>997</v>
+        <v>965</v>
       </c>
       <c r="G168" s="8" t="s">
-        <v>998</v>
+        <v>966</v>
       </c>
     </row>
     <row r="169" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8505,22 +8565,22 @@
         <v>168</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E169" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F169" s="6" t="s">
-        <v>999</v>
+        <v>967</v>
       </c>
       <c r="G169" s="8" t="s">
-        <v>1000</v>
+        <v>968</v>
       </c>
     </row>
     <row r="170" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8528,22 +8588,22 @@
         <v>169</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E170" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F170" s="6" t="s">
-        <v>1001</v>
+        <v>969</v>
       </c>
       <c r="G170" s="8" t="s">
-        <v>1002</v>
+        <v>970</v>
       </c>
     </row>
     <row r="171" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8551,22 +8611,22 @@
         <v>170</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E171" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F171" s="6" t="s">
-        <v>1003</v>
+        <v>971</v>
       </c>
       <c r="G171" s="8" t="s">
-        <v>1004</v>
+        <v>972</v>
       </c>
     </row>
     <row r="172" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8574,22 +8634,22 @@
         <v>171</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E172" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F172" s="6" t="s">
-        <v>1005</v>
+        <v>973</v>
       </c>
       <c r="G172" s="8" t="s">
-        <v>1006</v>
+        <v>974</v>
       </c>
     </row>
     <row r="173" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8597,22 +8657,22 @@
         <v>172</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E173" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F173" s="6" t="s">
-        <v>1007</v>
+        <v>975</v>
       </c>
       <c r="G173" s="8" t="s">
-        <v>1008</v>
+        <v>976</v>
       </c>
     </row>
     <row r="174" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8620,22 +8680,22 @@
         <v>173</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E174" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F174" s="6" t="s">
-        <v>1009</v>
+        <v>977</v>
       </c>
       <c r="G174" s="8" t="s">
-        <v>1010</v>
+        <v>978</v>
       </c>
     </row>
     <row r="175" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8643,22 +8703,22 @@
         <v>174</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E175" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F175" s="6" t="s">
-        <v>1011</v>
+        <v>979</v>
       </c>
       <c r="G175" s="8" t="s">
-        <v>1012</v>
+        <v>980</v>
       </c>
     </row>
     <row r="176" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8666,22 +8726,22 @@
         <v>175</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E176" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F176" s="6" t="s">
-        <v>1013</v>
+        <v>981</v>
       </c>
       <c r="G176" s="8" t="s">
-        <v>1014</v>
+        <v>982</v>
       </c>
     </row>
     <row r="177" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8689,22 +8749,22 @@
         <v>176</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E177" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F177" s="6" t="s">
-        <v>1015</v>
+        <v>983</v>
       </c>
       <c r="G177" s="8" t="s">
-        <v>1016</v>
+        <v>984</v>
       </c>
     </row>
     <row r="178" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8712,22 +8772,22 @@
         <v>177</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E178" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F178" s="6" t="s">
-        <v>1017</v>
+        <v>985</v>
       </c>
       <c r="G178" s="8" t="s">
-        <v>1018</v>
+        <v>986</v>
       </c>
     </row>
     <row r="179" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8735,22 +8795,22 @@
         <v>178</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E179" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F179" s="6" t="s">
-        <v>1019</v>
+        <v>987</v>
       </c>
       <c r="G179" s="8" t="s">
-        <v>1020</v>
+        <v>988</v>
       </c>
     </row>
     <row r="180" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8758,22 +8818,22 @@
         <v>179</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E180" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F180" s="6" t="s">
-        <v>1021</v>
+        <v>989</v>
       </c>
       <c r="G180" s="8" t="s">
-        <v>1022</v>
+        <v>990</v>
       </c>
     </row>
     <row r="181" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8781,22 +8841,22 @@
         <v>180</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E181" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F181" s="6" t="s">
-        <v>1023</v>
+        <v>991</v>
       </c>
       <c r="G181" s="8" t="s">
-        <v>1024</v>
+        <v>992</v>
       </c>
     </row>
     <row r="182" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8804,22 +8864,22 @@
         <v>181</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E182" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F182" s="6" t="s">
-        <v>1025</v>
+        <v>993</v>
       </c>
       <c r="G182" s="8" t="s">
-        <v>1026</v>
+        <v>994</v>
       </c>
     </row>
     <row r="183" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8827,22 +8887,22 @@
         <v>182</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E183" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F183" s="6" t="s">
-        <v>1027</v>
+        <v>995</v>
       </c>
       <c r="G183" s="8" t="s">
-        <v>1028</v>
+        <v>996</v>
       </c>
     </row>
     <row r="184" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8850,22 +8910,22 @@
         <v>183</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E184" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F184" s="6" t="s">
-        <v>1029</v>
+        <v>997</v>
       </c>
       <c r="G184" s="8" t="s">
-        <v>1030</v>
+        <v>998</v>
       </c>
     </row>
     <row r="185" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8873,22 +8933,22 @@
         <v>184</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E185" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F185" s="6" t="s">
-        <v>1031</v>
+        <v>999</v>
       </c>
       <c r="G185" s="8" t="s">
-        <v>1032</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="186" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8896,22 +8956,22 @@
         <v>185</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E186" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F186" s="6" t="s">
-        <v>1033</v>
+        <v>1001</v>
       </c>
       <c r="G186" s="8" t="s">
-        <v>1034</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="187" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8919,22 +8979,22 @@
         <v>186</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E187" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F187" s="6" t="s">
-        <v>1035</v>
+        <v>1003</v>
       </c>
       <c r="G187" s="8" t="s">
-        <v>1036</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="188" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8942,22 +9002,22 @@
         <v>187</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E188" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F188" s="6" t="s">
-        <v>1037</v>
+        <v>1005</v>
       </c>
       <c r="G188" s="8" t="s">
-        <v>1038</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="189" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8965,22 +9025,22 @@
         <v>188</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E189" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F189" s="6" t="s">
-        <v>1039</v>
+        <v>1007</v>
       </c>
       <c r="G189" s="8" t="s">
-        <v>1040</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="190" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8988,22 +9048,22 @@
         <v>189</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E190" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F190" s="6" t="s">
-        <v>1041</v>
+        <v>1009</v>
       </c>
       <c r="G190" s="8" t="s">
-        <v>1042</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="191" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9011,22 +9071,22 @@
         <v>190</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E191" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F191" s="6" t="s">
-        <v>1043</v>
+        <v>1011</v>
       </c>
       <c r="G191" s="8" t="s">
-        <v>1044</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="192" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9034,22 +9094,22 @@
         <v>191</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E192" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F192" s="6" t="s">
-        <v>1045</v>
+        <v>1013</v>
       </c>
       <c r="G192" s="8" t="s">
-        <v>1046</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="193" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9057,22 +9117,22 @@
         <v>192</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E193" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F193" s="6" t="s">
-        <v>1047</v>
+        <v>1015</v>
       </c>
       <c r="G193" s="8" t="s">
-        <v>1048</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="194" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9080,22 +9140,22 @@
         <v>193</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E194" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F194" s="6" t="s">
-        <v>1049</v>
+        <v>1017</v>
       </c>
       <c r="G194" s="8" t="s">
-        <v>1050</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="195" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9103,22 +9163,22 @@
         <v>194</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E195" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F195" s="6" t="s">
-        <v>1051</v>
+        <v>1019</v>
       </c>
       <c r="G195" s="8" t="s">
-        <v>1052</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="196" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9126,22 +9186,22 @@
         <v>195</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E196" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F196" s="6" t="s">
-        <v>1053</v>
+        <v>1021</v>
       </c>
       <c r="G196" s="8" t="s">
-        <v>1054</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="197" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9149,22 +9209,22 @@
         <v>196</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E197" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F197" s="6" t="s">
-        <v>1055</v>
+        <v>1023</v>
       </c>
       <c r="G197" s="8" t="s">
-        <v>1056</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="198" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9172,22 +9232,22 @@
         <v>197</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E198" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F198" s="6" t="s">
-        <v>1057</v>
+        <v>1025</v>
       </c>
       <c r="G198" s="8" t="s">
-        <v>1058</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="199" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9195,22 +9255,22 @@
         <v>198</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E199" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F199" s="6" t="s">
-        <v>1059</v>
+        <v>1027</v>
       </c>
       <c r="G199" s="8" t="s">
-        <v>1060</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="200" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9218,22 +9278,22 @@
         <v>199</v>
       </c>
       <c r="B200" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="C200" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="D200" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="C200" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="D200" s="1" t="s">
-        <v>406</v>
-      </c>
       <c r="E200" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F200" s="6" t="s">
-        <v>1061</v>
+        <v>1029</v>
       </c>
       <c r="G200" s="8" t="s">
-        <v>1062</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="201" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9241,22 +9301,22 @@
         <v>200</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E201" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F201" s="6" t="s">
-        <v>1063</v>
+        <v>1031</v>
       </c>
       <c r="G201" s="8" t="s">
-        <v>1064</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="202" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9264,22 +9324,22 @@
         <v>201</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E202" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F202" s="6" t="s">
-        <v>1065</v>
+        <v>1033</v>
       </c>
       <c r="G202" s="8" t="s">
-        <v>1066</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="203" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9287,22 +9347,22 @@
         <v>202</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E203" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F203" s="6" t="s">
-        <v>1067</v>
+        <v>1035</v>
       </c>
       <c r="G203" s="8" t="s">
-        <v>1068</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="204" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9310,22 +9370,22 @@
         <v>203</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E204" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F204" s="6" t="s">
-        <v>1069</v>
+        <v>1037</v>
       </c>
       <c r="G204" s="8" t="s">
-        <v>1070</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="205" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9333,22 +9393,22 @@
         <v>204</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E205" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F205" s="6" t="s">
-        <v>1071</v>
+        <v>1039</v>
       </c>
       <c r="G205" s="8" t="s">
-        <v>1072</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="206" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9356,22 +9416,22 @@
         <v>205</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C206" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E206" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F206" s="6" t="s">
-        <v>1073</v>
+        <v>1041</v>
       </c>
       <c r="G206" s="8" t="s">
-        <v>1074</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="207" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9379,22 +9439,22 @@
         <v>206</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E207" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F207" s="6" t="s">
-        <v>1075</v>
+        <v>1043</v>
       </c>
       <c r="G207" s="8" t="s">
-        <v>1076</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="208" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9402,22 +9462,22 @@
         <v>207</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C208" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E208" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F208" s="6" t="s">
-        <v>1077</v>
+        <v>1045</v>
       </c>
       <c r="G208" s="8" t="s">
-        <v>1078</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="209" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9425,22 +9485,22 @@
         <v>208</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E209" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F209" s="6" t="s">
-        <v>1079</v>
+        <v>1047</v>
       </c>
       <c r="G209" s="8" t="s">
-        <v>1080</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="210" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9448,22 +9508,22 @@
         <v>209</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E210" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F210" s="6" t="s">
-        <v>1081</v>
+        <v>1049</v>
       </c>
       <c r="G210" s="8" t="s">
-        <v>1082</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="211" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9471,22 +9531,22 @@
         <v>210</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E211" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F211" s="6" t="s">
-        <v>1083</v>
+        <v>1051</v>
       </c>
       <c r="G211" s="8" t="s">
-        <v>1084</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="212" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9494,22 +9554,22 @@
         <v>211</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E212" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F212" s="6" t="s">
-        <v>1085</v>
+        <v>1053</v>
       </c>
       <c r="G212" s="8" t="s">
-        <v>1086</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="213" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9517,22 +9577,22 @@
         <v>212</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C213" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E213" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F213" s="6" t="s">
-        <v>1087</v>
+        <v>1055</v>
       </c>
       <c r="G213" s="8" t="s">
-        <v>1088</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="214" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9540,22 +9600,22 @@
         <v>213</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E214" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F214" s="6" t="s">
-        <v>1089</v>
+        <v>1057</v>
       </c>
       <c r="G214" s="8" t="s">
-        <v>1090</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="215" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9563,22 +9623,22 @@
         <v>214</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E215" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F215" s="6" t="s">
-        <v>1091</v>
+        <v>1059</v>
       </c>
       <c r="G215" s="8" t="s">
-        <v>1092</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="216" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9586,22 +9646,22 @@
         <v>215</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E216" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F216" s="6" t="s">
-        <v>1093</v>
+        <v>1061</v>
       </c>
       <c r="G216" s="8" t="s">
-        <v>1094</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="217" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9609,22 +9669,22 @@
         <v>216</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E217" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F217" s="6" t="s">
-        <v>1095</v>
+        <v>1063</v>
       </c>
       <c r="G217" s="8" t="s">
-        <v>1096</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="218" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9632,22 +9692,22 @@
         <v>217</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C218" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E218" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F218" s="6" t="s">
-        <v>1097</v>
+        <v>1065</v>
       </c>
       <c r="G218" s="8" t="s">
-        <v>1098</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.3">
@@ -9655,22 +9715,22 @@
         <v>218</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C219" s="1" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E219" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F219" s="9" t="s">
-        <v>1099</v>
+        <v>1067</v>
       </c>
       <c r="G219" s="10" t="s">
-        <v>1100</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.3">
@@ -9678,22 +9738,22 @@
         <v>219</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C220" s="1" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E220" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F220" s="11" t="s">
-        <v>1101</v>
+        <v>1069</v>
       </c>
       <c r="G220" s="11" t="s">
-        <v>1102</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.3">
@@ -9701,22 +9761,22 @@
         <v>220</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C221" s="1" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E221" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F221" s="11" t="s">
-        <v>1103</v>
+        <v>1071</v>
       </c>
       <c r="G221" s="11" t="s">
-        <v>1104</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.3">
@@ -9724,22 +9784,22 @@
         <v>221</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C222" s="1" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E222" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F222" s="11" t="s">
-        <v>1105</v>
+        <v>1073</v>
       </c>
       <c r="G222" s="11" t="s">
-        <v>1106</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.3">
@@ -9747,22 +9807,22 @@
         <v>222</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C223" s="1" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E223" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F223" s="11" t="s">
-        <v>1107</v>
+        <v>1075</v>
       </c>
       <c r="G223" s="11" t="s">
-        <v>1108</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.3">
@@ -9770,22 +9830,22 @@
         <v>223</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C224" s="1" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E224" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F224" s="11" t="s">
-        <v>1109</v>
+        <v>1077</v>
       </c>
       <c r="G224" s="11" t="s">
-        <v>1110</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.3">
@@ -9793,22 +9853,22 @@
         <v>224</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C225" s="1" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E225" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F225" s="11" t="s">
-        <v>1111</v>
+        <v>1079</v>
       </c>
       <c r="G225" s="11" t="s">
-        <v>1112</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.3">
@@ -9816,22 +9876,22 @@
         <v>225</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C226" s="1" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E226" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F226" s="11" t="s">
-        <v>1113</v>
+        <v>1081</v>
       </c>
       <c r="G226" s="11" t="s">
-        <v>1114</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.3">
@@ -9839,22 +9899,22 @@
         <v>226</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C227" s="1" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E227" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F227" s="11" t="s">
-        <v>1115</v>
+        <v>1083</v>
       </c>
       <c r="G227" s="11" t="s">
-        <v>1116</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.3">
@@ -9862,22 +9922,22 @@
         <v>227</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C228" s="1" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E228" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F228" s="11" t="s">
-        <v>1117</v>
+        <v>1085</v>
       </c>
       <c r="G228" s="11" t="s">
-        <v>1118</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.3">
@@ -9885,22 +9945,22 @@
         <v>228</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C229" s="1" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E229" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F229" s="11" t="s">
-        <v>1119</v>
+        <v>1087</v>
       </c>
       <c r="G229" s="11" t="s">
-        <v>1120</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.3">
@@ -9908,22 +9968,22 @@
         <v>229</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C230" s="1" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E230" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F230" s="11" t="s">
-        <v>1121</v>
+        <v>1089</v>
       </c>
       <c r="G230" s="11" t="s">
-        <v>1122</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.3">
@@ -9931,22 +9991,22 @@
         <v>230</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C231" s="1" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E231" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F231" s="11" t="s">
-        <v>1123</v>
+        <v>1091</v>
       </c>
       <c r="G231" s="11" t="s">
-        <v>1124</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.3">
@@ -9954,22 +10014,22 @@
         <v>231</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C232" s="1" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E232" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F232" s="11" t="s">
-        <v>1125</v>
+        <v>1093</v>
       </c>
       <c r="G232" s="11" t="s">
-        <v>1126</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.3">
@@ -9977,22 +10037,22 @@
         <v>232</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C233" s="1" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E233" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F233" s="11" t="s">
-        <v>1127</v>
+        <v>1095</v>
       </c>
       <c r="G233" s="11" t="s">
-        <v>1128</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.3">
@@ -10000,22 +10060,22 @@
         <v>233</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C234" s="1" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E234" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F234" s="11" t="s">
-        <v>1129</v>
+        <v>1097</v>
       </c>
       <c r="G234" s="11" t="s">
-        <v>1130</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.3">
@@ -10023,22 +10083,22 @@
         <v>234</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C235" s="1" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E235" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F235" s="11" t="s">
-        <v>1131</v>
+        <v>1099</v>
       </c>
       <c r="G235" s="11" t="s">
-        <v>1132</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.3">
@@ -10046,22 +10106,22 @@
         <v>235</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E236" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F236" s="11" t="s">
-        <v>1133</v>
+        <v>1101</v>
       </c>
       <c r="G236" s="11" t="s">
-        <v>1134</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.3">
@@ -10069,22 +10129,22 @@
         <v>236</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C237" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E237" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F237" s="11" t="s">
-        <v>1135</v>
+        <v>1103</v>
       </c>
       <c r="G237" s="11" t="s">
-        <v>1136</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.3">
@@ -10092,22 +10152,22 @@
         <v>237</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C238" s="1" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E238" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F238" s="11" t="s">
-        <v>1137</v>
+        <v>1105</v>
       </c>
       <c r="G238" s="11" t="s">
-        <v>1138</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.3">
@@ -10115,22 +10175,22 @@
         <v>238</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C239" s="1" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E239" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F239" s="11" t="s">
-        <v>1139</v>
+        <v>1107</v>
       </c>
       <c r="G239" s="11" t="s">
-        <v>1140</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.3">
@@ -10138,22 +10198,22 @@
         <v>239</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C240" s="1" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E240" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F240" s="11" t="s">
-        <v>1141</v>
+        <v>1109</v>
       </c>
       <c r="G240" s="11" t="s">
-        <v>1142</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.3">
@@ -10161,22 +10221,22 @@
         <v>240</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C241" s="1" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E241" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F241" s="11" t="s">
-        <v>1143</v>
+        <v>1111</v>
       </c>
       <c r="G241" s="11" t="s">
-        <v>1144</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.3">
@@ -10184,22 +10244,22 @@
         <v>241</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C242" s="1" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E242" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F242" s="11" t="s">
-        <v>1145</v>
+        <v>1113</v>
       </c>
       <c r="G242" s="11" t="s">
-        <v>1146</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.3">
@@ -10207,22 +10267,22 @@
         <v>242</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C243" s="1" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E243" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F243" s="11" t="s">
-        <v>1147</v>
+        <v>1115</v>
       </c>
       <c r="G243" s="11" t="s">
-        <v>1148</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.3">
@@ -10230,22 +10290,22 @@
         <v>243</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C244" s="1" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E244" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F244" s="11" t="s">
-        <v>1149</v>
+        <v>1117</v>
       </c>
       <c r="G244" s="11" t="s">
-        <v>1150</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.3">
@@ -10253,22 +10313,22 @@
         <v>244</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C245" s="1" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E245" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F245" s="11" t="s">
-        <v>1151</v>
+        <v>1119</v>
       </c>
       <c r="G245" s="11" t="s">
-        <v>1152</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.3">
@@ -10276,22 +10336,22 @@
         <v>245</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="C246" s="1" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E246" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F246" s="11" t="s">
-        <v>1153</v>
+        <v>1121</v>
       </c>
       <c r="G246" s="11" t="s">
-        <v>1154</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.3">
@@ -10299,22 +10359,22 @@
         <v>246</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C247" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E247" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F247" s="11" t="s">
-        <v>1155</v>
+        <v>1123</v>
       </c>
       <c r="G247" s="11" t="s">
-        <v>1156</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.3">
@@ -10322,22 +10382,22 @@
         <v>247</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C248" s="1" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E248" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F248" s="11" t="s">
-        <v>1157</v>
+        <v>1125</v>
       </c>
       <c r="G248" s="11" t="s">
-        <v>1158</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.3">
@@ -10345,22 +10405,22 @@
         <v>248</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C249" s="1" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E249" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F249" s="11" t="s">
-        <v>1159</v>
+        <v>1127</v>
       </c>
       <c r="G249" s="11" t="s">
-        <v>1160</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.3">
@@ -10368,22 +10428,22 @@
         <v>249</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C250" s="1" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E250" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F250" s="11" t="s">
-        <v>1161</v>
+        <v>1129</v>
       </c>
       <c r="G250" s="11" t="s">
-        <v>1162</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.3">
@@ -10391,22 +10451,22 @@
         <v>250</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C251" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E251" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F251" s="11" t="s">
-        <v>1163</v>
+        <v>1131</v>
       </c>
       <c r="G251" s="11" t="s">
-        <v>1164</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.3">
@@ -10414,22 +10474,22 @@
         <v>251</v>
       </c>
       <c r="B252" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="C252" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="D252" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="C252" s="1" t="s">
-        <v>510</v>
-      </c>
-      <c r="D252" s="1" t="s">
-        <v>511</v>
-      </c>
       <c r="E252" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F252" s="11" t="s">
-        <v>1165</v>
+        <v>1133</v>
       </c>
       <c r="G252" s="11" t="s">
-        <v>1166</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.3">
@@ -10437,22 +10497,22 @@
         <v>252</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C253" s="1" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="E253" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F253" s="11" t="s">
-        <v>1167</v>
+        <v>1135</v>
       </c>
       <c r="G253" s="11" t="s">
-        <v>1168</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.3">
@@ -10460,22 +10520,22 @@
         <v>253</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="C254" s="1" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="E254" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F254" s="11" t="s">
-        <v>1169</v>
+        <v>1137</v>
       </c>
       <c r="G254" s="11" t="s">
-        <v>1170</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.3">
@@ -10483,22 +10543,22 @@
         <v>254</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="C255" s="1" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="E255" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F255" s="11" t="s">
-        <v>1171</v>
+        <v>1139</v>
       </c>
       <c r="G255" s="11" t="s">
-        <v>1172</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.3">
@@ -10506,22 +10566,22 @@
         <v>255</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="C256" s="1" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="E256" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F256" s="11" t="s">
-        <v>1173</v>
+        <v>1141</v>
       </c>
       <c r="G256" s="11" t="s">
-        <v>1174</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.3">
@@ -10529,22 +10589,22 @@
         <v>256</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="E257" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F257" s="11" t="s">
-        <v>1175</v>
+        <v>1143</v>
       </c>
       <c r="G257" s="11" t="s">
-        <v>1176</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.3">
@@ -10552,22 +10612,22 @@
         <v>257</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="E258" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F258" s="11" t="s">
-        <v>1177</v>
+        <v>1145</v>
       </c>
       <c r="G258" s="11" t="s">
-        <v>1178</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.3">
@@ -10575,22 +10635,22 @@
         <v>258</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C259" s="1" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="E259" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F259" s="11" t="s">
-        <v>1179</v>
+        <v>1147</v>
       </c>
       <c r="G259" s="11" t="s">
-        <v>1180</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.3">
@@ -10598,22 +10658,22 @@
         <v>259</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C260" s="1" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="E260" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F260" s="11" t="s">
-        <v>1181</v>
+        <v>1149</v>
       </c>
       <c r="G260" s="11" t="s">
-        <v>1182</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.3">
@@ -10621,22 +10681,22 @@
         <v>260</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="C261" s="1" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="E261" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F261" s="11" t="s">
-        <v>1183</v>
+        <v>1151</v>
       </c>
       <c r="G261" s="11" t="s">
-        <v>1184</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.3">
@@ -10644,22 +10704,22 @@
         <v>261</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C262" s="1" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="E262" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F262" s="11" t="s">
-        <v>1185</v>
+        <v>1153</v>
       </c>
       <c r="G262" s="11" t="s">
-        <v>1186</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.3">
@@ -10667,22 +10727,22 @@
         <v>262</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C263" s="1" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="E263" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F263" s="11" t="s">
-        <v>1187</v>
+        <v>1155</v>
       </c>
       <c r="G263" s="11" t="s">
-        <v>1188</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.3">
@@ -10690,22 +10750,22 @@
         <v>263</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="C264" s="1" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="E264" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F264" s="11" t="s">
-        <v>1189</v>
+        <v>1157</v>
       </c>
       <c r="G264" s="11" t="s">
-        <v>1190</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.3">
@@ -10713,22 +10773,22 @@
         <v>264</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="C265" s="1" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="E265" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F265" s="11" t="s">
-        <v>1191</v>
+        <v>1159</v>
       </c>
       <c r="G265" s="11" t="s">
-        <v>1192</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.3">
@@ -10736,22 +10796,22 @@
         <v>265</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="C266" s="1" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="E266" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F266" s="11" t="s">
-        <v>1193</v>
+        <v>1161</v>
       </c>
       <c r="G266" s="11" t="s">
-        <v>1194</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.3">
@@ -10759,22 +10819,22 @@
         <v>266</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="C267" s="1" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="E267" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F267" s="11" t="s">
-        <v>1195</v>
+        <v>1163</v>
       </c>
       <c r="G267" s="11" t="s">
-        <v>1196</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.3">
@@ -10782,22 +10842,22 @@
         <v>267</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="C268" s="1" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="E268" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F268" s="11" t="s">
-        <v>1197</v>
+        <v>1165</v>
       </c>
       <c r="G268" s="11" t="s">
-        <v>1198</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.3">
@@ -10805,22 +10865,22 @@
         <v>268</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="E269" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F269" s="11" t="s">
-        <v>1199</v>
+        <v>1167</v>
       </c>
       <c r="G269" s="11" t="s">
-        <v>1200</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.3">
@@ -10828,22 +10888,22 @@
         <v>269</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="E270" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F270" s="11" t="s">
-        <v>1201</v>
+        <v>1169</v>
       </c>
       <c r="G270" s="11" t="s">
-        <v>1202</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.3">
@@ -10851,22 +10911,22 @@
         <v>270</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="E271" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F271" s="11" t="s">
-        <v>1203</v>
+        <v>1171</v>
       </c>
       <c r="G271" s="11" t="s">
-        <v>1204</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.3">
@@ -10874,22 +10934,22 @@
         <v>271</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="E272" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F272" s="11" t="s">
-        <v>1205</v>
+        <v>1173</v>
       </c>
       <c r="G272" s="11" t="s">
-        <v>1206</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.3">
@@ -10897,22 +10957,22 @@
         <v>272</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="C273" s="1" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="E273" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F273" s="11" t="s">
-        <v>1207</v>
+        <v>1175</v>
       </c>
       <c r="G273" s="11" t="s">
-        <v>1208</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.3">
@@ -10920,22 +10980,22 @@
         <v>273</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="C274" s="1" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="E274" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F274" s="11" t="s">
-        <v>1209</v>
+        <v>1177</v>
       </c>
       <c r="G274" s="11" t="s">
-        <v>1210</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.3">
@@ -10943,22 +11003,22 @@
         <v>274</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C275" s="1" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="E275" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F275" s="11" t="s">
-        <v>1211</v>
+        <v>1179</v>
       </c>
       <c r="G275" s="11" t="s">
-        <v>1212</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.3">
@@ -10966,22 +11026,22 @@
         <v>275</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="C276" s="1" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="E276" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F276" s="11" t="s">
-        <v>1213</v>
+        <v>1181</v>
       </c>
       <c r="G276" s="11" t="s">
-        <v>1214</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.3">
@@ -10989,22 +11049,22 @@
         <v>276</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="C277" s="1" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="E277" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F277" s="11" t="s">
-        <v>1215</v>
+        <v>1183</v>
       </c>
       <c r="G277" s="11" t="s">
-        <v>1216</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.3">
@@ -11012,22 +11072,22 @@
         <v>277</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="C278" s="1" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="E278" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F278" s="11" t="s">
-        <v>1217</v>
+        <v>1185</v>
       </c>
       <c r="G278" s="11" t="s">
-        <v>1218</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="279" spans="1:7" x14ac:dyDescent="0.3">
@@ -11035,22 +11095,22 @@
         <v>278</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="C279" s="1" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="E279" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F279" s="11" t="s">
-        <v>1219</v>
+        <v>1187</v>
       </c>
       <c r="G279" s="11" t="s">
-        <v>1220</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="280" spans="1:7" x14ac:dyDescent="0.3">
@@ -11058,22 +11118,22 @@
         <v>279</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="C280" s="1" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="E280" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F280" s="11" t="s">
-        <v>1221</v>
+        <v>1189</v>
       </c>
       <c r="G280" s="11" t="s">
-        <v>1222</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.3">
@@ -11081,22 +11141,22 @@
         <v>280</v>
       </c>
       <c r="B281" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="C281" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="D281" s="1" t="s">
         <v>568</v>
       </c>
-      <c r="C281" s="1" t="s">
-        <v>569</v>
-      </c>
-      <c r="D281" s="1" t="s">
-        <v>570</v>
-      </c>
       <c r="E281" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F281" s="11" t="s">
-        <v>1223</v>
+        <v>1191</v>
       </c>
       <c r="G281" s="11" t="s">
-        <v>1224</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.3">
@@ -11104,22 +11164,22 @@
         <v>281</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C282" s="1" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="E282" s="4" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="F282" s="11" t="s">
-        <v>1225</v>
+        <v>1193</v>
       </c>
       <c r="G282" s="11" t="s">
-        <v>1226</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.3">
@@ -11127,22 +11187,22 @@
         <v>282</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="C283" s="1" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="E283" s="4" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="F283" s="11" t="s">
-        <v>1227</v>
+        <v>1195</v>
       </c>
       <c r="G283" s="11" t="s">
-        <v>1228</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.3">
@@ -11150,22 +11210,22 @@
         <v>283</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="C284" s="1" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="E284" s="4" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="F284" s="11" t="s">
-        <v>1229</v>
+        <v>1197</v>
       </c>
       <c r="G284" s="11" t="s">
-        <v>1230</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.3">
@@ -11173,22 +11233,22 @@
         <v>284</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="C285" s="1" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="E285" s="4" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="F285" s="11" t="s">
-        <v>1231</v>
+        <v>1199</v>
       </c>
       <c r="G285" s="11" t="s">
-        <v>1232</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.3">
@@ -11196,22 +11256,22 @@
         <v>285</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C286" s="1" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="E286" s="4" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="F286" s="11" t="s">
-        <v>1233</v>
+        <v>1201</v>
       </c>
       <c r="G286" s="11" t="s">
-        <v>1234</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.3">
@@ -11219,22 +11279,22 @@
         <v>286</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C287" s="1" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="E287" s="4" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="F287" s="11" t="s">
-        <v>1235</v>
+        <v>1203</v>
       </c>
       <c r="G287" s="11" t="s">
-        <v>1236</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.3">
@@ -11242,22 +11302,22 @@
         <v>287</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="C288" s="1" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="E288" s="4" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="F288" s="11" t="s">
-        <v>1237</v>
+        <v>1205</v>
       </c>
       <c r="G288" s="11" t="s">
-        <v>1238</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.3">
@@ -11265,22 +11325,22 @@
         <v>288</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="C289" s="1" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="E289" s="4" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="F289" s="11" t="s">
-        <v>1239</v>
+        <v>1207</v>
       </c>
       <c r="G289" s="11" t="s">
-        <v>1240</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.3">
@@ -11288,22 +11348,22 @@
         <v>289</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="C290" s="1" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="E290" s="4" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="F290" s="11" t="s">
-        <v>1241</v>
+        <v>1209</v>
       </c>
       <c r="G290" s="11" t="s">
-        <v>1242</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.3">
@@ -11311,22 +11371,22 @@
         <v>290</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="C291" s="1" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="E291" s="4" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="F291" s="11" t="s">
-        <v>1243</v>
+        <v>1211</v>
       </c>
       <c r="G291" s="11" t="s">
-        <v>1244</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.3">
@@ -11334,22 +11394,22 @@
         <v>291</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="C292" s="1" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="E292" s="4" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="F292" s="11" t="s">
-        <v>1245</v>
+        <v>1213</v>
       </c>
       <c r="G292" s="11" t="s">
-        <v>1246</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.3">
@@ -11357,22 +11417,22 @@
         <v>292</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="C293" s="1" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="E293" s="4" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="F293" s="11" t="s">
-        <v>1247</v>
+        <v>1215</v>
       </c>
       <c r="G293" s="11" t="s">
-        <v>1248</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.3">
@@ -11380,22 +11440,22 @@
         <v>293</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="C294" s="1" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="E294" s="4" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="F294" s="11" t="s">
-        <v>1249</v>
+        <v>1217</v>
       </c>
       <c r="G294" s="11" t="s">
-        <v>1250</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.3">
@@ -11403,22 +11463,22 @@
         <v>294</v>
       </c>
       <c r="B295" s="1" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="C295" s="1" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="E295" s="4" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="F295" s="11" t="s">
-        <v>1251</v>
+        <v>1219</v>
       </c>
       <c r="G295" s="11" t="s">
-        <v>1252</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.3">
@@ -11426,22 +11486,22 @@
         <v>295</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="C296" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="D296" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="E296" s="4" t="s">
         <v>601</v>
       </c>
-      <c r="D296" s="1" t="s">
-        <v>570</v>
-      </c>
-      <c r="E296" s="4" t="s">
-        <v>603</v>
-      </c>
       <c r="F296" s="11" t="s">
-        <v>1253</v>
+        <v>1221</v>
       </c>
       <c r="G296" s="11" t="s">
-        <v>1254</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.3">
@@ -11449,22 +11509,22 @@
         <v>296</v>
       </c>
       <c r="B297" s="1" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="C297" s="1" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="E297" s="4" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="F297" s="11" t="s">
-        <v>1255</v>
+        <v>1223</v>
       </c>
       <c r="G297" s="11" t="s">
-        <v>1256</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.3">
@@ -11472,22 +11532,22 @@
         <v>297</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="C298" s="1" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E298" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F298" s="11" t="s">
-        <v>1257</v>
+        <v>1225</v>
       </c>
       <c r="G298" s="11" t="s">
-        <v>1258</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="299" spans="1:7" x14ac:dyDescent="0.3">
@@ -11495,22 +11555,22 @@
         <v>298</v>
       </c>
       <c r="B299" s="1" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="C299" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E299" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F299" s="11" t="s">
-        <v>1259</v>
+        <v>1227</v>
       </c>
       <c r="G299" s="11" t="s">
-        <v>1260</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.3">
@@ -11518,22 +11578,22 @@
         <v>299</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C300" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E300" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F300" s="11" t="s">
-        <v>1261</v>
+        <v>1229</v>
       </c>
       <c r="G300" s="11" t="s">
-        <v>1262</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.3">
@@ -11541,22 +11601,22 @@
         <v>300</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="C301" s="1" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E301" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F301" s="11" t="s">
-        <v>1263</v>
+        <v>1231</v>
       </c>
       <c r="G301" s="11" t="s">
-        <v>1264</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="302" spans="1:7" x14ac:dyDescent="0.3">
@@ -11564,22 +11624,22 @@
         <v>301</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="C302" s="1" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E302" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F302" s="11" t="s">
-        <v>1265</v>
+        <v>1233</v>
       </c>
       <c r="G302" s="11" t="s">
-        <v>1266</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="303" spans="1:7" x14ac:dyDescent="0.3">
@@ -11587,22 +11647,22 @@
         <v>302</v>
       </c>
       <c r="B303" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="C303" s="1" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E303" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F303" s="11" t="s">
-        <v>1267</v>
+        <v>1235</v>
       </c>
       <c r="G303" s="11" t="s">
-        <v>1268</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="304" spans="1:7" x14ac:dyDescent="0.3">
@@ -11610,22 +11670,22 @@
         <v>303</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="C304" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E304" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F304" s="11" t="s">
-        <v>1269</v>
+        <v>1237</v>
       </c>
       <c r="G304" s="11" t="s">
-        <v>1270</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="305" spans="1:7" x14ac:dyDescent="0.3">
@@ -11633,22 +11693,22 @@
         <v>304</v>
       </c>
       <c r="B305" s="1" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="C305" s="1" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E305" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F305" s="11" t="s">
-        <v>1271</v>
+        <v>1239</v>
       </c>
       <c r="G305" s="11" t="s">
-        <v>1272</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="306" spans="1:7" x14ac:dyDescent="0.3">
@@ -11656,22 +11716,22 @@
         <v>305</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="C306" s="1" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E306" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F306" s="11" t="s">
-        <v>1273</v>
+        <v>1241</v>
       </c>
       <c r="G306" s="11" t="s">
-        <v>1274</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="307" spans="1:7" x14ac:dyDescent="0.3">
@@ -11679,22 +11739,22 @@
         <v>306</v>
       </c>
       <c r="B307" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="C307" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="D307" s="1" t="s">
         <v>622</v>
       </c>
-      <c r="C307" s="1" t="s">
-        <v>623</v>
-      </c>
-      <c r="D307" s="1" t="s">
-        <v>624</v>
-      </c>
       <c r="E307" s="4" t="s">
         <v>138</v>
       </c>
       <c r="F307" s="11" t="s">
-        <v>1275</v>
+        <v>1243</v>
       </c>
       <c r="G307" s="11" t="s">
-        <v>1276</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="308" spans="1:7" x14ac:dyDescent="0.3">
@@ -11702,22 +11762,22 @@
         <v>307</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="C308" s="1" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E308" s="4" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="F308" s="11" t="s">
-        <v>1277</v>
+        <v>1245</v>
       </c>
       <c r="G308" s="11" t="s">
-        <v>1278</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="309" spans="1:7" x14ac:dyDescent="0.3">
@@ -11725,22 +11785,22 @@
         <v>308</v>
       </c>
       <c r="B309" s="1" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="C309" s="1" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E309" s="4" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="F309" s="11" t="s">
-        <v>1279</v>
+        <v>1247</v>
       </c>
       <c r="G309" s="11" t="s">
-        <v>1280</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="310" spans="1:7" x14ac:dyDescent="0.3">
@@ -11748,22 +11808,22 @@
         <v>309</v>
       </c>
       <c r="B310" s="1" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="C310" s="1" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E310" s="4" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="F310" s="11" t="s">
-        <v>1281</v>
+        <v>1249</v>
       </c>
       <c r="G310" s="11" t="s">
-        <v>1282</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="311" spans="1:7" x14ac:dyDescent="0.3">
@@ -11771,22 +11831,22 @@
         <v>310</v>
       </c>
       <c r="B311" s="1" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="C311" s="1" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E311" s="4" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="F311" s="11" t="s">
-        <v>1283</v>
+        <v>1251</v>
       </c>
       <c r="G311" s="11" t="s">
-        <v>1284</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="312" spans="1:7" x14ac:dyDescent="0.3">
@@ -11794,22 +11854,22 @@
         <v>311</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="C312" s="1" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="D312" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E312" s="4" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="F312" s="11" t="s">
-        <v>1285</v>
+        <v>1253</v>
       </c>
       <c r="G312" s="11" t="s">
-        <v>1286</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="313" spans="1:7" x14ac:dyDescent="0.3">
@@ -11817,22 +11877,22 @@
         <v>312</v>
       </c>
       <c r="B313" s="1" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="C313" s="1" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E313" s="4" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="F313" s="11" t="s">
-        <v>1287</v>
+        <v>1255</v>
       </c>
       <c r="G313" s="11" t="s">
-        <v>1288</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="314" spans="1:7" x14ac:dyDescent="0.3">
@@ -11840,22 +11900,22 @@
         <v>313</v>
       </c>
       <c r="B314" s="1" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="C314" s="1" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E314" s="4" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="F314" s="11" t="s">
-        <v>1289</v>
+        <v>1257</v>
       </c>
       <c r="G314" s="11" t="s">
-        <v>1290</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="315" spans="1:7" x14ac:dyDescent="0.3">
@@ -11863,22 +11923,22 @@
         <v>314</v>
       </c>
       <c r="B315" s="1" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="C315" s="1" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E315" s="4" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="F315" s="11" t="s">
-        <v>1291</v>
+        <v>1259</v>
       </c>
       <c r="G315" s="11" t="s">
-        <v>1292</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="316" spans="1:7" x14ac:dyDescent="0.3">
@@ -11886,22 +11946,22 @@
         <v>315</v>
       </c>
       <c r="B316" s="1" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="C316" s="1" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="D316" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E316" s="4" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="F316" s="11" t="s">
-        <v>1293</v>
+        <v>1261</v>
       </c>
       <c r="G316" s="11" t="s">
-        <v>1294</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="317" spans="1:7" x14ac:dyDescent="0.3">
@@ -11909,22 +11969,22 @@
         <v>316</v>
       </c>
       <c r="B317" s="1" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C317" s="1" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E317" s="4" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="F317" s="11" t="s">
-        <v>1295</v>
+        <v>1263</v>
       </c>
       <c r="G317" s="11" t="s">
-        <v>1296</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="318" spans="1:7" x14ac:dyDescent="0.3">
@@ -11932,22 +11992,22 @@
         <v>317</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C318" s="1" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="D318" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E318" s="4" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="F318" s="11" t="s">
-        <v>1297</v>
+        <v>1265</v>
       </c>
       <c r="G318" s="11" t="s">
-        <v>1298</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="319" spans="1:7" x14ac:dyDescent="0.3">
@@ -11955,22 +12015,22 @@
         <v>318</v>
       </c>
       <c r="B319" s="1" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="C319" s="1" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E319" s="4" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="F319" s="11" t="s">
-        <v>1299</v>
+        <v>1267</v>
       </c>
       <c r="G319" s="11" t="s">
-        <v>1300</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="320" spans="1:7" x14ac:dyDescent="0.3">
@@ -11978,22 +12038,22 @@
         <v>319</v>
       </c>
       <c r="B320" s="1" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="C320" s="1" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E320" s="4" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="F320" s="11" t="s">
-        <v>1301</v>
+        <v>1269</v>
       </c>
       <c r="G320" s="11" t="s">
-        <v>1302</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="321" spans="1:7" x14ac:dyDescent="0.3">
@@ -12001,22 +12061,22 @@
         <v>320</v>
       </c>
       <c r="B321" s="1" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="C321" s="1" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="D321" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E321" s="4" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="F321" s="11" t="s">
-        <v>1303</v>
+        <v>1271</v>
       </c>
       <c r="G321" s="11" t="s">
-        <v>1304</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="322" spans="1:7" x14ac:dyDescent="0.3">
@@ -12024,22 +12084,22 @@
         <v>321</v>
       </c>
       <c r="B322" s="1" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="C322" s="1" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="D322" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E322" s="4" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="F322" s="11" t="s">
-        <v>1305</v>
+        <v>1273</v>
       </c>
       <c r="G322" s="11" t="s">
-        <v>1306</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="323" spans="1:7" x14ac:dyDescent="0.3">
@@ -12047,22 +12107,22 @@
         <v>322</v>
       </c>
       <c r="B323" s="1" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="C323" s="1" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E323" s="4" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="F323" s="11" t="s">
-        <v>1307</v>
+        <v>1275</v>
       </c>
       <c r="G323" s="11" t="s">
-        <v>1308</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="324" spans="1:7" x14ac:dyDescent="0.3">
@@ -12070,22 +12130,22 @@
         <v>323</v>
       </c>
       <c r="B324" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="C324" s="1" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="D324" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E324" s="4" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="F324" s="11" t="s">
-        <v>1309</v>
+        <v>1277</v>
       </c>
       <c r="G324" s="11" t="s">
-        <v>1310</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="325" spans="1:7" x14ac:dyDescent="0.3">
@@ -12093,22 +12153,22 @@
         <v>324</v>
       </c>
       <c r="B325" s="1" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="C325" s="1" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="D325" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E325" s="4" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="F325" s="11" t="s">
-        <v>1311</v>
+        <v>1279</v>
       </c>
       <c r="G325" s="11" t="s">
-        <v>1312</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="326" spans="1:7" x14ac:dyDescent="0.3">
@@ -12116,22 +12176,22 @@
         <v>325</v>
       </c>
       <c r="B326" s="1" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C326" s="1" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E326" s="4" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="F326" s="11" t="s">
-        <v>1313</v>
+        <v>1281</v>
       </c>
       <c r="G326" s="11" t="s">
-        <v>1314</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="327" spans="1:7" x14ac:dyDescent="0.3">
@@ -12139,22 +12199,22 @@
         <v>326</v>
       </c>
       <c r="B327" s="1" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="C327" s="1" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="D327" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E327" s="4" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="F327" s="11" t="s">
-        <v>1315</v>
+        <v>1283</v>
       </c>
       <c r="G327" s="11" t="s">
-        <v>1316</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="328" spans="1:7" x14ac:dyDescent="0.3">
@@ -12162,22 +12222,22 @@
         <v>327</v>
       </c>
       <c r="B328" s="1" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C328" s="1" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="D328" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E328" s="4" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="F328" s="11" t="s">
-        <v>1317</v>
+        <v>1285</v>
       </c>
       <c r="G328" s="11" t="s">
-        <v>1318</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="329" spans="1:7" x14ac:dyDescent="0.3">
@@ -12185,22 +12245,22 @@
         <v>328</v>
       </c>
       <c r="B329" s="1" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="C329" s="1" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="D329" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E329" s="4" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="F329" s="11" t="s">
-        <v>1319</v>
+        <v>1287</v>
       </c>
       <c r="G329" s="11" t="s">
-        <v>1320</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="330" spans="1:7" x14ac:dyDescent="0.3">
@@ -12208,22 +12268,22 @@
         <v>329</v>
       </c>
       <c r="B330" s="1" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="C330" s="1" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E330" s="4" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="F330" s="11" t="s">
-        <v>1321</v>
+        <v>1289</v>
       </c>
       <c r="G330" s="11" t="s">
-        <v>1322</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="331" spans="1:7" x14ac:dyDescent="0.3">
@@ -12231,22 +12291,22 @@
         <v>330</v>
       </c>
       <c r="B331" s="1" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C331" s="1" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E331" s="4" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="F331" s="11" t="s">
-        <v>1323</v>
+        <v>1291</v>
       </c>
       <c r="G331" s="11" t="s">
-        <v>1324</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="332" spans="1:7" x14ac:dyDescent="0.3">
@@ -12254,22 +12314,22 @@
         <v>331</v>
       </c>
       <c r="B332" s="1" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="C332" s="1" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E332" s="4" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="F332" s="11" t="s">
-        <v>1325</v>
+        <v>1293</v>
       </c>
       <c r="G332" s="11" t="s">
-        <v>1326</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="333" spans="1:7" x14ac:dyDescent="0.3">
@@ -12277,22 +12337,22 @@
         <v>332</v>
       </c>
       <c r="B333" s="1" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C333" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D333" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E333" s="4" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="F333" s="11" t="s">
-        <v>1327</v>
+        <v>1295</v>
       </c>
       <c r="G333" s="11" t="s">
-        <v>1328</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="334" spans="1:7" x14ac:dyDescent="0.3">
@@ -12300,22 +12360,22 @@
         <v>333</v>
       </c>
       <c r="B334" s="1" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="C334" s="1" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="D334" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E334" s="4" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="F334" s="11" t="s">
-        <v>1329</v>
+        <v>1297</v>
       </c>
       <c r="G334" s="11" t="s">
-        <v>1330</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="335" spans="1:7" x14ac:dyDescent="0.3">
@@ -12323,25 +12383,28 @@
         <v>334</v>
       </c>
       <c r="B335" s="1" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C335" s="1" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="D335" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E335" s="4" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="F335" s="11" t="s">
-        <v>1331</v>
+        <v>1299</v>
       </c>
       <c r="G335" s="11" t="s">
-        <v>1332</v>
+        <v>1300</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C70" r:id="rId1" xr:uid="{7898F87A-3AB3-4640-9D84-7651653723F2}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/files/Adhiparasakthi Students Data 1.xlsx
+++ b/files/Adhiparasakthi Students Data 1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vigne\Google_Backup\Github\sb4c\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E42DE63E-E73B-423E-9195-E867206429ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD490F28-3535-4073-904A-E89555E29F50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E3F0EEA9-6BAE-46A1-95E3-E9CE509FC50B}"/>
   </bookViews>
@@ -2625,12 +2625,6 @@
     <t>Edu#970864</t>
   </si>
   <si>
-    <t>EFIBM26927896787@edunetmail.com</t>
-  </si>
-  <si>
-    <t>Edu#666852</t>
-  </si>
-  <si>
     <t>EFIBM26220428119@edunetmail.com</t>
   </si>
   <si>
@@ -4084,6 +4078,12 @@
   </si>
   <si>
     <t>Edu#495569</t>
+  </si>
+  <si>
+    <t>EFIBM26239586755@edunetmail.com</t>
+  </si>
+  <si>
+    <t>Edu#289354</t>
   </si>
 </sst>
 </file>
@@ -6257,10 +6257,10 @@
         <v>138</v>
       </c>
       <c r="F68" s="12" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="G68" s="12" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6294,7 +6294,7 @@
         <v>141</v>
       </c>
       <c r="C70" s="16" t="s">
-        <v>1337</v>
+        <v>1335</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>188</v>
@@ -6303,10 +6303,10 @@
         <v>138</v>
       </c>
       <c r="F70" s="12" t="s">
-        <v>1335</v>
+        <v>1333</v>
       </c>
       <c r="G70" s="12" t="s">
-        <v>1336</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6510,10 +6510,10 @@
         <v>138</v>
       </c>
       <c r="F79" s="12" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
       <c r="G79" s="12" t="s">
-        <v>1334</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
@@ -6556,10 +6556,10 @@
         <v>138</v>
       </c>
       <c r="F81" s="11" t="s">
-        <v>1325</v>
+        <v>1323</v>
       </c>
       <c r="G81" s="11" t="s">
-        <v>1326</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
@@ -6625,10 +6625,10 @@
         <v>138</v>
       </c>
       <c r="F84" s="11" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="G84" s="11" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
@@ -6648,10 +6648,10 @@
         <v>138</v>
       </c>
       <c r="F85" s="11" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="G85" s="11" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
@@ -6763,10 +6763,10 @@
         <v>138</v>
       </c>
       <c r="F90" s="11" t="s">
-        <v>1317</v>
+        <v>1315</v>
       </c>
       <c r="G90" s="11" t="s">
-        <v>1318</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
@@ -6992,11 +6992,11 @@
       <c r="E100" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F100" s="6" t="s">
-        <v>863</v>
-      </c>
-      <c r="G100" s="8" t="s">
-        <v>864</v>
+      <c r="F100" s="5" t="s">
+        <v>1348</v>
+      </c>
+      <c r="G100" s="7" t="s">
+        <v>1349</v>
       </c>
     </row>
     <row r="101" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7016,10 +7016,10 @@
         <v>138</v>
       </c>
       <c r="F101" s="6" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="G101" s="8" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
     </row>
     <row r="102" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7039,10 +7039,10 @@
         <v>138</v>
       </c>
       <c r="F102" s="6" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="G102" s="8" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
     </row>
     <row r="103" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7062,10 +7062,10 @@
         <v>138</v>
       </c>
       <c r="F103" s="6" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="G103" s="8" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
     </row>
     <row r="104" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7085,10 +7085,10 @@
         <v>138</v>
       </c>
       <c r="F104" s="6" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G104" s="8" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
     </row>
     <row r="105" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7108,10 +7108,10 @@
         <v>138</v>
       </c>
       <c r="F105" s="12" t="s">
-        <v>1340</v>
+        <v>1338</v>
       </c>
       <c r="G105" s="12" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="106" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7131,10 +7131,10 @@
         <v>138</v>
       </c>
       <c r="F106" s="6" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="G106" s="8" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
     </row>
     <row r="107" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7154,10 +7154,10 @@
         <v>138</v>
       </c>
       <c r="F107" s="5" t="s">
-        <v>1348</v>
+        <v>1346</v>
       </c>
       <c r="G107" s="7" t="s">
-        <v>1349</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="108" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7177,10 +7177,10 @@
         <v>138</v>
       </c>
       <c r="F108" s="6" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="G108" s="8" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
     </row>
     <row r="109" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7200,10 +7200,10 @@
         <v>138</v>
       </c>
       <c r="F109" s="6" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="G109" s="8" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
     </row>
     <row r="110" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7223,10 +7223,10 @@
         <v>138</v>
       </c>
       <c r="F110" s="6" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="G110" s="8" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
     </row>
     <row r="111" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7246,10 +7246,10 @@
         <v>138</v>
       </c>
       <c r="F111" s="6" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="G111" s="8" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
     </row>
     <row r="112" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7269,10 +7269,10 @@
         <v>138</v>
       </c>
       <c r="F112" s="17" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
       <c r="G112" s="17" t="s">
-        <v>1347</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="113" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7292,10 +7292,10 @@
         <v>138</v>
       </c>
       <c r="F113" s="6" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="G113" s="8" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
     </row>
     <row r="114" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7315,10 +7315,10 @@
         <v>138</v>
       </c>
       <c r="F114" s="12" t="s">
-        <v>1342</v>
+        <v>1340</v>
       </c>
       <c r="G114" s="12" t="s">
-        <v>1343</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="115" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7338,10 +7338,10 @@
         <v>138</v>
       </c>
       <c r="F115" s="6" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="G115" s="8" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
     </row>
     <row r="116" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7361,10 +7361,10 @@
         <v>138</v>
       </c>
       <c r="F116" s="6" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="G116" s="8" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="117" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7384,10 +7384,10 @@
         <v>138</v>
       </c>
       <c r="F117" s="6" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="G117" s="8" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
     </row>
     <row r="118" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7404,10 +7404,10 @@
         <v>138</v>
       </c>
       <c r="F118" s="6" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="G118" s="8" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
     </row>
     <row r="119" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7427,10 +7427,10 @@
         <v>138</v>
       </c>
       <c r="F119" s="12" t="s">
-        <v>1338</v>
+        <v>1336</v>
       </c>
       <c r="G119" s="12" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="120" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7450,10 +7450,10 @@
         <v>138</v>
       </c>
       <c r="F120" s="6" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="G120" s="8" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
     </row>
     <row r="121" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7473,10 +7473,10 @@
         <v>138</v>
       </c>
       <c r="F121" s="12" t="s">
-        <v>1344</v>
+        <v>1342</v>
       </c>
       <c r="G121" s="12" t="s">
-        <v>1345</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="122" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7496,10 +7496,10 @@
         <v>138</v>
       </c>
       <c r="F122" s="6" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="G122" s="8" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
     </row>
     <row r="123" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7519,10 +7519,10 @@
         <v>138</v>
       </c>
       <c r="F123" s="6" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="G123" s="8" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
     </row>
     <row r="124" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7542,10 +7542,10 @@
         <v>138</v>
       </c>
       <c r="F124" s="6" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="G124" s="8" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
     </row>
     <row r="125" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7565,10 +7565,10 @@
         <v>138</v>
       </c>
       <c r="F125" s="12" t="s">
-        <v>1307</v>
+        <v>1305</v>
       </c>
       <c r="G125" s="12" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="126" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7588,10 +7588,10 @@
         <v>138</v>
       </c>
       <c r="F126" s="12" t="s">
-        <v>1321</v>
+        <v>1319</v>
       </c>
       <c r="G126" s="12" t="s">
-        <v>1322</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="127" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7611,10 +7611,10 @@
         <v>138</v>
       </c>
       <c r="F127" s="6" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="G127" s="8" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
     </row>
     <row r="128" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7634,10 +7634,10 @@
         <v>138</v>
       </c>
       <c r="F128" s="6" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="G128" s="8" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
     </row>
     <row r="129" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7657,10 +7657,10 @@
         <v>138</v>
       </c>
       <c r="F129" s="6" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="G129" s="8" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
     </row>
     <row r="130" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7680,10 +7680,10 @@
         <v>138</v>
       </c>
       <c r="F130" s="12" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="G130" s="12" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="131" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7703,10 +7703,10 @@
         <v>138</v>
       </c>
       <c r="F131" s="6" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="G131" s="8" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
     </row>
     <row r="132" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7726,10 +7726,10 @@
         <v>138</v>
       </c>
       <c r="F132" s="6" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="G132" s="8" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
     </row>
     <row r="133" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7749,10 +7749,10 @@
         <v>138</v>
       </c>
       <c r="F133" s="6" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="G133" s="8" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
     </row>
     <row r="134" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7772,10 +7772,10 @@
         <v>138</v>
       </c>
       <c r="F134" s="6" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="G134" s="8" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
     </row>
     <row r="135" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7795,10 +7795,10 @@
         <v>138</v>
       </c>
       <c r="F135" s="12" t="s">
-        <v>1313</v>
+        <v>1311</v>
       </c>
       <c r="G135" s="12" t="s">
-        <v>1314</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="136" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7818,10 +7818,10 @@
         <v>138</v>
       </c>
       <c r="F136" s="6" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="G136" s="8" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
     </row>
     <row r="137" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7841,10 +7841,10 @@
         <v>138</v>
       </c>
       <c r="F137" s="6" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="G137" s="8" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
     </row>
     <row r="138" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7864,10 +7864,10 @@
         <v>138</v>
       </c>
       <c r="F138" s="6" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="G138" s="8" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.3">
@@ -7887,10 +7887,10 @@
         <v>138</v>
       </c>
       <c r="F139" s="9" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="G139" s="10" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.3">
@@ -7910,10 +7910,10 @@
         <v>138</v>
       </c>
       <c r="F140" s="15" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="G140" s="15" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.3">
@@ -7933,10 +7933,10 @@
         <v>138</v>
       </c>
       <c r="F141" s="11" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
       <c r="G141" s="11" t="s">
-        <v>1304</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.3">
@@ -7956,10 +7956,10 @@
         <v>138</v>
       </c>
       <c r="F142" s="15" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="G142" s="15" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.3">
@@ -7979,10 +7979,10 @@
         <v>138</v>
       </c>
       <c r="F143" s="11" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="G143" s="11" t="s">
-        <v>1332</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.3">
@@ -8002,10 +8002,10 @@
         <v>138</v>
       </c>
       <c r="F144" s="11" t="s">
-        <v>1305</v>
+        <v>1303</v>
       </c>
       <c r="G144" s="11" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.3">
@@ -8025,10 +8025,10 @@
         <v>138</v>
       </c>
       <c r="F145" s="15" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="G145" s="15" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.3">
@@ -8048,10 +8048,10 @@
         <v>138</v>
       </c>
       <c r="F146" s="11" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="G146" s="11" t="s">
-        <v>1312</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.3">
@@ -8071,10 +8071,10 @@
         <v>138</v>
       </c>
       <c r="F147" s="15" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="G147" s="15" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.3">
@@ -8094,10 +8094,10 @@
         <v>138</v>
       </c>
       <c r="F148" s="15" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="G148" s="15" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.3">
@@ -8117,10 +8117,10 @@
         <v>138</v>
       </c>
       <c r="F149" s="15" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="G149" s="15" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.3">
@@ -8140,10 +8140,10 @@
         <v>138</v>
       </c>
       <c r="F150" s="15" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="G150" s="15" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.3">
@@ -8163,10 +8163,10 @@
         <v>138</v>
       </c>
       <c r="F151" s="15" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="G151" s="15" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.3">
@@ -8186,10 +8186,10 @@
         <v>138</v>
       </c>
       <c r="F152" s="11" t="s">
-        <v>1319</v>
+        <v>1317</v>
       </c>
       <c r="G152" s="11" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="153" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8209,10 +8209,10 @@
         <v>138</v>
       </c>
       <c r="F153" s="13" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="G153" s="14" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="154" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8232,10 +8232,10 @@
         <v>138</v>
       </c>
       <c r="F154" s="6" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="G154" s="8" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
     </row>
     <row r="155" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8255,10 +8255,10 @@
         <v>138</v>
       </c>
       <c r="F155" s="6" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="G155" s="8" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
     </row>
     <row r="156" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8278,10 +8278,10 @@
         <v>138</v>
       </c>
       <c r="F156" s="6" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="G156" s="8" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="157" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8301,10 +8301,10 @@
         <v>138</v>
       </c>
       <c r="F157" s="12" t="s">
-        <v>1323</v>
+        <v>1321</v>
       </c>
       <c r="G157" s="12" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="158" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8324,10 +8324,10 @@
         <v>138</v>
       </c>
       <c r="F158" s="6" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="G158" s="8" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
     </row>
     <row r="159" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8347,10 +8347,10 @@
         <v>138</v>
       </c>
       <c r="F159" s="6" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="G159" s="8" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
     </row>
     <row r="160" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8370,10 +8370,10 @@
         <v>138</v>
       </c>
       <c r="F160" s="12" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="G160" s="12" t="s">
-        <v>1310</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="161" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8393,10 +8393,10 @@
         <v>138</v>
       </c>
       <c r="F161" s="6" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="G161" s="8" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
     </row>
     <row r="162" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8416,10 +8416,10 @@
         <v>138</v>
       </c>
       <c r="F162" s="6" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="G162" s="8" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
     </row>
     <row r="163" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8439,10 +8439,10 @@
         <v>138</v>
       </c>
       <c r="F163" s="6" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="G163" s="8" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
     </row>
     <row r="164" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8462,10 +8462,10 @@
         <v>138</v>
       </c>
       <c r="F164" s="6" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="G164" s="8" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
     </row>
     <row r="165" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8485,10 +8485,10 @@
         <v>138</v>
       </c>
       <c r="F165" s="6" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="G165" s="8" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
     </row>
     <row r="166" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8508,10 +8508,10 @@
         <v>138</v>
       </c>
       <c r="F166" s="6" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="G166" s="8" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
     </row>
     <row r="167" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8531,10 +8531,10 @@
         <v>138</v>
       </c>
       <c r="F167" s="6" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="G167" s="8" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
     </row>
     <row r="168" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8554,10 +8554,10 @@
         <v>138</v>
       </c>
       <c r="F168" s="6" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="G168" s="8" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
     </row>
     <row r="169" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8577,10 +8577,10 @@
         <v>138</v>
       </c>
       <c r="F169" s="6" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="G169" s="8" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
     </row>
     <row r="170" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8600,10 +8600,10 @@
         <v>138</v>
       </c>
       <c r="F170" s="6" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="G170" s="8" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
     </row>
     <row r="171" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8623,10 +8623,10 @@
         <v>138</v>
       </c>
       <c r="F171" s="6" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="G171" s="8" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
     </row>
     <row r="172" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8646,10 +8646,10 @@
         <v>138</v>
       </c>
       <c r="F172" s="6" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="G172" s="8" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
     </row>
     <row r="173" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8669,10 +8669,10 @@
         <v>138</v>
       </c>
       <c r="F173" s="6" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="G173" s="8" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
     </row>
     <row r="174" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8692,10 +8692,10 @@
         <v>138</v>
       </c>
       <c r="F174" s="6" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="G174" s="8" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
     </row>
     <row r="175" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8715,10 +8715,10 @@
         <v>138</v>
       </c>
       <c r="F175" s="6" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="G175" s="8" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
     </row>
     <row r="176" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8738,10 +8738,10 @@
         <v>138</v>
       </c>
       <c r="F176" s="6" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="G176" s="8" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
     </row>
     <row r="177" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8761,10 +8761,10 @@
         <v>138</v>
       </c>
       <c r="F177" s="6" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="G177" s="8" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
     </row>
     <row r="178" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8784,10 +8784,10 @@
         <v>138</v>
       </c>
       <c r="F178" s="6" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="G178" s="8" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
     </row>
     <row r="179" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8807,10 +8807,10 @@
         <v>138</v>
       </c>
       <c r="F179" s="6" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="G179" s="8" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
     </row>
     <row r="180" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8830,10 +8830,10 @@
         <v>138</v>
       </c>
       <c r="F180" s="6" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="G180" s="8" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
     </row>
     <row r="181" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8853,10 +8853,10 @@
         <v>138</v>
       </c>
       <c r="F181" s="6" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="G181" s="8" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
     </row>
     <row r="182" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8876,10 +8876,10 @@
         <v>138</v>
       </c>
       <c r="F182" s="6" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="G182" s="8" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="183" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8899,10 +8899,10 @@
         <v>138</v>
       </c>
       <c r="F183" s="6" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="G183" s="8" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
     </row>
     <row r="184" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8922,10 +8922,10 @@
         <v>138</v>
       </c>
       <c r="F184" s="6" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="G184" s="8" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
     </row>
     <row r="185" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8945,10 +8945,10 @@
         <v>138</v>
       </c>
       <c r="F185" s="6" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="G185" s="8" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
     </row>
     <row r="186" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8968,10 +8968,10 @@
         <v>138</v>
       </c>
       <c r="F186" s="6" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="G186" s="8" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="187" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8991,10 +8991,10 @@
         <v>138</v>
       </c>
       <c r="F187" s="6" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="G187" s="8" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="188" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9014,10 +9014,10 @@
         <v>138</v>
       </c>
       <c r="F188" s="6" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="G188" s="8" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="189" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9037,10 +9037,10 @@
         <v>138</v>
       </c>
       <c r="F189" s="6" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="G189" s="8" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="190" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9060,10 +9060,10 @@
         <v>138</v>
       </c>
       <c r="F190" s="6" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="G190" s="8" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="191" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9083,10 +9083,10 @@
         <v>138</v>
       </c>
       <c r="F191" s="6" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="G191" s="8" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="192" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9106,10 +9106,10 @@
         <v>138</v>
       </c>
       <c r="F192" s="6" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="G192" s="8" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="193" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9129,10 +9129,10 @@
         <v>138</v>
       </c>
       <c r="F193" s="6" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="G193" s="8" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="194" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9152,10 +9152,10 @@
         <v>138</v>
       </c>
       <c r="F194" s="6" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="G194" s="8" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="195" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9175,10 +9175,10 @@
         <v>138</v>
       </c>
       <c r="F195" s="6" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="G195" s="8" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="196" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9198,10 +9198,10 @@
         <v>138</v>
       </c>
       <c r="F196" s="6" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="G196" s="8" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="197" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9221,10 +9221,10 @@
         <v>138</v>
       </c>
       <c r="F197" s="6" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="G197" s="8" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="198" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9244,10 +9244,10 @@
         <v>138</v>
       </c>
       <c r="F198" s="6" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="G198" s="8" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="199" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9267,10 +9267,10 @@
         <v>138</v>
       </c>
       <c r="F199" s="6" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="G199" s="8" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="200" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9290,10 +9290,10 @@
         <v>138</v>
       </c>
       <c r="F200" s="6" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="G200" s="8" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="201" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9313,10 +9313,10 @@
         <v>138</v>
       </c>
       <c r="F201" s="6" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="G201" s="8" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="202" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9336,10 +9336,10 @@
         <v>138</v>
       </c>
       <c r="F202" s="6" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="G202" s="8" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="203" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9359,10 +9359,10 @@
         <v>138</v>
       </c>
       <c r="F203" s="6" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="G203" s="8" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="204" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9382,10 +9382,10 @@
         <v>138</v>
       </c>
       <c r="F204" s="6" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="G204" s="8" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="205" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9405,10 +9405,10 @@
         <v>138</v>
       </c>
       <c r="F205" s="6" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="G205" s="8" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="206" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9428,10 +9428,10 @@
         <v>138</v>
       </c>
       <c r="F206" s="6" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="G206" s="8" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="207" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9451,10 +9451,10 @@
         <v>138</v>
       </c>
       <c r="F207" s="6" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="G207" s="8" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="208" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9474,10 +9474,10 @@
         <v>138</v>
       </c>
       <c r="F208" s="6" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="G208" s="8" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="209" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9497,10 +9497,10 @@
         <v>138</v>
       </c>
       <c r="F209" s="6" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="G209" s="8" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="210" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9520,10 +9520,10 @@
         <v>138</v>
       </c>
       <c r="F210" s="6" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="G210" s="8" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="211" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9543,10 +9543,10 @@
         <v>138</v>
       </c>
       <c r="F211" s="6" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="G211" s="8" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="212" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9566,10 +9566,10 @@
         <v>138</v>
       </c>
       <c r="F212" s="6" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="G212" s="8" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="213" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9589,10 +9589,10 @@
         <v>138</v>
       </c>
       <c r="F213" s="6" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="G213" s="8" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="214" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9612,10 +9612,10 @@
         <v>138</v>
       </c>
       <c r="F214" s="6" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="G214" s="8" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="215" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9635,10 +9635,10 @@
         <v>138</v>
       </c>
       <c r="F215" s="6" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="G215" s="8" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="216" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9658,10 +9658,10 @@
         <v>138</v>
       </c>
       <c r="F216" s="6" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="G216" s="8" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="217" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9681,10 +9681,10 @@
         <v>138</v>
       </c>
       <c r="F217" s="6" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="G217" s="8" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="218" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9704,10 +9704,10 @@
         <v>138</v>
       </c>
       <c r="F218" s="6" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="G218" s="8" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.3">
@@ -9727,10 +9727,10 @@
         <v>138</v>
       </c>
       <c r="F219" s="9" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="G219" s="10" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.3">
@@ -9750,10 +9750,10 @@
         <v>138</v>
       </c>
       <c r="F220" s="11" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="G220" s="11" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.3">
@@ -9773,10 +9773,10 @@
         <v>138</v>
       </c>
       <c r="F221" s="11" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="G221" s="11" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.3">
@@ -9796,10 +9796,10 @@
         <v>138</v>
       </c>
       <c r="F222" s="11" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="G222" s="11" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.3">
@@ -9819,10 +9819,10 @@
         <v>138</v>
       </c>
       <c r="F223" s="11" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="G223" s="11" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.3">
@@ -9842,10 +9842,10 @@
         <v>138</v>
       </c>
       <c r="F224" s="11" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="G224" s="11" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.3">
@@ -9865,10 +9865,10 @@
         <v>138</v>
       </c>
       <c r="F225" s="11" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="G225" s="11" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.3">
@@ -9888,10 +9888,10 @@
         <v>138</v>
       </c>
       <c r="F226" s="11" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="G226" s="11" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.3">
@@ -9911,10 +9911,10 @@
         <v>138</v>
       </c>
       <c r="F227" s="11" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="G227" s="11" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.3">
@@ -9934,10 +9934,10 @@
         <v>138</v>
       </c>
       <c r="F228" s="11" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="G228" s="11" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.3">
@@ -9957,10 +9957,10 @@
         <v>138</v>
       </c>
       <c r="F229" s="11" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="G229" s="11" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.3">
@@ -9980,10 +9980,10 @@
         <v>138</v>
       </c>
       <c r="F230" s="11" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="G230" s="11" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.3">
@@ -10003,10 +10003,10 @@
         <v>138</v>
       </c>
       <c r="F231" s="11" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="G231" s="11" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.3">
@@ -10026,10 +10026,10 @@
         <v>138</v>
       </c>
       <c r="F232" s="11" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="G232" s="11" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.3">
@@ -10049,10 +10049,10 @@
         <v>138</v>
       </c>
       <c r="F233" s="11" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="G233" s="11" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.3">
@@ -10072,10 +10072,10 @@
         <v>138</v>
       </c>
       <c r="F234" s="11" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="G234" s="11" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.3">
@@ -10095,10 +10095,10 @@
         <v>138</v>
       </c>
       <c r="F235" s="11" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="G235" s="11" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.3">
@@ -10118,10 +10118,10 @@
         <v>138</v>
       </c>
       <c r="F236" s="11" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="G236" s="11" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.3">
@@ -10141,10 +10141,10 @@
         <v>138</v>
       </c>
       <c r="F237" s="11" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="G237" s="11" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.3">
@@ -10164,10 +10164,10 @@
         <v>138</v>
       </c>
       <c r="F238" s="11" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="G238" s="11" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.3">
@@ -10187,10 +10187,10 @@
         <v>138</v>
       </c>
       <c r="F239" s="11" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="G239" s="11" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.3">
@@ -10210,10 +10210,10 @@
         <v>138</v>
       </c>
       <c r="F240" s="11" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="G240" s="11" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.3">
@@ -10233,10 +10233,10 @@
         <v>138</v>
       </c>
       <c r="F241" s="11" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="G241" s="11" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.3">
@@ -10256,10 +10256,10 @@
         <v>138</v>
       </c>
       <c r="F242" s="11" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
       <c r="G242" s="11" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.3">
@@ -10279,10 +10279,10 @@
         <v>138</v>
       </c>
       <c r="F243" s="11" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
       <c r="G243" s="11" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.3">
@@ -10302,10 +10302,10 @@
         <v>138</v>
       </c>
       <c r="F244" s="11" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="G244" s="11" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.3">
@@ -10325,10 +10325,10 @@
         <v>138</v>
       </c>
       <c r="F245" s="11" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
       <c r="G245" s="11" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.3">
@@ -10348,10 +10348,10 @@
         <v>138</v>
       </c>
       <c r="F246" s="11" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
       <c r="G246" s="11" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.3">
@@ -10371,10 +10371,10 @@
         <v>138</v>
       </c>
       <c r="F247" s="11" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="G247" s="11" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.3">
@@ -10394,10 +10394,10 @@
         <v>138</v>
       </c>
       <c r="F248" s="11" t="s">
-        <v>1125</v>
+        <v>1123</v>
       </c>
       <c r="G248" s="11" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.3">
@@ -10417,10 +10417,10 @@
         <v>138</v>
       </c>
       <c r="F249" s="11" t="s">
-        <v>1127</v>
+        <v>1125</v>
       </c>
       <c r="G249" s="11" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.3">
@@ -10440,10 +10440,10 @@
         <v>138</v>
       </c>
       <c r="F250" s="11" t="s">
-        <v>1129</v>
+        <v>1127</v>
       </c>
       <c r="G250" s="11" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.3">
@@ -10463,10 +10463,10 @@
         <v>138</v>
       </c>
       <c r="F251" s="11" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="G251" s="11" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.3">
@@ -10486,10 +10486,10 @@
         <v>138</v>
       </c>
       <c r="F252" s="11" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="G252" s="11" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.3">
@@ -10509,10 +10509,10 @@
         <v>138</v>
       </c>
       <c r="F253" s="11" t="s">
-        <v>1135</v>
+        <v>1133</v>
       </c>
       <c r="G253" s="11" t="s">
-        <v>1136</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.3">
@@ -10532,10 +10532,10 @@
         <v>138</v>
       </c>
       <c r="F254" s="11" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
       <c r="G254" s="11" t="s">
-        <v>1138</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.3">
@@ -10555,10 +10555,10 @@
         <v>138</v>
       </c>
       <c r="F255" s="11" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
       <c r="G255" s="11" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.3">
@@ -10578,10 +10578,10 @@
         <v>138</v>
       </c>
       <c r="F256" s="11" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="G256" s="11" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.3">
@@ -10601,10 +10601,10 @@
         <v>138</v>
       </c>
       <c r="F257" s="11" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
       <c r="G257" s="11" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.3">
@@ -10624,10 +10624,10 @@
         <v>138</v>
       </c>
       <c r="F258" s="11" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="G258" s="11" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.3">
@@ -10647,10 +10647,10 @@
         <v>138</v>
       </c>
       <c r="F259" s="11" t="s">
-        <v>1147</v>
+        <v>1145</v>
       </c>
       <c r="G259" s="11" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.3">
@@ -10670,10 +10670,10 @@
         <v>138</v>
       </c>
       <c r="F260" s="11" t="s">
-        <v>1149</v>
+        <v>1147</v>
       </c>
       <c r="G260" s="11" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.3">
@@ -10693,10 +10693,10 @@
         <v>138</v>
       </c>
       <c r="F261" s="11" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="G261" s="11" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.3">
@@ -10716,10 +10716,10 @@
         <v>138</v>
       </c>
       <c r="F262" s="11" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
       <c r="G262" s="11" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.3">
@@ -10739,10 +10739,10 @@
         <v>138</v>
       </c>
       <c r="F263" s="11" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="G263" s="11" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.3">
@@ -10762,10 +10762,10 @@
         <v>138</v>
       </c>
       <c r="F264" s="11" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="G264" s="11" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.3">
@@ -10785,10 +10785,10 @@
         <v>138</v>
       </c>
       <c r="F265" s="11" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="G265" s="11" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.3">
@@ -10808,10 +10808,10 @@
         <v>138</v>
       </c>
       <c r="F266" s="11" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="G266" s="11" t="s">
-        <v>1162</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.3">
@@ -10831,10 +10831,10 @@
         <v>138</v>
       </c>
       <c r="F267" s="11" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
       <c r="G267" s="11" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.3">
@@ -10854,10 +10854,10 @@
         <v>138</v>
       </c>
       <c r="F268" s="11" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="G268" s="11" t="s">
-        <v>1166</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.3">
@@ -10877,10 +10877,10 @@
         <v>138</v>
       </c>
       <c r="F269" s="11" t="s">
-        <v>1167</v>
+        <v>1165</v>
       </c>
       <c r="G269" s="11" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.3">
@@ -10900,10 +10900,10 @@
         <v>138</v>
       </c>
       <c r="F270" s="11" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="G270" s="11" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.3">
@@ -10923,10 +10923,10 @@
         <v>138</v>
       </c>
       <c r="F271" s="11" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
       <c r="G271" s="11" t="s">
-        <v>1172</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.3">
@@ -10946,10 +10946,10 @@
         <v>138</v>
       </c>
       <c r="F272" s="11" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="G272" s="11" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.3">
@@ -10969,10 +10969,10 @@
         <v>138</v>
       </c>
       <c r="F273" s="11" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="G273" s="11" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.3">
@@ -10992,10 +10992,10 @@
         <v>138</v>
       </c>
       <c r="F274" s="11" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="G274" s="11" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.3">
@@ -11015,10 +11015,10 @@
         <v>138</v>
       </c>
       <c r="F275" s="11" t="s">
-        <v>1179</v>
+        <v>1177</v>
       </c>
       <c r="G275" s="11" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.3">
@@ -11038,10 +11038,10 @@
         <v>138</v>
       </c>
       <c r="F276" s="11" t="s">
-        <v>1181</v>
+        <v>1179</v>
       </c>
       <c r="G276" s="11" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.3">
@@ -11061,10 +11061,10 @@
         <v>138</v>
       </c>
       <c r="F277" s="11" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
       <c r="G277" s="11" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.3">
@@ -11084,10 +11084,10 @@
         <v>138</v>
       </c>
       <c r="F278" s="11" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
       <c r="G278" s="11" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="279" spans="1:7" x14ac:dyDescent="0.3">
@@ -11107,10 +11107,10 @@
         <v>138</v>
       </c>
       <c r="F279" s="11" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="G279" s="11" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="280" spans="1:7" x14ac:dyDescent="0.3">
@@ -11130,10 +11130,10 @@
         <v>138</v>
       </c>
       <c r="F280" s="11" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
       <c r="G280" s="11" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.3">
@@ -11153,10 +11153,10 @@
         <v>138</v>
       </c>
       <c r="F281" s="11" t="s">
-        <v>1191</v>
+        <v>1189</v>
       </c>
       <c r="G281" s="11" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.3">
@@ -11176,10 +11176,10 @@
         <v>601</v>
       </c>
       <c r="F282" s="11" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
       <c r="G282" s="11" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.3">
@@ -11199,10 +11199,10 @@
         <v>601</v>
       </c>
       <c r="F283" s="11" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
       <c r="G283" s="11" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.3">
@@ -11222,10 +11222,10 @@
         <v>601</v>
       </c>
       <c r="F284" s="11" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="G284" s="11" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.3">
@@ -11245,10 +11245,10 @@
         <v>601</v>
       </c>
       <c r="F285" s="11" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
       <c r="G285" s="11" t="s">
-        <v>1200</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.3">
@@ -11268,10 +11268,10 @@
         <v>601</v>
       </c>
       <c r="F286" s="11" t="s">
-        <v>1201</v>
+        <v>1199</v>
       </c>
       <c r="G286" s="11" t="s">
-        <v>1202</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.3">
@@ -11291,10 +11291,10 @@
         <v>601</v>
       </c>
       <c r="F287" s="11" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
       <c r="G287" s="11" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.3">
@@ -11314,10 +11314,10 @@
         <v>601</v>
       </c>
       <c r="F288" s="11" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
       <c r="G288" s="11" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.3">
@@ -11337,10 +11337,10 @@
         <v>601</v>
       </c>
       <c r="F289" s="11" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="G289" s="11" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.3">
@@ -11360,10 +11360,10 @@
         <v>601</v>
       </c>
       <c r="F290" s="11" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="G290" s="11" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.3">
@@ -11383,10 +11383,10 @@
         <v>601</v>
       </c>
       <c r="F291" s="11" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="G291" s="11" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.3">
@@ -11406,10 +11406,10 @@
         <v>601</v>
       </c>
       <c r="F292" s="11" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="G292" s="11" t="s">
-        <v>1214</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.3">
@@ -11429,10 +11429,10 @@
         <v>601</v>
       </c>
       <c r="F293" s="11" t="s">
-        <v>1215</v>
+        <v>1213</v>
       </c>
       <c r="G293" s="11" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.3">
@@ -11452,10 +11452,10 @@
         <v>601</v>
       </c>
       <c r="F294" s="11" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
       <c r="G294" s="11" t="s">
-        <v>1218</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.3">
@@ -11475,10 +11475,10 @@
         <v>601</v>
       </c>
       <c r="F295" s="11" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
       <c r="G295" s="11" t="s">
-        <v>1220</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.3">
@@ -11498,10 +11498,10 @@
         <v>601</v>
       </c>
       <c r="F296" s="11" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="G296" s="11" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.3">
@@ -11521,10 +11521,10 @@
         <v>601</v>
       </c>
       <c r="F297" s="11" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="G297" s="11" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.3">
@@ -11544,10 +11544,10 @@
         <v>138</v>
       </c>
       <c r="F298" s="11" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="G298" s="11" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="299" spans="1:7" x14ac:dyDescent="0.3">
@@ -11567,10 +11567,10 @@
         <v>138</v>
       </c>
       <c r="F299" s="11" t="s">
-        <v>1227</v>
+        <v>1225</v>
       </c>
       <c r="G299" s="11" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.3">
@@ -11590,10 +11590,10 @@
         <v>138</v>
       </c>
       <c r="F300" s="11" t="s">
-        <v>1229</v>
+        <v>1227</v>
       </c>
       <c r="G300" s="11" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.3">
@@ -11613,10 +11613,10 @@
         <v>138</v>
       </c>
       <c r="F301" s="11" t="s">
-        <v>1231</v>
+        <v>1229</v>
       </c>
       <c r="G301" s="11" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="302" spans="1:7" x14ac:dyDescent="0.3">
@@ -11636,10 +11636,10 @@
         <v>138</v>
       </c>
       <c r="F302" s="11" t="s">
-        <v>1233</v>
+        <v>1231</v>
       </c>
       <c r="G302" s="11" t="s">
-        <v>1234</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="303" spans="1:7" x14ac:dyDescent="0.3">
@@ -11659,10 +11659,10 @@
         <v>138</v>
       </c>
       <c r="F303" s="11" t="s">
-        <v>1235</v>
+        <v>1233</v>
       </c>
       <c r="G303" s="11" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="304" spans="1:7" x14ac:dyDescent="0.3">
@@ -11682,10 +11682,10 @@
         <v>138</v>
       </c>
       <c r="F304" s="11" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="G304" s="11" t="s">
-        <v>1238</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="305" spans="1:7" x14ac:dyDescent="0.3">
@@ -11705,10 +11705,10 @@
         <v>138</v>
       </c>
       <c r="F305" s="11" t="s">
-        <v>1239</v>
+        <v>1237</v>
       </c>
       <c r="G305" s="11" t="s">
-        <v>1240</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="306" spans="1:7" x14ac:dyDescent="0.3">
@@ -11728,10 +11728,10 @@
         <v>138</v>
       </c>
       <c r="F306" s="11" t="s">
-        <v>1241</v>
+        <v>1239</v>
       </c>
       <c r="G306" s="11" t="s">
-        <v>1242</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="307" spans="1:7" x14ac:dyDescent="0.3">
@@ -11751,10 +11751,10 @@
         <v>138</v>
       </c>
       <c r="F307" s="11" t="s">
-        <v>1243</v>
+        <v>1241</v>
       </c>
       <c r="G307" s="11" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="308" spans="1:7" x14ac:dyDescent="0.3">
@@ -11774,10 +11774,10 @@
         <v>601</v>
       </c>
       <c r="F308" s="11" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="G308" s="11" t="s">
-        <v>1246</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="309" spans="1:7" x14ac:dyDescent="0.3">
@@ -11797,10 +11797,10 @@
         <v>601</v>
       </c>
       <c r="F309" s="11" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="G309" s="11" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="310" spans="1:7" x14ac:dyDescent="0.3">
@@ -11820,10 +11820,10 @@
         <v>601</v>
       </c>
       <c r="F310" s="11" t="s">
-        <v>1249</v>
+        <v>1247</v>
       </c>
       <c r="G310" s="11" t="s">
-        <v>1250</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="311" spans="1:7" x14ac:dyDescent="0.3">
@@ -11843,10 +11843,10 @@
         <v>601</v>
       </c>
       <c r="F311" s="11" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="G311" s="11" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="312" spans="1:7" x14ac:dyDescent="0.3">
@@ -11866,10 +11866,10 @@
         <v>601</v>
       </c>
       <c r="F312" s="11" t="s">
-        <v>1253</v>
+        <v>1251</v>
       </c>
       <c r="G312" s="11" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="313" spans="1:7" x14ac:dyDescent="0.3">
@@ -11889,10 +11889,10 @@
         <v>601</v>
       </c>
       <c r="F313" s="11" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
       <c r="G313" s="11" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="314" spans="1:7" x14ac:dyDescent="0.3">
@@ -11912,10 +11912,10 @@
         <v>601</v>
       </c>
       <c r="F314" s="11" t="s">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="G314" s="11" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="315" spans="1:7" x14ac:dyDescent="0.3">
@@ -11935,10 +11935,10 @@
         <v>601</v>
       </c>
       <c r="F315" s="11" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="G315" s="11" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="316" spans="1:7" x14ac:dyDescent="0.3">
@@ -11958,10 +11958,10 @@
         <v>601</v>
       </c>
       <c r="F316" s="11" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
       <c r="G316" s="11" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="317" spans="1:7" x14ac:dyDescent="0.3">
@@ -11981,10 +11981,10 @@
         <v>601</v>
       </c>
       <c r="F317" s="11" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="G317" s="11" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="318" spans="1:7" x14ac:dyDescent="0.3">
@@ -12004,10 +12004,10 @@
         <v>601</v>
       </c>
       <c r="F318" s="11" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="G318" s="11" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="319" spans="1:7" x14ac:dyDescent="0.3">
@@ -12027,10 +12027,10 @@
         <v>601</v>
       </c>
       <c r="F319" s="11" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="G319" s="11" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="320" spans="1:7" x14ac:dyDescent="0.3">
@@ -12050,10 +12050,10 @@
         <v>601</v>
       </c>
       <c r="F320" s="11" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="G320" s="11" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="321" spans="1:7" x14ac:dyDescent="0.3">
@@ -12073,10 +12073,10 @@
         <v>601</v>
       </c>
       <c r="F321" s="11" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="G321" s="11" t="s">
-        <v>1272</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="322" spans="1:7" x14ac:dyDescent="0.3">
@@ -12096,10 +12096,10 @@
         <v>601</v>
       </c>
       <c r="F322" s="11" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="G322" s="11" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="323" spans="1:7" x14ac:dyDescent="0.3">
@@ -12119,10 +12119,10 @@
         <v>601</v>
       </c>
       <c r="F323" s="11" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="G323" s="11" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="324" spans="1:7" x14ac:dyDescent="0.3">
@@ -12142,10 +12142,10 @@
         <v>601</v>
       </c>
       <c r="F324" s="11" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="G324" s="11" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="325" spans="1:7" x14ac:dyDescent="0.3">
@@ -12165,10 +12165,10 @@
         <v>601</v>
       </c>
       <c r="F325" s="11" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="G325" s="11" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="326" spans="1:7" x14ac:dyDescent="0.3">
@@ -12188,10 +12188,10 @@
         <v>601</v>
       </c>
       <c r="F326" s="11" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="G326" s="11" t="s">
-        <v>1282</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="327" spans="1:7" x14ac:dyDescent="0.3">
@@ -12211,10 +12211,10 @@
         <v>601</v>
       </c>
       <c r="F327" s="11" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
       <c r="G327" s="11" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="328" spans="1:7" x14ac:dyDescent="0.3">
@@ -12234,10 +12234,10 @@
         <v>601</v>
       </c>
       <c r="F328" s="11" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="G328" s="11" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="329" spans="1:7" x14ac:dyDescent="0.3">
@@ -12257,10 +12257,10 @@
         <v>601</v>
       </c>
       <c r="F329" s="11" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="G329" s="11" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="330" spans="1:7" x14ac:dyDescent="0.3">
@@ -12280,10 +12280,10 @@
         <v>601</v>
       </c>
       <c r="F330" s="11" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="G330" s="11" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="331" spans="1:7" x14ac:dyDescent="0.3">
@@ -12303,10 +12303,10 @@
         <v>601</v>
       </c>
       <c r="F331" s="11" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
       <c r="G331" s="11" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="332" spans="1:7" x14ac:dyDescent="0.3">
@@ -12326,10 +12326,10 @@
         <v>601</v>
       </c>
       <c r="F332" s="11" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="G332" s="11" t="s">
-        <v>1294</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="333" spans="1:7" x14ac:dyDescent="0.3">
@@ -12349,10 +12349,10 @@
         <v>601</v>
       </c>
       <c r="F333" s="11" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
       <c r="G333" s="11" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="334" spans="1:7" x14ac:dyDescent="0.3">
@@ -12372,10 +12372,10 @@
         <v>601</v>
       </c>
       <c r="F334" s="11" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
       <c r="G334" s="11" t="s">
-        <v>1298</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="335" spans="1:7" x14ac:dyDescent="0.3">
@@ -12395,10 +12395,10 @@
         <v>601</v>
       </c>
       <c r="F335" s="11" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
       <c r="G335" s="11" t="s">
-        <v>1300</v>
+        <v>1298</v>
       </c>
     </row>
   </sheetData>

--- a/files/Adhiparasakthi Students Data 1.xlsx
+++ b/files/Adhiparasakthi Students Data 1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vigne\Google_Backup\Github\sb4c\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD490F28-3535-4073-904A-E89555E29F50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9068965-0DAB-4809-907A-D230377F7526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E3F0EEA9-6BAE-46A1-95E3-E9CE509FC50B}"/>
   </bookViews>
@@ -2097,12 +2097,6 @@
     <t>Edu#183729</t>
   </si>
   <si>
-    <t>EFIBM26743576339@edunetmail.com</t>
-  </si>
-  <si>
-    <t>Edu#490046</t>
-  </si>
-  <si>
     <t>EFIBM26553612318@edunetmail.com</t>
   </si>
   <si>
@@ -2139,12 +2133,6 @@
     <t>Edu#608737</t>
   </si>
   <si>
-    <t>EFIBM26360853417@edunetmail.com</t>
-  </si>
-  <si>
-    <t>Edu#492772</t>
-  </si>
-  <si>
     <t>EFIBM26659426356@edunetmail.com</t>
   </si>
   <si>
@@ -2157,12 +2145,6 @@
     <t>Edu#339312</t>
   </si>
   <si>
-    <t>EFIBM26878225697@edunetmail.com</t>
-  </si>
-  <si>
-    <t>Edu#654433</t>
-  </si>
-  <si>
     <t>EFIBM26782492001@edunetmail.com</t>
   </si>
   <si>
@@ -2181,18 +2163,6 @@
     <t>Edu#473532</t>
   </si>
   <si>
-    <t>EFIBM26113293648@edunetmail.com</t>
-  </si>
-  <si>
-    <t>Edu#164760</t>
-  </si>
-  <si>
-    <t>EFIBM26599578227@edunetmail.com</t>
-  </si>
-  <si>
-    <t>Edu#475172</t>
-  </si>
-  <si>
     <t>EFIBM26393931815@edunetmail.com</t>
   </si>
   <si>
@@ -2247,18 +2217,6 @@
     <t>Edu#397344</t>
   </si>
   <si>
-    <t>EFIBM26510285390@edunetmail.com</t>
-  </si>
-  <si>
-    <t>Edu#525539</t>
-  </si>
-  <si>
-    <t>EFIBM26201151075@edunetmail.com</t>
-  </si>
-  <si>
-    <t>Edu#163318</t>
-  </si>
-  <si>
     <t>EFIBM26554940112@edunetmail.com</t>
   </si>
   <si>
@@ -2271,36 +2229,12 @@
     <t>Edu#772341</t>
   </si>
   <si>
-    <t>EFIBM26332815806@edunetmail.com</t>
-  </si>
-  <si>
-    <t>Edu#329059</t>
-  </si>
-  <si>
-    <t>EFIBM26296430672@edunetmail.com</t>
-  </si>
-  <si>
-    <t>Edu#952768</t>
-  </si>
-  <si>
     <t>EFIBM26906694710@edunetmail.com</t>
   </si>
   <si>
     <t>Edu#489998</t>
   </si>
   <si>
-    <t>EFIBM26875886927@edunetmail.com</t>
-  </si>
-  <si>
-    <t>Edu#226385</t>
-  </si>
-  <si>
-    <t>EFIBM26642205548@edunetmail.com</t>
-  </si>
-  <si>
-    <t>Edu#745499</t>
-  </si>
-  <si>
     <t>EFIBM26655345006@edunetmail.com</t>
   </si>
   <si>
@@ -2325,12 +2259,6 @@
     <t>Edu#943660</t>
   </si>
   <si>
-    <t>EFIBM26193499938@edunetmail.com</t>
-  </si>
-  <si>
-    <t>Edu#944149</t>
-  </si>
-  <si>
     <t>EFIBM26261028008@edunetmail.com</t>
   </si>
   <si>
@@ -2373,24 +2301,12 @@
     <t>Edu#486083</t>
   </si>
   <si>
-    <t>EFIBM26112862924@edunetmail.com</t>
-  </si>
-  <si>
-    <t>Edu#836226</t>
-  </si>
-  <si>
     <t>EFIBM26773050725@edunetmail.com</t>
   </si>
   <si>
     <t>Edu#187059</t>
   </si>
   <si>
-    <t>EFIBM26744256694@edunetmail.com</t>
-  </si>
-  <si>
-    <t>Edu#965706</t>
-  </si>
-  <si>
     <t>EFIBM26536359476@edunetmail.com</t>
   </si>
   <si>
@@ -2409,18 +2325,6 @@
     <t>Edu#500995</t>
   </si>
   <si>
-    <t>EFIBM26413321249@edunetmail.com</t>
-  </si>
-  <si>
-    <t>Edu#253900</t>
-  </si>
-  <si>
-    <t>EFIBM26253487687@edunetmail.com</t>
-  </si>
-  <si>
-    <t>Edu#461962</t>
-  </si>
-  <si>
     <t>EFIBM26234923863@edunetmail.com</t>
   </si>
   <si>
@@ -2673,12 +2577,6 @@
     <t>Edu#228882</t>
   </si>
   <si>
-    <t>EFIBM26618780005@edunetmail.com</t>
-  </si>
-  <si>
-    <t>Edu#900037</t>
-  </si>
-  <si>
     <t>EFIBM26387503884@edunetmail.com</t>
   </si>
   <si>
@@ -3441,12 +3339,6 @@
     <t>EduB5#310706</t>
   </si>
   <si>
-    <t>EFIBM26B5812799128@edunetmail.com</t>
-  </si>
-  <si>
-    <t>EduB5#203786</t>
-  </si>
-  <si>
     <t>EFIBM26B5460077008@edunetmail.com</t>
   </si>
   <si>
@@ -4084,6 +3976,114 @@
   </si>
   <si>
     <t>Edu#289354</t>
+  </si>
+  <si>
+    <t>EFIBM26172663636@edunetmail.com</t>
+  </si>
+  <si>
+    <t>Edu#911672</t>
+  </si>
+  <si>
+    <t>EFIBM26299118615@edunetmail.com</t>
+  </si>
+  <si>
+    <t>Edu#423363</t>
+  </si>
+  <si>
+    <t>EFIBM26329295084@edunetmail.com</t>
+  </si>
+  <si>
+    <t>Edu#224484</t>
+  </si>
+  <si>
+    <t>EFIBM26808604653@edunetmail.com</t>
+  </si>
+  <si>
+    <t>Edu#773461</t>
+  </si>
+  <si>
+    <t>EFIBM26740565248@edunetmail.com</t>
+  </si>
+  <si>
+    <t>Edu#256493</t>
+  </si>
+  <si>
+    <t>EFIBM26904273611@edunetmail.com</t>
+  </si>
+  <si>
+    <t>Edu#162317</t>
+  </si>
+  <si>
+    <t>EFIBM26966406083@edunetmail.com</t>
+  </si>
+  <si>
+    <t>Edu#470499</t>
+  </si>
+  <si>
+    <t>EFIBM26428325702@edunetmail.com</t>
+  </si>
+  <si>
+    <t>Edu#500130</t>
+  </si>
+  <si>
+    <t>EFIBM26183396184@edunetmail.com</t>
+  </si>
+  <si>
+    <t>Edu#323153</t>
+  </si>
+  <si>
+    <t>EFIBM26839145401@edunetmail.com</t>
+  </si>
+  <si>
+    <t>Edu#169804</t>
+  </si>
+  <si>
+    <t>EFIBM26709025372@edunetmail.com</t>
+  </si>
+  <si>
+    <t>Edu#147189</t>
+  </si>
+  <si>
+    <t>EFIBM26799582334@edunetmail.com</t>
+  </si>
+  <si>
+    <t>Edu#949635</t>
+  </si>
+  <si>
+    <t>EFIBM26930723266@edunetmail.com</t>
+  </si>
+  <si>
+    <t>Edu#749673</t>
+  </si>
+  <si>
+    <t>EFIBM26194233679@edunetmail.com</t>
+  </si>
+  <si>
+    <t>Edu#378451</t>
+  </si>
+  <si>
+    <t>EFIBM26603598399@edunetmail.com</t>
+  </si>
+  <si>
+    <t>Edu#419689</t>
+  </si>
+  <si>
+    <t>EFIBM26833184674@edunetmail.com</t>
+  </si>
+  <si>
+    <t>Edu#957219</t>
+  </si>
+  <si>
+    <t>EFIBM26268909953@edunetmail.com</t>
+  </si>
+  <si>
+    <t>Edu#928990</t>
+  </si>
+  <si>
+    <t>EFIBM26136939684@edunetmail.com</t>
+  </si>
+  <si>
+    <t>Edu#516848</t>
   </si>
 </sst>
 </file>
@@ -4807,11 +4807,11 @@
       <c r="E5" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F5" s="6" t="s">
-        <v>687</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>688</v>
+      <c r="F5" s="5" t="s">
+        <v>1318</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>1319</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -4831,10 +4831,10 @@
         <v>138</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -4854,10 +4854,10 @@
         <v>138</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -4877,10 +4877,10 @@
         <v>138</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -4900,10 +4900,10 @@
         <v>138</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -4923,10 +4923,10 @@
         <v>138</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -4946,10 +4946,10 @@
         <v>138</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -4968,11 +4968,11 @@
       <c r="E12" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F12" s="6" t="s">
-        <v>701</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>702</v>
+      <c r="F12" s="5" t="s">
+        <v>1320</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>1321</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -4992,10 +4992,10 @@
         <v>138</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5015,10 +5015,10 @@
         <v>138</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5037,11 +5037,11 @@
       <c r="E15" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F15" s="6" t="s">
-        <v>707</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>708</v>
+      <c r="F15" s="5" t="s">
+        <v>1338</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>1339</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5061,10 +5061,10 @@
         <v>138</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>709</v>
+        <v>703</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>710</v>
+        <v>704</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5084,10 +5084,10 @@
         <v>138</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5107,10 +5107,10 @@
         <v>138</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>714</v>
+        <v>708</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5129,11 +5129,11 @@
       <c r="E19" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F19" s="6" t="s">
-        <v>715</v>
-      </c>
-      <c r="G19" s="8" t="s">
-        <v>716</v>
+      <c r="F19" s="5" t="s">
+        <v>1340</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>1341</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5152,11 +5152,11 @@
       <c r="E20" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F20" s="6" t="s">
-        <v>717</v>
-      </c>
-      <c r="G20" s="8" t="s">
-        <v>718</v>
+      <c r="F20" s="5" t="s">
+        <v>1342</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>1343</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5176,10 +5176,10 @@
         <v>138</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>719</v>
+        <v>709</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>720</v>
+        <v>710</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5199,10 +5199,10 @@
         <v>138</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>721</v>
+        <v>711</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>722</v>
+        <v>712</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5222,10 +5222,10 @@
         <v>138</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>723</v>
+        <v>713</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>724</v>
+        <v>714</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5245,10 +5245,10 @@
         <v>138</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>725</v>
+        <v>715</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>726</v>
+        <v>716</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5268,10 +5268,10 @@
         <v>138</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>727</v>
+        <v>717</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>728</v>
+        <v>718</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5291,10 +5291,10 @@
         <v>138</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>729</v>
+        <v>719</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>730</v>
+        <v>720</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5314,10 +5314,10 @@
         <v>138</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>731</v>
+        <v>721</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>732</v>
+        <v>722</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5337,10 +5337,10 @@
         <v>138</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>733</v>
+        <v>723</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>734</v>
+        <v>724</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5360,10 +5360,10 @@
         <v>138</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>735</v>
+        <v>725</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>736</v>
+        <v>726</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5382,11 +5382,11 @@
       <c r="E30" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F30" s="6" t="s">
-        <v>737</v>
-      </c>
-      <c r="G30" s="8" t="s">
-        <v>738</v>
+      <c r="F30" s="5" t="s">
+        <v>1326</v>
+      </c>
+      <c r="G30" s="7" t="s">
+        <v>1327</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5405,11 +5405,11 @@
       <c r="E31" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F31" s="6" t="s">
-        <v>739</v>
-      </c>
-      <c r="G31" s="8" t="s">
-        <v>740</v>
+      <c r="F31" s="5" t="s">
+        <v>1336</v>
+      </c>
+      <c r="G31" s="7" t="s">
+        <v>1337</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5429,10 +5429,10 @@
         <v>138</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>741</v>
+        <v>727</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>742</v>
+        <v>728</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5452,10 +5452,10 @@
         <v>138</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>743</v>
+        <v>729</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>744</v>
+        <v>730</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5474,11 +5474,11 @@
       <c r="E34" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F34" s="6" t="s">
-        <v>745</v>
-      </c>
-      <c r="G34" s="8" t="s">
-        <v>746</v>
+      <c r="F34" s="5" t="s">
+        <v>1324</v>
+      </c>
+      <c r="G34" s="7" t="s">
+        <v>1325</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5497,11 +5497,11 @@
       <c r="E35" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F35" s="6" t="s">
-        <v>747</v>
-      </c>
-      <c r="G35" s="8" t="s">
-        <v>748</v>
+      <c r="F35" s="5" t="s">
+        <v>1334</v>
+      </c>
+      <c r="G35" s="7" t="s">
+        <v>1335</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5521,10 +5521,10 @@
         <v>138</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>749</v>
+        <v>731</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>750</v>
+        <v>732</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5543,11 +5543,11 @@
       <c r="E37" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F37" s="6" t="s">
-        <v>751</v>
-      </c>
-      <c r="G37" s="8" t="s">
-        <v>752</v>
+      <c r="F37" s="5" t="s">
+        <v>1344</v>
+      </c>
+      <c r="G37" s="7" t="s">
+        <v>1345</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5566,11 +5566,11 @@
       <c r="E38" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F38" s="6" t="s">
-        <v>753</v>
-      </c>
-      <c r="G38" s="8" t="s">
-        <v>754</v>
+      <c r="F38" s="5" t="s">
+        <v>1316</v>
+      </c>
+      <c r="G38" s="7" t="s">
+        <v>1317</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5590,10 +5590,10 @@
         <v>138</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>755</v>
+        <v>733</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>756</v>
+        <v>734</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5613,10 +5613,10 @@
         <v>138</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>757</v>
+        <v>735</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>758</v>
+        <v>736</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5636,10 +5636,10 @@
         <v>138</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>759</v>
+        <v>737</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>760</v>
+        <v>738</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5659,10 +5659,10 @@
         <v>138</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>761</v>
+        <v>739</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>762</v>
+        <v>740</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5681,11 +5681,11 @@
       <c r="E43" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F43" s="6" t="s">
-        <v>763</v>
-      </c>
-      <c r="G43" s="8" t="s">
-        <v>764</v>
+      <c r="F43" s="5" t="s">
+        <v>1322</v>
+      </c>
+      <c r="G43" s="7" t="s">
+        <v>1323</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5705,10 +5705,10 @@
         <v>138</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>765</v>
+        <v>741</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>766</v>
+        <v>742</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5728,10 +5728,10 @@
         <v>138</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>767</v>
+        <v>743</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>768</v>
+        <v>744</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5751,10 +5751,10 @@
         <v>138</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>769</v>
+        <v>745</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>770</v>
+        <v>746</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5774,10 +5774,10 @@
         <v>138</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>771</v>
+        <v>747</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>772</v>
+        <v>748</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5797,10 +5797,10 @@
         <v>138</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>773</v>
+        <v>749</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>774</v>
+        <v>750</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5820,10 +5820,10 @@
         <v>138</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>775</v>
+        <v>751</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>776</v>
+        <v>752</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5843,10 +5843,10 @@
         <v>138</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>777</v>
+        <v>753</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>778</v>
+        <v>754</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5865,11 +5865,11 @@
       <c r="E51" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F51" s="6" t="s">
-        <v>779</v>
-      </c>
-      <c r="G51" s="8" t="s">
-        <v>780</v>
+      <c r="F51" s="5" t="s">
+        <v>1348</v>
+      </c>
+      <c r="G51" s="7" t="s">
+        <v>1349</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5889,10 +5889,10 @@
         <v>138</v>
       </c>
       <c r="F52" s="6" t="s">
-        <v>781</v>
+        <v>755</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>782</v>
+        <v>756</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5911,11 +5911,11 @@
       <c r="E53" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F53" s="6" t="s">
-        <v>783</v>
-      </c>
-      <c r="G53" s="8" t="s">
-        <v>784</v>
+      <c r="F53" s="5" t="s">
+        <v>1330</v>
+      </c>
+      <c r="G53" s="7" t="s">
+        <v>1331</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5935,10 +5935,10 @@
         <v>138</v>
       </c>
       <c r="F54" s="6" t="s">
-        <v>785</v>
+        <v>757</v>
       </c>
       <c r="G54" s="8" t="s">
-        <v>786</v>
+        <v>758</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5958,10 +5958,10 @@
         <v>138</v>
       </c>
       <c r="F55" s="6" t="s">
-        <v>787</v>
+        <v>759</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>788</v>
+        <v>760</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5981,10 +5981,10 @@
         <v>138</v>
       </c>
       <c r="F56" s="6" t="s">
-        <v>789</v>
+        <v>761</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>790</v>
+        <v>762</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6003,11 +6003,11 @@
       <c r="E57" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F57" s="6" t="s">
-        <v>791</v>
-      </c>
-      <c r="G57" s="8" t="s">
-        <v>792</v>
+      <c r="F57" s="5" t="s">
+        <v>1328</v>
+      </c>
+      <c r="G57" s="7" t="s">
+        <v>1329</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6026,11 +6026,11 @@
       <c r="E58" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F58" s="6" t="s">
-        <v>793</v>
-      </c>
-      <c r="G58" s="8" t="s">
-        <v>794</v>
+      <c r="F58" s="5" t="s">
+        <v>1332</v>
+      </c>
+      <c r="G58" s="7" t="s">
+        <v>1333</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6050,10 +6050,10 @@
         <v>138</v>
       </c>
       <c r="F59" s="6" t="s">
-        <v>795</v>
+        <v>763</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>796</v>
+        <v>764</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6073,10 +6073,10 @@
         <v>138</v>
       </c>
       <c r="F60" s="6" t="s">
-        <v>797</v>
+        <v>765</v>
       </c>
       <c r="G60" s="8" t="s">
-        <v>798</v>
+        <v>766</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6096,10 +6096,10 @@
         <v>138</v>
       </c>
       <c r="F61" s="6" t="s">
-        <v>799</v>
+        <v>767</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>800</v>
+        <v>768</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6119,10 +6119,10 @@
         <v>138</v>
       </c>
       <c r="F62" s="6" t="s">
-        <v>801</v>
+        <v>769</v>
       </c>
       <c r="G62" s="8" t="s">
-        <v>802</v>
+        <v>770</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6142,10 +6142,10 @@
         <v>138</v>
       </c>
       <c r="F63" s="6" t="s">
-        <v>803</v>
+        <v>771</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>804</v>
+        <v>772</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6165,10 +6165,10 @@
         <v>138</v>
       </c>
       <c r="F64" s="6" t="s">
-        <v>805</v>
+        <v>773</v>
       </c>
       <c r="G64" s="8" t="s">
-        <v>806</v>
+        <v>774</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6188,10 +6188,10 @@
         <v>138</v>
       </c>
       <c r="F65" s="6" t="s">
-        <v>807</v>
+        <v>775</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>808</v>
+        <v>776</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6211,10 +6211,10 @@
         <v>138</v>
       </c>
       <c r="F66" s="6" t="s">
-        <v>809</v>
+        <v>777</v>
       </c>
       <c r="G66" s="8" t="s">
-        <v>810</v>
+        <v>778</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6234,10 +6234,10 @@
         <v>138</v>
       </c>
       <c r="F67" s="6" t="s">
-        <v>811</v>
+        <v>779</v>
       </c>
       <c r="G67" s="8" t="s">
-        <v>812</v>
+        <v>780</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6257,10 +6257,10 @@
         <v>138</v>
       </c>
       <c r="F68" s="12" t="s">
-        <v>1299</v>
+        <v>1263</v>
       </c>
       <c r="G68" s="12" t="s">
-        <v>1300</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6280,10 +6280,10 @@
         <v>138</v>
       </c>
       <c r="F69" s="6" t="s">
-        <v>813</v>
+        <v>781</v>
       </c>
       <c r="G69" s="8" t="s">
-        <v>814</v>
+        <v>782</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6294,7 +6294,7 @@
         <v>141</v>
       </c>
       <c r="C70" s="16" t="s">
-        <v>1335</v>
+        <v>1299</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>188</v>
@@ -6303,10 +6303,10 @@
         <v>138</v>
       </c>
       <c r="F70" s="12" t="s">
-        <v>1333</v>
+        <v>1297</v>
       </c>
       <c r="G70" s="12" t="s">
-        <v>1334</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6326,10 +6326,10 @@
         <v>138</v>
       </c>
       <c r="F71" s="6" t="s">
-        <v>815</v>
+        <v>783</v>
       </c>
       <c r="G71" s="8" t="s">
-        <v>816</v>
+        <v>784</v>
       </c>
     </row>
     <row r="72" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6349,10 +6349,10 @@
         <v>138</v>
       </c>
       <c r="F72" s="6" t="s">
-        <v>817</v>
+        <v>785</v>
       </c>
       <c r="G72" s="8" t="s">
-        <v>818</v>
+        <v>786</v>
       </c>
     </row>
     <row r="73" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6372,10 +6372,10 @@
         <v>138</v>
       </c>
       <c r="F73" s="6" t="s">
-        <v>819</v>
+        <v>787</v>
       </c>
       <c r="G73" s="8" t="s">
-        <v>820</v>
+        <v>788</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6395,10 +6395,10 @@
         <v>138</v>
       </c>
       <c r="F74" s="6" t="s">
-        <v>821</v>
+        <v>789</v>
       </c>
       <c r="G74" s="8" t="s">
-        <v>822</v>
+        <v>790</v>
       </c>
     </row>
     <row r="75" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6418,10 +6418,10 @@
         <v>138</v>
       </c>
       <c r="F75" s="6" t="s">
-        <v>823</v>
+        <v>791</v>
       </c>
       <c r="G75" s="8" t="s">
-        <v>824</v>
+        <v>792</v>
       </c>
     </row>
     <row r="76" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6441,10 +6441,10 @@
         <v>138</v>
       </c>
       <c r="F76" s="6" t="s">
-        <v>825</v>
+        <v>793</v>
       </c>
       <c r="G76" s="8" t="s">
-        <v>826</v>
+        <v>794</v>
       </c>
     </row>
     <row r="77" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6464,10 +6464,10 @@
         <v>138</v>
       </c>
       <c r="F77" s="6" t="s">
-        <v>827</v>
+        <v>795</v>
       </c>
       <c r="G77" s="8" t="s">
-        <v>828</v>
+        <v>796</v>
       </c>
     </row>
     <row r="78" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6487,10 +6487,10 @@
         <v>138</v>
       </c>
       <c r="F78" s="9" t="s">
-        <v>829</v>
+        <v>797</v>
       </c>
       <c r="G78" s="10" t="s">
-        <v>830</v>
+        <v>798</v>
       </c>
     </row>
     <row r="79" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6510,10 +6510,10 @@
         <v>138</v>
       </c>
       <c r="F79" s="12" t="s">
-        <v>1331</v>
+        <v>1295</v>
       </c>
       <c r="G79" s="12" t="s">
-        <v>1332</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
@@ -6533,10 +6533,10 @@
         <v>138</v>
       </c>
       <c r="F80" s="15" t="s">
-        <v>831</v>
+        <v>799</v>
       </c>
       <c r="G80" s="15" t="s">
-        <v>832</v>
+        <v>800</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
@@ -6556,10 +6556,10 @@
         <v>138</v>
       </c>
       <c r="F81" s="11" t="s">
-        <v>1323</v>
+        <v>1287</v>
       </c>
       <c r="G81" s="11" t="s">
-        <v>1324</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
@@ -6579,10 +6579,10 @@
         <v>138</v>
       </c>
       <c r="F82" s="15" t="s">
-        <v>833</v>
+        <v>801</v>
       </c>
       <c r="G82" s="15" t="s">
-        <v>834</v>
+        <v>802</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
@@ -6602,10 +6602,10 @@
         <v>138</v>
       </c>
       <c r="F83" s="15" t="s">
-        <v>835</v>
+        <v>803</v>
       </c>
       <c r="G83" s="15" t="s">
-        <v>836</v>
+        <v>804</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
@@ -6625,10 +6625,10 @@
         <v>138</v>
       </c>
       <c r="F84" s="11" t="s">
-        <v>1313</v>
+        <v>1277</v>
       </c>
       <c r="G84" s="11" t="s">
-        <v>1314</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
@@ -6648,10 +6648,10 @@
         <v>138</v>
       </c>
       <c r="F85" s="11" t="s">
-        <v>1325</v>
+        <v>1289</v>
       </c>
       <c r="G85" s="11" t="s">
-        <v>1326</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
@@ -6671,10 +6671,10 @@
         <v>138</v>
       </c>
       <c r="F86" s="15" t="s">
-        <v>837</v>
+        <v>805</v>
       </c>
       <c r="G86" s="15" t="s">
-        <v>838</v>
+        <v>806</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
@@ -6694,10 +6694,10 @@
         <v>138</v>
       </c>
       <c r="F87" s="15" t="s">
-        <v>839</v>
+        <v>807</v>
       </c>
       <c r="G87" s="15" t="s">
-        <v>840</v>
+        <v>808</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
@@ -6717,10 +6717,10 @@
         <v>138</v>
       </c>
       <c r="F88" s="15" t="s">
-        <v>841</v>
+        <v>809</v>
       </c>
       <c r="G88" s="15" t="s">
-        <v>842</v>
+        <v>810</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
@@ -6740,10 +6740,10 @@
         <v>138</v>
       </c>
       <c r="F89" s="15" t="s">
-        <v>843</v>
+        <v>811</v>
       </c>
       <c r="G89" s="15" t="s">
-        <v>844</v>
+        <v>812</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
@@ -6763,10 +6763,10 @@
         <v>138</v>
       </c>
       <c r="F90" s="11" t="s">
-        <v>1315</v>
+        <v>1279</v>
       </c>
       <c r="G90" s="11" t="s">
-        <v>1316</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
@@ -6786,10 +6786,10 @@
         <v>138</v>
       </c>
       <c r="F91" s="15" t="s">
-        <v>845</v>
+        <v>813</v>
       </c>
       <c r="G91" s="15" t="s">
-        <v>846</v>
+        <v>814</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
@@ -6809,10 +6809,10 @@
         <v>138</v>
       </c>
       <c r="F92" s="15" t="s">
-        <v>847</v>
+        <v>815</v>
       </c>
       <c r="G92" s="15" t="s">
-        <v>848</v>
+        <v>816</v>
       </c>
     </row>
     <row r="93" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6832,10 +6832,10 @@
         <v>138</v>
       </c>
       <c r="F93" s="13" t="s">
-        <v>849</v>
+        <v>817</v>
       </c>
       <c r="G93" s="14" t="s">
-        <v>850</v>
+        <v>818</v>
       </c>
     </row>
     <row r="94" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6855,10 +6855,10 @@
         <v>138</v>
       </c>
       <c r="F94" s="6" t="s">
-        <v>851</v>
+        <v>819</v>
       </c>
       <c r="G94" s="8" t="s">
-        <v>852</v>
+        <v>820</v>
       </c>
     </row>
     <row r="95" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6878,10 +6878,10 @@
         <v>138</v>
       </c>
       <c r="F95" s="6" t="s">
-        <v>853</v>
+        <v>821</v>
       </c>
       <c r="G95" s="8" t="s">
-        <v>854</v>
+        <v>822</v>
       </c>
     </row>
     <row r="96" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6901,10 +6901,10 @@
         <v>138</v>
       </c>
       <c r="F96" s="6" t="s">
-        <v>855</v>
+        <v>823</v>
       </c>
       <c r="G96" s="8" t="s">
-        <v>856</v>
+        <v>824</v>
       </c>
     </row>
     <row r="97" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6924,10 +6924,10 @@
         <v>138</v>
       </c>
       <c r="F97" s="6" t="s">
-        <v>857</v>
+        <v>825</v>
       </c>
       <c r="G97" s="8" t="s">
-        <v>858</v>
+        <v>826</v>
       </c>
     </row>
     <row r="98" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6947,10 +6947,10 @@
         <v>138</v>
       </c>
       <c r="F98" s="6" t="s">
-        <v>859</v>
+        <v>827</v>
       </c>
       <c r="G98" s="8" t="s">
-        <v>860</v>
+        <v>828</v>
       </c>
     </row>
     <row r="99" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6970,10 +6970,10 @@
         <v>138</v>
       </c>
       <c r="F99" s="6" t="s">
-        <v>861</v>
+        <v>829</v>
       </c>
       <c r="G99" s="8" t="s">
-        <v>862</v>
+        <v>830</v>
       </c>
     </row>
     <row r="100" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6993,10 +6993,10 @@
         <v>138</v>
       </c>
       <c r="F100" s="5" t="s">
-        <v>1348</v>
+        <v>1312</v>
       </c>
       <c r="G100" s="7" t="s">
-        <v>1349</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="101" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7016,10 +7016,10 @@
         <v>138</v>
       </c>
       <c r="F101" s="6" t="s">
-        <v>863</v>
+        <v>831</v>
       </c>
       <c r="G101" s="8" t="s">
-        <v>864</v>
+        <v>832</v>
       </c>
     </row>
     <row r="102" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7039,10 +7039,10 @@
         <v>138</v>
       </c>
       <c r="F102" s="6" t="s">
-        <v>865</v>
+        <v>833</v>
       </c>
       <c r="G102" s="8" t="s">
-        <v>866</v>
+        <v>834</v>
       </c>
     </row>
     <row r="103" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7062,10 +7062,10 @@
         <v>138</v>
       </c>
       <c r="F103" s="6" t="s">
-        <v>867</v>
+        <v>835</v>
       </c>
       <c r="G103" s="8" t="s">
-        <v>868</v>
+        <v>836</v>
       </c>
     </row>
     <row r="104" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7085,10 +7085,10 @@
         <v>138</v>
       </c>
       <c r="F104" s="6" t="s">
-        <v>869</v>
+        <v>837</v>
       </c>
       <c r="G104" s="8" t="s">
-        <v>870</v>
+        <v>838</v>
       </c>
     </row>
     <row r="105" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7108,10 +7108,10 @@
         <v>138</v>
       </c>
       <c r="F105" s="12" t="s">
-        <v>1338</v>
+        <v>1302</v>
       </c>
       <c r="G105" s="12" t="s">
-        <v>1339</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="106" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7131,10 +7131,10 @@
         <v>138</v>
       </c>
       <c r="F106" s="6" t="s">
-        <v>871</v>
+        <v>839</v>
       </c>
       <c r="G106" s="8" t="s">
-        <v>872</v>
+        <v>840</v>
       </c>
     </row>
     <row r="107" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7154,10 +7154,10 @@
         <v>138</v>
       </c>
       <c r="F107" s="5" t="s">
-        <v>1346</v>
+        <v>1310</v>
       </c>
       <c r="G107" s="7" t="s">
-        <v>1347</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="108" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7177,10 +7177,10 @@
         <v>138</v>
       </c>
       <c r="F108" s="6" t="s">
-        <v>873</v>
+        <v>841</v>
       </c>
       <c r="G108" s="8" t="s">
-        <v>874</v>
+        <v>842</v>
       </c>
     </row>
     <row r="109" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7200,10 +7200,10 @@
         <v>138</v>
       </c>
       <c r="F109" s="6" t="s">
-        <v>875</v>
+        <v>843</v>
       </c>
       <c r="G109" s="8" t="s">
-        <v>876</v>
+        <v>844</v>
       </c>
     </row>
     <row r="110" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7223,10 +7223,10 @@
         <v>138</v>
       </c>
       <c r="F110" s="6" t="s">
-        <v>877</v>
+        <v>845</v>
       </c>
       <c r="G110" s="8" t="s">
-        <v>878</v>
+        <v>846</v>
       </c>
     </row>
     <row r="111" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7245,11 +7245,11 @@
       <c r="E111" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F111" s="6" t="s">
-        <v>879</v>
-      </c>
-      <c r="G111" s="8" t="s">
-        <v>880</v>
+      <c r="F111" s="5" t="s">
+        <v>1314</v>
+      </c>
+      <c r="G111" s="7" t="s">
+        <v>1315</v>
       </c>
     </row>
     <row r="112" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7269,10 +7269,10 @@
         <v>138</v>
       </c>
       <c r="F112" s="17" t="s">
-        <v>1344</v>
+        <v>1308</v>
       </c>
       <c r="G112" s="17" t="s">
-        <v>1345</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="113" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7292,10 +7292,10 @@
         <v>138</v>
       </c>
       <c r="F113" s="6" t="s">
-        <v>881</v>
+        <v>847</v>
       </c>
       <c r="G113" s="8" t="s">
-        <v>882</v>
+        <v>848</v>
       </c>
     </row>
     <row r="114" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7315,10 +7315,10 @@
         <v>138</v>
       </c>
       <c r="F114" s="12" t="s">
-        <v>1340</v>
+        <v>1304</v>
       </c>
       <c r="G114" s="12" t="s">
-        <v>1341</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="115" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7338,10 +7338,10 @@
         <v>138</v>
       </c>
       <c r="F115" s="6" t="s">
-        <v>883</v>
+        <v>849</v>
       </c>
       <c r="G115" s="8" t="s">
-        <v>884</v>
+        <v>850</v>
       </c>
     </row>
     <row r="116" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7361,10 +7361,10 @@
         <v>138</v>
       </c>
       <c r="F116" s="6" t="s">
-        <v>885</v>
+        <v>851</v>
       </c>
       <c r="G116" s="8" t="s">
-        <v>886</v>
+        <v>852</v>
       </c>
     </row>
     <row r="117" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7384,10 +7384,10 @@
         <v>138</v>
       </c>
       <c r="F117" s="6" t="s">
-        <v>887</v>
+        <v>853</v>
       </c>
       <c r="G117" s="8" t="s">
-        <v>888</v>
+        <v>854</v>
       </c>
     </row>
     <row r="118" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7404,10 +7404,10 @@
         <v>138</v>
       </c>
       <c r="F118" s="6" t="s">
-        <v>889</v>
+        <v>855</v>
       </c>
       <c r="G118" s="8" t="s">
-        <v>890</v>
+        <v>856</v>
       </c>
     </row>
     <row r="119" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7427,10 +7427,10 @@
         <v>138</v>
       </c>
       <c r="F119" s="12" t="s">
-        <v>1336</v>
+        <v>1300</v>
       </c>
       <c r="G119" s="12" t="s">
-        <v>1337</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="120" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7450,10 +7450,10 @@
         <v>138</v>
       </c>
       <c r="F120" s="6" t="s">
-        <v>891</v>
+        <v>857</v>
       </c>
       <c r="G120" s="8" t="s">
-        <v>892</v>
+        <v>858</v>
       </c>
     </row>
     <row r="121" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7473,10 +7473,10 @@
         <v>138</v>
       </c>
       <c r="F121" s="12" t="s">
-        <v>1342</v>
+        <v>1306</v>
       </c>
       <c r="G121" s="12" t="s">
-        <v>1343</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="122" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7496,10 +7496,10 @@
         <v>138</v>
       </c>
       <c r="F122" s="6" t="s">
-        <v>893</v>
+        <v>859</v>
       </c>
       <c r="G122" s="8" t="s">
-        <v>894</v>
+        <v>860</v>
       </c>
     </row>
     <row r="123" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7519,10 +7519,10 @@
         <v>138</v>
       </c>
       <c r="F123" s="6" t="s">
-        <v>895</v>
+        <v>861</v>
       </c>
       <c r="G123" s="8" t="s">
-        <v>896</v>
+        <v>862</v>
       </c>
     </row>
     <row r="124" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7542,10 +7542,10 @@
         <v>138</v>
       </c>
       <c r="F124" s="6" t="s">
-        <v>897</v>
+        <v>863</v>
       </c>
       <c r="G124" s="8" t="s">
-        <v>898</v>
+        <v>864</v>
       </c>
     </row>
     <row r="125" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7565,10 +7565,10 @@
         <v>138</v>
       </c>
       <c r="F125" s="12" t="s">
-        <v>1305</v>
+        <v>1269</v>
       </c>
       <c r="G125" s="12" t="s">
-        <v>1306</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="126" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7588,10 +7588,10 @@
         <v>138</v>
       </c>
       <c r="F126" s="12" t="s">
-        <v>1319</v>
+        <v>1283</v>
       </c>
       <c r="G126" s="12" t="s">
-        <v>1320</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="127" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7611,10 +7611,10 @@
         <v>138</v>
       </c>
       <c r="F127" s="6" t="s">
-        <v>899</v>
+        <v>865</v>
       </c>
       <c r="G127" s="8" t="s">
-        <v>900</v>
+        <v>866</v>
       </c>
     </row>
     <row r="128" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7634,10 +7634,10 @@
         <v>138</v>
       </c>
       <c r="F128" s="6" t="s">
-        <v>901</v>
+        <v>867</v>
       </c>
       <c r="G128" s="8" t="s">
-        <v>902</v>
+        <v>868</v>
       </c>
     </row>
     <row r="129" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7657,10 +7657,10 @@
         <v>138</v>
       </c>
       <c r="F129" s="6" t="s">
-        <v>903</v>
+        <v>869</v>
       </c>
       <c r="G129" s="8" t="s">
-        <v>904</v>
+        <v>870</v>
       </c>
     </row>
     <row r="130" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7680,10 +7680,10 @@
         <v>138</v>
       </c>
       <c r="F130" s="12" t="s">
-        <v>1327</v>
+        <v>1291</v>
       </c>
       <c r="G130" s="12" t="s">
-        <v>1328</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="131" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7703,10 +7703,10 @@
         <v>138</v>
       </c>
       <c r="F131" s="6" t="s">
-        <v>905</v>
+        <v>871</v>
       </c>
       <c r="G131" s="8" t="s">
-        <v>906</v>
+        <v>872</v>
       </c>
     </row>
     <row r="132" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7726,10 +7726,10 @@
         <v>138</v>
       </c>
       <c r="F132" s="6" t="s">
-        <v>907</v>
+        <v>873</v>
       </c>
       <c r="G132" s="8" t="s">
-        <v>908</v>
+        <v>874</v>
       </c>
     </row>
     <row r="133" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7749,10 +7749,10 @@
         <v>138</v>
       </c>
       <c r="F133" s="6" t="s">
-        <v>909</v>
+        <v>875</v>
       </c>
       <c r="G133" s="8" t="s">
-        <v>910</v>
+        <v>876</v>
       </c>
     </row>
     <row r="134" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7772,10 +7772,10 @@
         <v>138</v>
       </c>
       <c r="F134" s="6" t="s">
-        <v>911</v>
+        <v>877</v>
       </c>
       <c r="G134" s="8" t="s">
-        <v>912</v>
+        <v>878</v>
       </c>
     </row>
     <row r="135" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7795,10 +7795,10 @@
         <v>138</v>
       </c>
       <c r="F135" s="12" t="s">
-        <v>1311</v>
+        <v>1275</v>
       </c>
       <c r="G135" s="12" t="s">
-        <v>1312</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="136" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7818,10 +7818,10 @@
         <v>138</v>
       </c>
       <c r="F136" s="6" t="s">
-        <v>913</v>
+        <v>879</v>
       </c>
       <c r="G136" s="8" t="s">
-        <v>914</v>
+        <v>880</v>
       </c>
     </row>
     <row r="137" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7841,10 +7841,10 @@
         <v>138</v>
       </c>
       <c r="F137" s="6" t="s">
-        <v>915</v>
+        <v>881</v>
       </c>
       <c r="G137" s="8" t="s">
-        <v>916</v>
+        <v>882</v>
       </c>
     </row>
     <row r="138" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7864,10 +7864,10 @@
         <v>138</v>
       </c>
       <c r="F138" s="6" t="s">
-        <v>917</v>
+        <v>883</v>
       </c>
       <c r="G138" s="8" t="s">
-        <v>918</v>
+        <v>884</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.3">
@@ -7887,10 +7887,10 @@
         <v>138</v>
       </c>
       <c r="F139" s="9" t="s">
-        <v>919</v>
+        <v>885</v>
       </c>
       <c r="G139" s="10" t="s">
-        <v>920</v>
+        <v>886</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.3">
@@ -7910,10 +7910,10 @@
         <v>138</v>
       </c>
       <c r="F140" s="15" t="s">
-        <v>921</v>
+        <v>887</v>
       </c>
       <c r="G140" s="15" t="s">
-        <v>922</v>
+        <v>888</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.3">
@@ -7933,10 +7933,10 @@
         <v>138</v>
       </c>
       <c r="F141" s="11" t="s">
-        <v>1301</v>
+        <v>1265</v>
       </c>
       <c r="G141" s="11" t="s">
-        <v>1302</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.3">
@@ -7956,10 +7956,10 @@
         <v>138</v>
       </c>
       <c r="F142" s="15" t="s">
-        <v>923</v>
+        <v>889</v>
       </c>
       <c r="G142" s="15" t="s">
-        <v>924</v>
+        <v>890</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.3">
@@ -7979,10 +7979,10 @@
         <v>138</v>
       </c>
       <c r="F143" s="11" t="s">
-        <v>1329</v>
+        <v>1293</v>
       </c>
       <c r="G143" s="11" t="s">
-        <v>1330</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.3">
@@ -8002,10 +8002,10 @@
         <v>138</v>
       </c>
       <c r="F144" s="11" t="s">
-        <v>1303</v>
+        <v>1267</v>
       </c>
       <c r="G144" s="11" t="s">
-        <v>1304</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.3">
@@ -8025,10 +8025,10 @@
         <v>138</v>
       </c>
       <c r="F145" s="15" t="s">
-        <v>925</v>
+        <v>891</v>
       </c>
       <c r="G145" s="15" t="s">
-        <v>926</v>
+        <v>892</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.3">
@@ -8048,10 +8048,10 @@
         <v>138</v>
       </c>
       <c r="F146" s="11" t="s">
-        <v>1309</v>
+        <v>1273</v>
       </c>
       <c r="G146" s="11" t="s">
-        <v>1310</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.3">
@@ -8071,10 +8071,10 @@
         <v>138</v>
       </c>
       <c r="F147" s="15" t="s">
-        <v>927</v>
+        <v>893</v>
       </c>
       <c r="G147" s="15" t="s">
-        <v>928</v>
+        <v>894</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.3">
@@ -8094,10 +8094,10 @@
         <v>138</v>
       </c>
       <c r="F148" s="15" t="s">
-        <v>929</v>
+        <v>895</v>
       </c>
       <c r="G148" s="15" t="s">
-        <v>930</v>
+        <v>896</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.3">
@@ -8117,10 +8117,10 @@
         <v>138</v>
       </c>
       <c r="F149" s="15" t="s">
-        <v>931</v>
+        <v>897</v>
       </c>
       <c r="G149" s="15" t="s">
-        <v>932</v>
+        <v>898</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.3">
@@ -8140,10 +8140,10 @@
         <v>138</v>
       </c>
       <c r="F150" s="15" t="s">
-        <v>933</v>
+        <v>899</v>
       </c>
       <c r="G150" s="15" t="s">
-        <v>934</v>
+        <v>900</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.3">
@@ -8163,10 +8163,10 @@
         <v>138</v>
       </c>
       <c r="F151" s="15" t="s">
-        <v>935</v>
+        <v>901</v>
       </c>
       <c r="G151" s="15" t="s">
-        <v>936</v>
+        <v>902</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.3">
@@ -8186,10 +8186,10 @@
         <v>138</v>
       </c>
       <c r="F152" s="11" t="s">
-        <v>1317</v>
+        <v>1281</v>
       </c>
       <c r="G152" s="11" t="s">
-        <v>1318</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="153" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8209,10 +8209,10 @@
         <v>138</v>
       </c>
       <c r="F153" s="13" t="s">
-        <v>937</v>
+        <v>903</v>
       </c>
       <c r="G153" s="14" t="s">
-        <v>938</v>
+        <v>904</v>
       </c>
     </row>
     <row r="154" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8232,10 +8232,10 @@
         <v>138</v>
       </c>
       <c r="F154" s="6" t="s">
-        <v>939</v>
+        <v>905</v>
       </c>
       <c r="G154" s="8" t="s">
-        <v>940</v>
+        <v>906</v>
       </c>
     </row>
     <row r="155" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8255,10 +8255,10 @@
         <v>138</v>
       </c>
       <c r="F155" s="6" t="s">
-        <v>941</v>
+        <v>907</v>
       </c>
       <c r="G155" s="8" t="s">
-        <v>942</v>
+        <v>908</v>
       </c>
     </row>
     <row r="156" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8278,10 +8278,10 @@
         <v>138</v>
       </c>
       <c r="F156" s="6" t="s">
-        <v>943</v>
+        <v>909</v>
       </c>
       <c r="G156" s="8" t="s">
-        <v>944</v>
+        <v>910</v>
       </c>
     </row>
     <row r="157" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8301,10 +8301,10 @@
         <v>138</v>
       </c>
       <c r="F157" s="12" t="s">
-        <v>1321</v>
+        <v>1285</v>
       </c>
       <c r="G157" s="12" t="s">
-        <v>1322</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="158" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8324,10 +8324,10 @@
         <v>138</v>
       </c>
       <c r="F158" s="6" t="s">
-        <v>945</v>
+        <v>911</v>
       </c>
       <c r="G158" s="8" t="s">
-        <v>946</v>
+        <v>912</v>
       </c>
     </row>
     <row r="159" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8347,10 +8347,10 @@
         <v>138</v>
       </c>
       <c r="F159" s="6" t="s">
-        <v>947</v>
+        <v>913</v>
       </c>
       <c r="G159" s="8" t="s">
-        <v>948</v>
+        <v>914</v>
       </c>
     </row>
     <row r="160" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8370,10 +8370,10 @@
         <v>138</v>
       </c>
       <c r="F160" s="12" t="s">
-        <v>1307</v>
+        <v>1271</v>
       </c>
       <c r="G160" s="12" t="s">
-        <v>1308</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="161" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8393,10 +8393,10 @@
         <v>138</v>
       </c>
       <c r="F161" s="6" t="s">
-        <v>949</v>
+        <v>915</v>
       </c>
       <c r="G161" s="8" t="s">
-        <v>950</v>
+        <v>916</v>
       </c>
     </row>
     <row r="162" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8416,10 +8416,10 @@
         <v>138</v>
       </c>
       <c r="F162" s="6" t="s">
-        <v>951</v>
+        <v>917</v>
       </c>
       <c r="G162" s="8" t="s">
-        <v>952</v>
+        <v>918</v>
       </c>
     </row>
     <row r="163" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8439,10 +8439,10 @@
         <v>138</v>
       </c>
       <c r="F163" s="6" t="s">
-        <v>953</v>
+        <v>919</v>
       </c>
       <c r="G163" s="8" t="s">
-        <v>954</v>
+        <v>920</v>
       </c>
     </row>
     <row r="164" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8462,10 +8462,10 @@
         <v>138</v>
       </c>
       <c r="F164" s="6" t="s">
-        <v>955</v>
+        <v>921</v>
       </c>
       <c r="G164" s="8" t="s">
-        <v>956</v>
+        <v>922</v>
       </c>
     </row>
     <row r="165" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8485,10 +8485,10 @@
         <v>138</v>
       </c>
       <c r="F165" s="6" t="s">
-        <v>957</v>
+        <v>923</v>
       </c>
       <c r="G165" s="8" t="s">
-        <v>958</v>
+        <v>924</v>
       </c>
     </row>
     <row r="166" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8508,10 +8508,10 @@
         <v>138</v>
       </c>
       <c r="F166" s="6" t="s">
-        <v>959</v>
+        <v>925</v>
       </c>
       <c r="G166" s="8" t="s">
-        <v>960</v>
+        <v>926</v>
       </c>
     </row>
     <row r="167" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8531,10 +8531,10 @@
         <v>138</v>
       </c>
       <c r="F167" s="6" t="s">
-        <v>961</v>
+        <v>927</v>
       </c>
       <c r="G167" s="8" t="s">
-        <v>962</v>
+        <v>928</v>
       </c>
     </row>
     <row r="168" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8554,10 +8554,10 @@
         <v>138</v>
       </c>
       <c r="F168" s="6" t="s">
-        <v>963</v>
+        <v>929</v>
       </c>
       <c r="G168" s="8" t="s">
-        <v>964</v>
+        <v>930</v>
       </c>
     </row>
     <row r="169" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8577,10 +8577,10 @@
         <v>138</v>
       </c>
       <c r="F169" s="6" t="s">
-        <v>965</v>
+        <v>931</v>
       </c>
       <c r="G169" s="8" t="s">
-        <v>966</v>
+        <v>932</v>
       </c>
     </row>
     <row r="170" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8600,10 +8600,10 @@
         <v>138</v>
       </c>
       <c r="F170" s="6" t="s">
-        <v>967</v>
+        <v>933</v>
       </c>
       <c r="G170" s="8" t="s">
-        <v>968</v>
+        <v>934</v>
       </c>
     </row>
     <row r="171" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8623,10 +8623,10 @@
         <v>138</v>
       </c>
       <c r="F171" s="6" t="s">
-        <v>969</v>
+        <v>935</v>
       </c>
       <c r="G171" s="8" t="s">
-        <v>970</v>
+        <v>936</v>
       </c>
     </row>
     <row r="172" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8646,10 +8646,10 @@
         <v>138</v>
       </c>
       <c r="F172" s="6" t="s">
-        <v>971</v>
+        <v>937</v>
       </c>
       <c r="G172" s="8" t="s">
-        <v>972</v>
+        <v>938</v>
       </c>
     </row>
     <row r="173" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8669,10 +8669,10 @@
         <v>138</v>
       </c>
       <c r="F173" s="6" t="s">
-        <v>973</v>
+        <v>939</v>
       </c>
       <c r="G173" s="8" t="s">
-        <v>974</v>
+        <v>940</v>
       </c>
     </row>
     <row r="174" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8692,10 +8692,10 @@
         <v>138</v>
       </c>
       <c r="F174" s="6" t="s">
-        <v>975</v>
+        <v>941</v>
       </c>
       <c r="G174" s="8" t="s">
-        <v>976</v>
+        <v>942</v>
       </c>
     </row>
     <row r="175" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8715,10 +8715,10 @@
         <v>138</v>
       </c>
       <c r="F175" s="6" t="s">
-        <v>977</v>
+        <v>943</v>
       </c>
       <c r="G175" s="8" t="s">
-        <v>978</v>
+        <v>944</v>
       </c>
     </row>
     <row r="176" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8738,10 +8738,10 @@
         <v>138</v>
       </c>
       <c r="F176" s="6" t="s">
-        <v>979</v>
+        <v>945</v>
       </c>
       <c r="G176" s="8" t="s">
-        <v>980</v>
+        <v>946</v>
       </c>
     </row>
     <row r="177" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8761,10 +8761,10 @@
         <v>138</v>
       </c>
       <c r="F177" s="6" t="s">
-        <v>981</v>
+        <v>947</v>
       </c>
       <c r="G177" s="8" t="s">
-        <v>982</v>
+        <v>948</v>
       </c>
     </row>
     <row r="178" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8784,10 +8784,10 @@
         <v>138</v>
       </c>
       <c r="F178" s="6" t="s">
-        <v>983</v>
+        <v>949</v>
       </c>
       <c r="G178" s="8" t="s">
-        <v>984</v>
+        <v>950</v>
       </c>
     </row>
     <row r="179" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8807,10 +8807,10 @@
         <v>138</v>
       </c>
       <c r="F179" s="6" t="s">
-        <v>985</v>
+        <v>951</v>
       </c>
       <c r="G179" s="8" t="s">
-        <v>986</v>
+        <v>952</v>
       </c>
     </row>
     <row r="180" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8830,10 +8830,10 @@
         <v>138</v>
       </c>
       <c r="F180" s="6" t="s">
-        <v>987</v>
+        <v>953</v>
       </c>
       <c r="G180" s="8" t="s">
-        <v>988</v>
+        <v>954</v>
       </c>
     </row>
     <row r="181" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8853,10 +8853,10 @@
         <v>138</v>
       </c>
       <c r="F181" s="6" t="s">
-        <v>989</v>
+        <v>955</v>
       </c>
       <c r="G181" s="8" t="s">
-        <v>990</v>
+        <v>956</v>
       </c>
     </row>
     <row r="182" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8876,10 +8876,10 @@
         <v>138</v>
       </c>
       <c r="F182" s="6" t="s">
-        <v>991</v>
+        <v>957</v>
       </c>
       <c r="G182" s="8" t="s">
-        <v>992</v>
+        <v>958</v>
       </c>
     </row>
     <row r="183" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8899,10 +8899,10 @@
         <v>138</v>
       </c>
       <c r="F183" s="6" t="s">
-        <v>993</v>
+        <v>959</v>
       </c>
       <c r="G183" s="8" t="s">
-        <v>994</v>
+        <v>960</v>
       </c>
     </row>
     <row r="184" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8922,10 +8922,10 @@
         <v>138</v>
       </c>
       <c r="F184" s="6" t="s">
-        <v>995</v>
+        <v>961</v>
       </c>
       <c r="G184" s="8" t="s">
-        <v>996</v>
+        <v>962</v>
       </c>
     </row>
     <row r="185" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8945,10 +8945,10 @@
         <v>138</v>
       </c>
       <c r="F185" s="6" t="s">
-        <v>997</v>
+        <v>963</v>
       </c>
       <c r="G185" s="8" t="s">
-        <v>998</v>
+        <v>964</v>
       </c>
     </row>
     <row r="186" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8968,10 +8968,10 @@
         <v>138</v>
       </c>
       <c r="F186" s="6" t="s">
-        <v>999</v>
+        <v>965</v>
       </c>
       <c r="G186" s="8" t="s">
-        <v>1000</v>
+        <v>966</v>
       </c>
     </row>
     <row r="187" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8991,10 +8991,10 @@
         <v>138</v>
       </c>
       <c r="F187" s="6" t="s">
-        <v>1001</v>
+        <v>967</v>
       </c>
       <c r="G187" s="8" t="s">
-        <v>1002</v>
+        <v>968</v>
       </c>
     </row>
     <row r="188" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9014,10 +9014,10 @@
         <v>138</v>
       </c>
       <c r="F188" s="6" t="s">
-        <v>1003</v>
+        <v>969</v>
       </c>
       <c r="G188" s="8" t="s">
-        <v>1004</v>
+        <v>970</v>
       </c>
     </row>
     <row r="189" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9037,10 +9037,10 @@
         <v>138</v>
       </c>
       <c r="F189" s="6" t="s">
-        <v>1005</v>
+        <v>971</v>
       </c>
       <c r="G189" s="8" t="s">
-        <v>1006</v>
+        <v>972</v>
       </c>
     </row>
     <row r="190" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9060,10 +9060,10 @@
         <v>138</v>
       </c>
       <c r="F190" s="6" t="s">
-        <v>1007</v>
+        <v>973</v>
       </c>
       <c r="G190" s="8" t="s">
-        <v>1008</v>
+        <v>974</v>
       </c>
     </row>
     <row r="191" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9083,10 +9083,10 @@
         <v>138</v>
       </c>
       <c r="F191" s="6" t="s">
-        <v>1009</v>
+        <v>975</v>
       </c>
       <c r="G191" s="8" t="s">
-        <v>1010</v>
+        <v>976</v>
       </c>
     </row>
     <row r="192" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9106,10 +9106,10 @@
         <v>138</v>
       </c>
       <c r="F192" s="6" t="s">
-        <v>1011</v>
+        <v>977</v>
       </c>
       <c r="G192" s="8" t="s">
-        <v>1012</v>
+        <v>978</v>
       </c>
     </row>
     <row r="193" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9129,10 +9129,10 @@
         <v>138</v>
       </c>
       <c r="F193" s="6" t="s">
-        <v>1013</v>
+        <v>979</v>
       </c>
       <c r="G193" s="8" t="s">
-        <v>1014</v>
+        <v>980</v>
       </c>
     </row>
     <row r="194" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9152,10 +9152,10 @@
         <v>138</v>
       </c>
       <c r="F194" s="6" t="s">
-        <v>1015</v>
+        <v>981</v>
       </c>
       <c r="G194" s="8" t="s">
-        <v>1016</v>
+        <v>982</v>
       </c>
     </row>
     <row r="195" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9175,10 +9175,10 @@
         <v>138</v>
       </c>
       <c r="F195" s="6" t="s">
-        <v>1017</v>
+        <v>983</v>
       </c>
       <c r="G195" s="8" t="s">
-        <v>1018</v>
+        <v>984</v>
       </c>
     </row>
     <row r="196" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9198,10 +9198,10 @@
         <v>138</v>
       </c>
       <c r="F196" s="6" t="s">
-        <v>1019</v>
+        <v>985</v>
       </c>
       <c r="G196" s="8" t="s">
-        <v>1020</v>
+        <v>986</v>
       </c>
     </row>
     <row r="197" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9221,10 +9221,10 @@
         <v>138</v>
       </c>
       <c r="F197" s="6" t="s">
-        <v>1021</v>
+        <v>987</v>
       </c>
       <c r="G197" s="8" t="s">
-        <v>1022</v>
+        <v>988</v>
       </c>
     </row>
     <row r="198" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9244,10 +9244,10 @@
         <v>138</v>
       </c>
       <c r="F198" s="6" t="s">
-        <v>1023</v>
+        <v>989</v>
       </c>
       <c r="G198" s="8" t="s">
-        <v>1024</v>
+        <v>990</v>
       </c>
     </row>
     <row r="199" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9267,10 +9267,10 @@
         <v>138</v>
       </c>
       <c r="F199" s="6" t="s">
-        <v>1025</v>
+        <v>991</v>
       </c>
       <c r="G199" s="8" t="s">
-        <v>1026</v>
+        <v>992</v>
       </c>
     </row>
     <row r="200" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9290,10 +9290,10 @@
         <v>138</v>
       </c>
       <c r="F200" s="6" t="s">
-        <v>1027</v>
+        <v>993</v>
       </c>
       <c r="G200" s="8" t="s">
-        <v>1028</v>
+        <v>994</v>
       </c>
     </row>
     <row r="201" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9313,10 +9313,10 @@
         <v>138</v>
       </c>
       <c r="F201" s="6" t="s">
-        <v>1029</v>
+        <v>995</v>
       </c>
       <c r="G201" s="8" t="s">
-        <v>1030</v>
+        <v>996</v>
       </c>
     </row>
     <row r="202" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9336,10 +9336,10 @@
         <v>138</v>
       </c>
       <c r="F202" s="6" t="s">
-        <v>1031</v>
+        <v>997</v>
       </c>
       <c r="G202" s="8" t="s">
-        <v>1032</v>
+        <v>998</v>
       </c>
     </row>
     <row r="203" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9359,10 +9359,10 @@
         <v>138</v>
       </c>
       <c r="F203" s="6" t="s">
-        <v>1033</v>
+        <v>999</v>
       </c>
       <c r="G203" s="8" t="s">
-        <v>1034</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="204" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9382,10 +9382,10 @@
         <v>138</v>
       </c>
       <c r="F204" s="6" t="s">
-        <v>1035</v>
+        <v>1001</v>
       </c>
       <c r="G204" s="8" t="s">
-        <v>1036</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="205" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9405,10 +9405,10 @@
         <v>138</v>
       </c>
       <c r="F205" s="6" t="s">
-        <v>1037</v>
+        <v>1003</v>
       </c>
       <c r="G205" s="8" t="s">
-        <v>1038</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="206" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9428,10 +9428,10 @@
         <v>138</v>
       </c>
       <c r="F206" s="6" t="s">
-        <v>1039</v>
+        <v>1005</v>
       </c>
       <c r="G206" s="8" t="s">
-        <v>1040</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="207" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9451,10 +9451,10 @@
         <v>138</v>
       </c>
       <c r="F207" s="6" t="s">
-        <v>1041</v>
+        <v>1007</v>
       </c>
       <c r="G207" s="8" t="s">
-        <v>1042</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="208" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9474,10 +9474,10 @@
         <v>138</v>
       </c>
       <c r="F208" s="6" t="s">
-        <v>1043</v>
+        <v>1009</v>
       </c>
       <c r="G208" s="8" t="s">
-        <v>1044</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="209" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9497,10 +9497,10 @@
         <v>138</v>
       </c>
       <c r="F209" s="6" t="s">
-        <v>1045</v>
+        <v>1011</v>
       </c>
       <c r="G209" s="8" t="s">
-        <v>1046</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="210" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9520,10 +9520,10 @@
         <v>138</v>
       </c>
       <c r="F210" s="6" t="s">
-        <v>1047</v>
+        <v>1013</v>
       </c>
       <c r="G210" s="8" t="s">
-        <v>1048</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="211" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9543,10 +9543,10 @@
         <v>138</v>
       </c>
       <c r="F211" s="6" t="s">
-        <v>1049</v>
+        <v>1015</v>
       </c>
       <c r="G211" s="8" t="s">
-        <v>1050</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="212" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9566,10 +9566,10 @@
         <v>138</v>
       </c>
       <c r="F212" s="6" t="s">
-        <v>1051</v>
+        <v>1017</v>
       </c>
       <c r="G212" s="8" t="s">
-        <v>1052</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="213" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9589,10 +9589,10 @@
         <v>138</v>
       </c>
       <c r="F213" s="6" t="s">
-        <v>1053</v>
+        <v>1019</v>
       </c>
       <c r="G213" s="8" t="s">
-        <v>1054</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="214" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9612,10 +9612,10 @@
         <v>138</v>
       </c>
       <c r="F214" s="6" t="s">
-        <v>1055</v>
+        <v>1021</v>
       </c>
       <c r="G214" s="8" t="s">
-        <v>1056</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="215" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9635,10 +9635,10 @@
         <v>138</v>
       </c>
       <c r="F215" s="6" t="s">
-        <v>1057</v>
+        <v>1023</v>
       </c>
       <c r="G215" s="8" t="s">
-        <v>1058</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="216" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9658,10 +9658,10 @@
         <v>138</v>
       </c>
       <c r="F216" s="6" t="s">
-        <v>1059</v>
+        <v>1025</v>
       </c>
       <c r="G216" s="8" t="s">
-        <v>1060</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="217" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9681,10 +9681,10 @@
         <v>138</v>
       </c>
       <c r="F217" s="6" t="s">
-        <v>1061</v>
+        <v>1027</v>
       </c>
       <c r="G217" s="8" t="s">
-        <v>1062</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="218" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9704,10 +9704,10 @@
         <v>138</v>
       </c>
       <c r="F218" s="6" t="s">
-        <v>1063</v>
+        <v>1029</v>
       </c>
       <c r="G218" s="8" t="s">
-        <v>1064</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.3">
@@ -9727,10 +9727,10 @@
         <v>138</v>
       </c>
       <c r="F219" s="9" t="s">
-        <v>1065</v>
+        <v>1031</v>
       </c>
       <c r="G219" s="10" t="s">
-        <v>1066</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.3">
@@ -9750,10 +9750,10 @@
         <v>138</v>
       </c>
       <c r="F220" s="11" t="s">
-        <v>1067</v>
+        <v>1033</v>
       </c>
       <c r="G220" s="11" t="s">
-        <v>1068</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.3">
@@ -9773,10 +9773,10 @@
         <v>138</v>
       </c>
       <c r="F221" s="11" t="s">
-        <v>1069</v>
+        <v>1035</v>
       </c>
       <c r="G221" s="11" t="s">
-        <v>1070</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.3">
@@ -9796,10 +9796,10 @@
         <v>138</v>
       </c>
       <c r="F222" s="11" t="s">
-        <v>1071</v>
+        <v>1037</v>
       </c>
       <c r="G222" s="11" t="s">
-        <v>1072</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.3">
@@ -9819,10 +9819,10 @@
         <v>138</v>
       </c>
       <c r="F223" s="11" t="s">
-        <v>1073</v>
+        <v>1039</v>
       </c>
       <c r="G223" s="11" t="s">
-        <v>1074</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.3">
@@ -9842,10 +9842,10 @@
         <v>138</v>
       </c>
       <c r="F224" s="11" t="s">
-        <v>1075</v>
+        <v>1041</v>
       </c>
       <c r="G224" s="11" t="s">
-        <v>1076</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.3">
@@ -9865,10 +9865,10 @@
         <v>138</v>
       </c>
       <c r="F225" s="11" t="s">
-        <v>1077</v>
+        <v>1043</v>
       </c>
       <c r="G225" s="11" t="s">
-        <v>1078</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.3">
@@ -9888,10 +9888,10 @@
         <v>138</v>
       </c>
       <c r="F226" s="11" t="s">
-        <v>1079</v>
+        <v>1045</v>
       </c>
       <c r="G226" s="11" t="s">
-        <v>1080</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.3">
@@ -9911,10 +9911,10 @@
         <v>138</v>
       </c>
       <c r="F227" s="11" t="s">
-        <v>1081</v>
+        <v>1047</v>
       </c>
       <c r="G227" s="11" t="s">
-        <v>1082</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.3">
@@ -9934,10 +9934,10 @@
         <v>138</v>
       </c>
       <c r="F228" s="11" t="s">
-        <v>1083</v>
+        <v>1049</v>
       </c>
       <c r="G228" s="11" t="s">
-        <v>1084</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.3">
@@ -9957,10 +9957,10 @@
         <v>138</v>
       </c>
       <c r="F229" s="11" t="s">
-        <v>1085</v>
+        <v>1051</v>
       </c>
       <c r="G229" s="11" t="s">
-        <v>1086</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.3">
@@ -9980,10 +9980,10 @@
         <v>138</v>
       </c>
       <c r="F230" s="11" t="s">
-        <v>1087</v>
+        <v>1053</v>
       </c>
       <c r="G230" s="11" t="s">
-        <v>1088</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.3">
@@ -10003,10 +10003,10 @@
         <v>138</v>
       </c>
       <c r="F231" s="11" t="s">
-        <v>1089</v>
+        <v>1055</v>
       </c>
       <c r="G231" s="11" t="s">
-        <v>1090</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.3">
@@ -10026,10 +10026,10 @@
         <v>138</v>
       </c>
       <c r="F232" s="11" t="s">
-        <v>1091</v>
+        <v>1057</v>
       </c>
       <c r="G232" s="11" t="s">
-        <v>1092</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.3">
@@ -10049,10 +10049,10 @@
         <v>138</v>
       </c>
       <c r="F233" s="11" t="s">
-        <v>1093</v>
+        <v>1059</v>
       </c>
       <c r="G233" s="11" t="s">
-        <v>1094</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.3">
@@ -10072,10 +10072,10 @@
         <v>138</v>
       </c>
       <c r="F234" s="11" t="s">
-        <v>1095</v>
+        <v>1061</v>
       </c>
       <c r="G234" s="11" t="s">
-        <v>1096</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.3">
@@ -10095,10 +10095,10 @@
         <v>138</v>
       </c>
       <c r="F235" s="11" t="s">
-        <v>1097</v>
+        <v>1063</v>
       </c>
       <c r="G235" s="11" t="s">
-        <v>1098</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.3">
@@ -10118,10 +10118,10 @@
         <v>138</v>
       </c>
       <c r="F236" s="11" t="s">
-        <v>1099</v>
+        <v>1065</v>
       </c>
       <c r="G236" s="11" t="s">
-        <v>1100</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.3">
@@ -10141,10 +10141,10 @@
         <v>138</v>
       </c>
       <c r="F237" s="11" t="s">
-        <v>1101</v>
+        <v>1067</v>
       </c>
       <c r="G237" s="11" t="s">
-        <v>1102</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.3">
@@ -10164,10 +10164,10 @@
         <v>138</v>
       </c>
       <c r="F238" s="11" t="s">
-        <v>1103</v>
+        <v>1069</v>
       </c>
       <c r="G238" s="11" t="s">
-        <v>1104</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.3">
@@ -10187,10 +10187,10 @@
         <v>138</v>
       </c>
       <c r="F239" s="11" t="s">
-        <v>1105</v>
+        <v>1071</v>
       </c>
       <c r="G239" s="11" t="s">
-        <v>1106</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.3">
@@ -10210,10 +10210,10 @@
         <v>138</v>
       </c>
       <c r="F240" s="11" t="s">
-        <v>1107</v>
+        <v>1073</v>
       </c>
       <c r="G240" s="11" t="s">
-        <v>1108</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.3">
@@ -10233,10 +10233,10 @@
         <v>138</v>
       </c>
       <c r="F241" s="11" t="s">
-        <v>1109</v>
+        <v>1075</v>
       </c>
       <c r="G241" s="11" t="s">
-        <v>1110</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.3">
@@ -10256,10 +10256,10 @@
         <v>138</v>
       </c>
       <c r="F242" s="11" t="s">
-        <v>1111</v>
+        <v>1077</v>
       </c>
       <c r="G242" s="11" t="s">
-        <v>1112</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.3">
@@ -10279,10 +10279,10 @@
         <v>138</v>
       </c>
       <c r="F243" s="11" t="s">
-        <v>1113</v>
+        <v>1079</v>
       </c>
       <c r="G243" s="11" t="s">
-        <v>1114</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.3">
@@ -10302,10 +10302,10 @@
         <v>138</v>
       </c>
       <c r="F244" s="11" t="s">
-        <v>1115</v>
+        <v>1081</v>
       </c>
       <c r="G244" s="11" t="s">
-        <v>1116</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.3">
@@ -10325,10 +10325,10 @@
         <v>138</v>
       </c>
       <c r="F245" s="11" t="s">
-        <v>1117</v>
+        <v>1083</v>
       </c>
       <c r="G245" s="11" t="s">
-        <v>1118</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.3">
@@ -10348,10 +10348,10 @@
         <v>138</v>
       </c>
       <c r="F246" s="11" t="s">
-        <v>1119</v>
+        <v>1085</v>
       </c>
       <c r="G246" s="11" t="s">
-        <v>1120</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.3">
@@ -10371,10 +10371,10 @@
         <v>138</v>
       </c>
       <c r="F247" s="11" t="s">
-        <v>1121</v>
+        <v>1087</v>
       </c>
       <c r="G247" s="11" t="s">
-        <v>1122</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.3">
@@ -10394,10 +10394,10 @@
         <v>138</v>
       </c>
       <c r="F248" s="11" t="s">
-        <v>1123</v>
+        <v>1089</v>
       </c>
       <c r="G248" s="11" t="s">
-        <v>1124</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.3">
@@ -10417,10 +10417,10 @@
         <v>138</v>
       </c>
       <c r="F249" s="11" t="s">
-        <v>1125</v>
+        <v>1091</v>
       </c>
       <c r="G249" s="11" t="s">
-        <v>1126</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.3">
@@ -10440,10 +10440,10 @@
         <v>138</v>
       </c>
       <c r="F250" s="11" t="s">
-        <v>1127</v>
+        <v>1093</v>
       </c>
       <c r="G250" s="11" t="s">
-        <v>1128</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.3">
@@ -10463,10 +10463,10 @@
         <v>138</v>
       </c>
       <c r="F251" s="11" t="s">
-        <v>1129</v>
+        <v>1095</v>
       </c>
       <c r="G251" s="11" t="s">
-        <v>1130</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.3">
@@ -10486,13 +10486,13 @@
         <v>138</v>
       </c>
       <c r="F252" s="11" t="s">
-        <v>1131</v>
+        <v>1097</v>
       </c>
       <c r="G252" s="11" t="s">
-        <v>1132</v>
-      </c>
-    </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="253" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A253" s="1">
         <v>252</v>
       </c>
@@ -10509,13 +10509,13 @@
         <v>138</v>
       </c>
       <c r="F253" s="11" t="s">
-        <v>1133</v>
+        <v>1099</v>
       </c>
       <c r="G253" s="11" t="s">
-        <v>1134</v>
-      </c>
-    </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="254" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A254" s="1">
         <v>253</v>
       </c>
@@ -10531,11 +10531,11 @@
       <c r="E254" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F254" s="11" t="s">
-        <v>1135</v>
-      </c>
-      <c r="G254" s="11" t="s">
-        <v>1136</v>
+      <c r="F254" s="5" t="s">
+        <v>1346</v>
+      </c>
+      <c r="G254" s="7" t="s">
+        <v>1347</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.3">
@@ -10555,10 +10555,10 @@
         <v>138</v>
       </c>
       <c r="F255" s="11" t="s">
-        <v>1137</v>
+        <v>1101</v>
       </c>
       <c r="G255" s="11" t="s">
-        <v>1138</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.3">
@@ -10578,10 +10578,10 @@
         <v>138</v>
       </c>
       <c r="F256" s="11" t="s">
-        <v>1139</v>
+        <v>1103</v>
       </c>
       <c r="G256" s="11" t="s">
-        <v>1140</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.3">
@@ -10601,10 +10601,10 @@
         <v>138</v>
       </c>
       <c r="F257" s="11" t="s">
-        <v>1141</v>
+        <v>1105</v>
       </c>
       <c r="G257" s="11" t="s">
-        <v>1142</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.3">
@@ -10624,10 +10624,10 @@
         <v>138</v>
       </c>
       <c r="F258" s="11" t="s">
-        <v>1143</v>
+        <v>1107</v>
       </c>
       <c r="G258" s="11" t="s">
-        <v>1144</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.3">
@@ -10647,10 +10647,10 @@
         <v>138</v>
       </c>
       <c r="F259" s="11" t="s">
-        <v>1145</v>
+        <v>1109</v>
       </c>
       <c r="G259" s="11" t="s">
-        <v>1146</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.3">
@@ -10670,10 +10670,10 @@
         <v>138</v>
       </c>
       <c r="F260" s="11" t="s">
-        <v>1147</v>
+        <v>1111</v>
       </c>
       <c r="G260" s="11" t="s">
-        <v>1148</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.3">
@@ -10693,10 +10693,10 @@
         <v>138</v>
       </c>
       <c r="F261" s="11" t="s">
-        <v>1149</v>
+        <v>1113</v>
       </c>
       <c r="G261" s="11" t="s">
-        <v>1150</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.3">
@@ -10716,10 +10716,10 @@
         <v>138</v>
       </c>
       <c r="F262" s="11" t="s">
-        <v>1151</v>
+        <v>1115</v>
       </c>
       <c r="G262" s="11" t="s">
-        <v>1152</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.3">
@@ -10739,10 +10739,10 @@
         <v>138</v>
       </c>
       <c r="F263" s="11" t="s">
-        <v>1153</v>
+        <v>1117</v>
       </c>
       <c r="G263" s="11" t="s">
-        <v>1154</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.3">
@@ -10762,10 +10762,10 @@
         <v>138</v>
       </c>
       <c r="F264" s="11" t="s">
-        <v>1155</v>
+        <v>1119</v>
       </c>
       <c r="G264" s="11" t="s">
-        <v>1156</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.3">
@@ -10785,10 +10785,10 @@
         <v>138</v>
       </c>
       <c r="F265" s="11" t="s">
-        <v>1157</v>
+        <v>1121</v>
       </c>
       <c r="G265" s="11" t="s">
-        <v>1158</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.3">
@@ -10808,10 +10808,10 @@
         <v>138</v>
       </c>
       <c r="F266" s="11" t="s">
-        <v>1159</v>
+        <v>1123</v>
       </c>
       <c r="G266" s="11" t="s">
-        <v>1160</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.3">
@@ -10831,10 +10831,10 @@
         <v>138</v>
       </c>
       <c r="F267" s="11" t="s">
-        <v>1161</v>
+        <v>1125</v>
       </c>
       <c r="G267" s="11" t="s">
-        <v>1162</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.3">
@@ -10854,10 +10854,10 @@
         <v>138</v>
       </c>
       <c r="F268" s="11" t="s">
-        <v>1163</v>
+        <v>1127</v>
       </c>
       <c r="G268" s="11" t="s">
-        <v>1164</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.3">
@@ -10877,10 +10877,10 @@
         <v>138</v>
       </c>
       <c r="F269" s="11" t="s">
-        <v>1165</v>
+        <v>1129</v>
       </c>
       <c r="G269" s="11" t="s">
-        <v>1166</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.3">
@@ -10900,10 +10900,10 @@
         <v>138</v>
       </c>
       <c r="F270" s="11" t="s">
-        <v>1167</v>
+        <v>1131</v>
       </c>
       <c r="G270" s="11" t="s">
-        <v>1168</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.3">
@@ -10923,10 +10923,10 @@
         <v>138</v>
       </c>
       <c r="F271" s="11" t="s">
-        <v>1169</v>
+        <v>1133</v>
       </c>
       <c r="G271" s="11" t="s">
-        <v>1170</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.3">
@@ -10946,10 +10946,10 @@
         <v>138</v>
       </c>
       <c r="F272" s="11" t="s">
-        <v>1171</v>
+        <v>1135</v>
       </c>
       <c r="G272" s="11" t="s">
-        <v>1172</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.3">
@@ -10969,10 +10969,10 @@
         <v>138</v>
       </c>
       <c r="F273" s="11" t="s">
-        <v>1173</v>
+        <v>1137</v>
       </c>
       <c r="G273" s="11" t="s">
-        <v>1174</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.3">
@@ -10992,10 +10992,10 @@
         <v>138</v>
       </c>
       <c r="F274" s="11" t="s">
-        <v>1175</v>
+        <v>1139</v>
       </c>
       <c r="G274" s="11" t="s">
-        <v>1176</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.3">
@@ -11015,10 +11015,10 @@
         <v>138</v>
       </c>
       <c r="F275" s="11" t="s">
-        <v>1177</v>
+        <v>1141</v>
       </c>
       <c r="G275" s="11" t="s">
-        <v>1178</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.3">
@@ -11038,10 +11038,10 @@
         <v>138</v>
       </c>
       <c r="F276" s="11" t="s">
-        <v>1179</v>
+        <v>1143</v>
       </c>
       <c r="G276" s="11" t="s">
-        <v>1180</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.3">
@@ -11061,10 +11061,10 @@
         <v>138</v>
       </c>
       <c r="F277" s="11" t="s">
-        <v>1181</v>
+        <v>1145</v>
       </c>
       <c r="G277" s="11" t="s">
-        <v>1182</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.3">
@@ -11084,10 +11084,10 @@
         <v>138</v>
       </c>
       <c r="F278" s="11" t="s">
-        <v>1183</v>
+        <v>1147</v>
       </c>
       <c r="G278" s="11" t="s">
-        <v>1184</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="279" spans="1:7" x14ac:dyDescent="0.3">
@@ -11107,10 +11107,10 @@
         <v>138</v>
       </c>
       <c r="F279" s="11" t="s">
-        <v>1185</v>
+        <v>1149</v>
       </c>
       <c r="G279" s="11" t="s">
-        <v>1186</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="280" spans="1:7" x14ac:dyDescent="0.3">
@@ -11130,10 +11130,10 @@
         <v>138</v>
       </c>
       <c r="F280" s="11" t="s">
-        <v>1187</v>
+        <v>1151</v>
       </c>
       <c r="G280" s="11" t="s">
-        <v>1188</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.3">
@@ -11153,10 +11153,10 @@
         <v>138</v>
       </c>
       <c r="F281" s="11" t="s">
-        <v>1189</v>
+        <v>1153</v>
       </c>
       <c r="G281" s="11" t="s">
-        <v>1190</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.3">
@@ -11176,10 +11176,10 @@
         <v>601</v>
       </c>
       <c r="F282" s="11" t="s">
-        <v>1191</v>
+        <v>1155</v>
       </c>
       <c r="G282" s="11" t="s">
-        <v>1192</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.3">
@@ -11199,10 +11199,10 @@
         <v>601</v>
       </c>
       <c r="F283" s="11" t="s">
-        <v>1193</v>
+        <v>1157</v>
       </c>
       <c r="G283" s="11" t="s">
-        <v>1194</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.3">
@@ -11222,10 +11222,10 @@
         <v>601</v>
       </c>
       <c r="F284" s="11" t="s">
-        <v>1195</v>
+        <v>1159</v>
       </c>
       <c r="G284" s="11" t="s">
-        <v>1196</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.3">
@@ -11245,10 +11245,10 @@
         <v>601</v>
       </c>
       <c r="F285" s="11" t="s">
-        <v>1197</v>
+        <v>1161</v>
       </c>
       <c r="G285" s="11" t="s">
-        <v>1198</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.3">
@@ -11268,10 +11268,10 @@
         <v>601</v>
       </c>
       <c r="F286" s="11" t="s">
-        <v>1199</v>
+        <v>1163</v>
       </c>
       <c r="G286" s="11" t="s">
-        <v>1200</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.3">
@@ -11291,10 +11291,10 @@
         <v>601</v>
       </c>
       <c r="F287" s="11" t="s">
-        <v>1201</v>
+        <v>1165</v>
       </c>
       <c r="G287" s="11" t="s">
-        <v>1202</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.3">
@@ -11314,10 +11314,10 @@
         <v>601</v>
       </c>
       <c r="F288" s="11" t="s">
-        <v>1203</v>
+        <v>1167</v>
       </c>
       <c r="G288" s="11" t="s">
-        <v>1204</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.3">
@@ -11337,10 +11337,10 @@
         <v>601</v>
       </c>
       <c r="F289" s="11" t="s">
-        <v>1205</v>
+        <v>1169</v>
       </c>
       <c r="G289" s="11" t="s">
-        <v>1206</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.3">
@@ -11360,10 +11360,10 @@
         <v>601</v>
       </c>
       <c r="F290" s="11" t="s">
-        <v>1207</v>
+        <v>1171</v>
       </c>
       <c r="G290" s="11" t="s">
-        <v>1208</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.3">
@@ -11383,10 +11383,10 @@
         <v>601</v>
       </c>
       <c r="F291" s="11" t="s">
-        <v>1209</v>
+        <v>1173</v>
       </c>
       <c r="G291" s="11" t="s">
-        <v>1210</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.3">
@@ -11406,10 +11406,10 @@
         <v>601</v>
       </c>
       <c r="F292" s="11" t="s">
-        <v>1211</v>
+        <v>1175</v>
       </c>
       <c r="G292" s="11" t="s">
-        <v>1212</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.3">
@@ -11429,10 +11429,10 @@
         <v>601</v>
       </c>
       <c r="F293" s="11" t="s">
-        <v>1213</v>
+        <v>1177</v>
       </c>
       <c r="G293" s="11" t="s">
-        <v>1214</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.3">
@@ -11452,10 +11452,10 @@
         <v>601</v>
       </c>
       <c r="F294" s="11" t="s">
-        <v>1215</v>
+        <v>1179</v>
       </c>
       <c r="G294" s="11" t="s">
-        <v>1216</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.3">
@@ -11475,10 +11475,10 @@
         <v>601</v>
       </c>
       <c r="F295" s="11" t="s">
-        <v>1217</v>
+        <v>1181</v>
       </c>
       <c r="G295" s="11" t="s">
-        <v>1218</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.3">
@@ -11498,10 +11498,10 @@
         <v>601</v>
       </c>
       <c r="F296" s="11" t="s">
-        <v>1219</v>
+        <v>1183</v>
       </c>
       <c r="G296" s="11" t="s">
-        <v>1220</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.3">
@@ -11521,10 +11521,10 @@
         <v>601</v>
       </c>
       <c r="F297" s="11" t="s">
-        <v>1221</v>
+        <v>1185</v>
       </c>
       <c r="G297" s="11" t="s">
-        <v>1222</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.3">
@@ -11544,10 +11544,10 @@
         <v>138</v>
       </c>
       <c r="F298" s="11" t="s">
-        <v>1223</v>
+        <v>1187</v>
       </c>
       <c r="G298" s="11" t="s">
-        <v>1224</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="299" spans="1:7" x14ac:dyDescent="0.3">
@@ -11567,10 +11567,10 @@
         <v>138</v>
       </c>
       <c r="F299" s="11" t="s">
-        <v>1225</v>
+        <v>1189</v>
       </c>
       <c r="G299" s="11" t="s">
-        <v>1226</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.3">
@@ -11590,10 +11590,10 @@
         <v>138</v>
       </c>
       <c r="F300" s="11" t="s">
-        <v>1227</v>
+        <v>1191</v>
       </c>
       <c r="G300" s="11" t="s">
-        <v>1228</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.3">
@@ -11613,10 +11613,10 @@
         <v>138</v>
       </c>
       <c r="F301" s="11" t="s">
-        <v>1229</v>
+        <v>1193</v>
       </c>
       <c r="G301" s="11" t="s">
-        <v>1230</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="302" spans="1:7" x14ac:dyDescent="0.3">
@@ -11636,10 +11636,10 @@
         <v>138</v>
       </c>
       <c r="F302" s="11" t="s">
-        <v>1231</v>
+        <v>1195</v>
       </c>
       <c r="G302" s="11" t="s">
-        <v>1232</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="303" spans="1:7" x14ac:dyDescent="0.3">
@@ -11659,10 +11659,10 @@
         <v>138</v>
       </c>
       <c r="F303" s="11" t="s">
-        <v>1233</v>
+        <v>1197</v>
       </c>
       <c r="G303" s="11" t="s">
-        <v>1234</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="304" spans="1:7" x14ac:dyDescent="0.3">
@@ -11682,10 +11682,10 @@
         <v>138</v>
       </c>
       <c r="F304" s="11" t="s">
-        <v>1235</v>
+        <v>1199</v>
       </c>
       <c r="G304" s="11" t="s">
-        <v>1236</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="305" spans="1:7" x14ac:dyDescent="0.3">
@@ -11705,10 +11705,10 @@
         <v>138</v>
       </c>
       <c r="F305" s="11" t="s">
-        <v>1237</v>
+        <v>1201</v>
       </c>
       <c r="G305" s="11" t="s">
-        <v>1238</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="306" spans="1:7" x14ac:dyDescent="0.3">
@@ -11728,10 +11728,10 @@
         <v>138</v>
       </c>
       <c r="F306" s="11" t="s">
-        <v>1239</v>
+        <v>1203</v>
       </c>
       <c r="G306" s="11" t="s">
-        <v>1240</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="307" spans="1:7" x14ac:dyDescent="0.3">
@@ -11751,10 +11751,10 @@
         <v>138</v>
       </c>
       <c r="F307" s="11" t="s">
-        <v>1241</v>
+        <v>1205</v>
       </c>
       <c r="G307" s="11" t="s">
-        <v>1242</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="308" spans="1:7" x14ac:dyDescent="0.3">
@@ -11774,10 +11774,10 @@
         <v>601</v>
       </c>
       <c r="F308" s="11" t="s">
-        <v>1243</v>
+        <v>1207</v>
       </c>
       <c r="G308" s="11" t="s">
-        <v>1244</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="309" spans="1:7" x14ac:dyDescent="0.3">
@@ -11797,10 +11797,10 @@
         <v>601</v>
       </c>
       <c r="F309" s="11" t="s">
-        <v>1245</v>
+        <v>1209</v>
       </c>
       <c r="G309" s="11" t="s">
-        <v>1246</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="310" spans="1:7" x14ac:dyDescent="0.3">
@@ -11820,10 +11820,10 @@
         <v>601</v>
       </c>
       <c r="F310" s="11" t="s">
-        <v>1247</v>
+        <v>1211</v>
       </c>
       <c r="G310" s="11" t="s">
-        <v>1248</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="311" spans="1:7" x14ac:dyDescent="0.3">
@@ -11843,10 +11843,10 @@
         <v>601</v>
       </c>
       <c r="F311" s="11" t="s">
-        <v>1249</v>
+        <v>1213</v>
       </c>
       <c r="G311" s="11" t="s">
-        <v>1250</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="312" spans="1:7" x14ac:dyDescent="0.3">
@@ -11866,10 +11866,10 @@
         <v>601</v>
       </c>
       <c r="F312" s="11" t="s">
-        <v>1251</v>
+        <v>1215</v>
       </c>
       <c r="G312" s="11" t="s">
-        <v>1252</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="313" spans="1:7" x14ac:dyDescent="0.3">
@@ -11889,10 +11889,10 @@
         <v>601</v>
       </c>
       <c r="F313" s="11" t="s">
-        <v>1253</v>
+        <v>1217</v>
       </c>
       <c r="G313" s="11" t="s">
-        <v>1254</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="314" spans="1:7" x14ac:dyDescent="0.3">
@@ -11912,10 +11912,10 @@
         <v>601</v>
       </c>
       <c r="F314" s="11" t="s">
-        <v>1255</v>
+        <v>1219</v>
       </c>
       <c r="G314" s="11" t="s">
-        <v>1256</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="315" spans="1:7" x14ac:dyDescent="0.3">
@@ -11935,10 +11935,10 @@
         <v>601</v>
       </c>
       <c r="F315" s="11" t="s">
-        <v>1257</v>
+        <v>1221</v>
       </c>
       <c r="G315" s="11" t="s">
-        <v>1258</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="316" spans="1:7" x14ac:dyDescent="0.3">
@@ -11958,10 +11958,10 @@
         <v>601</v>
       </c>
       <c r="F316" s="11" t="s">
-        <v>1259</v>
+        <v>1223</v>
       </c>
       <c r="G316" s="11" t="s">
-        <v>1260</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="317" spans="1:7" x14ac:dyDescent="0.3">
@@ -11981,10 +11981,10 @@
         <v>601</v>
       </c>
       <c r="F317" s="11" t="s">
-        <v>1261</v>
+        <v>1225</v>
       </c>
       <c r="G317" s="11" t="s">
-        <v>1262</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="318" spans="1:7" x14ac:dyDescent="0.3">
@@ -12004,10 +12004,10 @@
         <v>601</v>
       </c>
       <c r="F318" s="11" t="s">
-        <v>1263</v>
+        <v>1227</v>
       </c>
       <c r="G318" s="11" t="s">
-        <v>1264</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="319" spans="1:7" x14ac:dyDescent="0.3">
@@ -12027,10 +12027,10 @@
         <v>601</v>
       </c>
       <c r="F319" s="11" t="s">
-        <v>1265</v>
+        <v>1229</v>
       </c>
       <c r="G319" s="11" t="s">
-        <v>1266</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="320" spans="1:7" x14ac:dyDescent="0.3">
@@ -12050,10 +12050,10 @@
         <v>601</v>
       </c>
       <c r="F320" s="11" t="s">
-        <v>1267</v>
+        <v>1231</v>
       </c>
       <c r="G320" s="11" t="s">
-        <v>1268</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="321" spans="1:7" x14ac:dyDescent="0.3">
@@ -12073,10 +12073,10 @@
         <v>601</v>
       </c>
       <c r="F321" s="11" t="s">
-        <v>1269</v>
+        <v>1233</v>
       </c>
       <c r="G321" s="11" t="s">
-        <v>1270</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="322" spans="1:7" x14ac:dyDescent="0.3">
@@ -12096,10 +12096,10 @@
         <v>601</v>
       </c>
       <c r="F322" s="11" t="s">
-        <v>1271</v>
+        <v>1235</v>
       </c>
       <c r="G322" s="11" t="s">
-        <v>1272</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="323" spans="1:7" x14ac:dyDescent="0.3">
@@ -12119,10 +12119,10 @@
         <v>601</v>
       </c>
       <c r="F323" s="11" t="s">
-        <v>1273</v>
+        <v>1237</v>
       </c>
       <c r="G323" s="11" t="s">
-        <v>1274</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="324" spans="1:7" x14ac:dyDescent="0.3">
@@ -12142,10 +12142,10 @@
         <v>601</v>
       </c>
       <c r="F324" s="11" t="s">
-        <v>1275</v>
+        <v>1239</v>
       </c>
       <c r="G324" s="11" t="s">
-        <v>1276</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="325" spans="1:7" x14ac:dyDescent="0.3">
@@ -12165,10 +12165,10 @@
         <v>601</v>
       </c>
       <c r="F325" s="11" t="s">
-        <v>1277</v>
+        <v>1241</v>
       </c>
       <c r="G325" s="11" t="s">
-        <v>1278</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="326" spans="1:7" x14ac:dyDescent="0.3">
@@ -12188,10 +12188,10 @@
         <v>601</v>
       </c>
       <c r="F326" s="11" t="s">
-        <v>1279</v>
+        <v>1243</v>
       </c>
       <c r="G326" s="11" t="s">
-        <v>1280</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="327" spans="1:7" x14ac:dyDescent="0.3">
@@ -12211,10 +12211,10 @@
         <v>601</v>
       </c>
       <c r="F327" s="11" t="s">
-        <v>1281</v>
+        <v>1245</v>
       </c>
       <c r="G327" s="11" t="s">
-        <v>1282</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="328" spans="1:7" x14ac:dyDescent="0.3">
@@ -12234,10 +12234,10 @@
         <v>601</v>
       </c>
       <c r="F328" s="11" t="s">
-        <v>1283</v>
+        <v>1247</v>
       </c>
       <c r="G328" s="11" t="s">
-        <v>1284</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="329" spans="1:7" x14ac:dyDescent="0.3">
@@ -12257,10 +12257,10 @@
         <v>601</v>
       </c>
       <c r="F329" s="11" t="s">
-        <v>1285</v>
+        <v>1249</v>
       </c>
       <c r="G329" s="11" t="s">
-        <v>1286</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="330" spans="1:7" x14ac:dyDescent="0.3">
@@ -12280,10 +12280,10 @@
         <v>601</v>
       </c>
       <c r="F330" s="11" t="s">
-        <v>1287</v>
+        <v>1251</v>
       </c>
       <c r="G330" s="11" t="s">
-        <v>1288</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="331" spans="1:7" x14ac:dyDescent="0.3">
@@ -12303,10 +12303,10 @@
         <v>601</v>
       </c>
       <c r="F331" s="11" t="s">
-        <v>1289</v>
+        <v>1253</v>
       </c>
       <c r="G331" s="11" t="s">
-        <v>1290</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="332" spans="1:7" x14ac:dyDescent="0.3">
@@ -12326,10 +12326,10 @@
         <v>601</v>
       </c>
       <c r="F332" s="11" t="s">
-        <v>1291</v>
+        <v>1255</v>
       </c>
       <c r="G332" s="11" t="s">
-        <v>1292</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="333" spans="1:7" x14ac:dyDescent="0.3">
@@ -12349,10 +12349,10 @@
         <v>601</v>
       </c>
       <c r="F333" s="11" t="s">
-        <v>1293</v>
+        <v>1257</v>
       </c>
       <c r="G333" s="11" t="s">
-        <v>1294</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="334" spans="1:7" x14ac:dyDescent="0.3">
@@ -12372,10 +12372,10 @@
         <v>601</v>
       </c>
       <c r="F334" s="11" t="s">
-        <v>1295</v>
+        <v>1259</v>
       </c>
       <c r="G334" s="11" t="s">
-        <v>1296</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="335" spans="1:7" x14ac:dyDescent="0.3">
@@ -12395,10 +12395,10 @@
         <v>601</v>
       </c>
       <c r="F335" s="11" t="s">
-        <v>1297</v>
+        <v>1261</v>
       </c>
       <c r="G335" s="11" t="s">
-        <v>1298</v>
+        <v>1262</v>
       </c>
     </row>
   </sheetData>

--- a/files/Adhiparasakthi Students Data 1.xlsx
+++ b/files/Adhiparasakthi Students Data 1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vigne\Google_Backup\Github\sb4c\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9068965-0DAB-4809-907A-D230377F7526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB45A1C9-4AD2-4BB5-8505-7FA9AB59A824}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E3F0EEA9-6BAE-46A1-95E3-E9CE509FC50B}"/>
   </bookViews>
@@ -2127,12 +2127,6 @@
     <t>Edu#657008</t>
   </si>
   <si>
-    <t>EFIBM26694035553@edunetmail.com</t>
-  </si>
-  <si>
-    <t>Edu#608737</t>
-  </si>
-  <si>
     <t>EFIBM26659426356@edunetmail.com</t>
   </si>
   <si>
@@ -2175,12 +2169,6 @@
     <t>Edu#478453</t>
   </si>
   <si>
-    <t>EFIBM26279211917@edunetmail.com</t>
-  </si>
-  <si>
-    <t>Edu#636995</t>
-  </si>
-  <si>
     <t>EFIBM26737603942@edunetmail.com</t>
   </si>
   <si>
@@ -2307,12 +2295,6 @@
     <t>Edu#187059</t>
   </si>
   <si>
-    <t>EFIBM26536359476@edunetmail.com</t>
-  </si>
-  <si>
-    <t>Edu#980043</t>
-  </si>
-  <si>
     <t>EFIBM26363490650@edunetmail.com</t>
   </si>
   <si>
@@ -2349,18 +2331,6 @@
     <t>Edu#834895</t>
   </si>
   <si>
-    <t>EFIBM26626670598@edunetmail.com</t>
-  </si>
-  <si>
-    <t>Edu#792952</t>
-  </si>
-  <si>
-    <t>EFIBM26689322082@edunetmail.com</t>
-  </si>
-  <si>
-    <t>Edu#860699</t>
-  </si>
-  <si>
     <t>EFIBM26275867532@edunetmail.com</t>
   </si>
   <si>
@@ -2373,12 +2343,6 @@
     <t>Edu#136987</t>
   </si>
   <si>
-    <t>EFIBM26599292966@edunetmail.com</t>
-  </si>
-  <si>
-    <t>Edu#641736</t>
-  </si>
-  <si>
     <t>EFIBM26547021097@edunetmail.com</t>
   </si>
   <si>
@@ -4084,6 +4048,42 @@
   </si>
   <si>
     <t>Edu#516848</t>
+  </si>
+  <si>
+    <t>EFIBM26206523013@edunetmail.com</t>
+  </si>
+  <si>
+    <t>Edu#766427</t>
+  </si>
+  <si>
+    <t>EFIBM26698798100@edunetmail.com</t>
+  </si>
+  <si>
+    <t>Edu#592709</t>
+  </si>
+  <si>
+    <t>EFIBM26138385361@edunetmail.com</t>
+  </si>
+  <si>
+    <t>Edu#908491</t>
+  </si>
+  <si>
+    <t>EFIBM26603865979@edunetmail.com</t>
+  </si>
+  <si>
+    <t>Edu#212609</t>
+  </si>
+  <si>
+    <t>EFIBM26495829497@edunetmail.com</t>
+  </si>
+  <si>
+    <t>Edu#861961</t>
+  </si>
+  <si>
+    <t>EFIBM26671802618@edunetmail.com</t>
+  </si>
+  <si>
+    <t>Edu#594500</t>
   </si>
 </sst>
 </file>
@@ -4808,10 +4808,10 @@
         <v>138</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>1318</v>
+        <v>1306</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>1319</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -4945,11 +4945,11 @@
       <c r="E11" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F11" s="6" t="s">
-        <v>697</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>698</v>
+      <c r="F11" s="5" t="s">
+        <v>1338</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>1339</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -4969,10 +4969,10 @@
         <v>138</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>1320</v>
+        <v>1308</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>1321</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -4992,10 +4992,10 @@
         <v>138</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5015,10 +5015,10 @@
         <v>138</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5038,10 +5038,10 @@
         <v>138</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>1338</v>
+        <v>1326</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>1339</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5061,10 +5061,10 @@
         <v>138</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5084,10 +5084,10 @@
         <v>138</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5107,10 +5107,10 @@
         <v>138</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5130,10 +5130,10 @@
         <v>138</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>1340</v>
+        <v>1328</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>1341</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5153,10 +5153,10 @@
         <v>138</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>1342</v>
+        <v>1330</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>1343</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5176,10 +5176,10 @@
         <v>138</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5199,10 +5199,10 @@
         <v>138</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5221,11 +5221,11 @@
       <c r="E23" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F23" s="6" t="s">
-        <v>713</v>
-      </c>
-      <c r="G23" s="8" t="s">
-        <v>714</v>
+      <c r="F23" s="5" t="s">
+        <v>1348</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>1349</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5245,10 +5245,10 @@
         <v>138</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5268,10 +5268,10 @@
         <v>138</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5291,10 +5291,10 @@
         <v>138</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>720</v>
+        <v>716</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5314,10 +5314,10 @@
         <v>138</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>721</v>
+        <v>717</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5337,10 +5337,10 @@
         <v>138</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5360,10 +5360,10 @@
         <v>138</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>726</v>
+        <v>722</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5383,10 +5383,10 @@
         <v>138</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>1326</v>
+        <v>1314</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>1327</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5406,10 +5406,10 @@
         <v>138</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>1336</v>
+        <v>1324</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>1337</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5429,10 +5429,10 @@
         <v>138</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5452,10 +5452,10 @@
         <v>138</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5475,10 +5475,10 @@
         <v>138</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>1324</v>
+        <v>1312</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>1325</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5498,10 +5498,10 @@
         <v>138</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>1334</v>
+        <v>1322</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>1335</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5521,10 +5521,10 @@
         <v>138</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5544,10 +5544,10 @@
         <v>138</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>1344</v>
+        <v>1332</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>1345</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5567,10 +5567,10 @@
         <v>138</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>1316</v>
+        <v>1304</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>1317</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5590,10 +5590,10 @@
         <v>138</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5613,10 +5613,10 @@
         <v>138</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5636,10 +5636,10 @@
         <v>138</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5659,10 +5659,10 @@
         <v>138</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5682,10 +5682,10 @@
         <v>138</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>1322</v>
+        <v>1310</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>1323</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5705,10 +5705,10 @@
         <v>138</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5728,10 +5728,10 @@
         <v>138</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5751,10 +5751,10 @@
         <v>138</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>746</v>
+        <v>742</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5774,10 +5774,10 @@
         <v>138</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5797,10 +5797,10 @@
         <v>138</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5820,10 +5820,10 @@
         <v>138</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5843,10 +5843,10 @@
         <v>138</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5866,10 +5866,10 @@
         <v>138</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>1348</v>
+        <v>1336</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>1349</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5889,10 +5889,10 @@
         <v>138</v>
       </c>
       <c r="F52" s="6" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>756</v>
+        <v>752</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5912,10 +5912,10 @@
         <v>138</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>1330</v>
+        <v>1318</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>1331</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5934,11 +5934,11 @@
       <c r="E54" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F54" s="6" t="s">
-        <v>757</v>
-      </c>
-      <c r="G54" s="8" t="s">
-        <v>758</v>
+      <c r="F54" s="5" t="s">
+        <v>1346</v>
+      </c>
+      <c r="G54" s="7" t="s">
+        <v>1347</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5958,10 +5958,10 @@
         <v>138</v>
       </c>
       <c r="F55" s="6" t="s">
-        <v>759</v>
+        <v>753</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>760</v>
+        <v>754</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5981,10 +5981,10 @@
         <v>138</v>
       </c>
       <c r="F56" s="6" t="s">
-        <v>761</v>
+        <v>755</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>762</v>
+        <v>756</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6004,10 +6004,10 @@
         <v>138</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>1328</v>
+        <v>1316</v>
       </c>
       <c r="G57" s="7" t="s">
-        <v>1329</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6027,10 +6027,10 @@
         <v>138</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>1332</v>
+        <v>1320</v>
       </c>
       <c r="G58" s="7" t="s">
-        <v>1333</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6050,10 +6050,10 @@
         <v>138</v>
       </c>
       <c r="F59" s="6" t="s">
-        <v>763</v>
+        <v>757</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>764</v>
+        <v>758</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6073,10 +6073,10 @@
         <v>138</v>
       </c>
       <c r="F60" s="6" t="s">
-        <v>765</v>
+        <v>759</v>
       </c>
       <c r="G60" s="8" t="s">
-        <v>766</v>
+        <v>760</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6096,10 +6096,10 @@
         <v>138</v>
       </c>
       <c r="F61" s="6" t="s">
-        <v>767</v>
+        <v>761</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>768</v>
+        <v>762</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6119,10 +6119,10 @@
         <v>138</v>
       </c>
       <c r="F62" s="6" t="s">
-        <v>769</v>
+        <v>763</v>
       </c>
       <c r="G62" s="8" t="s">
-        <v>770</v>
+        <v>764</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6141,11 +6141,11 @@
       <c r="E63" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F63" s="6" t="s">
-        <v>771</v>
-      </c>
-      <c r="G63" s="8" t="s">
-        <v>772</v>
+      <c r="F63" s="5" t="s">
+        <v>1344</v>
+      </c>
+      <c r="G63" s="7" t="s">
+        <v>1345</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6164,11 +6164,11 @@
       <c r="E64" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F64" s="6" t="s">
-        <v>773</v>
-      </c>
-      <c r="G64" s="8" t="s">
-        <v>774</v>
+      <c r="F64" s="5" t="s">
+        <v>1340</v>
+      </c>
+      <c r="G64" s="7" t="s">
+        <v>1341</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6188,10 +6188,10 @@
         <v>138</v>
       </c>
       <c r="F65" s="6" t="s">
-        <v>775</v>
+        <v>765</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>776</v>
+        <v>766</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6211,10 +6211,10 @@
         <v>138</v>
       </c>
       <c r="F66" s="6" t="s">
-        <v>777</v>
+        <v>767</v>
       </c>
       <c r="G66" s="8" t="s">
-        <v>778</v>
+        <v>768</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6233,11 +6233,11 @@
       <c r="E67" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F67" s="6" t="s">
-        <v>779</v>
-      </c>
-      <c r="G67" s="8" t="s">
-        <v>780</v>
+      <c r="F67" s="5" t="s">
+        <v>1342</v>
+      </c>
+      <c r="G67" s="7" t="s">
+        <v>1343</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6257,10 +6257,10 @@
         <v>138</v>
       </c>
       <c r="F68" s="12" t="s">
-        <v>1263</v>
+        <v>1251</v>
       </c>
       <c r="G68" s="12" t="s">
-        <v>1264</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6280,10 +6280,10 @@
         <v>138</v>
       </c>
       <c r="F69" s="6" t="s">
-        <v>781</v>
+        <v>769</v>
       </c>
       <c r="G69" s="8" t="s">
-        <v>782</v>
+        <v>770</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6294,7 +6294,7 @@
         <v>141</v>
       </c>
       <c r="C70" s="16" t="s">
-        <v>1299</v>
+        <v>1287</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>188</v>
@@ -6303,10 +6303,10 @@
         <v>138</v>
       </c>
       <c r="F70" s="12" t="s">
-        <v>1297</v>
+        <v>1285</v>
       </c>
       <c r="G70" s="12" t="s">
-        <v>1298</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6326,10 +6326,10 @@
         <v>138</v>
       </c>
       <c r="F71" s="6" t="s">
-        <v>783</v>
+        <v>771</v>
       </c>
       <c r="G71" s="8" t="s">
-        <v>784</v>
+        <v>772</v>
       </c>
     </row>
     <row r="72" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6349,10 +6349,10 @@
         <v>138</v>
       </c>
       <c r="F72" s="6" t="s">
-        <v>785</v>
+        <v>773</v>
       </c>
       <c r="G72" s="8" t="s">
-        <v>786</v>
+        <v>774</v>
       </c>
     </row>
     <row r="73" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6372,10 +6372,10 @@
         <v>138</v>
       </c>
       <c r="F73" s="6" t="s">
-        <v>787</v>
+        <v>775</v>
       </c>
       <c r="G73" s="8" t="s">
-        <v>788</v>
+        <v>776</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6395,10 +6395,10 @@
         <v>138</v>
       </c>
       <c r="F74" s="6" t="s">
-        <v>789</v>
+        <v>777</v>
       </c>
       <c r="G74" s="8" t="s">
-        <v>790</v>
+        <v>778</v>
       </c>
     </row>
     <row r="75" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6418,10 +6418,10 @@
         <v>138</v>
       </c>
       <c r="F75" s="6" t="s">
-        <v>791</v>
+        <v>779</v>
       </c>
       <c r="G75" s="8" t="s">
-        <v>792</v>
+        <v>780</v>
       </c>
     </row>
     <row r="76" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6441,10 +6441,10 @@
         <v>138</v>
       </c>
       <c r="F76" s="6" t="s">
-        <v>793</v>
+        <v>781</v>
       </c>
       <c r="G76" s="8" t="s">
-        <v>794</v>
+        <v>782</v>
       </c>
     </row>
     <row r="77" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6464,10 +6464,10 @@
         <v>138</v>
       </c>
       <c r="F77" s="6" t="s">
-        <v>795</v>
+        <v>783</v>
       </c>
       <c r="G77" s="8" t="s">
-        <v>796</v>
+        <v>784</v>
       </c>
     </row>
     <row r="78" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6487,10 +6487,10 @@
         <v>138</v>
       </c>
       <c r="F78" s="9" t="s">
-        <v>797</v>
+        <v>785</v>
       </c>
       <c r="G78" s="10" t="s">
-        <v>798</v>
+        <v>786</v>
       </c>
     </row>
     <row r="79" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6510,10 +6510,10 @@
         <v>138</v>
       </c>
       <c r="F79" s="12" t="s">
-        <v>1295</v>
+        <v>1283</v>
       </c>
       <c r="G79" s="12" t="s">
-        <v>1296</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
@@ -6533,10 +6533,10 @@
         <v>138</v>
       </c>
       <c r="F80" s="15" t="s">
-        <v>799</v>
+        <v>787</v>
       </c>
       <c r="G80" s="15" t="s">
-        <v>800</v>
+        <v>788</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
@@ -6556,10 +6556,10 @@
         <v>138</v>
       </c>
       <c r="F81" s="11" t="s">
-        <v>1287</v>
+        <v>1275</v>
       </c>
       <c r="G81" s="11" t="s">
-        <v>1288</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
@@ -6579,10 +6579,10 @@
         <v>138</v>
       </c>
       <c r="F82" s="15" t="s">
-        <v>801</v>
+        <v>789</v>
       </c>
       <c r="G82" s="15" t="s">
-        <v>802</v>
+        <v>790</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
@@ -6602,10 +6602,10 @@
         <v>138</v>
       </c>
       <c r="F83" s="15" t="s">
-        <v>803</v>
+        <v>791</v>
       </c>
       <c r="G83" s="15" t="s">
-        <v>804</v>
+        <v>792</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
@@ -6625,10 +6625,10 @@
         <v>138</v>
       </c>
       <c r="F84" s="11" t="s">
-        <v>1277</v>
+        <v>1265</v>
       </c>
       <c r="G84" s="11" t="s">
-        <v>1278</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
@@ -6648,10 +6648,10 @@
         <v>138</v>
       </c>
       <c r="F85" s="11" t="s">
-        <v>1289</v>
+        <v>1277</v>
       </c>
       <c r="G85" s="11" t="s">
-        <v>1290</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
@@ -6671,10 +6671,10 @@
         <v>138</v>
       </c>
       <c r="F86" s="15" t="s">
-        <v>805</v>
+        <v>793</v>
       </c>
       <c r="G86" s="15" t="s">
-        <v>806</v>
+        <v>794</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
@@ -6694,10 +6694,10 @@
         <v>138</v>
       </c>
       <c r="F87" s="15" t="s">
-        <v>807</v>
+        <v>795</v>
       </c>
       <c r="G87" s="15" t="s">
-        <v>808</v>
+        <v>796</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
@@ -6717,10 +6717,10 @@
         <v>138</v>
       </c>
       <c r="F88" s="15" t="s">
-        <v>809</v>
+        <v>797</v>
       </c>
       <c r="G88" s="15" t="s">
-        <v>810</v>
+        <v>798</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
@@ -6740,10 +6740,10 @@
         <v>138</v>
       </c>
       <c r="F89" s="15" t="s">
-        <v>811</v>
+        <v>799</v>
       </c>
       <c r="G89" s="15" t="s">
-        <v>812</v>
+        <v>800</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
@@ -6763,10 +6763,10 @@
         <v>138</v>
       </c>
       <c r="F90" s="11" t="s">
-        <v>1279</v>
+        <v>1267</v>
       </c>
       <c r="G90" s="11" t="s">
-        <v>1280</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
@@ -6786,10 +6786,10 @@
         <v>138</v>
       </c>
       <c r="F91" s="15" t="s">
-        <v>813</v>
+        <v>801</v>
       </c>
       <c r="G91" s="15" t="s">
-        <v>814</v>
+        <v>802</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
@@ -6809,10 +6809,10 @@
         <v>138</v>
       </c>
       <c r="F92" s="15" t="s">
-        <v>815</v>
+        <v>803</v>
       </c>
       <c r="G92" s="15" t="s">
-        <v>816</v>
+        <v>804</v>
       </c>
     </row>
     <row r="93" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6832,10 +6832,10 @@
         <v>138</v>
       </c>
       <c r="F93" s="13" t="s">
-        <v>817</v>
+        <v>805</v>
       </c>
       <c r="G93" s="14" t="s">
-        <v>818</v>
+        <v>806</v>
       </c>
     </row>
     <row r="94" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6855,10 +6855,10 @@
         <v>138</v>
       </c>
       <c r="F94" s="6" t="s">
-        <v>819</v>
+        <v>807</v>
       </c>
       <c r="G94" s="8" t="s">
-        <v>820</v>
+        <v>808</v>
       </c>
     </row>
     <row r="95" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6878,10 +6878,10 @@
         <v>138</v>
       </c>
       <c r="F95" s="6" t="s">
-        <v>821</v>
+        <v>809</v>
       </c>
       <c r="G95" s="8" t="s">
-        <v>822</v>
+        <v>810</v>
       </c>
     </row>
     <row r="96" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6901,10 +6901,10 @@
         <v>138</v>
       </c>
       <c r="F96" s="6" t="s">
-        <v>823</v>
+        <v>811</v>
       </c>
       <c r="G96" s="8" t="s">
-        <v>824</v>
+        <v>812</v>
       </c>
     </row>
     <row r="97" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6924,10 +6924,10 @@
         <v>138</v>
       </c>
       <c r="F97" s="6" t="s">
-        <v>825</v>
+        <v>813</v>
       </c>
       <c r="G97" s="8" t="s">
-        <v>826</v>
+        <v>814</v>
       </c>
     </row>
     <row r="98" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6947,10 +6947,10 @@
         <v>138</v>
       </c>
       <c r="F98" s="6" t="s">
-        <v>827</v>
+        <v>815</v>
       </c>
       <c r="G98" s="8" t="s">
-        <v>828</v>
+        <v>816</v>
       </c>
     </row>
     <row r="99" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6970,10 +6970,10 @@
         <v>138</v>
       </c>
       <c r="F99" s="6" t="s">
-        <v>829</v>
+        <v>817</v>
       </c>
       <c r="G99" s="8" t="s">
-        <v>830</v>
+        <v>818</v>
       </c>
     </row>
     <row r="100" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6993,10 +6993,10 @@
         <v>138</v>
       </c>
       <c r="F100" s="5" t="s">
-        <v>1312</v>
+        <v>1300</v>
       </c>
       <c r="G100" s="7" t="s">
-        <v>1313</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="101" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7016,10 +7016,10 @@
         <v>138</v>
       </c>
       <c r="F101" s="6" t="s">
-        <v>831</v>
+        <v>819</v>
       </c>
       <c r="G101" s="8" t="s">
-        <v>832</v>
+        <v>820</v>
       </c>
     </row>
     <row r="102" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7039,10 +7039,10 @@
         <v>138</v>
       </c>
       <c r="F102" s="6" t="s">
-        <v>833</v>
+        <v>821</v>
       </c>
       <c r="G102" s="8" t="s">
-        <v>834</v>
+        <v>822</v>
       </c>
     </row>
     <row r="103" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7062,10 +7062,10 @@
         <v>138</v>
       </c>
       <c r="F103" s="6" t="s">
-        <v>835</v>
+        <v>823</v>
       </c>
       <c r="G103" s="8" t="s">
-        <v>836</v>
+        <v>824</v>
       </c>
     </row>
     <row r="104" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7085,10 +7085,10 @@
         <v>138</v>
       </c>
       <c r="F104" s="6" t="s">
-        <v>837</v>
+        <v>825</v>
       </c>
       <c r="G104" s="8" t="s">
-        <v>838</v>
+        <v>826</v>
       </c>
     </row>
     <row r="105" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7108,10 +7108,10 @@
         <v>138</v>
       </c>
       <c r="F105" s="12" t="s">
-        <v>1302</v>
+        <v>1290</v>
       </c>
       <c r="G105" s="12" t="s">
-        <v>1303</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="106" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7131,10 +7131,10 @@
         <v>138</v>
       </c>
       <c r="F106" s="6" t="s">
-        <v>839</v>
+        <v>827</v>
       </c>
       <c r="G106" s="8" t="s">
-        <v>840</v>
+        <v>828</v>
       </c>
     </row>
     <row r="107" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7154,10 +7154,10 @@
         <v>138</v>
       </c>
       <c r="F107" s="5" t="s">
-        <v>1310</v>
+        <v>1298</v>
       </c>
       <c r="G107" s="7" t="s">
-        <v>1311</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="108" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7177,10 +7177,10 @@
         <v>138</v>
       </c>
       <c r="F108" s="6" t="s">
-        <v>841</v>
+        <v>829</v>
       </c>
       <c r="G108" s="8" t="s">
-        <v>842</v>
+        <v>830</v>
       </c>
     </row>
     <row r="109" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7200,10 +7200,10 @@
         <v>138</v>
       </c>
       <c r="F109" s="6" t="s">
-        <v>843</v>
+        <v>831</v>
       </c>
       <c r="G109" s="8" t="s">
-        <v>844</v>
+        <v>832</v>
       </c>
     </row>
     <row r="110" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7223,10 +7223,10 @@
         <v>138</v>
       </c>
       <c r="F110" s="6" t="s">
-        <v>845</v>
+        <v>833</v>
       </c>
       <c r="G110" s="8" t="s">
-        <v>846</v>
+        <v>834</v>
       </c>
     </row>
     <row r="111" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7246,10 +7246,10 @@
         <v>138</v>
       </c>
       <c r="F111" s="5" t="s">
-        <v>1314</v>
+        <v>1302</v>
       </c>
       <c r="G111" s="7" t="s">
-        <v>1315</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="112" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7269,10 +7269,10 @@
         <v>138</v>
       </c>
       <c r="F112" s="17" t="s">
-        <v>1308</v>
+        <v>1296</v>
       </c>
       <c r="G112" s="17" t="s">
-        <v>1309</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="113" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7292,10 +7292,10 @@
         <v>138</v>
       </c>
       <c r="F113" s="6" t="s">
-        <v>847</v>
+        <v>835</v>
       </c>
       <c r="G113" s="8" t="s">
-        <v>848</v>
+        <v>836</v>
       </c>
     </row>
     <row r="114" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7315,10 +7315,10 @@
         <v>138</v>
       </c>
       <c r="F114" s="12" t="s">
-        <v>1304</v>
+        <v>1292</v>
       </c>
       <c r="G114" s="12" t="s">
-        <v>1305</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="115" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7338,10 +7338,10 @@
         <v>138</v>
       </c>
       <c r="F115" s="6" t="s">
-        <v>849</v>
+        <v>837</v>
       </c>
       <c r="G115" s="8" t="s">
-        <v>850</v>
+        <v>838</v>
       </c>
     </row>
     <row r="116" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7361,10 +7361,10 @@
         <v>138</v>
       </c>
       <c r="F116" s="6" t="s">
-        <v>851</v>
+        <v>839</v>
       </c>
       <c r="G116" s="8" t="s">
-        <v>852</v>
+        <v>840</v>
       </c>
     </row>
     <row r="117" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7384,10 +7384,10 @@
         <v>138</v>
       </c>
       <c r="F117" s="6" t="s">
-        <v>853</v>
+        <v>841</v>
       </c>
       <c r="G117" s="8" t="s">
-        <v>854</v>
+        <v>842</v>
       </c>
     </row>
     <row r="118" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7404,10 +7404,10 @@
         <v>138</v>
       </c>
       <c r="F118" s="6" t="s">
-        <v>855</v>
+        <v>843</v>
       </c>
       <c r="G118" s="8" t="s">
-        <v>856</v>
+        <v>844</v>
       </c>
     </row>
     <row r="119" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7427,10 +7427,10 @@
         <v>138</v>
       </c>
       <c r="F119" s="12" t="s">
-        <v>1300</v>
+        <v>1288</v>
       </c>
       <c r="G119" s="12" t="s">
-        <v>1301</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="120" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7450,10 +7450,10 @@
         <v>138</v>
       </c>
       <c r="F120" s="6" t="s">
-        <v>857</v>
+        <v>845</v>
       </c>
       <c r="G120" s="8" t="s">
-        <v>858</v>
+        <v>846</v>
       </c>
     </row>
     <row r="121" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7473,10 +7473,10 @@
         <v>138</v>
       </c>
       <c r="F121" s="12" t="s">
-        <v>1306</v>
+        <v>1294</v>
       </c>
       <c r="G121" s="12" t="s">
-        <v>1307</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="122" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7496,10 +7496,10 @@
         <v>138</v>
       </c>
       <c r="F122" s="6" t="s">
-        <v>859</v>
+        <v>847</v>
       </c>
       <c r="G122" s="8" t="s">
-        <v>860</v>
+        <v>848</v>
       </c>
     </row>
     <row r="123" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7519,10 +7519,10 @@
         <v>138</v>
       </c>
       <c r="F123" s="6" t="s">
-        <v>861</v>
+        <v>849</v>
       </c>
       <c r="G123" s="8" t="s">
-        <v>862</v>
+        <v>850</v>
       </c>
     </row>
     <row r="124" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7542,10 +7542,10 @@
         <v>138</v>
       </c>
       <c r="F124" s="6" t="s">
-        <v>863</v>
+        <v>851</v>
       </c>
       <c r="G124" s="8" t="s">
-        <v>864</v>
+        <v>852</v>
       </c>
     </row>
     <row r="125" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7565,10 +7565,10 @@
         <v>138</v>
       </c>
       <c r="F125" s="12" t="s">
-        <v>1269</v>
+        <v>1257</v>
       </c>
       <c r="G125" s="12" t="s">
-        <v>1270</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="126" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7588,10 +7588,10 @@
         <v>138</v>
       </c>
       <c r="F126" s="12" t="s">
-        <v>1283</v>
+        <v>1271</v>
       </c>
       <c r="G126" s="12" t="s">
-        <v>1284</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="127" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7611,10 +7611,10 @@
         <v>138</v>
       </c>
       <c r="F127" s="6" t="s">
-        <v>865</v>
+        <v>853</v>
       </c>
       <c r="G127" s="8" t="s">
-        <v>866</v>
+        <v>854</v>
       </c>
     </row>
     <row r="128" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7634,10 +7634,10 @@
         <v>138</v>
       </c>
       <c r="F128" s="6" t="s">
-        <v>867</v>
+        <v>855</v>
       </c>
       <c r="G128" s="8" t="s">
-        <v>868</v>
+        <v>856</v>
       </c>
     </row>
     <row r="129" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7657,10 +7657,10 @@
         <v>138</v>
       </c>
       <c r="F129" s="6" t="s">
-        <v>869</v>
+        <v>857</v>
       </c>
       <c r="G129" s="8" t="s">
-        <v>870</v>
+        <v>858</v>
       </c>
     </row>
     <row r="130" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7680,10 +7680,10 @@
         <v>138</v>
       </c>
       <c r="F130" s="12" t="s">
-        <v>1291</v>
+        <v>1279</v>
       </c>
       <c r="G130" s="12" t="s">
-        <v>1292</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="131" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7703,10 +7703,10 @@
         <v>138</v>
       </c>
       <c r="F131" s="6" t="s">
-        <v>871</v>
+        <v>859</v>
       </c>
       <c r="G131" s="8" t="s">
-        <v>872</v>
+        <v>860</v>
       </c>
     </row>
     <row r="132" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7726,10 +7726,10 @@
         <v>138</v>
       </c>
       <c r="F132" s="6" t="s">
-        <v>873</v>
+        <v>861</v>
       </c>
       <c r="G132" s="8" t="s">
-        <v>874</v>
+        <v>862</v>
       </c>
     </row>
     <row r="133" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7749,10 +7749,10 @@
         <v>138</v>
       </c>
       <c r="F133" s="6" t="s">
-        <v>875</v>
+        <v>863</v>
       </c>
       <c r="G133" s="8" t="s">
-        <v>876</v>
+        <v>864</v>
       </c>
     </row>
     <row r="134" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7772,10 +7772,10 @@
         <v>138</v>
       </c>
       <c r="F134" s="6" t="s">
-        <v>877</v>
+        <v>865</v>
       </c>
       <c r="G134" s="8" t="s">
-        <v>878</v>
+        <v>866</v>
       </c>
     </row>
     <row r="135" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7795,10 +7795,10 @@
         <v>138</v>
       </c>
       <c r="F135" s="12" t="s">
-        <v>1275</v>
+        <v>1263</v>
       </c>
       <c r="G135" s="12" t="s">
-        <v>1276</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="136" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7818,10 +7818,10 @@
         <v>138</v>
       </c>
       <c r="F136" s="6" t="s">
-        <v>879</v>
+        <v>867</v>
       </c>
       <c r="G136" s="8" t="s">
-        <v>880</v>
+        <v>868</v>
       </c>
     </row>
     <row r="137" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7841,10 +7841,10 @@
         <v>138</v>
       </c>
       <c r="F137" s="6" t="s">
-        <v>881</v>
+        <v>869</v>
       </c>
       <c r="G137" s="8" t="s">
-        <v>882</v>
+        <v>870</v>
       </c>
     </row>
     <row r="138" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7864,10 +7864,10 @@
         <v>138</v>
       </c>
       <c r="F138" s="6" t="s">
-        <v>883</v>
+        <v>871</v>
       </c>
       <c r="G138" s="8" t="s">
-        <v>884</v>
+        <v>872</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.3">
@@ -7887,10 +7887,10 @@
         <v>138</v>
       </c>
       <c r="F139" s="9" t="s">
-        <v>885</v>
+        <v>873</v>
       </c>
       <c r="G139" s="10" t="s">
-        <v>886</v>
+        <v>874</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.3">
@@ -7910,10 +7910,10 @@
         <v>138</v>
       </c>
       <c r="F140" s="15" t="s">
-        <v>887</v>
+        <v>875</v>
       </c>
       <c r="G140" s="15" t="s">
-        <v>888</v>
+        <v>876</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.3">
@@ -7933,10 +7933,10 @@
         <v>138</v>
       </c>
       <c r="F141" s="11" t="s">
-        <v>1265</v>
+        <v>1253</v>
       </c>
       <c r="G141" s="11" t="s">
-        <v>1266</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.3">
@@ -7956,10 +7956,10 @@
         <v>138</v>
       </c>
       <c r="F142" s="15" t="s">
-        <v>889</v>
+        <v>877</v>
       </c>
       <c r="G142" s="15" t="s">
-        <v>890</v>
+        <v>878</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.3">
@@ -7979,10 +7979,10 @@
         <v>138</v>
       </c>
       <c r="F143" s="11" t="s">
-        <v>1293</v>
+        <v>1281</v>
       </c>
       <c r="G143" s="11" t="s">
-        <v>1294</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.3">
@@ -8002,10 +8002,10 @@
         <v>138</v>
       </c>
       <c r="F144" s="11" t="s">
-        <v>1267</v>
+        <v>1255</v>
       </c>
       <c r="G144" s="11" t="s">
-        <v>1268</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.3">
@@ -8025,10 +8025,10 @@
         <v>138</v>
       </c>
       <c r="F145" s="15" t="s">
-        <v>891</v>
+        <v>879</v>
       </c>
       <c r="G145" s="15" t="s">
-        <v>892</v>
+        <v>880</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.3">
@@ -8048,10 +8048,10 @@
         <v>138</v>
       </c>
       <c r="F146" s="11" t="s">
-        <v>1273</v>
+        <v>1261</v>
       </c>
       <c r="G146" s="11" t="s">
-        <v>1274</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.3">
@@ -8071,10 +8071,10 @@
         <v>138</v>
       </c>
       <c r="F147" s="15" t="s">
-        <v>893</v>
+        <v>881</v>
       </c>
       <c r="G147" s="15" t="s">
-        <v>894</v>
+        <v>882</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.3">
@@ -8094,10 +8094,10 @@
         <v>138</v>
       </c>
       <c r="F148" s="15" t="s">
-        <v>895</v>
+        <v>883</v>
       </c>
       <c r="G148" s="15" t="s">
-        <v>896</v>
+        <v>884</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.3">
@@ -8117,10 +8117,10 @@
         <v>138</v>
       </c>
       <c r="F149" s="15" t="s">
-        <v>897</v>
+        <v>885</v>
       </c>
       <c r="G149" s="15" t="s">
-        <v>898</v>
+        <v>886</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.3">
@@ -8140,10 +8140,10 @@
         <v>138</v>
       </c>
       <c r="F150" s="15" t="s">
-        <v>899</v>
+        <v>887</v>
       </c>
       <c r="G150" s="15" t="s">
-        <v>900</v>
+        <v>888</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.3">
@@ -8163,10 +8163,10 @@
         <v>138</v>
       </c>
       <c r="F151" s="15" t="s">
-        <v>901</v>
+        <v>889</v>
       </c>
       <c r="G151" s="15" t="s">
-        <v>902</v>
+        <v>890</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.3">
@@ -8186,10 +8186,10 @@
         <v>138</v>
       </c>
       <c r="F152" s="11" t="s">
-        <v>1281</v>
+        <v>1269</v>
       </c>
       <c r="G152" s="11" t="s">
-        <v>1282</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="153" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8209,10 +8209,10 @@
         <v>138</v>
       </c>
       <c r="F153" s="13" t="s">
-        <v>903</v>
+        <v>891</v>
       </c>
       <c r="G153" s="14" t="s">
-        <v>904</v>
+        <v>892</v>
       </c>
     </row>
     <row r="154" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8232,10 +8232,10 @@
         <v>138</v>
       </c>
       <c r="F154" s="6" t="s">
-        <v>905</v>
+        <v>893</v>
       </c>
       <c r="G154" s="8" t="s">
-        <v>906</v>
+        <v>894</v>
       </c>
     </row>
     <row r="155" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8255,10 +8255,10 @@
         <v>138</v>
       </c>
       <c r="F155" s="6" t="s">
-        <v>907</v>
+        <v>895</v>
       </c>
       <c r="G155" s="8" t="s">
-        <v>908</v>
+        <v>896</v>
       </c>
     </row>
     <row r="156" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8278,10 +8278,10 @@
         <v>138</v>
       </c>
       <c r="F156" s="6" t="s">
-        <v>909</v>
+        <v>897</v>
       </c>
       <c r="G156" s="8" t="s">
-        <v>910</v>
+        <v>898</v>
       </c>
     </row>
     <row r="157" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8301,10 +8301,10 @@
         <v>138</v>
       </c>
       <c r="F157" s="12" t="s">
-        <v>1285</v>
+        <v>1273</v>
       </c>
       <c r="G157" s="12" t="s">
-        <v>1286</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="158" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8324,10 +8324,10 @@
         <v>138</v>
       </c>
       <c r="F158" s="6" t="s">
-        <v>911</v>
+        <v>899</v>
       </c>
       <c r="G158" s="8" t="s">
-        <v>912</v>
+        <v>900</v>
       </c>
     </row>
     <row r="159" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8347,10 +8347,10 @@
         <v>138</v>
       </c>
       <c r="F159" s="6" t="s">
-        <v>913</v>
+        <v>901</v>
       </c>
       <c r="G159" s="8" t="s">
-        <v>914</v>
+        <v>902</v>
       </c>
     </row>
     <row r="160" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8370,10 +8370,10 @@
         <v>138</v>
       </c>
       <c r="F160" s="12" t="s">
-        <v>1271</v>
+        <v>1259</v>
       </c>
       <c r="G160" s="12" t="s">
-        <v>1272</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="161" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8393,10 +8393,10 @@
         <v>138</v>
       </c>
       <c r="F161" s="6" t="s">
-        <v>915</v>
+        <v>903</v>
       </c>
       <c r="G161" s="8" t="s">
-        <v>916</v>
+        <v>904</v>
       </c>
     </row>
     <row r="162" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8416,10 +8416,10 @@
         <v>138</v>
       </c>
       <c r="F162" s="6" t="s">
-        <v>917</v>
+        <v>905</v>
       </c>
       <c r="G162" s="8" t="s">
-        <v>918</v>
+        <v>906</v>
       </c>
     </row>
     <row r="163" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8439,10 +8439,10 @@
         <v>138</v>
       </c>
       <c r="F163" s="6" t="s">
-        <v>919</v>
+        <v>907</v>
       </c>
       <c r="G163" s="8" t="s">
-        <v>920</v>
+        <v>908</v>
       </c>
     </row>
     <row r="164" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8462,10 +8462,10 @@
         <v>138</v>
       </c>
       <c r="F164" s="6" t="s">
-        <v>921</v>
+        <v>909</v>
       </c>
       <c r="G164" s="8" t="s">
-        <v>922</v>
+        <v>910</v>
       </c>
     </row>
     <row r="165" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8485,10 +8485,10 @@
         <v>138</v>
       </c>
       <c r="F165" s="6" t="s">
-        <v>923</v>
+        <v>911</v>
       </c>
       <c r="G165" s="8" t="s">
-        <v>924</v>
+        <v>912</v>
       </c>
     </row>
     <row r="166" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8508,10 +8508,10 @@
         <v>138</v>
       </c>
       <c r="F166" s="6" t="s">
-        <v>925</v>
+        <v>913</v>
       </c>
       <c r="G166" s="8" t="s">
-        <v>926</v>
+        <v>914</v>
       </c>
     </row>
     <row r="167" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8531,10 +8531,10 @@
         <v>138</v>
       </c>
       <c r="F167" s="6" t="s">
-        <v>927</v>
+        <v>915</v>
       </c>
       <c r="G167" s="8" t="s">
-        <v>928</v>
+        <v>916</v>
       </c>
     </row>
     <row r="168" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8554,10 +8554,10 @@
         <v>138</v>
       </c>
       <c r="F168" s="6" t="s">
-        <v>929</v>
+        <v>917</v>
       </c>
       <c r="G168" s="8" t="s">
-        <v>930</v>
+        <v>918</v>
       </c>
     </row>
     <row r="169" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8577,10 +8577,10 @@
         <v>138</v>
       </c>
       <c r="F169" s="6" t="s">
-        <v>931</v>
+        <v>919</v>
       </c>
       <c r="G169" s="8" t="s">
-        <v>932</v>
+        <v>920</v>
       </c>
     </row>
     <row r="170" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8600,10 +8600,10 @@
         <v>138</v>
       </c>
       <c r="F170" s="6" t="s">
-        <v>933</v>
+        <v>921</v>
       </c>
       <c r="G170" s="8" t="s">
-        <v>934</v>
+        <v>922</v>
       </c>
     </row>
     <row r="171" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8623,10 +8623,10 @@
         <v>138</v>
       </c>
       <c r="F171" s="6" t="s">
-        <v>935</v>
+        <v>923</v>
       </c>
       <c r="G171" s="8" t="s">
-        <v>936</v>
+        <v>924</v>
       </c>
     </row>
     <row r="172" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8646,10 +8646,10 @@
         <v>138</v>
       </c>
       <c r="F172" s="6" t="s">
-        <v>937</v>
+        <v>925</v>
       </c>
       <c r="G172" s="8" t="s">
-        <v>938</v>
+        <v>926</v>
       </c>
     </row>
     <row r="173" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8669,10 +8669,10 @@
         <v>138</v>
       </c>
       <c r="F173" s="6" t="s">
-        <v>939</v>
+        <v>927</v>
       </c>
       <c r="G173" s="8" t="s">
-        <v>940</v>
+        <v>928</v>
       </c>
     </row>
     <row r="174" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8692,10 +8692,10 @@
         <v>138</v>
       </c>
       <c r="F174" s="6" t="s">
-        <v>941</v>
+        <v>929</v>
       </c>
       <c r="G174" s="8" t="s">
-        <v>942</v>
+        <v>930</v>
       </c>
     </row>
     <row r="175" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8715,10 +8715,10 @@
         <v>138</v>
       </c>
       <c r="F175" s="6" t="s">
-        <v>943</v>
+        <v>931</v>
       </c>
       <c r="G175" s="8" t="s">
-        <v>944</v>
+        <v>932</v>
       </c>
     </row>
     <row r="176" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8738,10 +8738,10 @@
         <v>138</v>
       </c>
       <c r="F176" s="6" t="s">
-        <v>945</v>
+        <v>933</v>
       </c>
       <c r="G176" s="8" t="s">
-        <v>946</v>
+        <v>934</v>
       </c>
     </row>
     <row r="177" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8761,10 +8761,10 @@
         <v>138</v>
       </c>
       <c r="F177" s="6" t="s">
-        <v>947</v>
+        <v>935</v>
       </c>
       <c r="G177" s="8" t="s">
-        <v>948</v>
+        <v>936</v>
       </c>
     </row>
     <row r="178" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8784,10 +8784,10 @@
         <v>138</v>
       </c>
       <c r="F178" s="6" t="s">
-        <v>949</v>
+        <v>937</v>
       </c>
       <c r="G178" s="8" t="s">
-        <v>950</v>
+        <v>938</v>
       </c>
     </row>
     <row r="179" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8807,10 +8807,10 @@
         <v>138</v>
       </c>
       <c r="F179" s="6" t="s">
-        <v>951</v>
+        <v>939</v>
       </c>
       <c r="G179" s="8" t="s">
-        <v>952</v>
+        <v>940</v>
       </c>
     </row>
     <row r="180" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8830,10 +8830,10 @@
         <v>138</v>
       </c>
       <c r="F180" s="6" t="s">
-        <v>953</v>
+        <v>941</v>
       </c>
       <c r="G180" s="8" t="s">
-        <v>954</v>
+        <v>942</v>
       </c>
     </row>
     <row r="181" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8853,10 +8853,10 @@
         <v>138</v>
       </c>
       <c r="F181" s="6" t="s">
-        <v>955</v>
+        <v>943</v>
       </c>
       <c r="G181" s="8" t="s">
-        <v>956</v>
+        <v>944</v>
       </c>
     </row>
     <row r="182" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8876,10 +8876,10 @@
         <v>138</v>
       </c>
       <c r="F182" s="6" t="s">
-        <v>957</v>
+        <v>945</v>
       </c>
       <c r="G182" s="8" t="s">
-        <v>958</v>
+        <v>946</v>
       </c>
     </row>
     <row r="183" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8899,10 +8899,10 @@
         <v>138</v>
       </c>
       <c r="F183" s="6" t="s">
-        <v>959</v>
+        <v>947</v>
       </c>
       <c r="G183" s="8" t="s">
-        <v>960</v>
+        <v>948</v>
       </c>
     </row>
     <row r="184" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8922,10 +8922,10 @@
         <v>138</v>
       </c>
       <c r="F184" s="6" t="s">
-        <v>961</v>
+        <v>949</v>
       </c>
       <c r="G184" s="8" t="s">
-        <v>962</v>
+        <v>950</v>
       </c>
     </row>
     <row r="185" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8945,10 +8945,10 @@
         <v>138</v>
       </c>
       <c r="F185" s="6" t="s">
-        <v>963</v>
+        <v>951</v>
       </c>
       <c r="G185" s="8" t="s">
-        <v>964</v>
+        <v>952</v>
       </c>
     </row>
     <row r="186" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8968,10 +8968,10 @@
         <v>138</v>
       </c>
       <c r="F186" s="6" t="s">
-        <v>965</v>
+        <v>953</v>
       </c>
       <c r="G186" s="8" t="s">
-        <v>966</v>
+        <v>954</v>
       </c>
     </row>
     <row r="187" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8991,10 +8991,10 @@
         <v>138</v>
       </c>
       <c r="F187" s="6" t="s">
-        <v>967</v>
+        <v>955</v>
       </c>
       <c r="G187" s="8" t="s">
-        <v>968</v>
+        <v>956</v>
       </c>
     </row>
     <row r="188" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9014,10 +9014,10 @@
         <v>138</v>
       </c>
       <c r="F188" s="6" t="s">
-        <v>969</v>
+        <v>957</v>
       </c>
       <c r="G188" s="8" t="s">
-        <v>970</v>
+        <v>958</v>
       </c>
     </row>
     <row r="189" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9037,10 +9037,10 @@
         <v>138</v>
       </c>
       <c r="F189" s="6" t="s">
-        <v>971</v>
+        <v>959</v>
       </c>
       <c r="G189" s="8" t="s">
-        <v>972</v>
+        <v>960</v>
       </c>
     </row>
     <row r="190" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9060,10 +9060,10 @@
         <v>138</v>
       </c>
       <c r="F190" s="6" t="s">
-        <v>973</v>
+        <v>961</v>
       </c>
       <c r="G190" s="8" t="s">
-        <v>974</v>
+        <v>962</v>
       </c>
     </row>
     <row r="191" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9083,10 +9083,10 @@
         <v>138</v>
       </c>
       <c r="F191" s="6" t="s">
-        <v>975</v>
+        <v>963</v>
       </c>
       <c r="G191" s="8" t="s">
-        <v>976</v>
+        <v>964</v>
       </c>
     </row>
     <row r="192" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9106,10 +9106,10 @@
         <v>138</v>
       </c>
       <c r="F192" s="6" t="s">
-        <v>977</v>
+        <v>965</v>
       </c>
       <c r="G192" s="8" t="s">
-        <v>978</v>
+        <v>966</v>
       </c>
     </row>
     <row r="193" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9129,10 +9129,10 @@
         <v>138</v>
       </c>
       <c r="F193" s="6" t="s">
-        <v>979</v>
+        <v>967</v>
       </c>
       <c r="G193" s="8" t="s">
-        <v>980</v>
+        <v>968</v>
       </c>
     </row>
     <row r="194" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9152,10 +9152,10 @@
         <v>138</v>
       </c>
       <c r="F194" s="6" t="s">
-        <v>981</v>
+        <v>969</v>
       </c>
       <c r="G194" s="8" t="s">
-        <v>982</v>
+        <v>970</v>
       </c>
     </row>
     <row r="195" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9175,10 +9175,10 @@
         <v>138</v>
       </c>
       <c r="F195" s="6" t="s">
-        <v>983</v>
+        <v>971</v>
       </c>
       <c r="G195" s="8" t="s">
-        <v>984</v>
+        <v>972</v>
       </c>
     </row>
     <row r="196" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9198,10 +9198,10 @@
         <v>138</v>
       </c>
       <c r="F196" s="6" t="s">
-        <v>985</v>
+        <v>973</v>
       </c>
       <c r="G196" s="8" t="s">
-        <v>986</v>
+        <v>974</v>
       </c>
     </row>
     <row r="197" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9221,10 +9221,10 @@
         <v>138</v>
       </c>
       <c r="F197" s="6" t="s">
-        <v>987</v>
+        <v>975</v>
       </c>
       <c r="G197" s="8" t="s">
-        <v>988</v>
+        <v>976</v>
       </c>
     </row>
     <row r="198" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9244,10 +9244,10 @@
         <v>138</v>
       </c>
       <c r="F198" s="6" t="s">
-        <v>989</v>
+        <v>977</v>
       </c>
       <c r="G198" s="8" t="s">
-        <v>990</v>
+        <v>978</v>
       </c>
     </row>
     <row r="199" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9267,10 +9267,10 @@
         <v>138</v>
       </c>
       <c r="F199" s="6" t="s">
-        <v>991</v>
+        <v>979</v>
       </c>
       <c r="G199" s="8" t="s">
-        <v>992</v>
+        <v>980</v>
       </c>
     </row>
     <row r="200" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9290,10 +9290,10 @@
         <v>138</v>
       </c>
       <c r="F200" s="6" t="s">
-        <v>993</v>
+        <v>981</v>
       </c>
       <c r="G200" s="8" t="s">
-        <v>994</v>
+        <v>982</v>
       </c>
     </row>
     <row r="201" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9313,10 +9313,10 @@
         <v>138</v>
       </c>
       <c r="F201" s="6" t="s">
-        <v>995</v>
+        <v>983</v>
       </c>
       <c r="G201" s="8" t="s">
-        <v>996</v>
+        <v>984</v>
       </c>
     </row>
     <row r="202" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9336,10 +9336,10 @@
         <v>138</v>
       </c>
       <c r="F202" s="6" t="s">
-        <v>997</v>
+        <v>985</v>
       </c>
       <c r="G202" s="8" t="s">
-        <v>998</v>
+        <v>986</v>
       </c>
     </row>
     <row r="203" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9359,10 +9359,10 @@
         <v>138</v>
       </c>
       <c r="F203" s="6" t="s">
-        <v>999</v>
+        <v>987</v>
       </c>
       <c r="G203" s="8" t="s">
-        <v>1000</v>
+        <v>988</v>
       </c>
     </row>
     <row r="204" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9382,10 +9382,10 @@
         <v>138</v>
       </c>
       <c r="F204" s="6" t="s">
-        <v>1001</v>
+        <v>989</v>
       </c>
       <c r="G204" s="8" t="s">
-        <v>1002</v>
+        <v>990</v>
       </c>
     </row>
     <row r="205" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9405,10 +9405,10 @@
         <v>138</v>
       </c>
       <c r="F205" s="6" t="s">
-        <v>1003</v>
+        <v>991</v>
       </c>
       <c r="G205" s="8" t="s">
-        <v>1004</v>
+        <v>992</v>
       </c>
     </row>
     <row r="206" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9428,10 +9428,10 @@
         <v>138</v>
       </c>
       <c r="F206" s="6" t="s">
-        <v>1005</v>
+        <v>993</v>
       </c>
       <c r="G206" s="8" t="s">
-        <v>1006</v>
+        <v>994</v>
       </c>
     </row>
     <row r="207" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9451,10 +9451,10 @@
         <v>138</v>
       </c>
       <c r="F207" s="6" t="s">
-        <v>1007</v>
+        <v>995</v>
       </c>
       <c r="G207" s="8" t="s">
-        <v>1008</v>
+        <v>996</v>
       </c>
     </row>
     <row r="208" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9474,10 +9474,10 @@
         <v>138</v>
       </c>
       <c r="F208" s="6" t="s">
-        <v>1009</v>
+        <v>997</v>
       </c>
       <c r="G208" s="8" t="s">
-        <v>1010</v>
+        <v>998</v>
       </c>
     </row>
     <row r="209" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9497,10 +9497,10 @@
         <v>138</v>
       </c>
       <c r="F209" s="6" t="s">
-        <v>1011</v>
+        <v>999</v>
       </c>
       <c r="G209" s="8" t="s">
-        <v>1012</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="210" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9520,10 +9520,10 @@
         <v>138</v>
       </c>
       <c r="F210" s="6" t="s">
-        <v>1013</v>
+        <v>1001</v>
       </c>
       <c r="G210" s="8" t="s">
-        <v>1014</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="211" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9543,10 +9543,10 @@
         <v>138</v>
       </c>
       <c r="F211" s="6" t="s">
-        <v>1015</v>
+        <v>1003</v>
       </c>
       <c r="G211" s="8" t="s">
-        <v>1016</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="212" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9566,10 +9566,10 @@
         <v>138</v>
       </c>
       <c r="F212" s="6" t="s">
-        <v>1017</v>
+        <v>1005</v>
       </c>
       <c r="G212" s="8" t="s">
-        <v>1018</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="213" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9589,10 +9589,10 @@
         <v>138</v>
       </c>
       <c r="F213" s="6" t="s">
-        <v>1019</v>
+        <v>1007</v>
       </c>
       <c r="G213" s="8" t="s">
-        <v>1020</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="214" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9612,10 +9612,10 @@
         <v>138</v>
       </c>
       <c r="F214" s="6" t="s">
-        <v>1021</v>
+        <v>1009</v>
       </c>
       <c r="G214" s="8" t="s">
-        <v>1022</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="215" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9635,10 +9635,10 @@
         <v>138</v>
       </c>
       <c r="F215" s="6" t="s">
-        <v>1023</v>
+        <v>1011</v>
       </c>
       <c r="G215" s="8" t="s">
-        <v>1024</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="216" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9658,10 +9658,10 @@
         <v>138</v>
       </c>
       <c r="F216" s="6" t="s">
-        <v>1025</v>
+        <v>1013</v>
       </c>
       <c r="G216" s="8" t="s">
-        <v>1026</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="217" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9681,10 +9681,10 @@
         <v>138</v>
       </c>
       <c r="F217" s="6" t="s">
-        <v>1027</v>
+        <v>1015</v>
       </c>
       <c r="G217" s="8" t="s">
-        <v>1028</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="218" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9704,10 +9704,10 @@
         <v>138</v>
       </c>
       <c r="F218" s="6" t="s">
-        <v>1029</v>
+        <v>1017</v>
       </c>
       <c r="G218" s="8" t="s">
-        <v>1030</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.3">
@@ -9727,10 +9727,10 @@
         <v>138</v>
       </c>
       <c r="F219" s="9" t="s">
-        <v>1031</v>
+        <v>1019</v>
       </c>
       <c r="G219" s="10" t="s">
-        <v>1032</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.3">
@@ -9750,10 +9750,10 @@
         <v>138</v>
       </c>
       <c r="F220" s="11" t="s">
-        <v>1033</v>
+        <v>1021</v>
       </c>
       <c r="G220" s="11" t="s">
-        <v>1034</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.3">
@@ -9773,10 +9773,10 @@
         <v>138</v>
       </c>
       <c r="F221" s="11" t="s">
-        <v>1035</v>
+        <v>1023</v>
       </c>
       <c r="G221" s="11" t="s">
-        <v>1036</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.3">
@@ -9796,10 +9796,10 @@
         <v>138</v>
       </c>
       <c r="F222" s="11" t="s">
-        <v>1037</v>
+        <v>1025</v>
       </c>
       <c r="G222" s="11" t="s">
-        <v>1038</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.3">
@@ -9819,10 +9819,10 @@
         <v>138</v>
       </c>
       <c r="F223" s="11" t="s">
-        <v>1039</v>
+        <v>1027</v>
       </c>
       <c r="G223" s="11" t="s">
-        <v>1040</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.3">
@@ -9842,10 +9842,10 @@
         <v>138</v>
       </c>
       <c r="F224" s="11" t="s">
-        <v>1041</v>
+        <v>1029</v>
       </c>
       <c r="G224" s="11" t="s">
-        <v>1042</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.3">
@@ -9865,10 +9865,10 @@
         <v>138</v>
       </c>
       <c r="F225" s="11" t="s">
-        <v>1043</v>
+        <v>1031</v>
       </c>
       <c r="G225" s="11" t="s">
-        <v>1044</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.3">
@@ -9888,10 +9888,10 @@
         <v>138</v>
       </c>
       <c r="F226" s="11" t="s">
-        <v>1045</v>
+        <v>1033</v>
       </c>
       <c r="G226" s="11" t="s">
-        <v>1046</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.3">
@@ -9911,10 +9911,10 @@
         <v>138</v>
       </c>
       <c r="F227" s="11" t="s">
-        <v>1047</v>
+        <v>1035</v>
       </c>
       <c r="G227" s="11" t="s">
-        <v>1048</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.3">
@@ -9934,10 +9934,10 @@
         <v>138</v>
       </c>
       <c r="F228" s="11" t="s">
-        <v>1049</v>
+        <v>1037</v>
       </c>
       <c r="G228" s="11" t="s">
-        <v>1050</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.3">
@@ -9957,10 +9957,10 @@
         <v>138</v>
       </c>
       <c r="F229" s="11" t="s">
-        <v>1051</v>
+        <v>1039</v>
       </c>
       <c r="G229" s="11" t="s">
-        <v>1052</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.3">
@@ -9980,10 +9980,10 @@
         <v>138</v>
       </c>
       <c r="F230" s="11" t="s">
-        <v>1053</v>
+        <v>1041</v>
       </c>
       <c r="G230" s="11" t="s">
-        <v>1054</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.3">
@@ -10003,10 +10003,10 @@
         <v>138</v>
       </c>
       <c r="F231" s="11" t="s">
-        <v>1055</v>
+        <v>1043</v>
       </c>
       <c r="G231" s="11" t="s">
-        <v>1056</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.3">
@@ -10026,10 +10026,10 @@
         <v>138</v>
       </c>
       <c r="F232" s="11" t="s">
-        <v>1057</v>
+        <v>1045</v>
       </c>
       <c r="G232" s="11" t="s">
-        <v>1058</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.3">
@@ -10049,10 +10049,10 @@
         <v>138</v>
       </c>
       <c r="F233" s="11" t="s">
-        <v>1059</v>
+        <v>1047</v>
       </c>
       <c r="G233" s="11" t="s">
-        <v>1060</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.3">
@@ -10072,10 +10072,10 @@
         <v>138</v>
       </c>
       <c r="F234" s="11" t="s">
-        <v>1061</v>
+        <v>1049</v>
       </c>
       <c r="G234" s="11" t="s">
-        <v>1062</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.3">
@@ -10095,10 +10095,10 @@
         <v>138</v>
       </c>
       <c r="F235" s="11" t="s">
-        <v>1063</v>
+        <v>1051</v>
       </c>
       <c r="G235" s="11" t="s">
-        <v>1064</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.3">
@@ -10118,10 +10118,10 @@
         <v>138</v>
       </c>
       <c r="F236" s="11" t="s">
-        <v>1065</v>
+        <v>1053</v>
       </c>
       <c r="G236" s="11" t="s">
-        <v>1066</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.3">
@@ -10141,10 +10141,10 @@
         <v>138</v>
       </c>
       <c r="F237" s="11" t="s">
-        <v>1067</v>
+        <v>1055</v>
       </c>
       <c r="G237" s="11" t="s">
-        <v>1068</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.3">
@@ -10164,10 +10164,10 @@
         <v>138</v>
       </c>
       <c r="F238" s="11" t="s">
-        <v>1069</v>
+        <v>1057</v>
       </c>
       <c r="G238" s="11" t="s">
-        <v>1070</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.3">
@@ -10187,10 +10187,10 @@
         <v>138</v>
       </c>
       <c r="F239" s="11" t="s">
-        <v>1071</v>
+        <v>1059</v>
       </c>
       <c r="G239" s="11" t="s">
-        <v>1072</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.3">
@@ -10210,10 +10210,10 @@
         <v>138</v>
       </c>
       <c r="F240" s="11" t="s">
-        <v>1073</v>
+        <v>1061</v>
       </c>
       <c r="G240" s="11" t="s">
-        <v>1074</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.3">
@@ -10233,10 +10233,10 @@
         <v>138</v>
       </c>
       <c r="F241" s="11" t="s">
-        <v>1075</v>
+        <v>1063</v>
       </c>
       <c r="G241" s="11" t="s">
-        <v>1076</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.3">
@@ -10256,10 +10256,10 @@
         <v>138</v>
       </c>
       <c r="F242" s="11" t="s">
-        <v>1077</v>
+        <v>1065</v>
       </c>
       <c r="G242" s="11" t="s">
-        <v>1078</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.3">
@@ -10279,10 +10279,10 @@
         <v>138</v>
       </c>
       <c r="F243" s="11" t="s">
-        <v>1079</v>
+        <v>1067</v>
       </c>
       <c r="G243" s="11" t="s">
-        <v>1080</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.3">
@@ -10302,10 +10302,10 @@
         <v>138</v>
       </c>
       <c r="F244" s="11" t="s">
-        <v>1081</v>
+        <v>1069</v>
       </c>
       <c r="G244" s="11" t="s">
-        <v>1082</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.3">
@@ -10325,10 +10325,10 @@
         <v>138</v>
       </c>
       <c r="F245" s="11" t="s">
-        <v>1083</v>
+        <v>1071</v>
       </c>
       <c r="G245" s="11" t="s">
-        <v>1084</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.3">
@@ -10348,10 +10348,10 @@
         <v>138</v>
       </c>
       <c r="F246" s="11" t="s">
-        <v>1085</v>
+        <v>1073</v>
       </c>
       <c r="G246" s="11" t="s">
-        <v>1086</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.3">
@@ -10371,10 +10371,10 @@
         <v>138</v>
       </c>
       <c r="F247" s="11" t="s">
-        <v>1087</v>
+        <v>1075</v>
       </c>
       <c r="G247" s="11" t="s">
-        <v>1088</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.3">
@@ -10394,10 +10394,10 @@
         <v>138</v>
       </c>
       <c r="F248" s="11" t="s">
-        <v>1089</v>
+        <v>1077</v>
       </c>
       <c r="G248" s="11" t="s">
-        <v>1090</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.3">
@@ -10417,10 +10417,10 @@
         <v>138</v>
       </c>
       <c r="F249" s="11" t="s">
-        <v>1091</v>
+        <v>1079</v>
       </c>
       <c r="G249" s="11" t="s">
-        <v>1092</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.3">
@@ -10440,10 +10440,10 @@
         <v>138</v>
       </c>
       <c r="F250" s="11" t="s">
-        <v>1093</v>
+        <v>1081</v>
       </c>
       <c r="G250" s="11" t="s">
-        <v>1094</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.3">
@@ -10463,10 +10463,10 @@
         <v>138</v>
       </c>
       <c r="F251" s="11" t="s">
-        <v>1095</v>
+        <v>1083</v>
       </c>
       <c r="G251" s="11" t="s">
-        <v>1096</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.3">
@@ -10486,10 +10486,10 @@
         <v>138</v>
       </c>
       <c r="F252" s="11" t="s">
-        <v>1097</v>
+        <v>1085</v>
       </c>
       <c r="G252" s="11" t="s">
-        <v>1098</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="253" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -10509,10 +10509,10 @@
         <v>138</v>
       </c>
       <c r="F253" s="11" t="s">
-        <v>1099</v>
+        <v>1087</v>
       </c>
       <c r="G253" s="11" t="s">
-        <v>1100</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="254" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -10532,10 +10532,10 @@
         <v>138</v>
       </c>
       <c r="F254" s="5" t="s">
-        <v>1346</v>
+        <v>1334</v>
       </c>
       <c r="G254" s="7" t="s">
-        <v>1347</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.3">
@@ -10555,10 +10555,10 @@
         <v>138</v>
       </c>
       <c r="F255" s="11" t="s">
-        <v>1101</v>
+        <v>1089</v>
       </c>
       <c r="G255" s="11" t="s">
-        <v>1102</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.3">
@@ -10578,10 +10578,10 @@
         <v>138</v>
       </c>
       <c r="F256" s="11" t="s">
-        <v>1103</v>
+        <v>1091</v>
       </c>
       <c r="G256" s="11" t="s">
-        <v>1104</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.3">
@@ -10601,10 +10601,10 @@
         <v>138</v>
       </c>
       <c r="F257" s="11" t="s">
-        <v>1105</v>
+        <v>1093</v>
       </c>
       <c r="G257" s="11" t="s">
-        <v>1106</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.3">
@@ -10624,10 +10624,10 @@
         <v>138</v>
       </c>
       <c r="F258" s="11" t="s">
-        <v>1107</v>
+        <v>1095</v>
       </c>
       <c r="G258" s="11" t="s">
-        <v>1108</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.3">
@@ -10647,10 +10647,10 @@
         <v>138</v>
       </c>
       <c r="F259" s="11" t="s">
-        <v>1109</v>
+        <v>1097</v>
       </c>
       <c r="G259" s="11" t="s">
-        <v>1110</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.3">
@@ -10670,10 +10670,10 @@
         <v>138</v>
       </c>
       <c r="F260" s="11" t="s">
-        <v>1111</v>
+        <v>1099</v>
       </c>
       <c r="G260" s="11" t="s">
-        <v>1112</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.3">
@@ -10693,10 +10693,10 @@
         <v>138</v>
       </c>
       <c r="F261" s="11" t="s">
-        <v>1113</v>
+        <v>1101</v>
       </c>
       <c r="G261" s="11" t="s">
-        <v>1114</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.3">
@@ -10716,10 +10716,10 @@
         <v>138</v>
       </c>
       <c r="F262" s="11" t="s">
-        <v>1115</v>
+        <v>1103</v>
       </c>
       <c r="G262" s="11" t="s">
-        <v>1116</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.3">
@@ -10739,10 +10739,10 @@
         <v>138</v>
       </c>
       <c r="F263" s="11" t="s">
-        <v>1117</v>
+        <v>1105</v>
       </c>
       <c r="G263" s="11" t="s">
-        <v>1118</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.3">
@@ -10762,10 +10762,10 @@
         <v>138</v>
       </c>
       <c r="F264" s="11" t="s">
-        <v>1119</v>
+        <v>1107</v>
       </c>
       <c r="G264" s="11" t="s">
-        <v>1120</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.3">
@@ -10785,10 +10785,10 @@
         <v>138</v>
       </c>
       <c r="F265" s="11" t="s">
-        <v>1121</v>
+        <v>1109</v>
       </c>
       <c r="G265" s="11" t="s">
-        <v>1122</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.3">
@@ -10808,10 +10808,10 @@
         <v>138</v>
       </c>
       <c r="F266" s="11" t="s">
-        <v>1123</v>
+        <v>1111</v>
       </c>
       <c r="G266" s="11" t="s">
-        <v>1124</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.3">
@@ -10831,10 +10831,10 @@
         <v>138</v>
       </c>
       <c r="F267" s="11" t="s">
-        <v>1125</v>
+        <v>1113</v>
       </c>
       <c r="G267" s="11" t="s">
-        <v>1126</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.3">
@@ -10854,10 +10854,10 @@
         <v>138</v>
       </c>
       <c r="F268" s="11" t="s">
-        <v>1127</v>
+        <v>1115</v>
       </c>
       <c r="G268" s="11" t="s">
-        <v>1128</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.3">
@@ -10877,10 +10877,10 @@
         <v>138</v>
       </c>
       <c r="F269" s="11" t="s">
-        <v>1129</v>
+        <v>1117</v>
       </c>
       <c r="G269" s="11" t="s">
-        <v>1130</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.3">
@@ -10900,10 +10900,10 @@
         <v>138</v>
       </c>
       <c r="F270" s="11" t="s">
-        <v>1131</v>
+        <v>1119</v>
       </c>
       <c r="G270" s="11" t="s">
-        <v>1132</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.3">
@@ -10923,10 +10923,10 @@
         <v>138</v>
       </c>
       <c r="F271" s="11" t="s">
-        <v>1133</v>
+        <v>1121</v>
       </c>
       <c r="G271" s="11" t="s">
-        <v>1134</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.3">
@@ -10946,10 +10946,10 @@
         <v>138</v>
       </c>
       <c r="F272" s="11" t="s">
-        <v>1135</v>
+        <v>1123</v>
       </c>
       <c r="G272" s="11" t="s">
-        <v>1136</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.3">
@@ -10969,10 +10969,10 @@
         <v>138</v>
       </c>
       <c r="F273" s="11" t="s">
-        <v>1137</v>
+        <v>1125</v>
       </c>
       <c r="G273" s="11" t="s">
-        <v>1138</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.3">
@@ -10992,10 +10992,10 @@
         <v>138</v>
       </c>
       <c r="F274" s="11" t="s">
-        <v>1139</v>
+        <v>1127</v>
       </c>
       <c r="G274" s="11" t="s">
-        <v>1140</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.3">
@@ -11015,10 +11015,10 @@
         <v>138</v>
       </c>
       <c r="F275" s="11" t="s">
-        <v>1141</v>
+        <v>1129</v>
       </c>
       <c r="G275" s="11" t="s">
-        <v>1142</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.3">
@@ -11038,10 +11038,10 @@
         <v>138</v>
       </c>
       <c r="F276" s="11" t="s">
-        <v>1143</v>
+        <v>1131</v>
       </c>
       <c r="G276" s="11" t="s">
-        <v>1144</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.3">
@@ -11061,10 +11061,10 @@
         <v>138</v>
       </c>
       <c r="F277" s="11" t="s">
-        <v>1145</v>
+        <v>1133</v>
       </c>
       <c r="G277" s="11" t="s">
-        <v>1146</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.3">
@@ -11084,10 +11084,10 @@
         <v>138</v>
       </c>
       <c r="F278" s="11" t="s">
-        <v>1147</v>
+        <v>1135</v>
       </c>
       <c r="G278" s="11" t="s">
-        <v>1148</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="279" spans="1:7" x14ac:dyDescent="0.3">
@@ -11107,10 +11107,10 @@
         <v>138</v>
       </c>
       <c r="F279" s="11" t="s">
-        <v>1149</v>
+        <v>1137</v>
       </c>
       <c r="G279" s="11" t="s">
-        <v>1150</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="280" spans="1:7" x14ac:dyDescent="0.3">
@@ -11130,10 +11130,10 @@
         <v>138</v>
       </c>
       <c r="F280" s="11" t="s">
-        <v>1151</v>
+        <v>1139</v>
       </c>
       <c r="G280" s="11" t="s">
-        <v>1152</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.3">
@@ -11153,10 +11153,10 @@
         <v>138</v>
       </c>
       <c r="F281" s="11" t="s">
-        <v>1153</v>
+        <v>1141</v>
       </c>
       <c r="G281" s="11" t="s">
-        <v>1154</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.3">
@@ -11176,10 +11176,10 @@
         <v>601</v>
       </c>
       <c r="F282" s="11" t="s">
-        <v>1155</v>
+        <v>1143</v>
       </c>
       <c r="G282" s="11" t="s">
-        <v>1156</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.3">
@@ -11199,10 +11199,10 @@
         <v>601</v>
       </c>
       <c r="F283" s="11" t="s">
-        <v>1157</v>
+        <v>1145</v>
       </c>
       <c r="G283" s="11" t="s">
-        <v>1158</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.3">
@@ -11222,10 +11222,10 @@
         <v>601</v>
       </c>
       <c r="F284" s="11" t="s">
-        <v>1159</v>
+        <v>1147</v>
       </c>
       <c r="G284" s="11" t="s">
-        <v>1160</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.3">
@@ -11245,10 +11245,10 @@
         <v>601</v>
       </c>
       <c r="F285" s="11" t="s">
-        <v>1161</v>
+        <v>1149</v>
       </c>
       <c r="G285" s="11" t="s">
-        <v>1162</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.3">
@@ -11268,10 +11268,10 @@
         <v>601</v>
       </c>
       <c r="F286" s="11" t="s">
-        <v>1163</v>
+        <v>1151</v>
       </c>
       <c r="G286" s="11" t="s">
-        <v>1164</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.3">
@@ -11291,10 +11291,10 @@
         <v>601</v>
       </c>
       <c r="F287" s="11" t="s">
-        <v>1165</v>
+        <v>1153</v>
       </c>
       <c r="G287" s="11" t="s">
-        <v>1166</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.3">
@@ -11314,10 +11314,10 @@
         <v>601</v>
       </c>
       <c r="F288" s="11" t="s">
-        <v>1167</v>
+        <v>1155</v>
       </c>
       <c r="G288" s="11" t="s">
-        <v>1168</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.3">
@@ -11337,10 +11337,10 @@
         <v>601</v>
       </c>
       <c r="F289" s="11" t="s">
-        <v>1169</v>
+        <v>1157</v>
       </c>
       <c r="G289" s="11" t="s">
-        <v>1170</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.3">
@@ -11360,10 +11360,10 @@
         <v>601</v>
       </c>
       <c r="F290" s="11" t="s">
-        <v>1171</v>
+        <v>1159</v>
       </c>
       <c r="G290" s="11" t="s">
-        <v>1172</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.3">
@@ -11383,10 +11383,10 @@
         <v>601</v>
       </c>
       <c r="F291" s="11" t="s">
-        <v>1173</v>
+        <v>1161</v>
       </c>
       <c r="G291" s="11" t="s">
-        <v>1174</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.3">
@@ -11406,10 +11406,10 @@
         <v>601</v>
       </c>
       <c r="F292" s="11" t="s">
-        <v>1175</v>
+        <v>1163</v>
       </c>
       <c r="G292" s="11" t="s">
-        <v>1176</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.3">
@@ -11429,10 +11429,10 @@
         <v>601</v>
       </c>
       <c r="F293" s="11" t="s">
-        <v>1177</v>
+        <v>1165</v>
       </c>
       <c r="G293" s="11" t="s">
-        <v>1178</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.3">
@@ -11452,10 +11452,10 @@
         <v>601</v>
       </c>
       <c r="F294" s="11" t="s">
-        <v>1179</v>
+        <v>1167</v>
       </c>
       <c r="G294" s="11" t="s">
-        <v>1180</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.3">
@@ -11475,10 +11475,10 @@
         <v>601</v>
       </c>
       <c r="F295" s="11" t="s">
-        <v>1181</v>
+        <v>1169</v>
       </c>
       <c r="G295" s="11" t="s">
-        <v>1182</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.3">
@@ -11498,10 +11498,10 @@
         <v>601</v>
       </c>
       <c r="F296" s="11" t="s">
-        <v>1183</v>
+        <v>1171</v>
       </c>
       <c r="G296" s="11" t="s">
-        <v>1184</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.3">
@@ -11521,10 +11521,10 @@
         <v>601</v>
       </c>
       <c r="F297" s="11" t="s">
-        <v>1185</v>
+        <v>1173</v>
       </c>
       <c r="G297" s="11" t="s">
-        <v>1186</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.3">
@@ -11544,10 +11544,10 @@
         <v>138</v>
       </c>
       <c r="F298" s="11" t="s">
-        <v>1187</v>
+        <v>1175</v>
       </c>
       <c r="G298" s="11" t="s">
-        <v>1188</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="299" spans="1:7" x14ac:dyDescent="0.3">
@@ -11567,10 +11567,10 @@
         <v>138</v>
       </c>
       <c r="F299" s="11" t="s">
-        <v>1189</v>
+        <v>1177</v>
       </c>
       <c r="G299" s="11" t="s">
-        <v>1190</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.3">
@@ -11590,10 +11590,10 @@
         <v>138</v>
       </c>
       <c r="F300" s="11" t="s">
-        <v>1191</v>
+        <v>1179</v>
       </c>
       <c r="G300" s="11" t="s">
-        <v>1192</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.3">
@@ -11613,10 +11613,10 @@
         <v>138</v>
       </c>
       <c r="F301" s="11" t="s">
-        <v>1193</v>
+        <v>1181</v>
       </c>
       <c r="G301" s="11" t="s">
-        <v>1194</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="302" spans="1:7" x14ac:dyDescent="0.3">
@@ -11636,10 +11636,10 @@
         <v>138</v>
       </c>
       <c r="F302" s="11" t="s">
-        <v>1195</v>
+        <v>1183</v>
       </c>
       <c r="G302" s="11" t="s">
-        <v>1196</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="303" spans="1:7" x14ac:dyDescent="0.3">
@@ -11659,10 +11659,10 @@
         <v>138</v>
       </c>
       <c r="F303" s="11" t="s">
-        <v>1197</v>
+        <v>1185</v>
       </c>
       <c r="G303" s="11" t="s">
-        <v>1198</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="304" spans="1:7" x14ac:dyDescent="0.3">
@@ -11682,10 +11682,10 @@
         <v>138</v>
       </c>
       <c r="F304" s="11" t="s">
-        <v>1199</v>
+        <v>1187</v>
       </c>
       <c r="G304" s="11" t="s">
-        <v>1200</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="305" spans="1:7" x14ac:dyDescent="0.3">
@@ -11705,10 +11705,10 @@
         <v>138</v>
       </c>
       <c r="F305" s="11" t="s">
-        <v>1201</v>
+        <v>1189</v>
       </c>
       <c r="G305" s="11" t="s">
-        <v>1202</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="306" spans="1:7" x14ac:dyDescent="0.3">
@@ -11728,10 +11728,10 @@
         <v>138</v>
       </c>
       <c r="F306" s="11" t="s">
-        <v>1203</v>
+        <v>1191</v>
       </c>
       <c r="G306" s="11" t="s">
-        <v>1204</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="307" spans="1:7" x14ac:dyDescent="0.3">
@@ -11751,10 +11751,10 @@
         <v>138</v>
       </c>
       <c r="F307" s="11" t="s">
-        <v>1205</v>
+        <v>1193</v>
       </c>
       <c r="G307" s="11" t="s">
-        <v>1206</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="308" spans="1:7" x14ac:dyDescent="0.3">
@@ -11774,10 +11774,10 @@
         <v>601</v>
       </c>
       <c r="F308" s="11" t="s">
-        <v>1207</v>
+        <v>1195</v>
       </c>
       <c r="G308" s="11" t="s">
-        <v>1208</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="309" spans="1:7" x14ac:dyDescent="0.3">
@@ -11797,10 +11797,10 @@
         <v>601</v>
       </c>
       <c r="F309" s="11" t="s">
-        <v>1209</v>
+        <v>1197</v>
       </c>
       <c r="G309" s="11" t="s">
-        <v>1210</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="310" spans="1:7" x14ac:dyDescent="0.3">
@@ -11820,10 +11820,10 @@
         <v>601</v>
       </c>
       <c r="F310" s="11" t="s">
-        <v>1211</v>
+        <v>1199</v>
       </c>
       <c r="G310" s="11" t="s">
-        <v>1212</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="311" spans="1:7" x14ac:dyDescent="0.3">
@@ -11843,10 +11843,10 @@
         <v>601</v>
       </c>
       <c r="F311" s="11" t="s">
-        <v>1213</v>
+        <v>1201</v>
       </c>
       <c r="G311" s="11" t="s">
-        <v>1214</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="312" spans="1:7" x14ac:dyDescent="0.3">
@@ -11866,10 +11866,10 @@
         <v>601</v>
       </c>
       <c r="F312" s="11" t="s">
-        <v>1215</v>
+        <v>1203</v>
       </c>
       <c r="G312" s="11" t="s">
-        <v>1216</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="313" spans="1:7" x14ac:dyDescent="0.3">
@@ -11889,10 +11889,10 @@
         <v>601</v>
       </c>
       <c r="F313" s="11" t="s">
-        <v>1217</v>
+        <v>1205</v>
       </c>
       <c r="G313" s="11" t="s">
-        <v>1218</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="314" spans="1:7" x14ac:dyDescent="0.3">
@@ -11912,10 +11912,10 @@
         <v>601</v>
       </c>
       <c r="F314" s="11" t="s">
-        <v>1219</v>
+        <v>1207</v>
       </c>
       <c r="G314" s="11" t="s">
-        <v>1220</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="315" spans="1:7" x14ac:dyDescent="0.3">
@@ -11935,10 +11935,10 @@
         <v>601</v>
       </c>
       <c r="F315" s="11" t="s">
-        <v>1221</v>
+        <v>1209</v>
       </c>
       <c r="G315" s="11" t="s">
-        <v>1222</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="316" spans="1:7" x14ac:dyDescent="0.3">
@@ -11958,10 +11958,10 @@
         <v>601</v>
       </c>
       <c r="F316" s="11" t="s">
-        <v>1223</v>
+        <v>1211</v>
       </c>
       <c r="G316" s="11" t="s">
-        <v>1224</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="317" spans="1:7" x14ac:dyDescent="0.3">
@@ -11981,10 +11981,10 @@
         <v>601</v>
       </c>
       <c r="F317" s="11" t="s">
-        <v>1225</v>
+        <v>1213</v>
       </c>
       <c r="G317" s="11" t="s">
-        <v>1226</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="318" spans="1:7" x14ac:dyDescent="0.3">
@@ -12004,10 +12004,10 @@
         <v>601</v>
       </c>
       <c r="F318" s="11" t="s">
-        <v>1227</v>
+        <v>1215</v>
       </c>
       <c r="G318" s="11" t="s">
-        <v>1228</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="319" spans="1:7" x14ac:dyDescent="0.3">
@@ -12027,10 +12027,10 @@
         <v>601</v>
       </c>
       <c r="F319" s="11" t="s">
-        <v>1229</v>
+        <v>1217</v>
       </c>
       <c r="G319" s="11" t="s">
-        <v>1230</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="320" spans="1:7" x14ac:dyDescent="0.3">
@@ -12050,10 +12050,10 @@
         <v>601</v>
       </c>
       <c r="F320" s="11" t="s">
-        <v>1231</v>
+        <v>1219</v>
       </c>
       <c r="G320" s="11" t="s">
-        <v>1232</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="321" spans="1:7" x14ac:dyDescent="0.3">
@@ -12073,10 +12073,10 @@
         <v>601</v>
       </c>
       <c r="F321" s="11" t="s">
-        <v>1233</v>
+        <v>1221</v>
       </c>
       <c r="G321" s="11" t="s">
-        <v>1234</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="322" spans="1:7" x14ac:dyDescent="0.3">
@@ -12096,10 +12096,10 @@
         <v>601</v>
       </c>
       <c r="F322" s="11" t="s">
-        <v>1235</v>
+        <v>1223</v>
       </c>
       <c r="G322" s="11" t="s">
-        <v>1236</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="323" spans="1:7" x14ac:dyDescent="0.3">
@@ -12119,10 +12119,10 @@
         <v>601</v>
       </c>
       <c r="F323" s="11" t="s">
-        <v>1237</v>
+        <v>1225</v>
       </c>
       <c r="G323" s="11" t="s">
-        <v>1238</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="324" spans="1:7" x14ac:dyDescent="0.3">
@@ -12142,10 +12142,10 @@
         <v>601</v>
       </c>
       <c r="F324" s="11" t="s">
-        <v>1239</v>
+        <v>1227</v>
       </c>
       <c r="G324" s="11" t="s">
-        <v>1240</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="325" spans="1:7" x14ac:dyDescent="0.3">
@@ -12165,10 +12165,10 @@
         <v>601</v>
       </c>
       <c r="F325" s="11" t="s">
-        <v>1241</v>
+        <v>1229</v>
       </c>
       <c r="G325" s="11" t="s">
-        <v>1242</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="326" spans="1:7" x14ac:dyDescent="0.3">
@@ -12188,10 +12188,10 @@
         <v>601</v>
       </c>
       <c r="F326" s="11" t="s">
-        <v>1243</v>
+        <v>1231</v>
       </c>
       <c r="G326" s="11" t="s">
-        <v>1244</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="327" spans="1:7" x14ac:dyDescent="0.3">
@@ -12211,10 +12211,10 @@
         <v>601</v>
       </c>
       <c r="F327" s="11" t="s">
-        <v>1245</v>
+        <v>1233</v>
       </c>
       <c r="G327" s="11" t="s">
-        <v>1246</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="328" spans="1:7" x14ac:dyDescent="0.3">
@@ -12234,10 +12234,10 @@
         <v>601</v>
       </c>
       <c r="F328" s="11" t="s">
-        <v>1247</v>
+        <v>1235</v>
       </c>
       <c r="G328" s="11" t="s">
-        <v>1248</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="329" spans="1:7" x14ac:dyDescent="0.3">
@@ -12257,10 +12257,10 @@
         <v>601</v>
       </c>
       <c r="F329" s="11" t="s">
-        <v>1249</v>
+        <v>1237</v>
       </c>
       <c r="G329" s="11" t="s">
-        <v>1250</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="330" spans="1:7" x14ac:dyDescent="0.3">
@@ -12280,10 +12280,10 @@
         <v>601</v>
       </c>
       <c r="F330" s="11" t="s">
-        <v>1251</v>
+        <v>1239</v>
       </c>
       <c r="G330" s="11" t="s">
-        <v>1252</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="331" spans="1:7" x14ac:dyDescent="0.3">
@@ -12303,10 +12303,10 @@
         <v>601</v>
       </c>
       <c r="F331" s="11" t="s">
-        <v>1253</v>
+        <v>1241</v>
       </c>
       <c r="G331" s="11" t="s">
-        <v>1254</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="332" spans="1:7" x14ac:dyDescent="0.3">
@@ -12326,10 +12326,10 @@
         <v>601</v>
       </c>
       <c r="F332" s="11" t="s">
-        <v>1255</v>
+        <v>1243</v>
       </c>
       <c r="G332" s="11" t="s">
-        <v>1256</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="333" spans="1:7" x14ac:dyDescent="0.3">
@@ -12349,10 +12349,10 @@
         <v>601</v>
       </c>
       <c r="F333" s="11" t="s">
-        <v>1257</v>
+        <v>1245</v>
       </c>
       <c r="G333" s="11" t="s">
-        <v>1258</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="334" spans="1:7" x14ac:dyDescent="0.3">
@@ -12372,10 +12372,10 @@
         <v>601</v>
       </c>
       <c r="F334" s="11" t="s">
-        <v>1259</v>
+        <v>1247</v>
       </c>
       <c r="G334" s="11" t="s">
-        <v>1260</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="335" spans="1:7" x14ac:dyDescent="0.3">
@@ -12395,10 +12395,10 @@
         <v>601</v>
       </c>
       <c r="F335" s="11" t="s">
-        <v>1261</v>
+        <v>1249</v>
       </c>
       <c r="G335" s="11" t="s">
-        <v>1262</v>
+        <v>1250</v>
       </c>
     </row>
   </sheetData>

--- a/files/Adhiparasakthi Students Data 1.xlsx
+++ b/files/Adhiparasakthi Students Data 1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vigne\Google_Backup\Github\sb4c\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB45A1C9-4AD2-4BB5-8505-7FA9AB59A824}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2468640-8A19-47CC-9831-AE3624E4D893}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E3F0EEA9-6BAE-46A1-95E3-E9CE509FC50B}"/>
   </bookViews>
@@ -2205,12 +2205,6 @@
     <t>Edu#397344</t>
   </si>
   <si>
-    <t>EFIBM26554940112@edunetmail.com</t>
-  </si>
-  <si>
-    <t>Edu#292538</t>
-  </si>
-  <si>
     <t>EFIBM26341002483@edunetmail.com</t>
   </si>
   <si>
@@ -4002,12 +3996,6 @@
     <t>Edu#169804</t>
   </si>
   <si>
-    <t>EFIBM26709025372@edunetmail.com</t>
-  </si>
-  <si>
-    <t>Edu#147189</t>
-  </si>
-  <si>
     <t>EFIBM26799582334@edunetmail.com</t>
   </si>
   <si>
@@ -4084,6 +4072,18 @@
   </si>
   <si>
     <t>Edu#594500</t>
+  </si>
+  <si>
+    <t>EFIBM26148548547@edunetmail.com</t>
+  </si>
+  <si>
+    <t>Edu#230327</t>
+  </si>
+  <si>
+    <t>EFIBM26565009339@edunetmail.com</t>
+  </si>
+  <si>
+    <t>Edu#721620</t>
   </si>
 </sst>
 </file>
@@ -4808,10 +4808,10 @@
         <v>138</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>1307</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -4946,10 +4946,10 @@
         <v>138</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>1338</v>
+        <v>1334</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>1339</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -4969,10 +4969,10 @@
         <v>138</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5038,10 +5038,10 @@
         <v>138</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>1326</v>
+        <v>1322</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>1327</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5130,10 +5130,10 @@
         <v>138</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>1328</v>
+        <v>1324</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>1329</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5153,10 +5153,10 @@
         <v>138</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>1330</v>
+        <v>1326</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>1331</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5222,10 +5222,10 @@
         <v>138</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>1348</v>
+        <v>1344</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>1349</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5383,10 +5383,10 @@
         <v>138</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>1314</v>
+        <v>1312</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5406,10 +5406,10 @@
         <v>138</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>1324</v>
+        <v>1320</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>1325</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5428,11 +5428,11 @@
       <c r="E32" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F32" s="6" t="s">
-        <v>723</v>
-      </c>
-      <c r="G32" s="8" t="s">
-        <v>724</v>
+      <c r="F32" s="5" t="s">
+        <v>1348</v>
+      </c>
+      <c r="G32" s="7" t="s">
+        <v>1349</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5452,10 +5452,10 @@
         <v>138</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5475,10 +5475,10 @@
         <v>138</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>1312</v>
+        <v>1310</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>1313</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5498,10 +5498,10 @@
         <v>138</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>1322</v>
+        <v>1346</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>1323</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5521,10 +5521,10 @@
         <v>138</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5544,10 +5544,10 @@
         <v>138</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>1332</v>
+        <v>1328</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>1333</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5567,10 +5567,10 @@
         <v>138</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>1304</v>
+        <v>1302</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>1305</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5590,10 +5590,10 @@
         <v>138</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5613,10 +5613,10 @@
         <v>138</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5636,10 +5636,10 @@
         <v>138</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5659,10 +5659,10 @@
         <v>138</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5682,10 +5682,10 @@
         <v>138</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>1310</v>
+        <v>1308</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5705,10 +5705,10 @@
         <v>138</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5728,10 +5728,10 @@
         <v>138</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5751,10 +5751,10 @@
         <v>138</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5774,10 +5774,10 @@
         <v>138</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5797,10 +5797,10 @@
         <v>138</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5820,10 +5820,10 @@
         <v>138</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5843,10 +5843,10 @@
         <v>138</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5866,10 +5866,10 @@
         <v>138</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>1336</v>
+        <v>1332</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>1337</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5889,10 +5889,10 @@
         <v>138</v>
       </c>
       <c r="F52" s="6" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5912,10 +5912,10 @@
         <v>138</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>1318</v>
+        <v>1316</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>1319</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5935,10 +5935,10 @@
         <v>138</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>1346</v>
+        <v>1342</v>
       </c>
       <c r="G54" s="7" t="s">
-        <v>1347</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5958,10 +5958,10 @@
         <v>138</v>
       </c>
       <c r="F55" s="6" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5981,10 +5981,10 @@
         <v>138</v>
       </c>
       <c r="F56" s="6" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6004,10 +6004,10 @@
         <v>138</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="G57" s="7" t="s">
-        <v>1317</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6027,10 +6027,10 @@
         <v>138</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="G58" s="7" t="s">
-        <v>1321</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6050,10 +6050,10 @@
         <v>138</v>
       </c>
       <c r="F59" s="6" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6073,10 +6073,10 @@
         <v>138</v>
       </c>
       <c r="F60" s="6" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="G60" s="8" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6096,10 +6096,10 @@
         <v>138</v>
       </c>
       <c r="F61" s="6" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6119,10 +6119,10 @@
         <v>138</v>
       </c>
       <c r="F62" s="6" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="G62" s="8" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6142,10 +6142,10 @@
         <v>138</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>1344</v>
+        <v>1340</v>
       </c>
       <c r="G63" s="7" t="s">
-        <v>1345</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6165,10 +6165,10 @@
         <v>138</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>1340</v>
+        <v>1336</v>
       </c>
       <c r="G64" s="7" t="s">
-        <v>1341</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6188,10 +6188,10 @@
         <v>138</v>
       </c>
       <c r="F65" s="6" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6211,10 +6211,10 @@
         <v>138</v>
       </c>
       <c r="F66" s="6" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="G66" s="8" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6234,10 +6234,10 @@
         <v>138</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>1342</v>
+        <v>1338</v>
       </c>
       <c r="G67" s="7" t="s">
-        <v>1343</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6257,10 +6257,10 @@
         <v>138</v>
       </c>
       <c r="F68" s="12" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="G68" s="12" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6280,10 +6280,10 @@
         <v>138</v>
       </c>
       <c r="F69" s="6" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G69" s="8" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6294,7 +6294,7 @@
         <v>141</v>
       </c>
       <c r="C70" s="16" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>188</v>
@@ -6303,10 +6303,10 @@
         <v>138</v>
       </c>
       <c r="F70" s="12" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="G70" s="12" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6326,10 +6326,10 @@
         <v>138</v>
       </c>
       <c r="F71" s="6" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="G71" s="8" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
     </row>
     <row r="72" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6349,10 +6349,10 @@
         <v>138</v>
       </c>
       <c r="F72" s="6" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="G72" s="8" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
     </row>
     <row r="73" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6372,10 +6372,10 @@
         <v>138</v>
       </c>
       <c r="F73" s="6" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="G73" s="8" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6395,10 +6395,10 @@
         <v>138</v>
       </c>
       <c r="F74" s="6" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="G74" s="8" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
     </row>
     <row r="75" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6418,10 +6418,10 @@
         <v>138</v>
       </c>
       <c r="F75" s="6" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="G75" s="8" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
     </row>
     <row r="76" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6441,10 +6441,10 @@
         <v>138</v>
       </c>
       <c r="F76" s="6" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="G76" s="8" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
     </row>
     <row r="77" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6464,10 +6464,10 @@
         <v>138</v>
       </c>
       <c r="F77" s="6" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="G77" s="8" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="78" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6487,10 +6487,10 @@
         <v>138</v>
       </c>
       <c r="F78" s="9" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="G78" s="10" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
     </row>
     <row r="79" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6510,10 +6510,10 @@
         <v>138</v>
       </c>
       <c r="F79" s="12" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
       <c r="G79" s="12" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
@@ -6533,10 +6533,10 @@
         <v>138</v>
       </c>
       <c r="F80" s="15" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="G80" s="15" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
@@ -6556,10 +6556,10 @@
         <v>138</v>
       </c>
       <c r="F81" s="11" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="G81" s="11" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
@@ -6579,10 +6579,10 @@
         <v>138</v>
       </c>
       <c r="F82" s="15" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="G82" s="15" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
@@ -6602,10 +6602,10 @@
         <v>138</v>
       </c>
       <c r="F83" s="15" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="G83" s="15" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
@@ -6625,10 +6625,10 @@
         <v>138</v>
       </c>
       <c r="F84" s="11" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="G84" s="11" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
@@ -6648,10 +6648,10 @@
         <v>138</v>
       </c>
       <c r="F85" s="11" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="G85" s="11" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
@@ -6671,10 +6671,10 @@
         <v>138</v>
       </c>
       <c r="F86" s="15" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="G86" s="15" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
@@ -6694,10 +6694,10 @@
         <v>138</v>
       </c>
       <c r="F87" s="15" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="G87" s="15" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
@@ -6717,10 +6717,10 @@
         <v>138</v>
       </c>
       <c r="F88" s="15" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="G88" s="15" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
@@ -6740,10 +6740,10 @@
         <v>138</v>
       </c>
       <c r="F89" s="15" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="G89" s="15" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
@@ -6763,10 +6763,10 @@
         <v>138</v>
       </c>
       <c r="F90" s="11" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="G90" s="11" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
@@ -6786,10 +6786,10 @@
         <v>138</v>
       </c>
       <c r="F91" s="15" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="G91" s="15" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
@@ -6809,10 +6809,10 @@
         <v>138</v>
       </c>
       <c r="F92" s="15" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="G92" s="15" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
     </row>
     <row r="93" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6832,10 +6832,10 @@
         <v>138</v>
       </c>
       <c r="F93" s="13" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="G93" s="14" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
     </row>
     <row r="94" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6855,10 +6855,10 @@
         <v>138</v>
       </c>
       <c r="F94" s="6" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="G94" s="8" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
     </row>
     <row r="95" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6878,10 +6878,10 @@
         <v>138</v>
       </c>
       <c r="F95" s="6" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="G95" s="8" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
     </row>
     <row r="96" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6901,10 +6901,10 @@
         <v>138</v>
       </c>
       <c r="F96" s="6" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="G96" s="8" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
     </row>
     <row r="97" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6924,10 +6924,10 @@
         <v>138</v>
       </c>
       <c r="F97" s="6" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="G97" s="8" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
     </row>
     <row r="98" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6947,10 +6947,10 @@
         <v>138</v>
       </c>
       <c r="F98" s="6" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="G98" s="8" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
     </row>
     <row r="99" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6970,10 +6970,10 @@
         <v>138</v>
       </c>
       <c r="F99" s="6" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="G99" s="8" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
     </row>
     <row r="100" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6993,10 +6993,10 @@
         <v>138</v>
       </c>
       <c r="F100" s="5" t="s">
-        <v>1300</v>
+        <v>1298</v>
       </c>
       <c r="G100" s="7" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="101" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7016,10 +7016,10 @@
         <v>138</v>
       </c>
       <c r="F101" s="6" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="G101" s="8" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
     </row>
     <row r="102" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7039,10 +7039,10 @@
         <v>138</v>
       </c>
       <c r="F102" s="6" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="G102" s="8" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
     </row>
     <row r="103" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7062,10 +7062,10 @@
         <v>138</v>
       </c>
       <c r="F103" s="6" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="G103" s="8" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
     </row>
     <row r="104" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7085,10 +7085,10 @@
         <v>138</v>
       </c>
       <c r="F104" s="6" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="G104" s="8" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
     </row>
     <row r="105" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7108,10 +7108,10 @@
         <v>138</v>
       </c>
       <c r="F105" s="12" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="G105" s="12" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="106" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7131,10 +7131,10 @@
         <v>138</v>
       </c>
       <c r="F106" s="6" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="G106" s="8" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="107" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7154,10 +7154,10 @@
         <v>138</v>
       </c>
       <c r="F107" s="5" t="s">
-        <v>1298</v>
+        <v>1296</v>
       </c>
       <c r="G107" s="7" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="108" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7177,10 +7177,10 @@
         <v>138</v>
       </c>
       <c r="F108" s="6" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="G108" s="8" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
     </row>
     <row r="109" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7200,10 +7200,10 @@
         <v>138</v>
       </c>
       <c r="F109" s="6" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="G109" s="8" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
     </row>
     <row r="110" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7223,10 +7223,10 @@
         <v>138</v>
       </c>
       <c r="F110" s="6" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="G110" s="8" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
     </row>
     <row r="111" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7246,10 +7246,10 @@
         <v>138</v>
       </c>
       <c r="F111" s="5" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="G111" s="7" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="112" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7269,10 +7269,10 @@
         <v>138</v>
       </c>
       <c r="F112" s="17" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
       <c r="G112" s="17" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="113" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7292,10 +7292,10 @@
         <v>138</v>
       </c>
       <c r="F113" s="6" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="G113" s="8" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="114" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7315,10 +7315,10 @@
         <v>138</v>
       </c>
       <c r="F114" s="12" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="G114" s="12" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="115" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7338,10 +7338,10 @@
         <v>138</v>
       </c>
       <c r="F115" s="6" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="G115" s="8" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="116" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7361,10 +7361,10 @@
         <v>138</v>
       </c>
       <c r="F116" s="6" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="G116" s="8" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
     </row>
     <row r="117" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7384,10 +7384,10 @@
         <v>138</v>
       </c>
       <c r="F117" s="6" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="G117" s="8" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="118" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7404,10 +7404,10 @@
         <v>138</v>
       </c>
       <c r="F118" s="6" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="G118" s="8" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
     </row>
     <row r="119" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7427,10 +7427,10 @@
         <v>138</v>
       </c>
       <c r="F119" s="12" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="G119" s="12" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="120" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7450,10 +7450,10 @@
         <v>138</v>
       </c>
       <c r="F120" s="6" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="G120" s="8" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
     </row>
     <row r="121" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7473,10 +7473,10 @@
         <v>138</v>
       </c>
       <c r="F121" s="12" t="s">
-        <v>1294</v>
+        <v>1292</v>
       </c>
       <c r="G121" s="12" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="122" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7496,10 +7496,10 @@
         <v>138</v>
       </c>
       <c r="F122" s="6" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="G122" s="8" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
     </row>
     <row r="123" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7519,10 +7519,10 @@
         <v>138</v>
       </c>
       <c r="F123" s="6" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="G123" s="8" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
     </row>
     <row r="124" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7542,10 +7542,10 @@
         <v>138</v>
       </c>
       <c r="F124" s="6" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="G124" s="8" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
     </row>
     <row r="125" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7565,10 +7565,10 @@
         <v>138</v>
       </c>
       <c r="F125" s="12" t="s">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="G125" s="12" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="126" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7588,10 +7588,10 @@
         <v>138</v>
       </c>
       <c r="F126" s="12" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="G126" s="12" t="s">
-        <v>1272</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="127" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7611,10 +7611,10 @@
         <v>138</v>
       </c>
       <c r="F127" s="6" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="G127" s="8" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
     </row>
     <row r="128" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7634,10 +7634,10 @@
         <v>138</v>
       </c>
       <c r="F128" s="6" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="G128" s="8" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
     </row>
     <row r="129" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7657,10 +7657,10 @@
         <v>138</v>
       </c>
       <c r="F129" s="6" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="G129" s="8" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
     </row>
     <row r="130" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7680,10 +7680,10 @@
         <v>138</v>
       </c>
       <c r="F130" s="12" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="G130" s="12" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="131" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7703,10 +7703,10 @@
         <v>138</v>
       </c>
       <c r="F131" s="6" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="G131" s="8" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
     </row>
     <row r="132" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7726,10 +7726,10 @@
         <v>138</v>
       </c>
       <c r="F132" s="6" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="G132" s="8" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
     </row>
     <row r="133" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7749,10 +7749,10 @@
         <v>138</v>
       </c>
       <c r="F133" s="6" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="G133" s="8" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
     </row>
     <row r="134" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7772,10 +7772,10 @@
         <v>138</v>
       </c>
       <c r="F134" s="6" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="G134" s="8" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
     </row>
     <row r="135" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7795,10 +7795,10 @@
         <v>138</v>
       </c>
       <c r="F135" s="12" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="G135" s="12" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="136" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7818,10 +7818,10 @@
         <v>138</v>
       </c>
       <c r="F136" s="6" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="G136" s="8" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
     </row>
     <row r="137" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7841,10 +7841,10 @@
         <v>138</v>
       </c>
       <c r="F137" s="6" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="G137" s="8" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
     </row>
     <row r="138" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7864,10 +7864,10 @@
         <v>138</v>
       </c>
       <c r="F138" s="6" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G138" s="8" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.3">
@@ -7887,10 +7887,10 @@
         <v>138</v>
       </c>
       <c r="F139" s="9" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="G139" s="10" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.3">
@@ -7910,10 +7910,10 @@
         <v>138</v>
       </c>
       <c r="F140" s="15" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="G140" s="15" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.3">
@@ -7933,10 +7933,10 @@
         <v>138</v>
       </c>
       <c r="F141" s="11" t="s">
-        <v>1253</v>
+        <v>1251</v>
       </c>
       <c r="G141" s="11" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.3">
@@ -7956,10 +7956,10 @@
         <v>138</v>
       </c>
       <c r="F142" s="15" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="G142" s="15" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.3">
@@ -7979,10 +7979,10 @@
         <v>138</v>
       </c>
       <c r="F143" s="11" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="G143" s="11" t="s">
-        <v>1282</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.3">
@@ -8002,10 +8002,10 @@
         <v>138</v>
       </c>
       <c r="F144" s="11" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
       <c r="G144" s="11" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.3">
@@ -8025,10 +8025,10 @@
         <v>138</v>
       </c>
       <c r="F145" s="15" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="G145" s="15" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.3">
@@ -8048,10 +8048,10 @@
         <v>138</v>
       </c>
       <c r="F146" s="11" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
       <c r="G146" s="11" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.3">
@@ -8071,10 +8071,10 @@
         <v>138</v>
       </c>
       <c r="F147" s="15" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="G147" s="15" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.3">
@@ -8094,10 +8094,10 @@
         <v>138</v>
       </c>
       <c r="F148" s="15" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="G148" s="15" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.3">
@@ -8117,10 +8117,10 @@
         <v>138</v>
       </c>
       <c r="F149" s="15" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="G149" s="15" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.3">
@@ -8140,10 +8140,10 @@
         <v>138</v>
       </c>
       <c r="F150" s="15" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="G150" s="15" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.3">
@@ -8163,10 +8163,10 @@
         <v>138</v>
       </c>
       <c r="F151" s="15" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="G151" s="15" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.3">
@@ -8186,10 +8186,10 @@
         <v>138</v>
       </c>
       <c r="F152" s="11" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="G152" s="11" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="153" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8209,10 +8209,10 @@
         <v>138</v>
       </c>
       <c r="F153" s="13" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="G153" s="14" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
     </row>
     <row r="154" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8232,10 +8232,10 @@
         <v>138</v>
       </c>
       <c r="F154" s="6" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="G154" s="8" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
     </row>
     <row r="155" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8255,10 +8255,10 @@
         <v>138</v>
       </c>
       <c r="F155" s="6" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="G155" s="8" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
     </row>
     <row r="156" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8278,10 +8278,10 @@
         <v>138</v>
       </c>
       <c r="F156" s="6" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="G156" s="8" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
     </row>
     <row r="157" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8301,10 +8301,10 @@
         <v>138</v>
       </c>
       <c r="F157" s="12" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="G157" s="12" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="158" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8324,10 +8324,10 @@
         <v>138</v>
       </c>
       <c r="F158" s="6" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="G158" s="8" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
     </row>
     <row r="159" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8347,10 +8347,10 @@
         <v>138</v>
       </c>
       <c r="F159" s="6" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="G159" s="8" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
     </row>
     <row r="160" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8370,10 +8370,10 @@
         <v>138</v>
       </c>
       <c r="F160" s="12" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="G160" s="12" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="161" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8393,10 +8393,10 @@
         <v>138</v>
       </c>
       <c r="F161" s="6" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="G161" s="8" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
     </row>
     <row r="162" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8416,10 +8416,10 @@
         <v>138</v>
       </c>
       <c r="F162" s="6" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="G162" s="8" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
     </row>
     <row r="163" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8439,10 +8439,10 @@
         <v>138</v>
       </c>
       <c r="F163" s="6" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="G163" s="8" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
     </row>
     <row r="164" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8462,10 +8462,10 @@
         <v>138</v>
       </c>
       <c r="F164" s="6" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="G164" s="8" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
     </row>
     <row r="165" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8485,10 +8485,10 @@
         <v>138</v>
       </c>
       <c r="F165" s="6" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="G165" s="8" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
     </row>
     <row r="166" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8508,10 +8508,10 @@
         <v>138</v>
       </c>
       <c r="F166" s="6" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="G166" s="8" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
     </row>
     <row r="167" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8531,10 +8531,10 @@
         <v>138</v>
       </c>
       <c r="F167" s="6" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="G167" s="8" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
     </row>
     <row r="168" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8554,10 +8554,10 @@
         <v>138</v>
       </c>
       <c r="F168" s="6" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="G168" s="8" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
     </row>
     <row r="169" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8577,10 +8577,10 @@
         <v>138</v>
       </c>
       <c r="F169" s="6" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="G169" s="8" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
     </row>
     <row r="170" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8600,10 +8600,10 @@
         <v>138</v>
       </c>
       <c r="F170" s="6" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="G170" s="8" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
     </row>
     <row r="171" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8623,10 +8623,10 @@
         <v>138</v>
       </c>
       <c r="F171" s="6" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="G171" s="8" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
     </row>
     <row r="172" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8646,10 +8646,10 @@
         <v>138</v>
       </c>
       <c r="F172" s="6" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="G172" s="8" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
     </row>
     <row r="173" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8669,10 +8669,10 @@
         <v>138</v>
       </c>
       <c r="F173" s="6" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="G173" s="8" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
     </row>
     <row r="174" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8692,10 +8692,10 @@
         <v>138</v>
       </c>
       <c r="F174" s="6" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="G174" s="8" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
     </row>
     <row r="175" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8715,10 +8715,10 @@
         <v>138</v>
       </c>
       <c r="F175" s="6" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="G175" s="8" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
     </row>
     <row r="176" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8738,10 +8738,10 @@
         <v>138</v>
       </c>
       <c r="F176" s="6" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="G176" s="8" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
     </row>
     <row r="177" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8761,10 +8761,10 @@
         <v>138</v>
       </c>
       <c r="F177" s="6" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="G177" s="8" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
     </row>
     <row r="178" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8784,10 +8784,10 @@
         <v>138</v>
       </c>
       <c r="F178" s="6" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="G178" s="8" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
     </row>
     <row r="179" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8807,10 +8807,10 @@
         <v>138</v>
       </c>
       <c r="F179" s="6" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="G179" s="8" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="180" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8830,10 +8830,10 @@
         <v>138</v>
       </c>
       <c r="F180" s="6" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="G180" s="8" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
     </row>
     <row r="181" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8853,10 +8853,10 @@
         <v>138</v>
       </c>
       <c r="F181" s="6" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="G181" s="8" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
     </row>
     <row r="182" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8876,10 +8876,10 @@
         <v>138</v>
       </c>
       <c r="F182" s="6" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="G182" s="8" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="183" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8899,10 +8899,10 @@
         <v>138</v>
       </c>
       <c r="F183" s="6" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="G183" s="8" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
     </row>
     <row r="184" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8922,10 +8922,10 @@
         <v>138</v>
       </c>
       <c r="F184" s="6" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="G184" s="8" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
     </row>
     <row r="185" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8945,10 +8945,10 @@
         <v>138</v>
       </c>
       <c r="F185" s="6" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="G185" s="8" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
     </row>
     <row r="186" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8968,10 +8968,10 @@
         <v>138</v>
       </c>
       <c r="F186" s="6" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="G186" s="8" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
     </row>
     <row r="187" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8991,10 +8991,10 @@
         <v>138</v>
       </c>
       <c r="F187" s="6" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="G187" s="8" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
     </row>
     <row r="188" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9014,10 +9014,10 @@
         <v>138</v>
       </c>
       <c r="F188" s="6" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="G188" s="8" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
     </row>
     <row r="189" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9037,10 +9037,10 @@
         <v>138</v>
       </c>
       <c r="F189" s="6" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="G189" s="8" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
     </row>
     <row r="190" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9060,10 +9060,10 @@
         <v>138</v>
       </c>
       <c r="F190" s="6" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="G190" s="8" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
     </row>
     <row r="191" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9083,10 +9083,10 @@
         <v>138</v>
       </c>
       <c r="F191" s="6" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="G191" s="8" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
     </row>
     <row r="192" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9106,10 +9106,10 @@
         <v>138</v>
       </c>
       <c r="F192" s="6" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="G192" s="8" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
     </row>
     <row r="193" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9129,10 +9129,10 @@
         <v>138</v>
       </c>
       <c r="F193" s="6" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="G193" s="8" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
     </row>
     <row r="194" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9152,10 +9152,10 @@
         <v>138</v>
       </c>
       <c r="F194" s="6" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="G194" s="8" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
     </row>
     <row r="195" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9175,10 +9175,10 @@
         <v>138</v>
       </c>
       <c r="F195" s="6" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="G195" s="8" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
     </row>
     <row r="196" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9198,10 +9198,10 @@
         <v>138</v>
       </c>
       <c r="F196" s="6" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="G196" s="8" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
     </row>
     <row r="197" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9221,10 +9221,10 @@
         <v>138</v>
       </c>
       <c r="F197" s="6" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="G197" s="8" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
     </row>
     <row r="198" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9244,10 +9244,10 @@
         <v>138</v>
       </c>
       <c r="F198" s="6" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="G198" s="8" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
     </row>
     <row r="199" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9267,10 +9267,10 @@
         <v>138</v>
       </c>
       <c r="F199" s="6" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="G199" s="8" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
     </row>
     <row r="200" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9290,10 +9290,10 @@
         <v>138</v>
       </c>
       <c r="F200" s="6" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="G200" s="8" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
     </row>
     <row r="201" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9313,10 +9313,10 @@
         <v>138</v>
       </c>
       <c r="F201" s="6" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="G201" s="8" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
     </row>
     <row r="202" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9336,10 +9336,10 @@
         <v>138</v>
       </c>
       <c r="F202" s="6" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="G202" s="8" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
     </row>
     <row r="203" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9359,10 +9359,10 @@
         <v>138</v>
       </c>
       <c r="F203" s="6" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="G203" s="8" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
     </row>
     <row r="204" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9382,10 +9382,10 @@
         <v>138</v>
       </c>
       <c r="F204" s="6" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="G204" s="8" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
     </row>
     <row r="205" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9405,10 +9405,10 @@
         <v>138</v>
       </c>
       <c r="F205" s="6" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="G205" s="8" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
     </row>
     <row r="206" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9428,10 +9428,10 @@
         <v>138</v>
       </c>
       <c r="F206" s="6" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="G206" s="8" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="207" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9451,10 +9451,10 @@
         <v>138</v>
       </c>
       <c r="F207" s="6" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="G207" s="8" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
     </row>
     <row r="208" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9474,10 +9474,10 @@
         <v>138</v>
       </c>
       <c r="F208" s="6" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="G208" s="8" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
     </row>
     <row r="209" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9497,10 +9497,10 @@
         <v>138</v>
       </c>
       <c r="F209" s="6" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="G209" s="8" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
     </row>
     <row r="210" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9520,10 +9520,10 @@
         <v>138</v>
       </c>
       <c r="F210" s="6" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="G210" s="8" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="211" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9543,10 +9543,10 @@
         <v>138</v>
       </c>
       <c r="F211" s="6" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="G211" s="8" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="212" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9566,10 +9566,10 @@
         <v>138</v>
       </c>
       <c r="F212" s="6" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="G212" s="8" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="213" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9589,10 +9589,10 @@
         <v>138</v>
       </c>
       <c r="F213" s="6" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="G213" s="8" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="214" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9612,10 +9612,10 @@
         <v>138</v>
       </c>
       <c r="F214" s="6" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="G214" s="8" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="215" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9635,10 +9635,10 @@
         <v>138</v>
       </c>
       <c r="F215" s="6" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="G215" s="8" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="216" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9658,10 +9658,10 @@
         <v>138</v>
       </c>
       <c r="F216" s="6" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="G216" s="8" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="217" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9681,10 +9681,10 @@
         <v>138</v>
       </c>
       <c r="F217" s="6" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="G217" s="8" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="218" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9704,10 +9704,10 @@
         <v>138</v>
       </c>
       <c r="F218" s="6" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="G218" s="8" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.3">
@@ -9727,10 +9727,10 @@
         <v>138</v>
       </c>
       <c r="F219" s="9" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="G219" s="10" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.3">
@@ -9750,10 +9750,10 @@
         <v>138</v>
       </c>
       <c r="F220" s="11" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="G220" s="11" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.3">
@@ -9773,10 +9773,10 @@
         <v>138</v>
       </c>
       <c r="F221" s="11" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="G221" s="11" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.3">
@@ -9796,10 +9796,10 @@
         <v>138</v>
       </c>
       <c r="F222" s="11" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="G222" s="11" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.3">
@@ -9819,10 +9819,10 @@
         <v>138</v>
       </c>
       <c r="F223" s="11" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="G223" s="11" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.3">
@@ -9842,10 +9842,10 @@
         <v>138</v>
       </c>
       <c r="F224" s="11" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="G224" s="11" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.3">
@@ -9865,10 +9865,10 @@
         <v>138</v>
       </c>
       <c r="F225" s="11" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="G225" s="11" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.3">
@@ -9888,10 +9888,10 @@
         <v>138</v>
       </c>
       <c r="F226" s="11" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="G226" s="11" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.3">
@@ -9911,10 +9911,10 @@
         <v>138</v>
       </c>
       <c r="F227" s="11" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="G227" s="11" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.3">
@@ -9934,10 +9934,10 @@
         <v>138</v>
       </c>
       <c r="F228" s="11" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="G228" s="11" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.3">
@@ -9957,10 +9957,10 @@
         <v>138</v>
       </c>
       <c r="F229" s="11" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="G229" s="11" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.3">
@@ -9980,10 +9980,10 @@
         <v>138</v>
       </c>
       <c r="F230" s="11" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="G230" s="11" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.3">
@@ -10003,10 +10003,10 @@
         <v>138</v>
       </c>
       <c r="F231" s="11" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="G231" s="11" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.3">
@@ -10026,10 +10026,10 @@
         <v>138</v>
       </c>
       <c r="F232" s="11" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="G232" s="11" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.3">
@@ -10049,10 +10049,10 @@
         <v>138</v>
       </c>
       <c r="F233" s="11" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="G233" s="11" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.3">
@@ -10072,10 +10072,10 @@
         <v>138</v>
       </c>
       <c r="F234" s="11" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="G234" s="11" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.3">
@@ -10095,10 +10095,10 @@
         <v>138</v>
       </c>
       <c r="F235" s="11" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="G235" s="11" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.3">
@@ -10118,10 +10118,10 @@
         <v>138</v>
       </c>
       <c r="F236" s="11" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="G236" s="11" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.3">
@@ -10141,10 +10141,10 @@
         <v>138</v>
       </c>
       <c r="F237" s="11" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="G237" s="11" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.3">
@@ -10164,10 +10164,10 @@
         <v>138</v>
       </c>
       <c r="F238" s="11" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="G238" s="11" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.3">
@@ -10187,10 +10187,10 @@
         <v>138</v>
       </c>
       <c r="F239" s="11" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="G239" s="11" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.3">
@@ -10210,10 +10210,10 @@
         <v>138</v>
       </c>
       <c r="F240" s="11" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="G240" s="11" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.3">
@@ -10233,10 +10233,10 @@
         <v>138</v>
       </c>
       <c r="F241" s="11" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="G241" s="11" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.3">
@@ -10256,10 +10256,10 @@
         <v>138</v>
       </c>
       <c r="F242" s="11" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="G242" s="11" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.3">
@@ -10279,10 +10279,10 @@
         <v>138</v>
       </c>
       <c r="F243" s="11" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="G243" s="11" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.3">
@@ -10302,10 +10302,10 @@
         <v>138</v>
       </c>
       <c r="F244" s="11" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="G244" s="11" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.3">
@@ -10325,10 +10325,10 @@
         <v>138</v>
       </c>
       <c r="F245" s="11" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="G245" s="11" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.3">
@@ -10348,10 +10348,10 @@
         <v>138</v>
       </c>
       <c r="F246" s="11" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="G246" s="11" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.3">
@@ -10371,10 +10371,10 @@
         <v>138</v>
       </c>
       <c r="F247" s="11" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="G247" s="11" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.3">
@@ -10394,10 +10394,10 @@
         <v>138</v>
       </c>
       <c r="F248" s="11" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="G248" s="11" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.3">
@@ -10417,10 +10417,10 @@
         <v>138</v>
       </c>
       <c r="F249" s="11" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="G249" s="11" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.3">
@@ -10440,10 +10440,10 @@
         <v>138</v>
       </c>
       <c r="F250" s="11" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="G250" s="11" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.3">
@@ -10463,10 +10463,10 @@
         <v>138</v>
       </c>
       <c r="F251" s="11" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="G251" s="11" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.3">
@@ -10486,10 +10486,10 @@
         <v>138</v>
       </c>
       <c r="F252" s="11" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="G252" s="11" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="253" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -10509,10 +10509,10 @@
         <v>138</v>
       </c>
       <c r="F253" s="11" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="G253" s="11" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="254" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -10532,10 +10532,10 @@
         <v>138</v>
       </c>
       <c r="F254" s="5" t="s">
-        <v>1334</v>
+        <v>1330</v>
       </c>
       <c r="G254" s="7" t="s">
-        <v>1335</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.3">
@@ -10555,10 +10555,10 @@
         <v>138</v>
       </c>
       <c r="F255" s="11" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="G255" s="11" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.3">
@@ -10578,10 +10578,10 @@
         <v>138</v>
       </c>
       <c r="F256" s="11" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="G256" s="11" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.3">
@@ -10601,10 +10601,10 @@
         <v>138</v>
       </c>
       <c r="F257" s="11" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="G257" s="11" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.3">
@@ -10624,10 +10624,10 @@
         <v>138</v>
       </c>
       <c r="F258" s="11" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="G258" s="11" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.3">
@@ -10647,10 +10647,10 @@
         <v>138</v>
       </c>
       <c r="F259" s="11" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="G259" s="11" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.3">
@@ -10670,10 +10670,10 @@
         <v>138</v>
       </c>
       <c r="F260" s="11" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="G260" s="11" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.3">
@@ -10693,10 +10693,10 @@
         <v>138</v>
       </c>
       <c r="F261" s="11" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="G261" s="11" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.3">
@@ -10716,10 +10716,10 @@
         <v>138</v>
       </c>
       <c r="F262" s="11" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="G262" s="11" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.3">
@@ -10739,10 +10739,10 @@
         <v>138</v>
       </c>
       <c r="F263" s="11" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="G263" s="11" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.3">
@@ -10762,10 +10762,10 @@
         <v>138</v>
       </c>
       <c r="F264" s="11" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="G264" s="11" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.3">
@@ -10785,10 +10785,10 @@
         <v>138</v>
       </c>
       <c r="F265" s="11" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="G265" s="11" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.3">
@@ -10808,10 +10808,10 @@
         <v>138</v>
       </c>
       <c r="F266" s="11" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="G266" s="11" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.3">
@@ -10831,10 +10831,10 @@
         <v>138</v>
       </c>
       <c r="F267" s="11" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
       <c r="G267" s="11" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.3">
@@ -10854,10 +10854,10 @@
         <v>138</v>
       </c>
       <c r="F268" s="11" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
       <c r="G268" s="11" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.3">
@@ -10877,10 +10877,10 @@
         <v>138</v>
       </c>
       <c r="F269" s="11" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="G269" s="11" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.3">
@@ -10900,10 +10900,10 @@
         <v>138</v>
       </c>
       <c r="F270" s="11" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
       <c r="G270" s="11" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.3">
@@ -10923,10 +10923,10 @@
         <v>138</v>
       </c>
       <c r="F271" s="11" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
       <c r="G271" s="11" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.3">
@@ -10946,10 +10946,10 @@
         <v>138</v>
       </c>
       <c r="F272" s="11" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="G272" s="11" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.3">
@@ -10969,10 +10969,10 @@
         <v>138</v>
       </c>
       <c r="F273" s="11" t="s">
-        <v>1125</v>
+        <v>1123</v>
       </c>
       <c r="G273" s="11" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.3">
@@ -10992,10 +10992,10 @@
         <v>138</v>
       </c>
       <c r="F274" s="11" t="s">
-        <v>1127</v>
+        <v>1125</v>
       </c>
       <c r="G274" s="11" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.3">
@@ -11015,10 +11015,10 @@
         <v>138</v>
       </c>
       <c r="F275" s="11" t="s">
-        <v>1129</v>
+        <v>1127</v>
       </c>
       <c r="G275" s="11" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.3">
@@ -11038,10 +11038,10 @@
         <v>138</v>
       </c>
       <c r="F276" s="11" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="G276" s="11" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.3">
@@ -11061,10 +11061,10 @@
         <v>138</v>
       </c>
       <c r="F277" s="11" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="G277" s="11" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.3">
@@ -11084,10 +11084,10 @@
         <v>138</v>
       </c>
       <c r="F278" s="11" t="s">
-        <v>1135</v>
+        <v>1133</v>
       </c>
       <c r="G278" s="11" t="s">
-        <v>1136</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="279" spans="1:7" x14ac:dyDescent="0.3">
@@ -11107,10 +11107,10 @@
         <v>138</v>
       </c>
       <c r="F279" s="11" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
       <c r="G279" s="11" t="s">
-        <v>1138</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="280" spans="1:7" x14ac:dyDescent="0.3">
@@ -11130,10 +11130,10 @@
         <v>138</v>
       </c>
       <c r="F280" s="11" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
       <c r="G280" s="11" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.3">
@@ -11153,10 +11153,10 @@
         <v>138</v>
       </c>
       <c r="F281" s="11" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="G281" s="11" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.3">
@@ -11176,10 +11176,10 @@
         <v>601</v>
       </c>
       <c r="F282" s="11" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
       <c r="G282" s="11" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.3">
@@ -11199,10 +11199,10 @@
         <v>601</v>
       </c>
       <c r="F283" s="11" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="G283" s="11" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.3">
@@ -11222,10 +11222,10 @@
         <v>601</v>
       </c>
       <c r="F284" s="11" t="s">
-        <v>1147</v>
+        <v>1145</v>
       </c>
       <c r="G284" s="11" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.3">
@@ -11245,10 +11245,10 @@
         <v>601</v>
       </c>
       <c r="F285" s="11" t="s">
-        <v>1149</v>
+        <v>1147</v>
       </c>
       <c r="G285" s="11" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.3">
@@ -11268,10 +11268,10 @@
         <v>601</v>
       </c>
       <c r="F286" s="11" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="G286" s="11" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.3">
@@ -11291,10 +11291,10 @@
         <v>601</v>
       </c>
       <c r="F287" s="11" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
       <c r="G287" s="11" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.3">
@@ -11314,10 +11314,10 @@
         <v>601</v>
       </c>
       <c r="F288" s="11" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="G288" s="11" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.3">
@@ -11337,10 +11337,10 @@
         <v>601</v>
       </c>
       <c r="F289" s="11" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="G289" s="11" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.3">
@@ -11360,10 +11360,10 @@
         <v>601</v>
       </c>
       <c r="F290" s="11" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="G290" s="11" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.3">
@@ -11383,10 +11383,10 @@
         <v>601</v>
       </c>
       <c r="F291" s="11" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="G291" s="11" t="s">
-        <v>1162</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.3">
@@ -11406,10 +11406,10 @@
         <v>601</v>
       </c>
       <c r="F292" s="11" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
       <c r="G292" s="11" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.3">
@@ -11429,10 +11429,10 @@
         <v>601</v>
       </c>
       <c r="F293" s="11" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="G293" s="11" t="s">
-        <v>1166</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.3">
@@ -11452,10 +11452,10 @@
         <v>601</v>
       </c>
       <c r="F294" s="11" t="s">
-        <v>1167</v>
+        <v>1165</v>
       </c>
       <c r="G294" s="11" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.3">
@@ -11475,10 +11475,10 @@
         <v>601</v>
       </c>
       <c r="F295" s="11" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="G295" s="11" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.3">
@@ -11498,10 +11498,10 @@
         <v>601</v>
       </c>
       <c r="F296" s="11" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
       <c r="G296" s="11" t="s">
-        <v>1172</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.3">
@@ -11521,10 +11521,10 @@
         <v>601</v>
       </c>
       <c r="F297" s="11" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="G297" s="11" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.3">
@@ -11544,10 +11544,10 @@
         <v>138</v>
       </c>
       <c r="F298" s="11" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="G298" s="11" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="299" spans="1:7" x14ac:dyDescent="0.3">
@@ -11567,10 +11567,10 @@
         <v>138</v>
       </c>
       <c r="F299" s="11" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="G299" s="11" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.3">
@@ -11590,10 +11590,10 @@
         <v>138</v>
       </c>
       <c r="F300" s="11" t="s">
-        <v>1179</v>
+        <v>1177</v>
       </c>
       <c r="G300" s="11" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.3">
@@ -11613,10 +11613,10 @@
         <v>138</v>
       </c>
       <c r="F301" s="11" t="s">
-        <v>1181</v>
+        <v>1179</v>
       </c>
       <c r="G301" s="11" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="302" spans="1:7" x14ac:dyDescent="0.3">
@@ -11636,10 +11636,10 @@
         <v>138</v>
       </c>
       <c r="F302" s="11" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
       <c r="G302" s="11" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="303" spans="1:7" x14ac:dyDescent="0.3">
@@ -11659,10 +11659,10 @@
         <v>138</v>
       </c>
       <c r="F303" s="11" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
       <c r="G303" s="11" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="304" spans="1:7" x14ac:dyDescent="0.3">
@@ -11682,10 +11682,10 @@
         <v>138</v>
       </c>
       <c r="F304" s="11" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="G304" s="11" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="305" spans="1:7" x14ac:dyDescent="0.3">
@@ -11705,10 +11705,10 @@
         <v>138</v>
       </c>
       <c r="F305" s="11" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
       <c r="G305" s="11" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="306" spans="1:7" x14ac:dyDescent="0.3">
@@ -11728,10 +11728,10 @@
         <v>138</v>
       </c>
       <c r="F306" s="11" t="s">
-        <v>1191</v>
+        <v>1189</v>
       </c>
       <c r="G306" s="11" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="307" spans="1:7" x14ac:dyDescent="0.3">
@@ -11751,10 +11751,10 @@
         <v>138</v>
       </c>
       <c r="F307" s="11" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
       <c r="G307" s="11" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="308" spans="1:7" x14ac:dyDescent="0.3">
@@ -11774,10 +11774,10 @@
         <v>601</v>
       </c>
       <c r="F308" s="11" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
       <c r="G308" s="11" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="309" spans="1:7" x14ac:dyDescent="0.3">
@@ -11797,10 +11797,10 @@
         <v>601</v>
       </c>
       <c r="F309" s="11" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="G309" s="11" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="310" spans="1:7" x14ac:dyDescent="0.3">
@@ -11820,10 +11820,10 @@
         <v>601</v>
       </c>
       <c r="F310" s="11" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
       <c r="G310" s="11" t="s">
-        <v>1200</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="311" spans="1:7" x14ac:dyDescent="0.3">
@@ -11843,10 +11843,10 @@
         <v>601</v>
       </c>
       <c r="F311" s="11" t="s">
-        <v>1201</v>
+        <v>1199</v>
       </c>
       <c r="G311" s="11" t="s">
-        <v>1202</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="312" spans="1:7" x14ac:dyDescent="0.3">
@@ -11866,10 +11866,10 @@
         <v>601</v>
       </c>
       <c r="F312" s="11" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
       <c r="G312" s="11" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="313" spans="1:7" x14ac:dyDescent="0.3">
@@ -11889,10 +11889,10 @@
         <v>601</v>
       </c>
       <c r="F313" s="11" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
       <c r="G313" s="11" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="314" spans="1:7" x14ac:dyDescent="0.3">
@@ -11912,10 +11912,10 @@
         <v>601</v>
       </c>
       <c r="F314" s="11" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="G314" s="11" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="315" spans="1:7" x14ac:dyDescent="0.3">
@@ -11935,10 +11935,10 @@
         <v>601</v>
       </c>
       <c r="F315" s="11" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="G315" s="11" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="316" spans="1:7" x14ac:dyDescent="0.3">
@@ -11958,10 +11958,10 @@
         <v>601</v>
       </c>
       <c r="F316" s="11" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="G316" s="11" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="317" spans="1:7" x14ac:dyDescent="0.3">
@@ -11981,10 +11981,10 @@
         <v>601</v>
       </c>
       <c r="F317" s="11" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="G317" s="11" t="s">
-        <v>1214</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="318" spans="1:7" x14ac:dyDescent="0.3">
@@ -12004,10 +12004,10 @@
         <v>601</v>
       </c>
       <c r="F318" s="11" t="s">
-        <v>1215</v>
+        <v>1213</v>
       </c>
       <c r="G318" s="11" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="319" spans="1:7" x14ac:dyDescent="0.3">
@@ -12027,10 +12027,10 @@
         <v>601</v>
       </c>
       <c r="F319" s="11" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
       <c r="G319" s="11" t="s">
-        <v>1218</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="320" spans="1:7" x14ac:dyDescent="0.3">
@@ -12050,10 +12050,10 @@
         <v>601</v>
       </c>
       <c r="F320" s="11" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
       <c r="G320" s="11" t="s">
-        <v>1220</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="321" spans="1:7" x14ac:dyDescent="0.3">
@@ -12073,10 +12073,10 @@
         <v>601</v>
       </c>
       <c r="F321" s="11" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="G321" s="11" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="322" spans="1:7" x14ac:dyDescent="0.3">
@@ -12096,10 +12096,10 @@
         <v>601</v>
       </c>
       <c r="F322" s="11" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="G322" s="11" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="323" spans="1:7" x14ac:dyDescent="0.3">
@@ -12119,10 +12119,10 @@
         <v>601</v>
       </c>
       <c r="F323" s="11" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="G323" s="11" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="324" spans="1:7" x14ac:dyDescent="0.3">
@@ -12142,10 +12142,10 @@
         <v>601</v>
       </c>
       <c r="F324" s="11" t="s">
-        <v>1227</v>
+        <v>1225</v>
       </c>
       <c r="G324" s="11" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="325" spans="1:7" x14ac:dyDescent="0.3">
@@ -12165,10 +12165,10 @@
         <v>601</v>
       </c>
       <c r="F325" s="11" t="s">
-        <v>1229</v>
+        <v>1227</v>
       </c>
       <c r="G325" s="11" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="326" spans="1:7" x14ac:dyDescent="0.3">
@@ -12188,10 +12188,10 @@
         <v>601</v>
       </c>
       <c r="F326" s="11" t="s">
-        <v>1231</v>
+        <v>1229</v>
       </c>
       <c r="G326" s="11" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="327" spans="1:7" x14ac:dyDescent="0.3">
@@ -12211,10 +12211,10 @@
         <v>601</v>
       </c>
       <c r="F327" s="11" t="s">
-        <v>1233</v>
+        <v>1231</v>
       </c>
       <c r="G327" s="11" t="s">
-        <v>1234</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="328" spans="1:7" x14ac:dyDescent="0.3">
@@ -12234,10 +12234,10 @@
         <v>601</v>
       </c>
       <c r="F328" s="11" t="s">
-        <v>1235</v>
+        <v>1233</v>
       </c>
       <c r="G328" s="11" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="329" spans="1:7" x14ac:dyDescent="0.3">
@@ -12257,10 +12257,10 @@
         <v>601</v>
       </c>
       <c r="F329" s="11" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="G329" s="11" t="s">
-        <v>1238</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="330" spans="1:7" x14ac:dyDescent="0.3">
@@ -12280,10 +12280,10 @@
         <v>601</v>
       </c>
       <c r="F330" s="11" t="s">
-        <v>1239</v>
+        <v>1237</v>
       </c>
       <c r="G330" s="11" t="s">
-        <v>1240</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="331" spans="1:7" x14ac:dyDescent="0.3">
@@ -12303,10 +12303,10 @@
         <v>601</v>
       </c>
       <c r="F331" s="11" t="s">
-        <v>1241</v>
+        <v>1239</v>
       </c>
       <c r="G331" s="11" t="s">
-        <v>1242</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="332" spans="1:7" x14ac:dyDescent="0.3">
@@ -12326,10 +12326,10 @@
         <v>601</v>
       </c>
       <c r="F332" s="11" t="s">
-        <v>1243</v>
+        <v>1241</v>
       </c>
       <c r="G332" s="11" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="333" spans="1:7" x14ac:dyDescent="0.3">
@@ -12349,10 +12349,10 @@
         <v>601</v>
       </c>
       <c r="F333" s="11" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="G333" s="11" t="s">
-        <v>1246</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="334" spans="1:7" x14ac:dyDescent="0.3">
@@ -12372,10 +12372,10 @@
         <v>601</v>
       </c>
       <c r="F334" s="11" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="G334" s="11" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="335" spans="1:7" x14ac:dyDescent="0.3">
@@ -12395,10 +12395,10 @@
         <v>601</v>
       </c>
       <c r="F335" s="11" t="s">
-        <v>1249</v>
+        <v>1247</v>
       </c>
       <c r="G335" s="11" t="s">
-        <v>1250</v>
+        <v>1248</v>
       </c>
     </row>
   </sheetData>

--- a/files/Adhiparasakthi Students Data 1.xlsx
+++ b/files/Adhiparasakthi Students Data 1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vigne\Google_Backup\Github\sb4c\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2468640-8A19-47CC-9831-AE3624E4D893}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE9D8B73-C598-4A38-924A-A9B546FB280D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E3F0EEA9-6BAE-46A1-95E3-E9CE509FC50B}"/>
   </bookViews>
@@ -3996,12 +3996,6 @@
     <t>Edu#169804</t>
   </si>
   <si>
-    <t>EFIBM26799582334@edunetmail.com</t>
-  </si>
-  <si>
-    <t>Edu#949635</t>
-  </si>
-  <si>
     <t>EFIBM26930723266@edunetmail.com</t>
   </si>
   <si>
@@ -4084,6 +4078,12 @@
   </si>
   <si>
     <t>Edu#721620</t>
+  </si>
+  <si>
+    <t>EFIBM26862294589@edunetmail.com</t>
+  </si>
+  <si>
+    <t>Edu#745509</t>
   </si>
 </sst>
 </file>
@@ -4946,10 +4946,10 @@
         <v>138</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>1334</v>
+        <v>1332</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>1335</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5038,10 +5038,10 @@
         <v>138</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>1322</v>
+        <v>1320</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>1323</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5130,10 +5130,10 @@
         <v>138</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>1325</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5153,10 +5153,10 @@
         <v>138</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>1326</v>
+        <v>1324</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5222,10 +5222,10 @@
         <v>138</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>1344</v>
+        <v>1342</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>1345</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5406,10 +5406,10 @@
         <v>138</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>1320</v>
+        <v>1348</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>1321</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5429,10 +5429,10 @@
         <v>138</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>1348</v>
+        <v>1346</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>1349</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5498,10 +5498,10 @@
         <v>138</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>1347</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5544,10 +5544,10 @@
         <v>138</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5866,10 +5866,10 @@
         <v>138</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>1332</v>
+        <v>1330</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5935,10 +5935,10 @@
         <v>138</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>1342</v>
+        <v>1340</v>
       </c>
       <c r="G54" s="7" t="s">
-        <v>1343</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6142,10 +6142,10 @@
         <v>138</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>1340</v>
+        <v>1338</v>
       </c>
       <c r="G63" s="7" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6165,10 +6165,10 @@
         <v>138</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>1336</v>
+        <v>1334</v>
       </c>
       <c r="G64" s="7" t="s">
-        <v>1337</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6234,10 +6234,10 @@
         <v>138</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>1338</v>
+        <v>1336</v>
       </c>
       <c r="G67" s="7" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -10532,10 +10532,10 @@
         <v>138</v>
       </c>
       <c r="F254" s="5" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="G254" s="7" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.3">

--- a/files/Adhiparasakthi Students Data 1.xlsx
+++ b/files/Adhiparasakthi Students Data 1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vigne\Google_Backup\Github\sb4c\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE9D8B73-C598-4A38-924A-A9B546FB280D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61DE02D3-5BEB-4A48-9699-E5E406AAE2B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E3F0EEA9-6BAE-46A1-95E3-E9CE509FC50B}"/>
   </bookViews>
@@ -2133,12 +2133,6 @@
     <t>Edu#685474</t>
   </si>
   <si>
-    <t>EFIBM26276534165@edunetmail.com</t>
-  </si>
-  <si>
-    <t>Edu#339312</t>
-  </si>
-  <si>
     <t>EFIBM26782492001@edunetmail.com</t>
   </si>
   <si>
@@ -2289,12 +2283,6 @@
     <t>Edu#187059</t>
   </si>
   <si>
-    <t>EFIBM26363490650@edunetmail.com</t>
-  </si>
-  <si>
-    <t>Edu#378493</t>
-  </si>
-  <si>
     <t>EFIBM26753901309@edunetmail.com</t>
   </si>
   <si>
@@ -4084,6 +4072,18 @@
   </si>
   <si>
     <t>Edu#745509</t>
+  </si>
+  <si>
+    <t>EFIBM26648601890@edunetmail.com</t>
+  </si>
+  <si>
+    <t>Edu#136384</t>
+  </si>
+  <si>
+    <t>EFIBM26147829154@edunetmail.com</t>
+  </si>
+  <si>
+    <t>Edu#274107</t>
   </si>
 </sst>
 </file>
@@ -4808,10 +4808,10 @@
         <v>138</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>1304</v>
+        <v>1300</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>1305</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -4946,10 +4946,10 @@
         <v>138</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>1332</v>
+        <v>1328</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>1333</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -4969,10 +4969,10 @@
         <v>138</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>1306</v>
+        <v>1302</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>1307</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5014,11 +5014,11 @@
       <c r="E14" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F14" s="6" t="s">
-        <v>699</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>700</v>
+      <c r="F14" s="5" t="s">
+        <v>1348</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>1349</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5038,10 +5038,10 @@
         <v>138</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>1320</v>
+        <v>1316</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>1321</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5061,10 +5061,10 @@
         <v>138</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5084,10 +5084,10 @@
         <v>138</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5107,10 +5107,10 @@
         <v>138</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5130,10 +5130,10 @@
         <v>138</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>1322</v>
+        <v>1318</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>1323</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5153,10 +5153,10 @@
         <v>138</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>1324</v>
+        <v>1320</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>1325</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5176,10 +5176,10 @@
         <v>138</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5199,10 +5199,10 @@
         <v>138</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5222,10 +5222,10 @@
         <v>138</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>1342</v>
+        <v>1338</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>1343</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5245,10 +5245,10 @@
         <v>138</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5268,10 +5268,10 @@
         <v>138</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5291,10 +5291,10 @@
         <v>138</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5314,10 +5314,10 @@
         <v>138</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5337,10 +5337,10 @@
         <v>138</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5360,10 +5360,10 @@
         <v>138</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5383,10 +5383,10 @@
         <v>138</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>1312</v>
+        <v>1308</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>1313</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5406,10 +5406,10 @@
         <v>138</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>1348</v>
+        <v>1344</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>1349</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5429,10 +5429,10 @@
         <v>138</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>1346</v>
+        <v>1342</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>1347</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5452,10 +5452,10 @@
         <v>138</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5475,10 +5475,10 @@
         <v>138</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>1310</v>
+        <v>1306</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>1311</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5498,10 +5498,10 @@
         <v>138</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>1344</v>
+        <v>1340</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>1345</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5521,10 +5521,10 @@
         <v>138</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5544,10 +5544,10 @@
         <v>138</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>1326</v>
+        <v>1322</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>1327</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5567,10 +5567,10 @@
         <v>138</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>1302</v>
+        <v>1298</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>1303</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5590,10 +5590,10 @@
         <v>138</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5613,10 +5613,10 @@
         <v>138</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5636,10 +5636,10 @@
         <v>138</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5659,10 +5659,10 @@
         <v>138</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5682,10 +5682,10 @@
         <v>138</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>1308</v>
+        <v>1304</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>1309</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5705,10 +5705,10 @@
         <v>138</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5728,10 +5728,10 @@
         <v>138</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5751,10 +5751,10 @@
         <v>138</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5774,10 +5774,10 @@
         <v>138</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5797,10 +5797,10 @@
         <v>138</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5820,10 +5820,10 @@
         <v>138</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5843,10 +5843,10 @@
         <v>138</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5866,10 +5866,10 @@
         <v>138</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>1330</v>
+        <v>1326</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>1331</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5889,10 +5889,10 @@
         <v>138</v>
       </c>
       <c r="F52" s="6" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5912,10 +5912,10 @@
         <v>138</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>1316</v>
+        <v>1312</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>1317</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5935,10 +5935,10 @@
         <v>138</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>1340</v>
+        <v>1336</v>
       </c>
       <c r="G54" s="7" t="s">
-        <v>1341</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5957,11 +5957,11 @@
       <c r="E55" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F55" s="6" t="s">
-        <v>751</v>
-      </c>
-      <c r="G55" s="8" t="s">
-        <v>752</v>
+      <c r="F55" s="5" t="s">
+        <v>1346</v>
+      </c>
+      <c r="G55" s="7" t="s">
+        <v>1347</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5981,10 +5981,10 @@
         <v>138</v>
       </c>
       <c r="F56" s="6" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6004,10 +6004,10 @@
         <v>138</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>1314</v>
+        <v>1310</v>
       </c>
       <c r="G57" s="7" t="s">
-        <v>1315</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6027,10 +6027,10 @@
         <v>138</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>1318</v>
+        <v>1314</v>
       </c>
       <c r="G58" s="7" t="s">
-        <v>1319</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6050,10 +6050,10 @@
         <v>138</v>
       </c>
       <c r="F59" s="6" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>756</v>
+        <v>752</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6073,10 +6073,10 @@
         <v>138</v>
       </c>
       <c r="F60" s="6" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="G60" s="8" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6096,10 +6096,10 @@
         <v>138</v>
       </c>
       <c r="F61" s="6" t="s">
-        <v>759</v>
+        <v>755</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>760</v>
+        <v>756</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6119,10 +6119,10 @@
         <v>138</v>
       </c>
       <c r="F62" s="6" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
       <c r="G62" s="8" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6142,10 +6142,10 @@
         <v>138</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>1338</v>
+        <v>1334</v>
       </c>
       <c r="G63" s="7" t="s">
-        <v>1339</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6165,10 +6165,10 @@
         <v>138</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>1334</v>
+        <v>1330</v>
       </c>
       <c r="G64" s="7" t="s">
-        <v>1335</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6188,10 +6188,10 @@
         <v>138</v>
       </c>
       <c r="F65" s="6" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>764</v>
+        <v>760</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6211,10 +6211,10 @@
         <v>138</v>
       </c>
       <c r="F66" s="6" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
       <c r="G66" s="8" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6234,10 +6234,10 @@
         <v>138</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>1336</v>
+        <v>1332</v>
       </c>
       <c r="G67" s="7" t="s">
-        <v>1337</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6257,10 +6257,10 @@
         <v>138</v>
       </c>
       <c r="F68" s="12" t="s">
-        <v>1249</v>
+        <v>1245</v>
       </c>
       <c r="G68" s="12" t="s">
-        <v>1250</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6280,10 +6280,10 @@
         <v>138</v>
       </c>
       <c r="F69" s="6" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="G69" s="8" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6294,7 +6294,7 @@
         <v>141</v>
       </c>
       <c r="C70" s="16" t="s">
-        <v>1285</v>
+        <v>1281</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>188</v>
@@ -6303,10 +6303,10 @@
         <v>138</v>
       </c>
       <c r="F70" s="12" t="s">
-        <v>1283</v>
+        <v>1279</v>
       </c>
       <c r="G70" s="12" t="s">
-        <v>1284</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6326,10 +6326,10 @@
         <v>138</v>
       </c>
       <c r="F71" s="6" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
       <c r="G71" s="8" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
     </row>
     <row r="72" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6349,10 +6349,10 @@
         <v>138</v>
       </c>
       <c r="F72" s="6" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
       <c r="G72" s="8" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
     </row>
     <row r="73" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6372,10 +6372,10 @@
         <v>138</v>
       </c>
       <c r="F73" s="6" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="G73" s="8" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6395,10 +6395,10 @@
         <v>138</v>
       </c>
       <c r="F74" s="6" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="G74" s="8" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
     </row>
     <row r="75" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6418,10 +6418,10 @@
         <v>138</v>
       </c>
       <c r="F75" s="6" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="G75" s="8" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
     </row>
     <row r="76" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6441,10 +6441,10 @@
         <v>138</v>
       </c>
       <c r="F76" s="6" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="G76" s="8" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
     </row>
     <row r="77" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6464,10 +6464,10 @@
         <v>138</v>
       </c>
       <c r="F77" s="6" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
       <c r="G77" s="8" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
     </row>
     <row r="78" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6487,10 +6487,10 @@
         <v>138</v>
       </c>
       <c r="F78" s="9" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="G78" s="10" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
     </row>
     <row r="79" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6510,10 +6510,10 @@
         <v>138</v>
       </c>
       <c r="F79" s="12" t="s">
-        <v>1281</v>
+        <v>1277</v>
       </c>
       <c r="G79" s="12" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
@@ -6533,10 +6533,10 @@
         <v>138</v>
       </c>
       <c r="F80" s="15" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="G80" s="15" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
@@ -6556,10 +6556,10 @@
         <v>138</v>
       </c>
       <c r="F81" s="11" t="s">
-        <v>1273</v>
+        <v>1269</v>
       </c>
       <c r="G81" s="11" t="s">
-        <v>1274</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
@@ -6579,10 +6579,10 @@
         <v>138</v>
       </c>
       <c r="F82" s="15" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
       <c r="G82" s="15" t="s">
-        <v>788</v>
+        <v>784</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
@@ -6602,10 +6602,10 @@
         <v>138</v>
       </c>
       <c r="F83" s="15" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
       <c r="G83" s="15" t="s">
-        <v>790</v>
+        <v>786</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
@@ -6625,10 +6625,10 @@
         <v>138</v>
       </c>
       <c r="F84" s="11" t="s">
-        <v>1263</v>
+        <v>1259</v>
       </c>
       <c r="G84" s="11" t="s">
-        <v>1264</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
@@ -6648,10 +6648,10 @@
         <v>138</v>
       </c>
       <c r="F85" s="11" t="s">
-        <v>1275</v>
+        <v>1271</v>
       </c>
       <c r="G85" s="11" t="s">
-        <v>1276</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
@@ -6671,10 +6671,10 @@
         <v>138</v>
       </c>
       <c r="F86" s="15" t="s">
-        <v>791</v>
+        <v>787</v>
       </c>
       <c r="G86" s="15" t="s">
-        <v>792</v>
+        <v>788</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
@@ -6694,10 +6694,10 @@
         <v>138</v>
       </c>
       <c r="F87" s="15" t="s">
-        <v>793</v>
+        <v>789</v>
       </c>
       <c r="G87" s="15" t="s">
-        <v>794</v>
+        <v>790</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
@@ -6717,10 +6717,10 @@
         <v>138</v>
       </c>
       <c r="F88" s="15" t="s">
-        <v>795</v>
+        <v>791</v>
       </c>
       <c r="G88" s="15" t="s">
-        <v>796</v>
+        <v>792</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
@@ -6740,10 +6740,10 @@
         <v>138</v>
       </c>
       <c r="F89" s="15" t="s">
-        <v>797</v>
+        <v>793</v>
       </c>
       <c r="G89" s="15" t="s">
-        <v>798</v>
+        <v>794</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
@@ -6763,10 +6763,10 @@
         <v>138</v>
       </c>
       <c r="F90" s="11" t="s">
-        <v>1265</v>
+        <v>1261</v>
       </c>
       <c r="G90" s="11" t="s">
-        <v>1266</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
@@ -6786,10 +6786,10 @@
         <v>138</v>
       </c>
       <c r="F91" s="15" t="s">
-        <v>799</v>
+        <v>795</v>
       </c>
       <c r="G91" s="15" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
@@ -6809,10 +6809,10 @@
         <v>138</v>
       </c>
       <c r="F92" s="15" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
       <c r="G92" s="15" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
     </row>
     <row r="93" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6832,10 +6832,10 @@
         <v>138</v>
       </c>
       <c r="F93" s="13" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="G93" s="14" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
     </row>
     <row r="94" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6855,10 +6855,10 @@
         <v>138</v>
       </c>
       <c r="F94" s="6" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="G94" s="8" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
     </row>
     <row r="95" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6878,10 +6878,10 @@
         <v>138</v>
       </c>
       <c r="F95" s="6" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
       <c r="G95" s="8" t="s">
-        <v>808</v>
+        <v>804</v>
       </c>
     </row>
     <row r="96" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6901,10 +6901,10 @@
         <v>138</v>
       </c>
       <c r="F96" s="6" t="s">
-        <v>809</v>
+        <v>805</v>
       </c>
       <c r="G96" s="8" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
     </row>
     <row r="97" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6924,10 +6924,10 @@
         <v>138</v>
       </c>
       <c r="F97" s="6" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="G97" s="8" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
     </row>
     <row r="98" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6947,10 +6947,10 @@
         <v>138</v>
       </c>
       <c r="F98" s="6" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
       <c r="G98" s="8" t="s">
-        <v>814</v>
+        <v>810</v>
       </c>
     </row>
     <row r="99" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6970,10 +6970,10 @@
         <v>138</v>
       </c>
       <c r="F99" s="6" t="s">
-        <v>815</v>
+        <v>811</v>
       </c>
       <c r="G99" s="8" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
     </row>
     <row r="100" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6993,10 +6993,10 @@
         <v>138</v>
       </c>
       <c r="F100" s="5" t="s">
-        <v>1298</v>
+        <v>1294</v>
       </c>
       <c r="G100" s="7" t="s">
-        <v>1299</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="101" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7016,10 +7016,10 @@
         <v>138</v>
       </c>
       <c r="F101" s="6" t="s">
-        <v>817</v>
+        <v>813</v>
       </c>
       <c r="G101" s="8" t="s">
-        <v>818</v>
+        <v>814</v>
       </c>
     </row>
     <row r="102" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7039,10 +7039,10 @@
         <v>138</v>
       </c>
       <c r="F102" s="6" t="s">
-        <v>819</v>
+        <v>815</v>
       </c>
       <c r="G102" s="8" t="s">
-        <v>820</v>
+        <v>816</v>
       </c>
     </row>
     <row r="103" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7062,10 +7062,10 @@
         <v>138</v>
       </c>
       <c r="F103" s="6" t="s">
-        <v>821</v>
+        <v>817</v>
       </c>
       <c r="G103" s="8" t="s">
-        <v>822</v>
+        <v>818</v>
       </c>
     </row>
     <row r="104" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7085,10 +7085,10 @@
         <v>138</v>
       </c>
       <c r="F104" s="6" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="G104" s="8" t="s">
-        <v>824</v>
+        <v>820</v>
       </c>
     </row>
     <row r="105" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7108,10 +7108,10 @@
         <v>138</v>
       </c>
       <c r="F105" s="12" t="s">
-        <v>1288</v>
+        <v>1284</v>
       </c>
       <c r="G105" s="12" t="s">
-        <v>1289</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="106" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7131,10 +7131,10 @@
         <v>138</v>
       </c>
       <c r="F106" s="6" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
       <c r="G106" s="8" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
     </row>
     <row r="107" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7154,10 +7154,10 @@
         <v>138</v>
       </c>
       <c r="F107" s="5" t="s">
-        <v>1296</v>
+        <v>1292</v>
       </c>
       <c r="G107" s="7" t="s">
-        <v>1297</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="108" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7177,10 +7177,10 @@
         <v>138</v>
       </c>
       <c r="F108" s="6" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="G108" s="8" t="s">
-        <v>828</v>
+        <v>824</v>
       </c>
     </row>
     <row r="109" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7200,10 +7200,10 @@
         <v>138</v>
       </c>
       <c r="F109" s="6" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
       <c r="G109" s="8" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
     </row>
     <row r="110" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7223,10 +7223,10 @@
         <v>138</v>
       </c>
       <c r="F110" s="6" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="G110" s="8" t="s">
-        <v>832</v>
+        <v>828</v>
       </c>
     </row>
     <row r="111" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7246,10 +7246,10 @@
         <v>138</v>
       </c>
       <c r="F111" s="5" t="s">
-        <v>1300</v>
+        <v>1296</v>
       </c>
       <c r="G111" s="7" t="s">
-        <v>1301</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="112" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7269,10 +7269,10 @@
         <v>138</v>
       </c>
       <c r="F112" s="17" t="s">
-        <v>1294</v>
+        <v>1290</v>
       </c>
       <c r="G112" s="17" t="s">
-        <v>1295</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="113" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7292,10 +7292,10 @@
         <v>138</v>
       </c>
       <c r="F113" s="6" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="G113" s="8" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
     </row>
     <row r="114" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7315,10 +7315,10 @@
         <v>138</v>
       </c>
       <c r="F114" s="12" t="s">
-        <v>1290</v>
+        <v>1286</v>
       </c>
       <c r="G114" s="12" t="s">
-        <v>1291</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="115" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7338,10 +7338,10 @@
         <v>138</v>
       </c>
       <c r="F115" s="6" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="G115" s="8" t="s">
-        <v>836</v>
+        <v>832</v>
       </c>
     </row>
     <row r="116" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7361,10 +7361,10 @@
         <v>138</v>
       </c>
       <c r="F116" s="6" t="s">
-        <v>837</v>
+        <v>833</v>
       </c>
       <c r="G116" s="8" t="s">
-        <v>838</v>
+        <v>834</v>
       </c>
     </row>
     <row r="117" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7384,10 +7384,10 @@
         <v>138</v>
       </c>
       <c r="F117" s="6" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="G117" s="8" t="s">
-        <v>840</v>
+        <v>836</v>
       </c>
     </row>
     <row r="118" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7404,10 +7404,10 @@
         <v>138</v>
       </c>
       <c r="F118" s="6" t="s">
-        <v>841</v>
+        <v>837</v>
       </c>
       <c r="G118" s="8" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
     </row>
     <row r="119" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7427,10 +7427,10 @@
         <v>138</v>
       </c>
       <c r="F119" s="12" t="s">
-        <v>1286</v>
+        <v>1282</v>
       </c>
       <c r="G119" s="12" t="s">
-        <v>1287</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="120" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7450,10 +7450,10 @@
         <v>138</v>
       </c>
       <c r="F120" s="6" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="G120" s="8" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
     </row>
     <row r="121" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7473,10 +7473,10 @@
         <v>138</v>
       </c>
       <c r="F121" s="12" t="s">
-        <v>1292</v>
+        <v>1288</v>
       </c>
       <c r="G121" s="12" t="s">
-        <v>1293</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="122" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7496,10 +7496,10 @@
         <v>138</v>
       </c>
       <c r="F122" s="6" t="s">
-        <v>845</v>
+        <v>841</v>
       </c>
       <c r="G122" s="8" t="s">
-        <v>846</v>
+        <v>842</v>
       </c>
     </row>
     <row r="123" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7519,10 +7519,10 @@
         <v>138</v>
       </c>
       <c r="F123" s="6" t="s">
-        <v>847</v>
+        <v>843</v>
       </c>
       <c r="G123" s="8" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
     </row>
     <row r="124" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7542,10 +7542,10 @@
         <v>138</v>
       </c>
       <c r="F124" s="6" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="G124" s="8" t="s">
-        <v>850</v>
+        <v>846</v>
       </c>
     </row>
     <row r="125" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7565,10 +7565,10 @@
         <v>138</v>
       </c>
       <c r="F125" s="12" t="s">
-        <v>1255</v>
+        <v>1251</v>
       </c>
       <c r="G125" s="12" t="s">
-        <v>1256</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="126" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7588,10 +7588,10 @@
         <v>138</v>
       </c>
       <c r="F126" s="12" t="s">
-        <v>1269</v>
+        <v>1265</v>
       </c>
       <c r="G126" s="12" t="s">
-        <v>1270</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="127" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7611,10 +7611,10 @@
         <v>138</v>
       </c>
       <c r="F127" s="6" t="s">
-        <v>851</v>
+        <v>847</v>
       </c>
       <c r="G127" s="8" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
     </row>
     <row r="128" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7634,10 +7634,10 @@
         <v>138</v>
       </c>
       <c r="F128" s="6" t="s">
-        <v>853</v>
+        <v>849</v>
       </c>
       <c r="G128" s="8" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
     </row>
     <row r="129" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7657,10 +7657,10 @@
         <v>138</v>
       </c>
       <c r="F129" s="6" t="s">
-        <v>855</v>
+        <v>851</v>
       </c>
       <c r="G129" s="8" t="s">
-        <v>856</v>
+        <v>852</v>
       </c>
     </row>
     <row r="130" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7680,10 +7680,10 @@
         <v>138</v>
       </c>
       <c r="F130" s="12" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="G130" s="12" t="s">
-        <v>1278</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="131" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7703,10 +7703,10 @@
         <v>138</v>
       </c>
       <c r="F131" s="6" t="s">
-        <v>857</v>
+        <v>853</v>
       </c>
       <c r="G131" s="8" t="s">
-        <v>858</v>
+        <v>854</v>
       </c>
     </row>
     <row r="132" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7726,10 +7726,10 @@
         <v>138</v>
       </c>
       <c r="F132" s="6" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="G132" s="8" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
     </row>
     <row r="133" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7749,10 +7749,10 @@
         <v>138</v>
       </c>
       <c r="F133" s="6" t="s">
-        <v>861</v>
+        <v>857</v>
       </c>
       <c r="G133" s="8" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
     </row>
     <row r="134" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7772,10 +7772,10 @@
         <v>138</v>
       </c>
       <c r="F134" s="6" t="s">
-        <v>863</v>
+        <v>859</v>
       </c>
       <c r="G134" s="8" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
     </row>
     <row r="135" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7795,10 +7795,10 @@
         <v>138</v>
       </c>
       <c r="F135" s="12" t="s">
-        <v>1261</v>
+        <v>1257</v>
       </c>
       <c r="G135" s="12" t="s">
-        <v>1262</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="136" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7818,10 +7818,10 @@
         <v>138</v>
       </c>
       <c r="F136" s="6" t="s">
-        <v>865</v>
+        <v>861</v>
       </c>
       <c r="G136" s="8" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
     </row>
     <row r="137" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7841,10 +7841,10 @@
         <v>138</v>
       </c>
       <c r="F137" s="6" t="s">
-        <v>867</v>
+        <v>863</v>
       </c>
       <c r="G137" s="8" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
     </row>
     <row r="138" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7864,10 +7864,10 @@
         <v>138</v>
       </c>
       <c r="F138" s="6" t="s">
-        <v>869</v>
+        <v>865</v>
       </c>
       <c r="G138" s="8" t="s">
-        <v>870</v>
+        <v>866</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.3">
@@ -7887,10 +7887,10 @@
         <v>138</v>
       </c>
       <c r="F139" s="9" t="s">
-        <v>871</v>
+        <v>867</v>
       </c>
       <c r="G139" s="10" t="s">
-        <v>872</v>
+        <v>868</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.3">
@@ -7910,10 +7910,10 @@
         <v>138</v>
       </c>
       <c r="F140" s="15" t="s">
-        <v>873</v>
+        <v>869</v>
       </c>
       <c r="G140" s="15" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.3">
@@ -7933,10 +7933,10 @@
         <v>138</v>
       </c>
       <c r="F141" s="11" t="s">
-        <v>1251</v>
+        <v>1247</v>
       </c>
       <c r="G141" s="11" t="s">
-        <v>1252</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.3">
@@ -7956,10 +7956,10 @@
         <v>138</v>
       </c>
       <c r="F142" s="15" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="G142" s="15" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.3">
@@ -7979,10 +7979,10 @@
         <v>138</v>
       </c>
       <c r="F143" s="11" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="G143" s="11" t="s">
-        <v>1280</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.3">
@@ -8002,10 +8002,10 @@
         <v>138</v>
       </c>
       <c r="F144" s="11" t="s">
-        <v>1253</v>
+        <v>1249</v>
       </c>
       <c r="G144" s="11" t="s">
-        <v>1254</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.3">
@@ -8025,10 +8025,10 @@
         <v>138</v>
       </c>
       <c r="F145" s="15" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="G145" s="15" t="s">
-        <v>878</v>
+        <v>874</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.3">
@@ -8048,10 +8048,10 @@
         <v>138</v>
       </c>
       <c r="F146" s="11" t="s">
-        <v>1259</v>
+        <v>1255</v>
       </c>
       <c r="G146" s="11" t="s">
-        <v>1260</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.3">
@@ -8071,10 +8071,10 @@
         <v>138</v>
       </c>
       <c r="F147" s="15" t="s">
-        <v>879</v>
+        <v>875</v>
       </c>
       <c r="G147" s="15" t="s">
-        <v>880</v>
+        <v>876</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.3">
@@ -8094,10 +8094,10 @@
         <v>138</v>
       </c>
       <c r="F148" s="15" t="s">
-        <v>881</v>
+        <v>877</v>
       </c>
       <c r="G148" s="15" t="s">
-        <v>882</v>
+        <v>878</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.3">
@@ -8117,10 +8117,10 @@
         <v>138</v>
       </c>
       <c r="F149" s="15" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
       <c r="G149" s="15" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.3">
@@ -8140,10 +8140,10 @@
         <v>138</v>
       </c>
       <c r="F150" s="15" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="G150" s="15" t="s">
-        <v>886</v>
+        <v>882</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.3">
@@ -8163,10 +8163,10 @@
         <v>138</v>
       </c>
       <c r="F151" s="15" t="s">
-        <v>887</v>
+        <v>883</v>
       </c>
       <c r="G151" s="15" t="s">
-        <v>888</v>
+        <v>884</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.3">
@@ -8186,10 +8186,10 @@
         <v>138</v>
       </c>
       <c r="F152" s="11" t="s">
-        <v>1267</v>
+        <v>1263</v>
       </c>
       <c r="G152" s="11" t="s">
-        <v>1268</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="153" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8209,10 +8209,10 @@
         <v>138</v>
       </c>
       <c r="F153" s="13" t="s">
-        <v>889</v>
+        <v>885</v>
       </c>
       <c r="G153" s="14" t="s">
-        <v>890</v>
+        <v>886</v>
       </c>
     </row>
     <row r="154" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8232,10 +8232,10 @@
         <v>138</v>
       </c>
       <c r="F154" s="6" t="s">
-        <v>891</v>
+        <v>887</v>
       </c>
       <c r="G154" s="8" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
     </row>
     <row r="155" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8255,10 +8255,10 @@
         <v>138</v>
       </c>
       <c r="F155" s="6" t="s">
-        <v>893</v>
+        <v>889</v>
       </c>
       <c r="G155" s="8" t="s">
-        <v>894</v>
+        <v>890</v>
       </c>
     </row>
     <row r="156" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8278,10 +8278,10 @@
         <v>138</v>
       </c>
       <c r="F156" s="6" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
       <c r="G156" s="8" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
     </row>
     <row r="157" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8301,10 +8301,10 @@
         <v>138</v>
       </c>
       <c r="F157" s="12" t="s">
-        <v>1271</v>
+        <v>1267</v>
       </c>
       <c r="G157" s="12" t="s">
-        <v>1272</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="158" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8324,10 +8324,10 @@
         <v>138</v>
       </c>
       <c r="F158" s="6" t="s">
-        <v>897</v>
+        <v>893</v>
       </c>
       <c r="G158" s="8" t="s">
-        <v>898</v>
+        <v>894</v>
       </c>
     </row>
     <row r="159" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8347,10 +8347,10 @@
         <v>138</v>
       </c>
       <c r="F159" s="6" t="s">
-        <v>899</v>
+        <v>895</v>
       </c>
       <c r="G159" s="8" t="s">
-        <v>900</v>
+        <v>896</v>
       </c>
     </row>
     <row r="160" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8370,10 +8370,10 @@
         <v>138</v>
       </c>
       <c r="F160" s="12" t="s">
-        <v>1257</v>
+        <v>1253</v>
       </c>
       <c r="G160" s="12" t="s">
-        <v>1258</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="161" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8393,10 +8393,10 @@
         <v>138</v>
       </c>
       <c r="F161" s="6" t="s">
-        <v>901</v>
+        <v>897</v>
       </c>
       <c r="G161" s="8" t="s">
-        <v>902</v>
+        <v>898</v>
       </c>
     </row>
     <row r="162" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8416,10 +8416,10 @@
         <v>138</v>
       </c>
       <c r="F162" s="6" t="s">
-        <v>903</v>
+        <v>899</v>
       </c>
       <c r="G162" s="8" t="s">
-        <v>904</v>
+        <v>900</v>
       </c>
     </row>
     <row r="163" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8439,10 +8439,10 @@
         <v>138</v>
       </c>
       <c r="F163" s="6" t="s">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="G163" s="8" t="s">
-        <v>906</v>
+        <v>902</v>
       </c>
     </row>
     <row r="164" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8462,10 +8462,10 @@
         <v>138</v>
       </c>
       <c r="F164" s="6" t="s">
-        <v>907</v>
+        <v>903</v>
       </c>
       <c r="G164" s="8" t="s">
-        <v>908</v>
+        <v>904</v>
       </c>
     </row>
     <row r="165" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8485,10 +8485,10 @@
         <v>138</v>
       </c>
       <c r="F165" s="6" t="s">
-        <v>909</v>
+        <v>905</v>
       </c>
       <c r="G165" s="8" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
     </row>
     <row r="166" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8508,10 +8508,10 @@
         <v>138</v>
       </c>
       <c r="F166" s="6" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
       <c r="G166" s="8" t="s">
-        <v>912</v>
+        <v>908</v>
       </c>
     </row>
     <row r="167" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8531,10 +8531,10 @@
         <v>138</v>
       </c>
       <c r="F167" s="6" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="G167" s="8" t="s">
-        <v>914</v>
+        <v>910</v>
       </c>
     </row>
     <row r="168" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8554,10 +8554,10 @@
         <v>138</v>
       </c>
       <c r="F168" s="6" t="s">
-        <v>915</v>
+        <v>911</v>
       </c>
       <c r="G168" s="8" t="s">
-        <v>916</v>
+        <v>912</v>
       </c>
     </row>
     <row r="169" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8577,10 +8577,10 @@
         <v>138</v>
       </c>
       <c r="F169" s="6" t="s">
-        <v>917</v>
+        <v>913</v>
       </c>
       <c r="G169" s="8" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
     </row>
     <row r="170" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8600,10 +8600,10 @@
         <v>138</v>
       </c>
       <c r="F170" s="6" t="s">
-        <v>919</v>
+        <v>915</v>
       </c>
       <c r="G170" s="8" t="s">
-        <v>920</v>
+        <v>916</v>
       </c>
     </row>
     <row r="171" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8623,10 +8623,10 @@
         <v>138</v>
       </c>
       <c r="F171" s="6" t="s">
-        <v>921</v>
+        <v>917</v>
       </c>
       <c r="G171" s="8" t="s">
-        <v>922</v>
+        <v>918</v>
       </c>
     </row>
     <row r="172" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8646,10 +8646,10 @@
         <v>138</v>
       </c>
       <c r="F172" s="6" t="s">
-        <v>923</v>
+        <v>919</v>
       </c>
       <c r="G172" s="8" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
     </row>
     <row r="173" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8669,10 +8669,10 @@
         <v>138</v>
       </c>
       <c r="F173" s="6" t="s">
-        <v>925</v>
+        <v>921</v>
       </c>
       <c r="G173" s="8" t="s">
-        <v>926</v>
+        <v>922</v>
       </c>
     </row>
     <row r="174" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8692,10 +8692,10 @@
         <v>138</v>
       </c>
       <c r="F174" s="6" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="G174" s="8" t="s">
-        <v>928</v>
+        <v>924</v>
       </c>
     </row>
     <row r="175" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8715,10 +8715,10 @@
         <v>138</v>
       </c>
       <c r="F175" s="6" t="s">
-        <v>929</v>
+        <v>925</v>
       </c>
       <c r="G175" s="8" t="s">
-        <v>930</v>
+        <v>926</v>
       </c>
     </row>
     <row r="176" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8738,10 +8738,10 @@
         <v>138</v>
       </c>
       <c r="F176" s="6" t="s">
-        <v>931</v>
+        <v>927</v>
       </c>
       <c r="G176" s="8" t="s">
-        <v>932</v>
+        <v>928</v>
       </c>
     </row>
     <row r="177" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8761,10 +8761,10 @@
         <v>138</v>
       </c>
       <c r="F177" s="6" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
       <c r="G177" s="8" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
     </row>
     <row r="178" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8784,10 +8784,10 @@
         <v>138</v>
       </c>
       <c r="F178" s="6" t="s">
-        <v>935</v>
+        <v>931</v>
       </c>
       <c r="G178" s="8" t="s">
-        <v>936</v>
+        <v>932</v>
       </c>
     </row>
     <row r="179" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8807,10 +8807,10 @@
         <v>138</v>
       </c>
       <c r="F179" s="6" t="s">
-        <v>937</v>
+        <v>933</v>
       </c>
       <c r="G179" s="8" t="s">
-        <v>938</v>
+        <v>934</v>
       </c>
     </row>
     <row r="180" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8830,10 +8830,10 @@
         <v>138</v>
       </c>
       <c r="F180" s="6" t="s">
-        <v>939</v>
+        <v>935</v>
       </c>
       <c r="G180" s="8" t="s">
-        <v>940</v>
+        <v>936</v>
       </c>
     </row>
     <row r="181" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8853,10 +8853,10 @@
         <v>138</v>
       </c>
       <c r="F181" s="6" t="s">
-        <v>941</v>
+        <v>937</v>
       </c>
       <c r="G181" s="8" t="s">
-        <v>942</v>
+        <v>938</v>
       </c>
     </row>
     <row r="182" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8876,10 +8876,10 @@
         <v>138</v>
       </c>
       <c r="F182" s="6" t="s">
-        <v>943</v>
+        <v>939</v>
       </c>
       <c r="G182" s="8" t="s">
-        <v>944</v>
+        <v>940</v>
       </c>
     </row>
     <row r="183" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8899,10 +8899,10 @@
         <v>138</v>
       </c>
       <c r="F183" s="6" t="s">
-        <v>945</v>
+        <v>941</v>
       </c>
       <c r="G183" s="8" t="s">
-        <v>946</v>
+        <v>942</v>
       </c>
     </row>
     <row r="184" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8922,10 +8922,10 @@
         <v>138</v>
       </c>
       <c r="F184" s="6" t="s">
-        <v>947</v>
+        <v>943</v>
       </c>
       <c r="G184" s="8" t="s">
-        <v>948</v>
+        <v>944</v>
       </c>
     </row>
     <row r="185" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8945,10 +8945,10 @@
         <v>138</v>
       </c>
       <c r="F185" s="6" t="s">
-        <v>949</v>
+        <v>945</v>
       </c>
       <c r="G185" s="8" t="s">
-        <v>950</v>
+        <v>946</v>
       </c>
     </row>
     <row r="186" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8968,10 +8968,10 @@
         <v>138</v>
       </c>
       <c r="F186" s="6" t="s">
-        <v>951</v>
+        <v>947</v>
       </c>
       <c r="G186" s="8" t="s">
-        <v>952</v>
+        <v>948</v>
       </c>
     </row>
     <row r="187" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8991,10 +8991,10 @@
         <v>138</v>
       </c>
       <c r="F187" s="6" t="s">
-        <v>953</v>
+        <v>949</v>
       </c>
       <c r="G187" s="8" t="s">
-        <v>954</v>
+        <v>950</v>
       </c>
     </row>
     <row r="188" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9014,10 +9014,10 @@
         <v>138</v>
       </c>
       <c r="F188" s="6" t="s">
-        <v>955</v>
+        <v>951</v>
       </c>
       <c r="G188" s="8" t="s">
-        <v>956</v>
+        <v>952</v>
       </c>
     </row>
     <row r="189" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9037,10 +9037,10 @@
         <v>138</v>
       </c>
       <c r="F189" s="6" t="s">
-        <v>957</v>
+        <v>953</v>
       </c>
       <c r="G189" s="8" t="s">
-        <v>958</v>
+        <v>954</v>
       </c>
     </row>
     <row r="190" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9060,10 +9060,10 @@
         <v>138</v>
       </c>
       <c r="F190" s="6" t="s">
-        <v>959</v>
+        <v>955</v>
       </c>
       <c r="G190" s="8" t="s">
-        <v>960</v>
+        <v>956</v>
       </c>
     </row>
     <row r="191" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9083,10 +9083,10 @@
         <v>138</v>
       </c>
       <c r="F191" s="6" t="s">
-        <v>961</v>
+        <v>957</v>
       </c>
       <c r="G191" s="8" t="s">
-        <v>962</v>
+        <v>958</v>
       </c>
     </row>
     <row r="192" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9106,10 +9106,10 @@
         <v>138</v>
       </c>
       <c r="F192" s="6" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="G192" s="8" t="s">
-        <v>964</v>
+        <v>960</v>
       </c>
     </row>
     <row r="193" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9129,10 +9129,10 @@
         <v>138</v>
       </c>
       <c r="F193" s="6" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="G193" s="8" t="s">
-        <v>966</v>
+        <v>962</v>
       </c>
     </row>
     <row r="194" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9152,10 +9152,10 @@
         <v>138</v>
       </c>
       <c r="F194" s="6" t="s">
-        <v>967</v>
+        <v>963</v>
       </c>
       <c r="G194" s="8" t="s">
-        <v>968</v>
+        <v>964</v>
       </c>
     </row>
     <row r="195" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9175,10 +9175,10 @@
         <v>138</v>
       </c>
       <c r="F195" s="6" t="s">
-        <v>969</v>
+        <v>965</v>
       </c>
       <c r="G195" s="8" t="s">
-        <v>970</v>
+        <v>966</v>
       </c>
     </row>
     <row r="196" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9198,10 +9198,10 @@
         <v>138</v>
       </c>
       <c r="F196" s="6" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="G196" s="8" t="s">
-        <v>972</v>
+        <v>968</v>
       </c>
     </row>
     <row r="197" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9221,10 +9221,10 @@
         <v>138</v>
       </c>
       <c r="F197" s="6" t="s">
-        <v>973</v>
+        <v>969</v>
       </c>
       <c r="G197" s="8" t="s">
-        <v>974</v>
+        <v>970</v>
       </c>
     </row>
     <row r="198" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9244,10 +9244,10 @@
         <v>138</v>
       </c>
       <c r="F198" s="6" t="s">
-        <v>975</v>
+        <v>971</v>
       </c>
       <c r="G198" s="8" t="s">
-        <v>976</v>
+        <v>972</v>
       </c>
     </row>
     <row r="199" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9267,10 +9267,10 @@
         <v>138</v>
       </c>
       <c r="F199" s="6" t="s">
-        <v>977</v>
+        <v>973</v>
       </c>
       <c r="G199" s="8" t="s">
-        <v>978</v>
+        <v>974</v>
       </c>
     </row>
     <row r="200" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9290,10 +9290,10 @@
         <v>138</v>
       </c>
       <c r="F200" s="6" t="s">
-        <v>979</v>
+        <v>975</v>
       </c>
       <c r="G200" s="8" t="s">
-        <v>980</v>
+        <v>976</v>
       </c>
     </row>
     <row r="201" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9313,10 +9313,10 @@
         <v>138</v>
       </c>
       <c r="F201" s="6" t="s">
-        <v>981</v>
+        <v>977</v>
       </c>
       <c r="G201" s="8" t="s">
-        <v>982</v>
+        <v>978</v>
       </c>
     </row>
     <row r="202" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9336,10 +9336,10 @@
         <v>138</v>
       </c>
       <c r="F202" s="6" t="s">
-        <v>983</v>
+        <v>979</v>
       </c>
       <c r="G202" s="8" t="s">
-        <v>984</v>
+        <v>980</v>
       </c>
     </row>
     <row r="203" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9359,10 +9359,10 @@
         <v>138</v>
       </c>
       <c r="F203" s="6" t="s">
-        <v>985</v>
+        <v>981</v>
       </c>
       <c r="G203" s="8" t="s">
-        <v>986</v>
+        <v>982</v>
       </c>
     </row>
     <row r="204" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9382,10 +9382,10 @@
         <v>138</v>
       </c>
       <c r="F204" s="6" t="s">
-        <v>987</v>
+        <v>983</v>
       </c>
       <c r="G204" s="8" t="s">
-        <v>988</v>
+        <v>984</v>
       </c>
     </row>
     <row r="205" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9405,10 +9405,10 @@
         <v>138</v>
       </c>
       <c r="F205" s="6" t="s">
-        <v>989</v>
+        <v>985</v>
       </c>
       <c r="G205" s="8" t="s">
-        <v>990</v>
+        <v>986</v>
       </c>
     </row>
     <row r="206" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9428,10 +9428,10 @@
         <v>138</v>
       </c>
       <c r="F206" s="6" t="s">
-        <v>991</v>
+        <v>987</v>
       </c>
       <c r="G206" s="8" t="s">
-        <v>992</v>
+        <v>988</v>
       </c>
     </row>
     <row r="207" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9451,10 +9451,10 @@
         <v>138</v>
       </c>
       <c r="F207" s="6" t="s">
-        <v>993</v>
+        <v>989</v>
       </c>
       <c r="G207" s="8" t="s">
-        <v>994</v>
+        <v>990</v>
       </c>
     </row>
     <row r="208" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9474,10 +9474,10 @@
         <v>138</v>
       </c>
       <c r="F208" s="6" t="s">
-        <v>995</v>
+        <v>991</v>
       </c>
       <c r="G208" s="8" t="s">
-        <v>996</v>
+        <v>992</v>
       </c>
     </row>
     <row r="209" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9497,10 +9497,10 @@
         <v>138</v>
       </c>
       <c r="F209" s="6" t="s">
-        <v>997</v>
+        <v>993</v>
       </c>
       <c r="G209" s="8" t="s">
-        <v>998</v>
+        <v>994</v>
       </c>
     </row>
     <row r="210" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9520,10 +9520,10 @@
         <v>138</v>
       </c>
       <c r="F210" s="6" t="s">
-        <v>999</v>
+        <v>995</v>
       </c>
       <c r="G210" s="8" t="s">
-        <v>1000</v>
+        <v>996</v>
       </c>
     </row>
     <row r="211" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9543,10 +9543,10 @@
         <v>138</v>
       </c>
       <c r="F211" s="6" t="s">
-        <v>1001</v>
+        <v>997</v>
       </c>
       <c r="G211" s="8" t="s">
-        <v>1002</v>
+        <v>998</v>
       </c>
     </row>
     <row r="212" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9566,10 +9566,10 @@
         <v>138</v>
       </c>
       <c r="F212" s="6" t="s">
-        <v>1003</v>
+        <v>999</v>
       </c>
       <c r="G212" s="8" t="s">
-        <v>1004</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="213" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9589,10 +9589,10 @@
         <v>138</v>
       </c>
       <c r="F213" s="6" t="s">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="G213" s="8" t="s">
-        <v>1006</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="214" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9612,10 +9612,10 @@
         <v>138</v>
       </c>
       <c r="F214" s="6" t="s">
-        <v>1007</v>
+        <v>1003</v>
       </c>
       <c r="G214" s="8" t="s">
-        <v>1008</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="215" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9635,10 +9635,10 @@
         <v>138</v>
       </c>
       <c r="F215" s="6" t="s">
-        <v>1009</v>
+        <v>1005</v>
       </c>
       <c r="G215" s="8" t="s">
-        <v>1010</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="216" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9658,10 +9658,10 @@
         <v>138</v>
       </c>
       <c r="F216" s="6" t="s">
-        <v>1011</v>
+        <v>1007</v>
       </c>
       <c r="G216" s="8" t="s">
-        <v>1012</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="217" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9681,10 +9681,10 @@
         <v>138</v>
       </c>
       <c r="F217" s="6" t="s">
-        <v>1013</v>
+        <v>1009</v>
       </c>
       <c r="G217" s="8" t="s">
-        <v>1014</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="218" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9704,10 +9704,10 @@
         <v>138</v>
       </c>
       <c r="F218" s="6" t="s">
-        <v>1015</v>
+        <v>1011</v>
       </c>
       <c r="G218" s="8" t="s">
-        <v>1016</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.3">
@@ -9727,10 +9727,10 @@
         <v>138</v>
       </c>
       <c r="F219" s="9" t="s">
-        <v>1017</v>
+        <v>1013</v>
       </c>
       <c r="G219" s="10" t="s">
-        <v>1018</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.3">
@@ -9750,10 +9750,10 @@
         <v>138</v>
       </c>
       <c r="F220" s="11" t="s">
-        <v>1019</v>
+        <v>1015</v>
       </c>
       <c r="G220" s="11" t="s">
-        <v>1020</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.3">
@@ -9773,10 +9773,10 @@
         <v>138</v>
       </c>
       <c r="F221" s="11" t="s">
-        <v>1021</v>
+        <v>1017</v>
       </c>
       <c r="G221" s="11" t="s">
-        <v>1022</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.3">
@@ -9796,10 +9796,10 @@
         <v>138</v>
       </c>
       <c r="F222" s="11" t="s">
-        <v>1023</v>
+        <v>1019</v>
       </c>
       <c r="G222" s="11" t="s">
-        <v>1024</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.3">
@@ -9819,10 +9819,10 @@
         <v>138</v>
       </c>
       <c r="F223" s="11" t="s">
-        <v>1025</v>
+        <v>1021</v>
       </c>
       <c r="G223" s="11" t="s">
-        <v>1026</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.3">
@@ -9842,10 +9842,10 @@
         <v>138</v>
       </c>
       <c r="F224" s="11" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
       <c r="G224" s="11" t="s">
-        <v>1028</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.3">
@@ -9865,10 +9865,10 @@
         <v>138</v>
       </c>
       <c r="F225" s="11" t="s">
-        <v>1029</v>
+        <v>1025</v>
       </c>
       <c r="G225" s="11" t="s">
-        <v>1030</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.3">
@@ -9888,10 +9888,10 @@
         <v>138</v>
       </c>
       <c r="F226" s="11" t="s">
-        <v>1031</v>
+        <v>1027</v>
       </c>
       <c r="G226" s="11" t="s">
-        <v>1032</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.3">
@@ -9911,10 +9911,10 @@
         <v>138</v>
       </c>
       <c r="F227" s="11" t="s">
-        <v>1033</v>
+        <v>1029</v>
       </c>
       <c r="G227" s="11" t="s">
-        <v>1034</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.3">
@@ -9934,10 +9934,10 @@
         <v>138</v>
       </c>
       <c r="F228" s="11" t="s">
-        <v>1035</v>
+        <v>1031</v>
       </c>
       <c r="G228" s="11" t="s">
-        <v>1036</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.3">
@@ -9957,10 +9957,10 @@
         <v>138</v>
       </c>
       <c r="F229" s="11" t="s">
-        <v>1037</v>
+        <v>1033</v>
       </c>
       <c r="G229" s="11" t="s">
-        <v>1038</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.3">
@@ -9980,10 +9980,10 @@
         <v>138</v>
       </c>
       <c r="F230" s="11" t="s">
-        <v>1039</v>
+        <v>1035</v>
       </c>
       <c r="G230" s="11" t="s">
-        <v>1040</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.3">
@@ -10003,10 +10003,10 @@
         <v>138</v>
       </c>
       <c r="F231" s="11" t="s">
-        <v>1041</v>
+        <v>1037</v>
       </c>
       <c r="G231" s="11" t="s">
-        <v>1042</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.3">
@@ -10026,10 +10026,10 @@
         <v>138</v>
       </c>
       <c r="F232" s="11" t="s">
-        <v>1043</v>
+        <v>1039</v>
       </c>
       <c r="G232" s="11" t="s">
-        <v>1044</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.3">
@@ -10049,10 +10049,10 @@
         <v>138</v>
       </c>
       <c r="F233" s="11" t="s">
-        <v>1045</v>
+        <v>1041</v>
       </c>
       <c r="G233" s="11" t="s">
-        <v>1046</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.3">
@@ -10072,10 +10072,10 @@
         <v>138</v>
       </c>
       <c r="F234" s="11" t="s">
-        <v>1047</v>
+        <v>1043</v>
       </c>
       <c r="G234" s="11" t="s">
-        <v>1048</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.3">
@@ -10095,10 +10095,10 @@
         <v>138</v>
       </c>
       <c r="F235" s="11" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="G235" s="11" t="s">
-        <v>1050</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.3">
@@ -10118,10 +10118,10 @@
         <v>138</v>
       </c>
       <c r="F236" s="11" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="G236" s="11" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.3">
@@ -10141,10 +10141,10 @@
         <v>138</v>
       </c>
       <c r="F237" s="11" t="s">
-        <v>1053</v>
+        <v>1049</v>
       </c>
       <c r="G237" s="11" t="s">
-        <v>1054</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.3">
@@ -10164,10 +10164,10 @@
         <v>138</v>
       </c>
       <c r="F238" s="11" t="s">
-        <v>1055</v>
+        <v>1051</v>
       </c>
       <c r="G238" s="11" t="s">
-        <v>1056</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.3">
@@ -10187,10 +10187,10 @@
         <v>138</v>
       </c>
       <c r="F239" s="11" t="s">
-        <v>1057</v>
+        <v>1053</v>
       </c>
       <c r="G239" s="11" t="s">
-        <v>1058</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.3">
@@ -10210,10 +10210,10 @@
         <v>138</v>
       </c>
       <c r="F240" s="11" t="s">
-        <v>1059</v>
+        <v>1055</v>
       </c>
       <c r="G240" s="11" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.3">
@@ -10233,10 +10233,10 @@
         <v>138</v>
       </c>
       <c r="F241" s="11" t="s">
-        <v>1061</v>
+        <v>1057</v>
       </c>
       <c r="G241" s="11" t="s">
-        <v>1062</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.3">
@@ -10256,10 +10256,10 @@
         <v>138</v>
       </c>
       <c r="F242" s="11" t="s">
-        <v>1063</v>
+        <v>1059</v>
       </c>
       <c r="G242" s="11" t="s">
-        <v>1064</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.3">
@@ -10279,10 +10279,10 @@
         <v>138</v>
       </c>
       <c r="F243" s="11" t="s">
-        <v>1065</v>
+        <v>1061</v>
       </c>
       <c r="G243" s="11" t="s">
-        <v>1066</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.3">
@@ -10302,10 +10302,10 @@
         <v>138</v>
       </c>
       <c r="F244" s="11" t="s">
-        <v>1067</v>
+        <v>1063</v>
       </c>
       <c r="G244" s="11" t="s">
-        <v>1068</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.3">
@@ -10325,10 +10325,10 @@
         <v>138</v>
       </c>
       <c r="F245" s="11" t="s">
-        <v>1069</v>
+        <v>1065</v>
       </c>
       <c r="G245" s="11" t="s">
-        <v>1070</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.3">
@@ -10348,10 +10348,10 @@
         <v>138</v>
       </c>
       <c r="F246" s="11" t="s">
-        <v>1071</v>
+        <v>1067</v>
       </c>
       <c r="G246" s="11" t="s">
-        <v>1072</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.3">
@@ -10371,10 +10371,10 @@
         <v>138</v>
       </c>
       <c r="F247" s="11" t="s">
-        <v>1073</v>
+        <v>1069</v>
       </c>
       <c r="G247" s="11" t="s">
-        <v>1074</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.3">
@@ -10394,10 +10394,10 @@
         <v>138</v>
       </c>
       <c r="F248" s="11" t="s">
-        <v>1075</v>
+        <v>1071</v>
       </c>
       <c r="G248" s="11" t="s">
-        <v>1076</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.3">
@@ -10417,10 +10417,10 @@
         <v>138</v>
       </c>
       <c r="F249" s="11" t="s">
-        <v>1077</v>
+        <v>1073</v>
       </c>
       <c r="G249" s="11" t="s">
-        <v>1078</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.3">
@@ -10440,10 +10440,10 @@
         <v>138</v>
       </c>
       <c r="F250" s="11" t="s">
-        <v>1079</v>
+        <v>1075</v>
       </c>
       <c r="G250" s="11" t="s">
-        <v>1080</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.3">
@@ -10463,10 +10463,10 @@
         <v>138</v>
       </c>
       <c r="F251" s="11" t="s">
-        <v>1081</v>
+        <v>1077</v>
       </c>
       <c r="G251" s="11" t="s">
-        <v>1082</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.3">
@@ -10486,10 +10486,10 @@
         <v>138</v>
       </c>
       <c r="F252" s="11" t="s">
-        <v>1083</v>
+        <v>1079</v>
       </c>
       <c r="G252" s="11" t="s">
-        <v>1084</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="253" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -10509,10 +10509,10 @@
         <v>138</v>
       </c>
       <c r="F253" s="11" t="s">
-        <v>1085</v>
+        <v>1081</v>
       </c>
       <c r="G253" s="11" t="s">
-        <v>1086</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="254" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -10532,10 +10532,10 @@
         <v>138</v>
       </c>
       <c r="F254" s="5" t="s">
-        <v>1328</v>
+        <v>1324</v>
       </c>
       <c r="G254" s="7" t="s">
-        <v>1329</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.3">
@@ -10555,10 +10555,10 @@
         <v>138</v>
       </c>
       <c r="F255" s="11" t="s">
-        <v>1087</v>
+        <v>1083</v>
       </c>
       <c r="G255" s="11" t="s">
-        <v>1088</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.3">
@@ -10578,10 +10578,10 @@
         <v>138</v>
       </c>
       <c r="F256" s="11" t="s">
-        <v>1089</v>
+        <v>1085</v>
       </c>
       <c r="G256" s="11" t="s">
-        <v>1090</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.3">
@@ -10601,10 +10601,10 @@
         <v>138</v>
       </c>
       <c r="F257" s="11" t="s">
-        <v>1091</v>
+        <v>1087</v>
       </c>
       <c r="G257" s="11" t="s">
-        <v>1092</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.3">
@@ -10624,10 +10624,10 @@
         <v>138</v>
       </c>
       <c r="F258" s="11" t="s">
-        <v>1093</v>
+        <v>1089</v>
       </c>
       <c r="G258" s="11" t="s">
-        <v>1094</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.3">
@@ -10647,10 +10647,10 @@
         <v>138</v>
       </c>
       <c r="F259" s="11" t="s">
-        <v>1095</v>
+        <v>1091</v>
       </c>
       <c r="G259" s="11" t="s">
-        <v>1096</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.3">
@@ -10670,10 +10670,10 @@
         <v>138</v>
       </c>
       <c r="F260" s="11" t="s">
-        <v>1097</v>
+        <v>1093</v>
       </c>
       <c r="G260" s="11" t="s">
-        <v>1098</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.3">
@@ -10693,10 +10693,10 @@
         <v>138</v>
       </c>
       <c r="F261" s="11" t="s">
-        <v>1099</v>
+        <v>1095</v>
       </c>
       <c r="G261" s="11" t="s">
-        <v>1100</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.3">
@@ -10716,10 +10716,10 @@
         <v>138</v>
       </c>
       <c r="F262" s="11" t="s">
-        <v>1101</v>
+        <v>1097</v>
       </c>
       <c r="G262" s="11" t="s">
-        <v>1102</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.3">
@@ -10739,10 +10739,10 @@
         <v>138</v>
       </c>
       <c r="F263" s="11" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="G263" s="11" t="s">
-        <v>1104</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.3">
@@ -10762,10 +10762,10 @@
         <v>138</v>
       </c>
       <c r="F264" s="11" t="s">
-        <v>1105</v>
+        <v>1101</v>
       </c>
       <c r="G264" s="11" t="s">
-        <v>1106</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.3">
@@ -10785,10 +10785,10 @@
         <v>138</v>
       </c>
       <c r="F265" s="11" t="s">
-        <v>1107</v>
+        <v>1103</v>
       </c>
       <c r="G265" s="11" t="s">
-        <v>1108</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.3">
@@ -10808,10 +10808,10 @@
         <v>138</v>
       </c>
       <c r="F266" s="11" t="s">
-        <v>1109</v>
+        <v>1105</v>
       </c>
       <c r="G266" s="11" t="s">
-        <v>1110</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.3">
@@ -10831,10 +10831,10 @@
         <v>138</v>
       </c>
       <c r="F267" s="11" t="s">
-        <v>1111</v>
+        <v>1107</v>
       </c>
       <c r="G267" s="11" t="s">
-        <v>1112</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.3">
@@ -10854,10 +10854,10 @@
         <v>138</v>
       </c>
       <c r="F268" s="11" t="s">
-        <v>1113</v>
+        <v>1109</v>
       </c>
       <c r="G268" s="11" t="s">
-        <v>1114</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.3">
@@ -10877,10 +10877,10 @@
         <v>138</v>
       </c>
       <c r="F269" s="11" t="s">
-        <v>1115</v>
+        <v>1111</v>
       </c>
       <c r="G269" s="11" t="s">
-        <v>1116</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.3">
@@ -10900,10 +10900,10 @@
         <v>138</v>
       </c>
       <c r="F270" s="11" t="s">
-        <v>1117</v>
+        <v>1113</v>
       </c>
       <c r="G270" s="11" t="s">
-        <v>1118</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.3">
@@ -10923,10 +10923,10 @@
         <v>138</v>
       </c>
       <c r="F271" s="11" t="s">
-        <v>1119</v>
+        <v>1115</v>
       </c>
       <c r="G271" s="11" t="s">
-        <v>1120</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.3">
@@ -10946,10 +10946,10 @@
         <v>138</v>
       </c>
       <c r="F272" s="11" t="s">
-        <v>1121</v>
+        <v>1117</v>
       </c>
       <c r="G272" s="11" t="s">
-        <v>1122</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.3">
@@ -10969,10 +10969,10 @@
         <v>138</v>
       </c>
       <c r="F273" s="11" t="s">
-        <v>1123</v>
+        <v>1119</v>
       </c>
       <c r="G273" s="11" t="s">
-        <v>1124</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.3">
@@ -10992,10 +10992,10 @@
         <v>138</v>
       </c>
       <c r="F274" s="11" t="s">
-        <v>1125</v>
+        <v>1121</v>
       </c>
       <c r="G274" s="11" t="s">
-        <v>1126</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.3">
@@ -11015,10 +11015,10 @@
         <v>138</v>
       </c>
       <c r="F275" s="11" t="s">
-        <v>1127</v>
+        <v>1123</v>
       </c>
       <c r="G275" s="11" t="s">
-        <v>1128</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.3">
@@ -11038,10 +11038,10 @@
         <v>138</v>
       </c>
       <c r="F276" s="11" t="s">
-        <v>1129</v>
+        <v>1125</v>
       </c>
       <c r="G276" s="11" t="s">
-        <v>1130</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.3">
@@ -11061,10 +11061,10 @@
         <v>138</v>
       </c>
       <c r="F277" s="11" t="s">
-        <v>1131</v>
+        <v>1127</v>
       </c>
       <c r="G277" s="11" t="s">
-        <v>1132</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.3">
@@ -11084,10 +11084,10 @@
         <v>138</v>
       </c>
       <c r="F278" s="11" t="s">
-        <v>1133</v>
+        <v>1129</v>
       </c>
       <c r="G278" s="11" t="s">
-        <v>1134</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="279" spans="1:7" x14ac:dyDescent="0.3">
@@ -11107,10 +11107,10 @@
         <v>138</v>
       </c>
       <c r="F279" s="11" t="s">
-        <v>1135</v>
+        <v>1131</v>
       </c>
       <c r="G279" s="11" t="s">
-        <v>1136</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="280" spans="1:7" x14ac:dyDescent="0.3">
@@ -11130,10 +11130,10 @@
         <v>138</v>
       </c>
       <c r="F280" s="11" t="s">
-        <v>1137</v>
+        <v>1133</v>
       </c>
       <c r="G280" s="11" t="s">
-        <v>1138</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.3">
@@ -11153,10 +11153,10 @@
         <v>138</v>
       </c>
       <c r="F281" s="11" t="s">
-        <v>1139</v>
+        <v>1135</v>
       </c>
       <c r="G281" s="11" t="s">
-        <v>1140</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.3">
@@ -11176,10 +11176,10 @@
         <v>601</v>
       </c>
       <c r="F282" s="11" t="s">
-        <v>1141</v>
+        <v>1137</v>
       </c>
       <c r="G282" s="11" t="s">
-        <v>1142</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.3">
@@ -11199,10 +11199,10 @@
         <v>601</v>
       </c>
       <c r="F283" s="11" t="s">
-        <v>1143</v>
+        <v>1139</v>
       </c>
       <c r="G283" s="11" t="s">
-        <v>1144</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.3">
@@ -11222,10 +11222,10 @@
         <v>601</v>
       </c>
       <c r="F284" s="11" t="s">
-        <v>1145</v>
+        <v>1141</v>
       </c>
       <c r="G284" s="11" t="s">
-        <v>1146</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.3">
@@ -11245,10 +11245,10 @@
         <v>601</v>
       </c>
       <c r="F285" s="11" t="s">
-        <v>1147</v>
+        <v>1143</v>
       </c>
       <c r="G285" s="11" t="s">
-        <v>1148</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.3">
@@ -11268,10 +11268,10 @@
         <v>601</v>
       </c>
       <c r="F286" s="11" t="s">
-        <v>1149</v>
+        <v>1145</v>
       </c>
       <c r="G286" s="11" t="s">
-        <v>1150</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.3">
@@ -11291,10 +11291,10 @@
         <v>601</v>
       </c>
       <c r="F287" s="11" t="s">
-        <v>1151</v>
+        <v>1147</v>
       </c>
       <c r="G287" s="11" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.3">
@@ -11314,10 +11314,10 @@
         <v>601</v>
       </c>
       <c r="F288" s="11" t="s">
-        <v>1153</v>
+        <v>1149</v>
       </c>
       <c r="G288" s="11" t="s">
-        <v>1154</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.3">
@@ -11337,10 +11337,10 @@
         <v>601</v>
       </c>
       <c r="F289" s="11" t="s">
-        <v>1155</v>
+        <v>1151</v>
       </c>
       <c r="G289" s="11" t="s">
-        <v>1156</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.3">
@@ -11360,10 +11360,10 @@
         <v>601</v>
       </c>
       <c r="F290" s="11" t="s">
-        <v>1157</v>
+        <v>1153</v>
       </c>
       <c r="G290" s="11" t="s">
-        <v>1158</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.3">
@@ -11383,10 +11383,10 @@
         <v>601</v>
       </c>
       <c r="F291" s="11" t="s">
-        <v>1159</v>
+        <v>1155</v>
       </c>
       <c r="G291" s="11" t="s">
-        <v>1160</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.3">
@@ -11406,10 +11406,10 @@
         <v>601</v>
       </c>
       <c r="F292" s="11" t="s">
-        <v>1161</v>
+        <v>1157</v>
       </c>
       <c r="G292" s="11" t="s">
-        <v>1162</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.3">
@@ -11429,10 +11429,10 @@
         <v>601</v>
       </c>
       <c r="F293" s="11" t="s">
-        <v>1163</v>
+        <v>1159</v>
       </c>
       <c r="G293" s="11" t="s">
-        <v>1164</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.3">
@@ -11452,10 +11452,10 @@
         <v>601</v>
       </c>
       <c r="F294" s="11" t="s">
-        <v>1165</v>
+        <v>1161</v>
       </c>
       <c r="G294" s="11" t="s">
-        <v>1166</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.3">
@@ -11475,10 +11475,10 @@
         <v>601</v>
       </c>
       <c r="F295" s="11" t="s">
-        <v>1167</v>
+        <v>1163</v>
       </c>
       <c r="G295" s="11" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.3">
@@ -11498,10 +11498,10 @@
         <v>601</v>
       </c>
       <c r="F296" s="11" t="s">
-        <v>1169</v>
+        <v>1165</v>
       </c>
       <c r="G296" s="11" t="s">
-        <v>1170</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.3">
@@ -11521,10 +11521,10 @@
         <v>601</v>
       </c>
       <c r="F297" s="11" t="s">
-        <v>1171</v>
+        <v>1167</v>
       </c>
       <c r="G297" s="11" t="s">
-        <v>1172</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.3">
@@ -11544,10 +11544,10 @@
         <v>138</v>
       </c>
       <c r="F298" s="11" t="s">
-        <v>1173</v>
+        <v>1169</v>
       </c>
       <c r="G298" s="11" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="299" spans="1:7" x14ac:dyDescent="0.3">
@@ -11567,10 +11567,10 @@
         <v>138</v>
       </c>
       <c r="F299" s="11" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
       <c r="G299" s="11" t="s">
-        <v>1176</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.3">
@@ -11590,10 +11590,10 @@
         <v>138</v>
       </c>
       <c r="F300" s="11" t="s">
-        <v>1177</v>
+        <v>1173</v>
       </c>
       <c r="G300" s="11" t="s">
-        <v>1178</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.3">
@@ -11613,10 +11613,10 @@
         <v>138</v>
       </c>
       <c r="F301" s="11" t="s">
-        <v>1179</v>
+        <v>1175</v>
       </c>
       <c r="G301" s="11" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="302" spans="1:7" x14ac:dyDescent="0.3">
@@ -11636,10 +11636,10 @@
         <v>138</v>
       </c>
       <c r="F302" s="11" t="s">
-        <v>1181</v>
+        <v>1177</v>
       </c>
       <c r="G302" s="11" t="s">
-        <v>1182</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="303" spans="1:7" x14ac:dyDescent="0.3">
@@ -11659,10 +11659,10 @@
         <v>138</v>
       </c>
       <c r="F303" s="11" t="s">
-        <v>1183</v>
+        <v>1179</v>
       </c>
       <c r="G303" s="11" t="s">
-        <v>1184</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="304" spans="1:7" x14ac:dyDescent="0.3">
@@ -11682,10 +11682,10 @@
         <v>138</v>
       </c>
       <c r="F304" s="11" t="s">
-        <v>1185</v>
+        <v>1181</v>
       </c>
       <c r="G304" s="11" t="s">
-        <v>1186</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="305" spans="1:7" x14ac:dyDescent="0.3">
@@ -11705,10 +11705,10 @@
         <v>138</v>
       </c>
       <c r="F305" s="11" t="s">
-        <v>1187</v>
+        <v>1183</v>
       </c>
       <c r="G305" s="11" t="s">
-        <v>1188</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="306" spans="1:7" x14ac:dyDescent="0.3">
@@ -11728,10 +11728,10 @@
         <v>138</v>
       </c>
       <c r="F306" s="11" t="s">
-        <v>1189</v>
+        <v>1185</v>
       </c>
       <c r="G306" s="11" t="s">
-        <v>1190</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="307" spans="1:7" x14ac:dyDescent="0.3">
@@ -11751,10 +11751,10 @@
         <v>138</v>
       </c>
       <c r="F307" s="11" t="s">
-        <v>1191</v>
+        <v>1187</v>
       </c>
       <c r="G307" s="11" t="s">
-        <v>1192</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="308" spans="1:7" x14ac:dyDescent="0.3">
@@ -11774,10 +11774,10 @@
         <v>601</v>
       </c>
       <c r="F308" s="11" t="s">
-        <v>1193</v>
+        <v>1189</v>
       </c>
       <c r="G308" s="11" t="s">
-        <v>1194</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="309" spans="1:7" x14ac:dyDescent="0.3">
@@ -11797,10 +11797,10 @@
         <v>601</v>
       </c>
       <c r="F309" s="11" t="s">
-        <v>1195</v>
+        <v>1191</v>
       </c>
       <c r="G309" s="11" t="s">
-        <v>1196</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="310" spans="1:7" x14ac:dyDescent="0.3">
@@ -11820,10 +11820,10 @@
         <v>601</v>
       </c>
       <c r="F310" s="11" t="s">
-        <v>1197</v>
+        <v>1193</v>
       </c>
       <c r="G310" s="11" t="s">
-        <v>1198</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="311" spans="1:7" x14ac:dyDescent="0.3">
@@ -11843,10 +11843,10 @@
         <v>601</v>
       </c>
       <c r="F311" s="11" t="s">
-        <v>1199</v>
+        <v>1195</v>
       </c>
       <c r="G311" s="11" t="s">
-        <v>1200</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="312" spans="1:7" x14ac:dyDescent="0.3">
@@ -11866,10 +11866,10 @@
         <v>601</v>
       </c>
       <c r="F312" s="11" t="s">
-        <v>1201</v>
+        <v>1197</v>
       </c>
       <c r="G312" s="11" t="s">
-        <v>1202</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="313" spans="1:7" x14ac:dyDescent="0.3">
@@ -11889,10 +11889,10 @@
         <v>601</v>
       </c>
       <c r="F313" s="11" t="s">
-        <v>1203</v>
+        <v>1199</v>
       </c>
       <c r="G313" s="11" t="s">
-        <v>1204</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="314" spans="1:7" x14ac:dyDescent="0.3">
@@ -11912,10 +11912,10 @@
         <v>601</v>
       </c>
       <c r="F314" s="11" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="G314" s="11" t="s">
-        <v>1206</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="315" spans="1:7" x14ac:dyDescent="0.3">
@@ -11935,10 +11935,10 @@
         <v>601</v>
       </c>
       <c r="F315" s="11" t="s">
-        <v>1207</v>
+        <v>1203</v>
       </c>
       <c r="G315" s="11" t="s">
-        <v>1208</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="316" spans="1:7" x14ac:dyDescent="0.3">
@@ -11958,10 +11958,10 @@
         <v>601</v>
       </c>
       <c r="F316" s="11" t="s">
-        <v>1209</v>
+        <v>1205</v>
       </c>
       <c r="G316" s="11" t="s">
-        <v>1210</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="317" spans="1:7" x14ac:dyDescent="0.3">
@@ -11981,10 +11981,10 @@
         <v>601</v>
       </c>
       <c r="F317" s="11" t="s">
-        <v>1211</v>
+        <v>1207</v>
       </c>
       <c r="G317" s="11" t="s">
-        <v>1212</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="318" spans="1:7" x14ac:dyDescent="0.3">
@@ -12004,10 +12004,10 @@
         <v>601</v>
       </c>
       <c r="F318" s="11" t="s">
-        <v>1213</v>
+        <v>1209</v>
       </c>
       <c r="G318" s="11" t="s">
-        <v>1214</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="319" spans="1:7" x14ac:dyDescent="0.3">
@@ -12027,10 +12027,10 @@
         <v>601</v>
       </c>
       <c r="F319" s="11" t="s">
-        <v>1215</v>
+        <v>1211</v>
       </c>
       <c r="G319" s="11" t="s">
-        <v>1216</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="320" spans="1:7" x14ac:dyDescent="0.3">
@@ -12050,10 +12050,10 @@
         <v>601</v>
       </c>
       <c r="F320" s="11" t="s">
-        <v>1217</v>
+        <v>1213</v>
       </c>
       <c r="G320" s="11" t="s">
-        <v>1218</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="321" spans="1:7" x14ac:dyDescent="0.3">
@@ -12073,10 +12073,10 @@
         <v>601</v>
       </c>
       <c r="F321" s="11" t="s">
-        <v>1219</v>
+        <v>1215</v>
       </c>
       <c r="G321" s="11" t="s">
-        <v>1220</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="322" spans="1:7" x14ac:dyDescent="0.3">
@@ -12096,10 +12096,10 @@
         <v>601</v>
       </c>
       <c r="F322" s="11" t="s">
-        <v>1221</v>
+        <v>1217</v>
       </c>
       <c r="G322" s="11" t="s">
-        <v>1222</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="323" spans="1:7" x14ac:dyDescent="0.3">
@@ -12119,10 +12119,10 @@
         <v>601</v>
       </c>
       <c r="F323" s="11" t="s">
-        <v>1223</v>
+        <v>1219</v>
       </c>
       <c r="G323" s="11" t="s">
-        <v>1224</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="324" spans="1:7" x14ac:dyDescent="0.3">
@@ -12142,10 +12142,10 @@
         <v>601</v>
       </c>
       <c r="F324" s="11" t="s">
-        <v>1225</v>
+        <v>1221</v>
       </c>
       <c r="G324" s="11" t="s">
-        <v>1226</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="325" spans="1:7" x14ac:dyDescent="0.3">
@@ -12165,10 +12165,10 @@
         <v>601</v>
       </c>
       <c r="F325" s="11" t="s">
-        <v>1227</v>
+        <v>1223</v>
       </c>
       <c r="G325" s="11" t="s">
-        <v>1228</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="326" spans="1:7" x14ac:dyDescent="0.3">
@@ -12188,10 +12188,10 @@
         <v>601</v>
       </c>
       <c r="F326" s="11" t="s">
-        <v>1229</v>
+        <v>1225</v>
       </c>
       <c r="G326" s="11" t="s">
-        <v>1230</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="327" spans="1:7" x14ac:dyDescent="0.3">
@@ -12211,10 +12211,10 @@
         <v>601</v>
       </c>
       <c r="F327" s="11" t="s">
-        <v>1231</v>
+        <v>1227</v>
       </c>
       <c r="G327" s="11" t="s">
-        <v>1232</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="328" spans="1:7" x14ac:dyDescent="0.3">
@@ -12234,10 +12234,10 @@
         <v>601</v>
       </c>
       <c r="F328" s="11" t="s">
-        <v>1233</v>
+        <v>1229</v>
       </c>
       <c r="G328" s="11" t="s">
-        <v>1234</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="329" spans="1:7" x14ac:dyDescent="0.3">
@@ -12257,10 +12257,10 @@
         <v>601</v>
       </c>
       <c r="F329" s="11" t="s">
-        <v>1235</v>
+        <v>1231</v>
       </c>
       <c r="G329" s="11" t="s">
-        <v>1236</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="330" spans="1:7" x14ac:dyDescent="0.3">
@@ -12280,10 +12280,10 @@
         <v>601</v>
       </c>
       <c r="F330" s="11" t="s">
-        <v>1237</v>
+        <v>1233</v>
       </c>
       <c r="G330" s="11" t="s">
-        <v>1238</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="331" spans="1:7" x14ac:dyDescent="0.3">
@@ -12303,10 +12303,10 @@
         <v>601</v>
       </c>
       <c r="F331" s="11" t="s">
-        <v>1239</v>
+        <v>1235</v>
       </c>
       <c r="G331" s="11" t="s">
-        <v>1240</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="332" spans="1:7" x14ac:dyDescent="0.3">
@@ -12326,10 +12326,10 @@
         <v>601</v>
       </c>
       <c r="F332" s="11" t="s">
-        <v>1241</v>
+        <v>1237</v>
       </c>
       <c r="G332" s="11" t="s">
-        <v>1242</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="333" spans="1:7" x14ac:dyDescent="0.3">
@@ -12349,10 +12349,10 @@
         <v>601</v>
       </c>
       <c r="F333" s="11" t="s">
-        <v>1243</v>
+        <v>1239</v>
       </c>
       <c r="G333" s="11" t="s">
-        <v>1244</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="334" spans="1:7" x14ac:dyDescent="0.3">
@@ -12372,10 +12372,10 @@
         <v>601</v>
       </c>
       <c r="F334" s="11" t="s">
-        <v>1245</v>
+        <v>1241</v>
       </c>
       <c r="G334" s="11" t="s">
-        <v>1246</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="335" spans="1:7" x14ac:dyDescent="0.3">
@@ -12395,10 +12395,10 @@
         <v>601</v>
       </c>
       <c r="F335" s="11" t="s">
-        <v>1247</v>
+        <v>1243</v>
       </c>
       <c r="G335" s="11" t="s">
-        <v>1248</v>
+        <v>1244</v>
       </c>
     </row>
   </sheetData>

--- a/files/Adhiparasakthi Students Data 1.xlsx
+++ b/files/Adhiparasakthi Students Data 1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vigne\Google_Backup\Github\sb4c\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61DE02D3-5BEB-4A48-9699-E5E406AAE2B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{734A2556-586D-42FD-AB9D-09E4AB13F11E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E3F0EEA9-6BAE-46A1-95E3-E9CE509FC50B}"/>
   </bookViews>
@@ -2313,12 +2313,6 @@
     <t>Edu#834895</t>
   </si>
   <si>
-    <t>EFIBM26275867532@edunetmail.com</t>
-  </si>
-  <si>
-    <t>Edu#588599</t>
-  </si>
-  <si>
     <t>EFIBM26641306107@edunetmail.com</t>
   </si>
   <si>
@@ -4084,6 +4078,12 @@
   </si>
   <si>
     <t>Edu#274107</t>
+  </si>
+  <si>
+    <t>EFIBM26892186049@edunetmail.com</t>
+  </si>
+  <si>
+    <t>Edu#501743</t>
   </si>
 </sst>
 </file>
@@ -4808,10 +4808,10 @@
         <v>138</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>1300</v>
+        <v>1298</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -4946,10 +4946,10 @@
         <v>138</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -4969,10 +4969,10 @@
         <v>138</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5015,10 +5015,10 @@
         <v>138</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>1348</v>
+        <v>1346</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>1349</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5038,10 +5038,10 @@
         <v>138</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>1317</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5130,10 +5130,10 @@
         <v>138</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>1318</v>
+        <v>1316</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>1319</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5153,10 +5153,10 @@
         <v>138</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>1321</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5222,10 +5222,10 @@
         <v>138</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>1338</v>
+        <v>1336</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>1339</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5383,10 +5383,10 @@
         <v>138</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5406,10 +5406,10 @@
         <v>138</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>1344</v>
+        <v>1342</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>1345</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5429,10 +5429,10 @@
         <v>138</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>1342</v>
+        <v>1340</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>1343</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5475,10 +5475,10 @@
         <v>138</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>1307</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5498,10 +5498,10 @@
         <v>138</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>1340</v>
+        <v>1338</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5544,10 +5544,10 @@
         <v>138</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>1322</v>
+        <v>1320</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>1323</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5567,10 +5567,10 @@
         <v>138</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>1298</v>
+        <v>1296</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5682,10 +5682,10 @@
         <v>138</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>1304</v>
+        <v>1302</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>1305</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5866,10 +5866,10 @@
         <v>138</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>1326</v>
+        <v>1324</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5912,10 +5912,10 @@
         <v>138</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>1312</v>
+        <v>1310</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>1313</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5935,10 +5935,10 @@
         <v>138</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>1336</v>
+        <v>1334</v>
       </c>
       <c r="G54" s="7" t="s">
-        <v>1337</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5958,10 +5958,10 @@
         <v>138</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>1347</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6004,10 +6004,10 @@
         <v>138</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>1310</v>
+        <v>1308</v>
       </c>
       <c r="G57" s="7" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6027,10 +6027,10 @@
         <v>138</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>1314</v>
+        <v>1312</v>
       </c>
       <c r="G58" s="7" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6142,10 +6142,10 @@
         <v>138</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>1334</v>
+        <v>1332</v>
       </c>
       <c r="G63" s="7" t="s">
-        <v>1335</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6165,10 +6165,10 @@
         <v>138</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="G64" s="7" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6187,11 +6187,11 @@
       <c r="E65" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F65" s="6" t="s">
-        <v>759</v>
-      </c>
-      <c r="G65" s="8" t="s">
-        <v>760</v>
+      <c r="F65" s="5" t="s">
+        <v>1348</v>
+      </c>
+      <c r="G65" s="7" t="s">
+        <v>1349</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6211,10 +6211,10 @@
         <v>138</v>
       </c>
       <c r="F66" s="6" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="G66" s="8" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6234,10 +6234,10 @@
         <v>138</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>1332</v>
+        <v>1330</v>
       </c>
       <c r="G67" s="7" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6257,10 +6257,10 @@
         <v>138</v>
       </c>
       <c r="F68" s="12" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="G68" s="12" t="s">
-        <v>1246</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6280,10 +6280,10 @@
         <v>138</v>
       </c>
       <c r="F69" s="6" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="G69" s="8" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6294,7 +6294,7 @@
         <v>141</v>
       </c>
       <c r="C70" s="16" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>188</v>
@@ -6303,10 +6303,10 @@
         <v>138</v>
       </c>
       <c r="F70" s="12" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="G70" s="12" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6326,10 +6326,10 @@
         <v>138</v>
       </c>
       <c r="F71" s="6" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="G71" s="8" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
     </row>
     <row r="72" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6349,10 +6349,10 @@
         <v>138</v>
       </c>
       <c r="F72" s="6" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="G72" s="8" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
     </row>
     <row r="73" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6372,10 +6372,10 @@
         <v>138</v>
       </c>
       <c r="F73" s="6" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G73" s="8" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6395,10 +6395,10 @@
         <v>138</v>
       </c>
       <c r="F74" s="6" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="G74" s="8" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
     </row>
     <row r="75" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6418,10 +6418,10 @@
         <v>138</v>
       </c>
       <c r="F75" s="6" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="G75" s="8" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
     </row>
     <row r="76" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6441,10 +6441,10 @@
         <v>138</v>
       </c>
       <c r="F76" s="6" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="G76" s="8" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
     </row>
     <row r="77" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6464,10 +6464,10 @@
         <v>138</v>
       </c>
       <c r="F77" s="6" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="G77" s="8" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
     </row>
     <row r="78" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6487,10 +6487,10 @@
         <v>138</v>
       </c>
       <c r="F78" s="9" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="G78" s="10" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
     </row>
     <row r="79" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6510,10 +6510,10 @@
         <v>138</v>
       </c>
       <c r="F79" s="12" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="G79" s="12" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
@@ -6533,10 +6533,10 @@
         <v>138</v>
       </c>
       <c r="F80" s="15" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="G80" s="15" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
@@ -6556,10 +6556,10 @@
         <v>138</v>
       </c>
       <c r="F81" s="11" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="G81" s="11" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
@@ -6579,10 +6579,10 @@
         <v>138</v>
       </c>
       <c r="F82" s="15" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="G82" s="15" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
@@ -6602,10 +6602,10 @@
         <v>138</v>
       </c>
       <c r="F83" s="15" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="G83" s="15" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
@@ -6625,10 +6625,10 @@
         <v>138</v>
       </c>
       <c r="F84" s="11" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="G84" s="11" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
@@ -6648,10 +6648,10 @@
         <v>138</v>
       </c>
       <c r="F85" s="11" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="G85" s="11" t="s">
-        <v>1272</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
@@ -6671,10 +6671,10 @@
         <v>138</v>
       </c>
       <c r="F86" s="15" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="G86" s="15" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
@@ -6694,10 +6694,10 @@
         <v>138</v>
       </c>
       <c r="F87" s="15" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="G87" s="15" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
@@ -6717,10 +6717,10 @@
         <v>138</v>
       </c>
       <c r="F88" s="15" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="G88" s="15" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
@@ -6740,10 +6740,10 @@
         <v>138</v>
       </c>
       <c r="F89" s="15" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="G89" s="15" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
@@ -6763,10 +6763,10 @@
         <v>138</v>
       </c>
       <c r="F90" s="11" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
       <c r="G90" s="11" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
@@ -6786,10 +6786,10 @@
         <v>138</v>
       </c>
       <c r="F91" s="15" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="G91" s="15" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
@@ -6809,10 +6809,10 @@
         <v>138</v>
       </c>
       <c r="F92" s="15" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="G92" s="15" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
     </row>
     <row r="93" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6832,10 +6832,10 @@
         <v>138</v>
       </c>
       <c r="F93" s="13" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="G93" s="14" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
     </row>
     <row r="94" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6855,10 +6855,10 @@
         <v>138</v>
       </c>
       <c r="F94" s="6" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="G94" s="8" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
     </row>
     <row r="95" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6878,10 +6878,10 @@
         <v>138</v>
       </c>
       <c r="F95" s="6" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="G95" s="8" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
     </row>
     <row r="96" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6901,10 +6901,10 @@
         <v>138</v>
       </c>
       <c r="F96" s="6" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="G96" s="8" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
     </row>
     <row r="97" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6924,10 +6924,10 @@
         <v>138</v>
       </c>
       <c r="F97" s="6" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="G97" s="8" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
     </row>
     <row r="98" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6947,10 +6947,10 @@
         <v>138</v>
       </c>
       <c r="F98" s="6" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="G98" s="8" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
     </row>
     <row r="99" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6970,10 +6970,10 @@
         <v>138</v>
       </c>
       <c r="F99" s="6" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="G99" s="8" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
     </row>
     <row r="100" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6993,10 +6993,10 @@
         <v>138</v>
       </c>
       <c r="F100" s="5" t="s">
-        <v>1294</v>
+        <v>1292</v>
       </c>
       <c r="G100" s="7" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="101" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7016,10 +7016,10 @@
         <v>138</v>
       </c>
       <c r="F101" s="6" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="G101" s="8" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
     </row>
     <row r="102" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7039,10 +7039,10 @@
         <v>138</v>
       </c>
       <c r="F102" s="6" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="G102" s="8" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
     </row>
     <row r="103" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7062,10 +7062,10 @@
         <v>138</v>
       </c>
       <c r="F103" s="6" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="G103" s="8" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
     </row>
     <row r="104" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7085,10 +7085,10 @@
         <v>138</v>
       </c>
       <c r="F104" s="6" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="G104" s="8" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
     </row>
     <row r="105" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7108,10 +7108,10 @@
         <v>138</v>
       </c>
       <c r="F105" s="12" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
       <c r="G105" s="12" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="106" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7131,10 +7131,10 @@
         <v>138</v>
       </c>
       <c r="F106" s="6" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="G106" s="8" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
     </row>
     <row r="107" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7154,10 +7154,10 @@
         <v>138</v>
       </c>
       <c r="F107" s="5" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="G107" s="7" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="108" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7177,10 +7177,10 @@
         <v>138</v>
       </c>
       <c r="F108" s="6" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="G108" s="8" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
     </row>
     <row r="109" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7200,10 +7200,10 @@
         <v>138</v>
       </c>
       <c r="F109" s="6" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="G109" s="8" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
     </row>
     <row r="110" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7223,10 +7223,10 @@
         <v>138</v>
       </c>
       <c r="F110" s="6" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="G110" s="8" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="111" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7246,10 +7246,10 @@
         <v>138</v>
       </c>
       <c r="F111" s="5" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
       <c r="G111" s="7" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="112" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7269,10 +7269,10 @@
         <v>138</v>
       </c>
       <c r="F112" s="17" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="G112" s="17" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="113" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7292,10 +7292,10 @@
         <v>138</v>
       </c>
       <c r="F113" s="6" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="G113" s="8" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
     </row>
     <row r="114" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7315,10 +7315,10 @@
         <v>138</v>
       </c>
       <c r="F114" s="12" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="G114" s="12" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="115" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7338,10 +7338,10 @@
         <v>138</v>
       </c>
       <c r="F115" s="6" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="G115" s="8" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
     </row>
     <row r="116" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7361,10 +7361,10 @@
         <v>138</v>
       </c>
       <c r="F116" s="6" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="G116" s="8" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
     </row>
     <row r="117" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7384,10 +7384,10 @@
         <v>138</v>
       </c>
       <c r="F117" s="6" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="G117" s="8" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="118" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7404,10 +7404,10 @@
         <v>138</v>
       </c>
       <c r="F118" s="6" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="G118" s="8" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="119" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7427,10 +7427,10 @@
         <v>138</v>
       </c>
       <c r="F119" s="12" t="s">
-        <v>1282</v>
+        <v>1280</v>
       </c>
       <c r="G119" s="12" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="120" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7450,10 +7450,10 @@
         <v>138</v>
       </c>
       <c r="F120" s="6" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="G120" s="8" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
     </row>
     <row r="121" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7473,10 +7473,10 @@
         <v>138</v>
       </c>
       <c r="F121" s="12" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="G121" s="12" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="122" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7496,10 +7496,10 @@
         <v>138</v>
       </c>
       <c r="F122" s="6" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="G122" s="8" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="123" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7519,10 +7519,10 @@
         <v>138</v>
       </c>
       <c r="F123" s="6" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="G123" s="8" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
     </row>
     <row r="124" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7542,10 +7542,10 @@
         <v>138</v>
       </c>
       <c r="F124" s="6" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="G124" s="8" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
     </row>
     <row r="125" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7565,10 +7565,10 @@
         <v>138</v>
       </c>
       <c r="F125" s="12" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="G125" s="12" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="126" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7588,10 +7588,10 @@
         <v>138</v>
       </c>
       <c r="F126" s="12" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="G126" s="12" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="127" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7611,10 +7611,10 @@
         <v>138</v>
       </c>
       <c r="F127" s="6" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="G127" s="8" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
     </row>
     <row r="128" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7634,10 +7634,10 @@
         <v>138</v>
       </c>
       <c r="F128" s="6" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="G128" s="8" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
     </row>
     <row r="129" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7657,10 +7657,10 @@
         <v>138</v>
       </c>
       <c r="F129" s="6" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="G129" s="8" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
     </row>
     <row r="130" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7680,10 +7680,10 @@
         <v>138</v>
       </c>
       <c r="F130" s="12" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="G130" s="12" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="131" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7703,10 +7703,10 @@
         <v>138</v>
       </c>
       <c r="F131" s="6" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="G131" s="8" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
     </row>
     <row r="132" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7726,10 +7726,10 @@
         <v>138</v>
       </c>
       <c r="F132" s="6" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="G132" s="8" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
     </row>
     <row r="133" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7749,10 +7749,10 @@
         <v>138</v>
       </c>
       <c r="F133" s="6" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="G133" s="8" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
     </row>
     <row r="134" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7772,10 +7772,10 @@
         <v>138</v>
       </c>
       <c r="F134" s="6" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="G134" s="8" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
     </row>
     <row r="135" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7795,10 +7795,10 @@
         <v>138</v>
       </c>
       <c r="F135" s="12" t="s">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="G135" s="12" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="136" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7818,10 +7818,10 @@
         <v>138</v>
       </c>
       <c r="F136" s="6" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="G136" s="8" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
     </row>
     <row r="137" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7841,10 +7841,10 @@
         <v>138</v>
       </c>
       <c r="F137" s="6" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="G137" s="8" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
     </row>
     <row r="138" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7864,10 +7864,10 @@
         <v>138</v>
       </c>
       <c r="F138" s="6" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="G138" s="8" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.3">
@@ -7887,10 +7887,10 @@
         <v>138</v>
       </c>
       <c r="F139" s="9" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="G139" s="10" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.3">
@@ -7910,10 +7910,10 @@
         <v>138</v>
       </c>
       <c r="F140" s="15" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="G140" s="15" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.3">
@@ -7933,10 +7933,10 @@
         <v>138</v>
       </c>
       <c r="F141" s="11" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="G141" s="11" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.3">
@@ -7956,10 +7956,10 @@
         <v>138</v>
       </c>
       <c r="F142" s="15" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G142" s="15" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.3">
@@ -7979,10 +7979,10 @@
         <v>138</v>
       </c>
       <c r="F143" s="11" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="G143" s="11" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.3">
@@ -8002,10 +8002,10 @@
         <v>138</v>
       </c>
       <c r="F144" s="11" t="s">
-        <v>1249</v>
+        <v>1247</v>
       </c>
       <c r="G144" s="11" t="s">
-        <v>1250</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.3">
@@ -8025,10 +8025,10 @@
         <v>138</v>
       </c>
       <c r="F145" s="15" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="G145" s="15" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.3">
@@ -8048,10 +8048,10 @@
         <v>138</v>
       </c>
       <c r="F146" s="11" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
       <c r="G146" s="11" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.3">
@@ -8071,10 +8071,10 @@
         <v>138</v>
       </c>
       <c r="F147" s="15" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="G147" s="15" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.3">
@@ -8094,10 +8094,10 @@
         <v>138</v>
       </c>
       <c r="F148" s="15" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="G148" s="15" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.3">
@@ -8117,10 +8117,10 @@
         <v>138</v>
       </c>
       <c r="F149" s="15" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="G149" s="15" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.3">
@@ -8140,10 +8140,10 @@
         <v>138</v>
       </c>
       <c r="F150" s="15" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="G150" s="15" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.3">
@@ -8163,10 +8163,10 @@
         <v>138</v>
       </c>
       <c r="F151" s="15" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="G151" s="15" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.3">
@@ -8186,10 +8186,10 @@
         <v>138</v>
       </c>
       <c r="F152" s="11" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="G152" s="11" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="153" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8209,10 +8209,10 @@
         <v>138</v>
       </c>
       <c r="F153" s="13" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="G153" s="14" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
     </row>
     <row r="154" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8232,10 +8232,10 @@
         <v>138</v>
       </c>
       <c r="F154" s="6" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="G154" s="8" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
     </row>
     <row r="155" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8255,10 +8255,10 @@
         <v>138</v>
       </c>
       <c r="F155" s="6" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="G155" s="8" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
     </row>
     <row r="156" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8278,10 +8278,10 @@
         <v>138</v>
       </c>
       <c r="F156" s="6" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="G156" s="8" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
     </row>
     <row r="157" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8301,10 +8301,10 @@
         <v>138</v>
       </c>
       <c r="F157" s="12" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="G157" s="12" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="158" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8324,10 +8324,10 @@
         <v>138</v>
       </c>
       <c r="F158" s="6" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="G158" s="8" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
     </row>
     <row r="159" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8347,10 +8347,10 @@
         <v>138</v>
       </c>
       <c r="F159" s="6" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="G159" s="8" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
     </row>
     <row r="160" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8370,10 +8370,10 @@
         <v>138</v>
       </c>
       <c r="F160" s="12" t="s">
-        <v>1253</v>
+        <v>1251</v>
       </c>
       <c r="G160" s="12" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="161" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8393,10 +8393,10 @@
         <v>138</v>
       </c>
       <c r="F161" s="6" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="G161" s="8" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
     </row>
     <row r="162" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8416,10 +8416,10 @@
         <v>138</v>
       </c>
       <c r="F162" s="6" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="G162" s="8" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
     </row>
     <row r="163" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8439,10 +8439,10 @@
         <v>138</v>
       </c>
       <c r="F163" s="6" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="G163" s="8" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
     </row>
     <row r="164" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8462,10 +8462,10 @@
         <v>138</v>
       </c>
       <c r="F164" s="6" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="G164" s="8" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
     </row>
     <row r="165" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8485,10 +8485,10 @@
         <v>138</v>
       </c>
       <c r="F165" s="6" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="G165" s="8" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
     </row>
     <row r="166" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8508,10 +8508,10 @@
         <v>138</v>
       </c>
       <c r="F166" s="6" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="G166" s="8" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
     </row>
     <row r="167" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8531,10 +8531,10 @@
         <v>138</v>
       </c>
       <c r="F167" s="6" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="G167" s="8" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
     </row>
     <row r="168" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8554,10 +8554,10 @@
         <v>138</v>
       </c>
       <c r="F168" s="6" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="G168" s="8" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
     </row>
     <row r="169" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8577,10 +8577,10 @@
         <v>138</v>
       </c>
       <c r="F169" s="6" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="G169" s="8" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
     </row>
     <row r="170" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8600,10 +8600,10 @@
         <v>138</v>
       </c>
       <c r="F170" s="6" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="G170" s="8" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
     </row>
     <row r="171" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8623,10 +8623,10 @@
         <v>138</v>
       </c>
       <c r="F171" s="6" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="G171" s="8" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
     </row>
     <row r="172" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8646,10 +8646,10 @@
         <v>138</v>
       </c>
       <c r="F172" s="6" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="G172" s="8" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
     </row>
     <row r="173" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8669,10 +8669,10 @@
         <v>138</v>
       </c>
       <c r="F173" s="6" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="G173" s="8" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
     </row>
     <row r="174" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8692,10 +8692,10 @@
         <v>138</v>
       </c>
       <c r="F174" s="6" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="G174" s="8" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
     </row>
     <row r="175" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8715,10 +8715,10 @@
         <v>138</v>
       </c>
       <c r="F175" s="6" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="G175" s="8" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
     </row>
     <row r="176" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8738,10 +8738,10 @@
         <v>138</v>
       </c>
       <c r="F176" s="6" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="G176" s="8" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
     </row>
     <row r="177" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8761,10 +8761,10 @@
         <v>138</v>
       </c>
       <c r="F177" s="6" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="G177" s="8" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
     </row>
     <row r="178" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8784,10 +8784,10 @@
         <v>138</v>
       </c>
       <c r="F178" s="6" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="G178" s="8" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
     </row>
     <row r="179" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8807,10 +8807,10 @@
         <v>138</v>
       </c>
       <c r="F179" s="6" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="G179" s="8" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
     </row>
     <row r="180" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8830,10 +8830,10 @@
         <v>138</v>
       </c>
       <c r="F180" s="6" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="G180" s="8" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
     </row>
     <row r="181" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8853,10 +8853,10 @@
         <v>138</v>
       </c>
       <c r="F181" s="6" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="G181" s="8" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
     </row>
     <row r="182" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8876,10 +8876,10 @@
         <v>138</v>
       </c>
       <c r="F182" s="6" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="G182" s="8" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="183" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8899,10 +8899,10 @@
         <v>138</v>
       </c>
       <c r="F183" s="6" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="G183" s="8" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
     </row>
     <row r="184" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8922,10 +8922,10 @@
         <v>138</v>
       </c>
       <c r="F184" s="6" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="G184" s="8" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
     </row>
     <row r="185" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8945,10 +8945,10 @@
         <v>138</v>
       </c>
       <c r="F185" s="6" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="G185" s="8" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="186" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8968,10 +8968,10 @@
         <v>138</v>
       </c>
       <c r="F186" s="6" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="G186" s="8" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
     </row>
     <row r="187" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8991,10 +8991,10 @@
         <v>138</v>
       </c>
       <c r="F187" s="6" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="G187" s="8" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
     </row>
     <row r="188" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9014,10 +9014,10 @@
         <v>138</v>
       </c>
       <c r="F188" s="6" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="G188" s="8" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
     </row>
     <row r="189" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9037,10 +9037,10 @@
         <v>138</v>
       </c>
       <c r="F189" s="6" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="G189" s="8" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
     </row>
     <row r="190" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9060,10 +9060,10 @@
         <v>138</v>
       </c>
       <c r="F190" s="6" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="G190" s="8" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
     </row>
     <row r="191" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9083,10 +9083,10 @@
         <v>138</v>
       </c>
       <c r="F191" s="6" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="G191" s="8" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
     </row>
     <row r="192" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9106,10 +9106,10 @@
         <v>138</v>
       </c>
       <c r="F192" s="6" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="G192" s="8" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
     </row>
     <row r="193" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9129,10 +9129,10 @@
         <v>138</v>
       </c>
       <c r="F193" s="6" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="G193" s="8" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
     </row>
     <row r="194" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9152,10 +9152,10 @@
         <v>138</v>
       </c>
       <c r="F194" s="6" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="G194" s="8" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
     </row>
     <row r="195" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9175,10 +9175,10 @@
         <v>138</v>
       </c>
       <c r="F195" s="6" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="G195" s="8" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
     </row>
     <row r="196" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9198,10 +9198,10 @@
         <v>138</v>
       </c>
       <c r="F196" s="6" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="G196" s="8" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
     </row>
     <row r="197" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9221,10 +9221,10 @@
         <v>138</v>
       </c>
       <c r="F197" s="6" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="G197" s="8" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
     </row>
     <row r="198" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9244,10 +9244,10 @@
         <v>138</v>
       </c>
       <c r="F198" s="6" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="G198" s="8" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
     </row>
     <row r="199" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9267,10 +9267,10 @@
         <v>138</v>
       </c>
       <c r="F199" s="6" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="G199" s="8" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
     </row>
     <row r="200" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9290,10 +9290,10 @@
         <v>138</v>
       </c>
       <c r="F200" s="6" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="G200" s="8" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
     </row>
     <row r="201" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9313,10 +9313,10 @@
         <v>138</v>
       </c>
       <c r="F201" s="6" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="G201" s="8" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
     </row>
     <row r="202" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9336,10 +9336,10 @@
         <v>138</v>
       </c>
       <c r="F202" s="6" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="G202" s="8" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
     </row>
     <row r="203" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9359,10 +9359,10 @@
         <v>138</v>
       </c>
       <c r="F203" s="6" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="G203" s="8" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
     </row>
     <row r="204" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9382,10 +9382,10 @@
         <v>138</v>
       </c>
       <c r="F204" s="6" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="G204" s="8" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
     </row>
     <row r="205" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9405,10 +9405,10 @@
         <v>138</v>
       </c>
       <c r="F205" s="6" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="G205" s="8" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
     </row>
     <row r="206" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9428,10 +9428,10 @@
         <v>138</v>
       </c>
       <c r="F206" s="6" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="G206" s="8" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
     </row>
     <row r="207" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9451,10 +9451,10 @@
         <v>138</v>
       </c>
       <c r="F207" s="6" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="G207" s="8" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
     </row>
     <row r="208" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9474,10 +9474,10 @@
         <v>138</v>
       </c>
       <c r="F208" s="6" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="G208" s="8" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
     </row>
     <row r="209" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9497,10 +9497,10 @@
         <v>138</v>
       </c>
       <c r="F209" s="6" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="G209" s="8" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="210" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9520,10 +9520,10 @@
         <v>138</v>
       </c>
       <c r="F210" s="6" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="G210" s="8" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
     </row>
     <row r="211" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9543,10 +9543,10 @@
         <v>138</v>
       </c>
       <c r="F211" s="6" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="G211" s="8" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
     </row>
     <row r="212" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9566,10 +9566,10 @@
         <v>138</v>
       </c>
       <c r="F212" s="6" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="G212" s="8" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
     </row>
     <row r="213" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9589,10 +9589,10 @@
         <v>138</v>
       </c>
       <c r="F213" s="6" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="G213" s="8" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="214" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9612,10 +9612,10 @@
         <v>138</v>
       </c>
       <c r="F214" s="6" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="G214" s="8" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="215" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9635,10 +9635,10 @@
         <v>138</v>
       </c>
       <c r="F215" s="6" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="G215" s="8" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="216" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9658,10 +9658,10 @@
         <v>138</v>
       </c>
       <c r="F216" s="6" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="G216" s="8" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="217" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9681,10 +9681,10 @@
         <v>138</v>
       </c>
       <c r="F217" s="6" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="G217" s="8" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="218" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9704,10 +9704,10 @@
         <v>138</v>
       </c>
       <c r="F218" s="6" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="G218" s="8" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.3">
@@ -9727,10 +9727,10 @@
         <v>138</v>
       </c>
       <c r="F219" s="9" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="G219" s="10" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.3">
@@ -9750,10 +9750,10 @@
         <v>138</v>
       </c>
       <c r="F220" s="11" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="G220" s="11" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.3">
@@ -9773,10 +9773,10 @@
         <v>138</v>
       </c>
       <c r="F221" s="11" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="G221" s="11" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.3">
@@ -9796,10 +9796,10 @@
         <v>138</v>
       </c>
       <c r="F222" s="11" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="G222" s="11" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.3">
@@ -9819,10 +9819,10 @@
         <v>138</v>
       </c>
       <c r="F223" s="11" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="G223" s="11" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.3">
@@ -9842,10 +9842,10 @@
         <v>138</v>
       </c>
       <c r="F224" s="11" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="G224" s="11" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.3">
@@ -9865,10 +9865,10 @@
         <v>138</v>
       </c>
       <c r="F225" s="11" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="G225" s="11" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.3">
@@ -9888,10 +9888,10 @@
         <v>138</v>
       </c>
       <c r="F226" s="11" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="G226" s="11" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.3">
@@ -9911,10 +9911,10 @@
         <v>138</v>
       </c>
       <c r="F227" s="11" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="G227" s="11" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.3">
@@ -9934,10 +9934,10 @@
         <v>138</v>
       </c>
       <c r="F228" s="11" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="G228" s="11" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.3">
@@ -9957,10 +9957,10 @@
         <v>138</v>
       </c>
       <c r="F229" s="11" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="G229" s="11" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.3">
@@ -9980,10 +9980,10 @@
         <v>138</v>
       </c>
       <c r="F230" s="11" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="G230" s="11" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.3">
@@ -10003,10 +10003,10 @@
         <v>138</v>
       </c>
       <c r="F231" s="11" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="G231" s="11" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.3">
@@ -10026,10 +10026,10 @@
         <v>138</v>
       </c>
       <c r="F232" s="11" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="G232" s="11" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.3">
@@ -10049,10 +10049,10 @@
         <v>138</v>
       </c>
       <c r="F233" s="11" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="G233" s="11" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.3">
@@ -10072,10 +10072,10 @@
         <v>138</v>
       </c>
       <c r="F234" s="11" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="G234" s="11" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.3">
@@ -10095,10 +10095,10 @@
         <v>138</v>
       </c>
       <c r="F235" s="11" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="G235" s="11" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.3">
@@ -10118,10 +10118,10 @@
         <v>138</v>
       </c>
       <c r="F236" s="11" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="G236" s="11" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.3">
@@ -10141,10 +10141,10 @@
         <v>138</v>
       </c>
       <c r="F237" s="11" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="G237" s="11" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.3">
@@ -10164,10 +10164,10 @@
         <v>138</v>
       </c>
       <c r="F238" s="11" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="G238" s="11" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.3">
@@ -10187,10 +10187,10 @@
         <v>138</v>
       </c>
       <c r="F239" s="11" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="G239" s="11" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.3">
@@ -10210,10 +10210,10 @@
         <v>138</v>
       </c>
       <c r="F240" s="11" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="G240" s="11" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.3">
@@ -10233,10 +10233,10 @@
         <v>138</v>
       </c>
       <c r="F241" s="11" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="G241" s="11" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.3">
@@ -10256,10 +10256,10 @@
         <v>138</v>
       </c>
       <c r="F242" s="11" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="G242" s="11" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.3">
@@ -10279,10 +10279,10 @@
         <v>138</v>
       </c>
       <c r="F243" s="11" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="G243" s="11" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.3">
@@ -10302,10 +10302,10 @@
         <v>138</v>
       </c>
       <c r="F244" s="11" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="G244" s="11" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.3">
@@ -10325,10 +10325,10 @@
         <v>138</v>
       </c>
       <c r="F245" s="11" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="G245" s="11" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.3">
@@ -10348,10 +10348,10 @@
         <v>138</v>
       </c>
       <c r="F246" s="11" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="G246" s="11" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.3">
@@ -10371,10 +10371,10 @@
         <v>138</v>
       </c>
       <c r="F247" s="11" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="G247" s="11" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.3">
@@ -10394,10 +10394,10 @@
         <v>138</v>
       </c>
       <c r="F248" s="11" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="G248" s="11" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.3">
@@ -10417,10 +10417,10 @@
         <v>138</v>
       </c>
       <c r="F249" s="11" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="G249" s="11" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.3">
@@ -10440,10 +10440,10 @@
         <v>138</v>
       </c>
       <c r="F250" s="11" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="G250" s="11" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.3">
@@ -10463,10 +10463,10 @@
         <v>138</v>
       </c>
       <c r="F251" s="11" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="G251" s="11" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.3">
@@ -10486,10 +10486,10 @@
         <v>138</v>
       </c>
       <c r="F252" s="11" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="G252" s="11" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="253" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -10509,10 +10509,10 @@
         <v>138</v>
       </c>
       <c r="F253" s="11" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="G253" s="11" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="254" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -10532,10 +10532,10 @@
         <v>138</v>
       </c>
       <c r="F254" s="5" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
       <c r="G254" s="7" t="s">
-        <v>1325</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.3">
@@ -10555,10 +10555,10 @@
         <v>138</v>
       </c>
       <c r="F255" s="11" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="G255" s="11" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.3">
@@ -10578,10 +10578,10 @@
         <v>138</v>
       </c>
       <c r="F256" s="11" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="G256" s="11" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.3">
@@ -10601,10 +10601,10 @@
         <v>138</v>
       </c>
       <c r="F257" s="11" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="G257" s="11" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.3">
@@ -10624,10 +10624,10 @@
         <v>138</v>
       </c>
       <c r="F258" s="11" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="G258" s="11" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.3">
@@ -10647,10 +10647,10 @@
         <v>138</v>
       </c>
       <c r="F259" s="11" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="G259" s="11" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.3">
@@ -10670,10 +10670,10 @@
         <v>138</v>
       </c>
       <c r="F260" s="11" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="G260" s="11" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.3">
@@ -10693,10 +10693,10 @@
         <v>138</v>
       </c>
       <c r="F261" s="11" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="G261" s="11" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.3">
@@ -10716,10 +10716,10 @@
         <v>138</v>
       </c>
       <c r="F262" s="11" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="G262" s="11" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.3">
@@ -10739,10 +10739,10 @@
         <v>138</v>
       </c>
       <c r="F263" s="11" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="G263" s="11" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.3">
@@ -10762,10 +10762,10 @@
         <v>138</v>
       </c>
       <c r="F264" s="11" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="G264" s="11" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.3">
@@ -10785,10 +10785,10 @@
         <v>138</v>
       </c>
       <c r="F265" s="11" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="G265" s="11" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.3">
@@ -10808,10 +10808,10 @@
         <v>138</v>
       </c>
       <c r="F266" s="11" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="G266" s="11" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.3">
@@ -10831,10 +10831,10 @@
         <v>138</v>
       </c>
       <c r="F267" s="11" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="G267" s="11" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.3">
@@ -10854,10 +10854,10 @@
         <v>138</v>
       </c>
       <c r="F268" s="11" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="G268" s="11" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.3">
@@ -10877,10 +10877,10 @@
         <v>138</v>
       </c>
       <c r="F269" s="11" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="G269" s="11" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.3">
@@ -10900,10 +10900,10 @@
         <v>138</v>
       </c>
       <c r="F270" s="11" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
       <c r="G270" s="11" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.3">
@@ -10923,10 +10923,10 @@
         <v>138</v>
       </c>
       <c r="F271" s="11" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
       <c r="G271" s="11" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.3">
@@ -10946,10 +10946,10 @@
         <v>138</v>
       </c>
       <c r="F272" s="11" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="G272" s="11" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.3">
@@ -10969,10 +10969,10 @@
         <v>138</v>
       </c>
       <c r="F273" s="11" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
       <c r="G273" s="11" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.3">
@@ -10992,10 +10992,10 @@
         <v>138</v>
       </c>
       <c r="F274" s="11" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
       <c r="G274" s="11" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.3">
@@ -11015,10 +11015,10 @@
         <v>138</v>
       </c>
       <c r="F275" s="11" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="G275" s="11" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.3">
@@ -11038,10 +11038,10 @@
         <v>138</v>
       </c>
       <c r="F276" s="11" t="s">
-        <v>1125</v>
+        <v>1123</v>
       </c>
       <c r="G276" s="11" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.3">
@@ -11061,10 +11061,10 @@
         <v>138</v>
       </c>
       <c r="F277" s="11" t="s">
-        <v>1127</v>
+        <v>1125</v>
       </c>
       <c r="G277" s="11" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.3">
@@ -11084,10 +11084,10 @@
         <v>138</v>
       </c>
       <c r="F278" s="11" t="s">
-        <v>1129</v>
+        <v>1127</v>
       </c>
       <c r="G278" s="11" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="279" spans="1:7" x14ac:dyDescent="0.3">
@@ -11107,10 +11107,10 @@
         <v>138</v>
       </c>
       <c r="F279" s="11" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="G279" s="11" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="280" spans="1:7" x14ac:dyDescent="0.3">
@@ -11130,10 +11130,10 @@
         <v>138</v>
       </c>
       <c r="F280" s="11" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="G280" s="11" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.3">
@@ -11153,10 +11153,10 @@
         <v>138</v>
       </c>
       <c r="F281" s="11" t="s">
-        <v>1135</v>
+        <v>1133</v>
       </c>
       <c r="G281" s="11" t="s">
-        <v>1136</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.3">
@@ -11176,10 +11176,10 @@
         <v>601</v>
       </c>
       <c r="F282" s="11" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
       <c r="G282" s="11" t="s">
-        <v>1138</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.3">
@@ -11199,10 +11199,10 @@
         <v>601</v>
       </c>
       <c r="F283" s="11" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
       <c r="G283" s="11" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.3">
@@ -11222,10 +11222,10 @@
         <v>601</v>
       </c>
       <c r="F284" s="11" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="G284" s="11" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.3">
@@ -11245,10 +11245,10 @@
         <v>601</v>
       </c>
       <c r="F285" s="11" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
       <c r="G285" s="11" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.3">
@@ -11268,10 +11268,10 @@
         <v>601</v>
       </c>
       <c r="F286" s="11" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="G286" s="11" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.3">
@@ -11291,10 +11291,10 @@
         <v>601</v>
       </c>
       <c r="F287" s="11" t="s">
-        <v>1147</v>
+        <v>1145</v>
       </c>
       <c r="G287" s="11" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.3">
@@ -11314,10 +11314,10 @@
         <v>601</v>
       </c>
       <c r="F288" s="11" t="s">
-        <v>1149</v>
+        <v>1147</v>
       </c>
       <c r="G288" s="11" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.3">
@@ -11337,10 +11337,10 @@
         <v>601</v>
       </c>
       <c r="F289" s="11" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="G289" s="11" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.3">
@@ -11360,10 +11360,10 @@
         <v>601</v>
       </c>
       <c r="F290" s="11" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
       <c r="G290" s="11" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.3">
@@ -11383,10 +11383,10 @@
         <v>601</v>
       </c>
       <c r="F291" s="11" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="G291" s="11" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.3">
@@ -11406,10 +11406,10 @@
         <v>601</v>
       </c>
       <c r="F292" s="11" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="G292" s="11" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.3">
@@ -11429,10 +11429,10 @@
         <v>601</v>
       </c>
       <c r="F293" s="11" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="G293" s="11" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.3">
@@ -11452,10 +11452,10 @@
         <v>601</v>
       </c>
       <c r="F294" s="11" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="G294" s="11" t="s">
-        <v>1162</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.3">
@@ -11475,10 +11475,10 @@
         <v>601</v>
       </c>
       <c r="F295" s="11" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
       <c r="G295" s="11" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.3">
@@ -11498,10 +11498,10 @@
         <v>601</v>
       </c>
       <c r="F296" s="11" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="G296" s="11" t="s">
-        <v>1166</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.3">
@@ -11521,10 +11521,10 @@
         <v>601</v>
       </c>
       <c r="F297" s="11" t="s">
-        <v>1167</v>
+        <v>1165</v>
       </c>
       <c r="G297" s="11" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.3">
@@ -11544,10 +11544,10 @@
         <v>138</v>
       </c>
       <c r="F298" s="11" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="G298" s="11" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="299" spans="1:7" x14ac:dyDescent="0.3">
@@ -11567,10 +11567,10 @@
         <v>138</v>
       </c>
       <c r="F299" s="11" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
       <c r="G299" s="11" t="s">
-        <v>1172</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.3">
@@ -11590,10 +11590,10 @@
         <v>138</v>
       </c>
       <c r="F300" s="11" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="G300" s="11" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.3">
@@ -11613,10 +11613,10 @@
         <v>138</v>
       </c>
       <c r="F301" s="11" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="G301" s="11" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="302" spans="1:7" x14ac:dyDescent="0.3">
@@ -11636,10 +11636,10 @@
         <v>138</v>
       </c>
       <c r="F302" s="11" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="G302" s="11" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="303" spans="1:7" x14ac:dyDescent="0.3">
@@ -11659,10 +11659,10 @@
         <v>138</v>
       </c>
       <c r="F303" s="11" t="s">
-        <v>1179</v>
+        <v>1177</v>
       </c>
       <c r="G303" s="11" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="304" spans="1:7" x14ac:dyDescent="0.3">
@@ -11682,10 +11682,10 @@
         <v>138</v>
       </c>
       <c r="F304" s="11" t="s">
-        <v>1181</v>
+        <v>1179</v>
       </c>
       <c r="G304" s="11" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="305" spans="1:7" x14ac:dyDescent="0.3">
@@ -11705,10 +11705,10 @@
         <v>138</v>
       </c>
       <c r="F305" s="11" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
       <c r="G305" s="11" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="306" spans="1:7" x14ac:dyDescent="0.3">
@@ -11728,10 +11728,10 @@
         <v>138</v>
       </c>
       <c r="F306" s="11" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
       <c r="G306" s="11" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="307" spans="1:7" x14ac:dyDescent="0.3">
@@ -11751,10 +11751,10 @@
         <v>138</v>
       </c>
       <c r="F307" s="11" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="G307" s="11" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="308" spans="1:7" x14ac:dyDescent="0.3">
@@ -11774,10 +11774,10 @@
         <v>601</v>
       </c>
       <c r="F308" s="11" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
       <c r="G308" s="11" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="309" spans="1:7" x14ac:dyDescent="0.3">
@@ -11797,10 +11797,10 @@
         <v>601</v>
       </c>
       <c r="F309" s="11" t="s">
-        <v>1191</v>
+        <v>1189</v>
       </c>
       <c r="G309" s="11" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="310" spans="1:7" x14ac:dyDescent="0.3">
@@ -11820,10 +11820,10 @@
         <v>601</v>
       </c>
       <c r="F310" s="11" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
       <c r="G310" s="11" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="311" spans="1:7" x14ac:dyDescent="0.3">
@@ -11843,10 +11843,10 @@
         <v>601</v>
       </c>
       <c r="F311" s="11" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
       <c r="G311" s="11" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="312" spans="1:7" x14ac:dyDescent="0.3">
@@ -11866,10 +11866,10 @@
         <v>601</v>
       </c>
       <c r="F312" s="11" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="G312" s="11" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="313" spans="1:7" x14ac:dyDescent="0.3">
@@ -11889,10 +11889,10 @@
         <v>601</v>
       </c>
       <c r="F313" s="11" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
       <c r="G313" s="11" t="s">
-        <v>1200</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="314" spans="1:7" x14ac:dyDescent="0.3">
@@ -11912,10 +11912,10 @@
         <v>601</v>
       </c>
       <c r="F314" s="11" t="s">
-        <v>1201</v>
+        <v>1199</v>
       </c>
       <c r="G314" s="11" t="s">
-        <v>1202</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="315" spans="1:7" x14ac:dyDescent="0.3">
@@ -11935,10 +11935,10 @@
         <v>601</v>
       </c>
       <c r="F315" s="11" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
       <c r="G315" s="11" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="316" spans="1:7" x14ac:dyDescent="0.3">
@@ -11958,10 +11958,10 @@
         <v>601</v>
       </c>
       <c r="F316" s="11" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
       <c r="G316" s="11" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="317" spans="1:7" x14ac:dyDescent="0.3">
@@ -11981,10 +11981,10 @@
         <v>601</v>
       </c>
       <c r="F317" s="11" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="G317" s="11" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="318" spans="1:7" x14ac:dyDescent="0.3">
@@ -12004,10 +12004,10 @@
         <v>601</v>
       </c>
       <c r="F318" s="11" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="G318" s="11" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="319" spans="1:7" x14ac:dyDescent="0.3">
@@ -12027,10 +12027,10 @@
         <v>601</v>
       </c>
       <c r="F319" s="11" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="G319" s="11" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="320" spans="1:7" x14ac:dyDescent="0.3">
@@ -12050,10 +12050,10 @@
         <v>601</v>
       </c>
       <c r="F320" s="11" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="G320" s="11" t="s">
-        <v>1214</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="321" spans="1:7" x14ac:dyDescent="0.3">
@@ -12073,10 +12073,10 @@
         <v>601</v>
       </c>
       <c r="F321" s="11" t="s">
-        <v>1215</v>
+        <v>1213</v>
       </c>
       <c r="G321" s="11" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="322" spans="1:7" x14ac:dyDescent="0.3">
@@ -12096,10 +12096,10 @@
         <v>601</v>
       </c>
       <c r="F322" s="11" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
       <c r="G322" s="11" t="s">
-        <v>1218</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="323" spans="1:7" x14ac:dyDescent="0.3">
@@ -12119,10 +12119,10 @@
         <v>601</v>
       </c>
       <c r="F323" s="11" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
       <c r="G323" s="11" t="s">
-        <v>1220</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="324" spans="1:7" x14ac:dyDescent="0.3">
@@ -12142,10 +12142,10 @@
         <v>601</v>
       </c>
       <c r="F324" s="11" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="G324" s="11" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="325" spans="1:7" x14ac:dyDescent="0.3">
@@ -12165,10 +12165,10 @@
         <v>601</v>
       </c>
       <c r="F325" s="11" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="G325" s="11" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="326" spans="1:7" x14ac:dyDescent="0.3">
@@ -12188,10 +12188,10 @@
         <v>601</v>
       </c>
       <c r="F326" s="11" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="G326" s="11" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="327" spans="1:7" x14ac:dyDescent="0.3">
@@ -12211,10 +12211,10 @@
         <v>601</v>
       </c>
       <c r="F327" s="11" t="s">
-        <v>1227</v>
+        <v>1225</v>
       </c>
       <c r="G327" s="11" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="328" spans="1:7" x14ac:dyDescent="0.3">
@@ -12234,10 +12234,10 @@
         <v>601</v>
       </c>
       <c r="F328" s="11" t="s">
-        <v>1229</v>
+        <v>1227</v>
       </c>
       <c r="G328" s="11" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="329" spans="1:7" x14ac:dyDescent="0.3">
@@ -12257,10 +12257,10 @@
         <v>601</v>
       </c>
       <c r="F329" s="11" t="s">
-        <v>1231</v>
+        <v>1229</v>
       </c>
       <c r="G329" s="11" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="330" spans="1:7" x14ac:dyDescent="0.3">
@@ -12280,10 +12280,10 @@
         <v>601</v>
       </c>
       <c r="F330" s="11" t="s">
-        <v>1233</v>
+        <v>1231</v>
       </c>
       <c r="G330" s="11" t="s">
-        <v>1234</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="331" spans="1:7" x14ac:dyDescent="0.3">
@@ -12303,10 +12303,10 @@
         <v>601</v>
       </c>
       <c r="F331" s="11" t="s">
-        <v>1235</v>
+        <v>1233</v>
       </c>
       <c r="G331" s="11" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="332" spans="1:7" x14ac:dyDescent="0.3">
@@ -12326,10 +12326,10 @@
         <v>601</v>
       </c>
       <c r="F332" s="11" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="G332" s="11" t="s">
-        <v>1238</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="333" spans="1:7" x14ac:dyDescent="0.3">
@@ -12349,10 +12349,10 @@
         <v>601</v>
       </c>
       <c r="F333" s="11" t="s">
-        <v>1239</v>
+        <v>1237</v>
       </c>
       <c r="G333" s="11" t="s">
-        <v>1240</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="334" spans="1:7" x14ac:dyDescent="0.3">
@@ -12372,10 +12372,10 @@
         <v>601</v>
       </c>
       <c r="F334" s="11" t="s">
-        <v>1241</v>
+        <v>1239</v>
       </c>
       <c r="G334" s="11" t="s">
-        <v>1242</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="335" spans="1:7" x14ac:dyDescent="0.3">
@@ -12395,10 +12395,10 @@
         <v>601</v>
       </c>
       <c r="F335" s="11" t="s">
-        <v>1243</v>
+        <v>1241</v>
       </c>
       <c r="G335" s="11" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
     </row>
   </sheetData>
